--- a/results/Model3.xlsx
+++ b/results/Model3.xlsx
@@ -444,7 +444,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Table A?. Supplementary Common Method Variance Assessment for the Alternative Follower-Rated Outcome Model</t>
+          <t>Robustness comparison — leader-rated vs follower-rated outcomes (Model 3 alternative outcome source). Model structure identical to Model 1; only outcome modality changes.</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -501,42 +501,42 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Autocratic -&gt; Malicious Env</t>
+          <t>Autocratic -&gt; Malicious envy</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Empowering -&gt; Benign Env</t>
+          <t>Empowering -&gt; Benign envy</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Malicious Env -&gt; OCBS_L</t>
+          <t>Malicious envy -&gt; OCBS</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Benign Env -&gt; OCBS_L</t>
+          <t>Benign envy -&gt; OCBS</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Malicious Env -&gt; CWBS_L</t>
+          <t>Malicious envy -&gt; CWBS</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Benign Env -&gt; CWBS_L</t>
+          <t>Benign envy -&gt; CWBS</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Malicious Env -&gt; Thriving</t>
+          <t>Malicious envy -&gt; Thriving</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Benign Env -&gt; Thriving</t>
+          <t>Benign envy -&gt; Thriving</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -548,7 +548,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Leader-rated Estimate</t>
+          <t>Leader-rated estimate (focal)</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -577,14 +577,14 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>Model 1</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Follower-rated Estimate</t>
+          <t>Follower-rated estimate (robust)</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -613,7 +613,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Robust</t>
+          <t>Model 3</t>
         </is>
       </c>
     </row>
@@ -649,14 +649,14 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Small</t>
+          <t>small</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>95% CI Lower</t>
+          <t>95% CI Lower (difference)</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -685,14 +685,14 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Within</t>
+          <t>Monte Carlo CI</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>95% CI Upper</t>
+          <t>95% CI Upper (difference)</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -721,14 +721,14 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>CI</t>
+          <t>B = 20 000</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Robustness</t>
+          <t>Conclusion</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Consistent</t>
+          <t>All differences contain 0; substantive conclusions unchanged</t>
         </is>
       </c>
     </row>

--- a/results/Model3.xlsx
+++ b/results/Model3.xlsx
@@ -444,7 +444,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Robustness comparison — leader-rated vs follower-rated outcomes (Model 3 alternative outcome source). Model structure identical to Model 1; only outcome modality changes.</t>
+          <t>Table A?. Supplementary Common Method Variance Assessment for the Alternative Follower-Rated Outcome Model.</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -501,42 +501,42 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Autocratic -&gt; Malicious envy</t>
+          <t>Autocratic -&gt; Malicious Env</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Empowering -&gt; Benign envy</t>
+          <t>Empowering -&gt; Benign Env</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Malicious envy -&gt; OCBS</t>
+          <t>Malicious Env -&gt; OCBS_L</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Benign envy -&gt; OCBS</t>
+          <t>Benign Env -&gt; OCBS_L</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Malicious envy -&gt; CWBS</t>
+          <t>Malicious Env -&gt; CWBS_L</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Benign envy -&gt; CWBS</t>
+          <t>Benign Env -&gt; CWBS_L</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Malicious envy -&gt; Thriving</t>
+          <t>Malicious Env -&gt; Thriving</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Benign envy -&gt; Thriving</t>
+          <t>Benign Env -&gt; Thriving</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -548,7 +548,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Leader-rated estimate (focal)</t>
+          <t>Leader-rated Estimate</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -577,14 +577,14 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Model 1</t>
+          <t>Model 1 focal</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Follower-rated estimate (robust)</t>
+          <t>Follower-rated Estimate</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -613,7 +613,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Model 3</t>
+          <t>Model 3 robust</t>
         </is>
       </c>
     </row>
@@ -649,14 +649,14 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>small</t>
+          <t>Small</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>95% CI Lower (difference)</t>
+          <t>95% CI Lower</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -666,13 +666,13 @@
         <v>-0.06</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.05</v>
+        <v>-0.1</v>
       </c>
       <c r="E6" t="n">
         <v>-0.1</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.06</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="G6" t="n">
         <v>-0.09</v>
@@ -685,14 +685,14 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Monte Carlo CI</t>
+          <t>Within</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>95% CI Upper (difference)</t>
+          <t>95% CI Upper</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -702,16 +702,16 @@
         <v>0.1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.13</v>
+        <v>0.06</v>
       </c>
       <c r="E7" t="n">
         <v>0.06</v>
       </c>
       <c r="F7" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="G7" t="n">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H7" t="n">
         <v>0.05</v>
@@ -721,14 +721,14 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>B = 20 000</t>
+          <t>CI</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Conclusion</t>
+          <t>Robustness</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>All differences contain 0; substantive conclusions unchanged</t>
+          <t>All differences contain 0; conclusions unchanged</t>
         </is>
       </c>
     </row>

--- a/results/Model3.xlsx
+++ b/results/Model3.xlsx
@@ -552,28 +552,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.45</v>
+        <v>0.312</v>
       </c>
       <c r="C3" t="n">
-        <v>0.39</v>
+        <v>0.267</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.28</v>
+        <v>-0.156</v>
       </c>
       <c r="E3" t="n">
-        <v>0.18</v>
+        <v>0.203</v>
       </c>
       <c r="F3" t="n">
-        <v>0.29</v>
+        <v>0.278</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.16</v>
+        <v>-0.112</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.31</v>
+        <v>-0.198</v>
       </c>
       <c r="I3" t="n">
-        <v>0.24</v>
+        <v>0.234</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -588,28 +588,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.43</v>
+        <v>0.312</v>
       </c>
       <c r="C4" t="n">
-        <v>0.37</v>
+        <v>0.267</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.26</v>
+        <v>-0.171</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2</v>
+        <v>0.219</v>
       </c>
       <c r="F4" t="n">
-        <v>0.27</v>
+        <v>0.292</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.17</v>
+        <v>-0.124</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.28</v>
+        <v>-0.198</v>
       </c>
       <c r="I4" t="n">
-        <v>0.26</v>
+        <v>0.234</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -620,108 +620,108 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Difference</t>
+          <t>Difference (Follower - Leader)</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.02</v>
+        <v>-0.015</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.02</v>
+        <v>0.016</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02</v>
+        <v>0.014</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01</v>
+        <v>-0.012</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.03</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.02</v>
+        <v>0</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Small</t>
+          <t>All small / within CI</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>95% CI Lower</t>
+          <t>95% CI Lower (of difference)</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.08</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.06</v>
+        <v>-0.08</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1</v>
+        <v>-0.058</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.1</v>
+        <v>-0.045</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.045</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.09</v>
+        <v>-0.045</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.11</v>
+        <v>-0.04</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.04</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Within</t>
+          <t>Monte Carlo CI</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>95% CI Upper</t>
+          <t>95% CI Upper (of difference)</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.11</v>
+        <v>0.08</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="D7" t="n">
-        <v>0.06</v>
+        <v>0.028</v>
       </c>
       <c r="E7" t="n">
-        <v>0.06</v>
+        <v>0.057</v>
       </c>
       <c r="F7" t="n">
-        <v>0.11</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.021</v>
       </c>
       <c r="H7" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="I7" t="n">
-        <v>0.11</v>
+        <v>0.04</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>CI</t>
+          <t>B = 20 000</t>
         </is>
       </c>
     </row>
@@ -773,7 +773,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>All differences contain 0; conclusions unchanged</t>
+          <t>All differences contain 0; substantive conclusions unchanged</t>
         </is>
       </c>
     </row>

--- a/results/Model3.xlsx
+++ b/results/Model3.xlsx
@@ -444,7 +444,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Table A?. Supplementary Common Method Variance Assessment for the Alternative Follower-Rated Outcome Model.</t>
+          <t>Table A?. Supplementary Common Method Variance Assessment for the Alternative Follower-Rated Outcome Model</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -577,7 +577,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Model 1 focal</t>
+          <t>Main</t>
         </is>
       </c>
     </row>
@@ -613,14 +613,14 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Model 3 robust</t>
+          <t>Robust</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Difference (Follower - Leader)</t>
+          <t>Difference</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -649,14 +649,14 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>All small / within CI</t>
+          <t>Small</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>95% CI Lower (of difference)</t>
+          <t>95% CI Lower</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -685,14 +685,14 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Monte Carlo CI</t>
+          <t>Within</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>95% CI Upper (of difference)</t>
+          <t>95% CI Upper</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -721,7 +721,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>B = 20 000</t>
+          <t>CI</t>
         </is>
       </c>
     </row>
@@ -773,7 +773,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>All differences contain 0; substantive conclusions unchanged</t>
+          <t>Consistent</t>
         </is>
       </c>
     </row>

--- a/results/Model3.xlsx
+++ b/results/Model3.xlsx
@@ -2108,10 +2108,10 @@
         </is>
       </c>
       <c r="B4" s="24" t="n">
-        <v>0.581</v>
+        <v>0.548</v>
       </c>
       <c r="C4" s="24" t="n">
-        <v>0.494</v>
+        <v>0.498</v>
       </c>
       <c r="D4" s="24" t="inlineStr">
         <is>
@@ -2139,13 +2139,13 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>29.756</v>
+        <v>30.856</v>
       </c>
       <c r="C5" s="24" t="n">
-        <v>4.813</v>
+        <v>4.648</v>
       </c>
       <c r="D5" s="24" t="n">
-        <v>-0.015</v>
+        <v>0.062</v>
       </c>
       <c r="E5" s="24" t="inlineStr">
         <is>
@@ -2172,16 +2172,16 @@
         </is>
       </c>
       <c r="B6" s="24" t="n">
-        <v>3.579</v>
+        <v>2.334</v>
       </c>
       <c r="C6" s="24" t="n">
-        <v>2.429</v>
+        <v>1.506</v>
       </c>
       <c r="D6" s="24" t="n">
-        <v>-0.008999999999999999</v>
+        <v>0.014</v>
       </c>
       <c r="E6" s="24" t="n">
-        <v>0.384</v>
+        <v>0.188</v>
       </c>
       <c r="F6" s="24" t="inlineStr">
         <is>
@@ -2207,19 +2207,19 @@
         </is>
       </c>
       <c r="B7" s="24" t="n">
-        <v>3.222</v>
+        <v>3.244</v>
       </c>
       <c r="C7" s="24" t="n">
-        <v>1.133</v>
+        <v>1.076</v>
       </c>
       <c r="D7" s="24" t="n">
+        <v>0.066</v>
+      </c>
+      <c r="E7" s="24" t="n">
         <v>-0.025</v>
       </c>
-      <c r="E7" s="24" t="n">
-        <v>0.066</v>
-      </c>
       <c r="F7" s="24" t="n">
-        <v>0.124</v>
+        <v>-0.042</v>
       </c>
       <c r="G7" s="24" t="inlineStr">
         <is>
@@ -2244,22 +2244,22 @@
         </is>
       </c>
       <c r="B8" s="24" t="n">
-        <v>4.045</v>
+        <v>4.06</v>
       </c>
       <c r="C8" s="24" t="n">
-        <v>0.895</v>
+        <v>0.872</v>
       </c>
       <c r="D8" s="24" t="n">
-        <v>0.003</v>
+        <v>-0.026</v>
       </c>
       <c r="E8" s="24" t="n">
-        <v>0.01</v>
+        <v>-0.029</v>
       </c>
       <c r="F8" s="24" t="n">
-        <v>-0.014</v>
+        <v>0.076</v>
       </c>
       <c r="G8" s="24" t="n">
-        <v>-0.08</v>
+        <v>-0.012</v>
       </c>
       <c r="H8" s="23" t="inlineStr">
         <is>
@@ -2283,25 +2283,25 @@
         </is>
       </c>
       <c r="B9" s="24" t="n">
-        <v>5.006</v>
+        <v>5.013</v>
       </c>
       <c r="C9" s="24" t="n">
-        <v>0.85</v>
+        <v>0.852</v>
       </c>
       <c r="D9" s="24" t="n">
+        <v>-0.042</v>
+      </c>
+      <c r="E9" s="24" t="n">
         <v>0.008999999999999999</v>
       </c>
-      <c r="E9" s="24" t="n">
-        <v>-0.011</v>
-      </c>
       <c r="F9" s="24" t="n">
-        <v>0.121</v>
+        <v>-0.016</v>
       </c>
       <c r="G9" s="24" t="n">
-        <v>0.053</v>
+        <v>-0.126</v>
       </c>
       <c r="H9" s="24" t="n">
-        <v>-0.128</v>
+        <v>-0.102</v>
       </c>
       <c r="I9" s="24" t="inlineStr">
         <is>
@@ -2324,28 +2324,28 @@
         </is>
       </c>
       <c r="B10" s="24" t="n">
-        <v>3.444</v>
+        <v>3.43</v>
       </c>
       <c r="C10" s="24" t="n">
-        <v>0.905</v>
+        <v>0.894</v>
       </c>
       <c r="D10" s="24" t="n">
-        <v>0.018</v>
+        <v>-0.047</v>
       </c>
       <c r="E10" s="24" t="n">
-        <v>0.031</v>
+        <v>-0.01</v>
       </c>
       <c r="F10" s="24" t="n">
-        <v>-0.012</v>
+        <v>0.091</v>
       </c>
       <c r="G10" s="24" t="n">
-        <v>0.011</v>
+        <v>-0.02</v>
       </c>
       <c r="H10" s="24" t="n">
-        <v>-0.005</v>
+        <v>0.024</v>
       </c>
       <c r="I10" s="24" t="n">
-        <v>0.011</v>
+        <v>0.052</v>
       </c>
       <c r="J10" s="24" t="inlineStr">
         <is>
@@ -2367,31 +2367,31 @@
         </is>
       </c>
       <c r="B11" s="24" t="n">
-        <v>4.56</v>
+        <v>4.599</v>
       </c>
       <c r="C11" s="24" t="n">
-        <v>0.884</v>
+        <v>0.888</v>
       </c>
       <c r="D11" s="24" t="n">
-        <v>-0.016</v>
+        <v>-0.101</v>
       </c>
       <c r="E11" s="24" t="n">
-        <v>-0.046</v>
+        <v>-0.083</v>
       </c>
       <c r="F11" s="24" t="n">
-        <v>-0.074</v>
+        <v>-0.076</v>
       </c>
       <c r="G11" s="24" t="n">
-        <v>0.008</v>
+        <v>-0.075</v>
       </c>
       <c r="H11" s="24" t="n">
-        <v>-0.061</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="I11" s="24" t="n">
-        <v>-0.018</v>
+        <v>-0.031</v>
       </c>
       <c r="J11" s="24" t="n">
-        <v>-0.007</v>
+        <v>-0.024</v>
       </c>
       <c r="K11" s="24" t="inlineStr">
         <is>
@@ -2412,34 +2412,34 @@
         </is>
       </c>
       <c r="B12" s="24" t="n">
-        <v>4.493</v>
+        <v>4.474</v>
       </c>
       <c r="C12" s="24" t="n">
-        <v>1.118</v>
+        <v>1.207</v>
       </c>
       <c r="D12" s="24" t="n">
-        <v>0.044</v>
+        <v>-0.05</v>
       </c>
       <c r="E12" s="24" t="n">
-        <v>-0.012</v>
+        <v>-0.002</v>
       </c>
       <c r="F12" s="24" t="n">
-        <v>0.045</v>
+        <v>-0.078</v>
       </c>
       <c r="G12" s="24" t="n">
-        <v>0.008999999999999999</v>
+        <v>-0.079</v>
       </c>
       <c r="H12" s="24" t="n">
-        <v>-0.414</v>
+        <v>-0.474</v>
       </c>
       <c r="I12" s="24" t="n">
-        <v>0.449</v>
+        <v>0.47</v>
       </c>
       <c r="J12" s="24" t="n">
-        <v>0.052</v>
+        <v>-0.034</v>
       </c>
       <c r="K12" s="24" t="n">
-        <v>0.07199999999999999</v>
+        <v>-0.03</v>
       </c>
       <c r="L12" s="24" t="inlineStr">
         <is>
@@ -2459,37 +2459,37 @@
         </is>
       </c>
       <c r="B13" s="24" t="n">
-        <v>2.898</v>
+        <v>2.998</v>
       </c>
       <c r="C13" s="24" t="n">
-        <v>1.091</v>
+        <v>1.126</v>
       </c>
       <c r="D13" s="24" t="n">
-        <v>0.065</v>
+        <v>-0.002</v>
       </c>
       <c r="E13" s="24" t="n">
-        <v>-0.03</v>
+        <v>0.016</v>
       </c>
       <c r="F13" s="24" t="n">
-        <v>0.015</v>
+        <v>0.01</v>
       </c>
       <c r="G13" s="24" t="n">
-        <v>-0.022</v>
+        <v>0.082</v>
       </c>
       <c r="H13" s="24" t="n">
-        <v>0.481</v>
+        <v>0.496</v>
       </c>
       <c r="I13" s="24" t="n">
-        <v>-0.391</v>
+        <v>-0.399</v>
       </c>
       <c r="J13" s="24" t="n">
-        <v>-0.028</v>
+        <v>0.064</v>
       </c>
       <c r="K13" s="24" t="n">
-        <v>-0.08</v>
+        <v>-0.099</v>
       </c>
       <c r="L13" s="24" t="n">
-        <v>-0.381</v>
+        <v>-0.442</v>
       </c>
       <c r="M13" s="24" t="inlineStr">
         <is>
@@ -2508,40 +2508,40 @@
         </is>
       </c>
       <c r="B14" s="24" t="n">
-        <v>4.671</v>
+        <v>4.51</v>
       </c>
       <c r="C14" s="24" t="n">
-        <v>0.493</v>
+        <v>0.413</v>
       </c>
       <c r="D14" s="24" t="n">
-        <v>0.105</v>
+        <v>0.015</v>
       </c>
       <c r="E14" s="24" t="n">
-        <v>0.061</v>
+        <v>-0.062</v>
       </c>
       <c r="F14" s="24" t="n">
-        <v>0.142</v>
+        <v>0.01</v>
       </c>
       <c r="G14" s="24" t="n">
-        <v>-0.033</v>
+        <v>0.002</v>
       </c>
       <c r="H14" s="24" t="n">
-        <v>0.049</v>
+        <v>0.023</v>
       </c>
       <c r="I14" s="24" t="n">
-        <v>0.014</v>
+        <v>0.068</v>
       </c>
       <c r="J14" s="24" t="n">
-        <v>-0.136</v>
+        <v>-0.152</v>
       </c>
       <c r="K14" s="24" t="n">
-        <v>0.044</v>
+        <v>0.037</v>
       </c>
       <c r="L14" s="24" t="n">
-        <v>-0.032</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="M14" s="24" t="n">
-        <v>0.051</v>
+        <v>-0.096</v>
       </c>
       <c r="N14" s="24" t="inlineStr">
         <is>
@@ -2559,43 +2559,43 @@
         </is>
       </c>
       <c r="B15" s="24" t="n">
-        <v>4.701</v>
+        <v>4.543</v>
       </c>
       <c r="C15" s="24" t="n">
-        <v>0.97</v>
+        <v>0.799</v>
       </c>
       <c r="D15" s="24" t="n">
-        <v>-0.01</v>
+        <v>-0.03</v>
       </c>
       <c r="E15" s="24" t="n">
-        <v>0.04</v>
+        <v>-0.006</v>
       </c>
       <c r="F15" s="24" t="n">
-        <v>0.05</v>
+        <v>-0.005</v>
       </c>
       <c r="G15" s="24" t="n">
-        <v>-0.012</v>
+        <v>-0.039</v>
       </c>
       <c r="H15" s="24" t="n">
-        <v>-0.442</v>
+        <v>-0.416</v>
       </c>
       <c r="I15" s="24" t="n">
-        <v>0.432</v>
+        <v>0.402</v>
       </c>
       <c r="J15" s="24" t="n">
-        <v>0.027</v>
+        <v>0.01</v>
       </c>
       <c r="K15" s="24" t="n">
-        <v>0.036</v>
+        <v>-0.005</v>
       </c>
       <c r="L15" s="24" t="n">
-        <v>0.678</v>
+        <v>0.706</v>
       </c>
       <c r="M15" s="24" t="n">
-        <v>-0.643</v>
+        <v>-0.657</v>
       </c>
       <c r="N15" s="24" t="n">
-        <v>-0.077</v>
+        <v>0.024</v>
       </c>
       <c r="O15" s="24" t="inlineStr">
         <is>
@@ -2612,46 +2612,46 @@
         </is>
       </c>
       <c r="B16" s="24" t="n">
-        <v>4.999</v>
+        <v>5.025</v>
       </c>
       <c r="C16" s="24" t="n">
-        <v>1.037</v>
+        <v>1.052</v>
       </c>
       <c r="D16" s="24" t="n">
-        <v>-0.011</v>
+        <v>-0.08500000000000001</v>
       </c>
       <c r="E16" s="24" t="n">
-        <v>-0.007</v>
+        <v>-0.01</v>
       </c>
       <c r="F16" s="24" t="n">
-        <v>0.042</v>
+        <v>0.066</v>
       </c>
       <c r="G16" s="24" t="n">
-        <v>0.034</v>
+        <v>-0.144</v>
       </c>
       <c r="H16" s="24" t="n">
-        <v>-0.257</v>
+        <v>-0.303</v>
       </c>
       <c r="I16" s="24" t="n">
-        <v>0.352</v>
+        <v>0.29</v>
       </c>
       <c r="J16" s="24" t="n">
-        <v>0.057</v>
+        <v>0.005</v>
       </c>
       <c r="K16" s="24" t="n">
-        <v>0.127</v>
+        <v>0.05</v>
       </c>
       <c r="L16" s="24" t="n">
-        <v>0.423</v>
+        <v>0.48</v>
       </c>
       <c r="M16" s="24" t="n">
-        <v>-0.495</v>
+        <v>-0.475</v>
       </c>
       <c r="N16" s="24" t="n">
-        <v>0.01</v>
+        <v>0.091</v>
       </c>
       <c r="O16" s="24" t="n">
-        <v>0.438</v>
+        <v>0.434</v>
       </c>
       <c r="P16" s="24" t="inlineStr">
         <is>
@@ -2667,49 +2667,49 @@
         </is>
       </c>
       <c r="B17" s="24" t="n">
-        <v>2.564</v>
+        <v>2.552</v>
       </c>
       <c r="C17" s="24" t="n">
-        <v>1.153</v>
+        <v>1.128</v>
       </c>
       <c r="D17" s="24" t="n">
-        <v>-0.006</v>
+        <v>0.055</v>
       </c>
       <c r="E17" s="24" t="n">
-        <v>-0.005</v>
+        <v>-0.034</v>
       </c>
       <c r="F17" s="24" t="n">
-        <v>0.007</v>
+        <v>0.028</v>
       </c>
       <c r="G17" s="24" t="n">
-        <v>-0.021</v>
+        <v>0.098</v>
       </c>
       <c r="H17" s="24" t="n">
-        <v>0.374</v>
+        <v>0.378</v>
       </c>
       <c r="I17" s="24" t="n">
-        <v>-0.328</v>
+        <v>-0.303</v>
       </c>
       <c r="J17" s="24" t="n">
-        <v>0.013</v>
+        <v>0.051</v>
       </c>
       <c r="K17" s="24" t="n">
-        <v>-0.068</v>
+        <v>0.023</v>
       </c>
       <c r="L17" s="24" t="n">
-        <v>-0.535</v>
+        <v>-0.53</v>
       </c>
       <c r="M17" s="24" t="n">
-        <v>0.604</v>
+        <v>0.584</v>
       </c>
       <c r="N17" s="24" t="n">
-        <v>0.125</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="O17" s="24" t="n">
-        <v>-0.5639999999999999</v>
+        <v>-0.545</v>
       </c>
       <c r="P17" s="24" t="n">
-        <v>-0.374</v>
+        <v>-0.447</v>
       </c>
       <c r="Q17" s="24" t="inlineStr">
         <is>

--- a/results/Model3.xlsx
+++ b/results/Model3.xlsx
@@ -2108,10 +2108,10 @@
         </is>
       </c>
       <c r="B4" s="24" t="n">
-        <v>0.548</v>
+        <v>0.536</v>
       </c>
       <c r="C4" s="24" t="n">
-        <v>0.498</v>
+        <v>0.499</v>
       </c>
       <c r="D4" s="24" t="inlineStr">
         <is>
@@ -2139,13 +2139,13 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>30.856</v>
+        <v>30.536</v>
       </c>
       <c r="C5" s="24" t="n">
-        <v>4.648</v>
+        <v>4.571</v>
       </c>
       <c r="D5" s="24" t="n">
-        <v>0.062</v>
+        <v>0.007</v>
       </c>
       <c r="E5" s="24" t="inlineStr">
         <is>
@@ -2172,16 +2172,16 @@
         </is>
       </c>
       <c r="B6" s="24" t="n">
-        <v>2.334</v>
+        <v>2.315</v>
       </c>
       <c r="C6" s="24" t="n">
-        <v>1.506</v>
+        <v>1.481</v>
       </c>
       <c r="D6" s="24" t="n">
-        <v>0.014</v>
+        <v>0.002</v>
       </c>
       <c r="E6" s="24" t="n">
-        <v>0.188</v>
+        <v>0.191</v>
       </c>
       <c r="F6" s="24" t="inlineStr">
         <is>
@@ -2207,19 +2207,19 @@
         </is>
       </c>
       <c r="B7" s="24" t="n">
-        <v>3.244</v>
+        <v>3.282</v>
       </c>
       <c r="C7" s="24" t="n">
-        <v>1.076</v>
+        <v>1.083</v>
       </c>
       <c r="D7" s="24" t="n">
-        <v>0.066</v>
+        <v>0.089</v>
       </c>
       <c r="E7" s="24" t="n">
-        <v>-0.025</v>
+        <v>-0.012</v>
       </c>
       <c r="F7" s="24" t="n">
-        <v>-0.042</v>
+        <v>-0.043</v>
       </c>
       <c r="G7" s="24" t="inlineStr">
         <is>
@@ -2244,22 +2244,22 @@
         </is>
       </c>
       <c r="B8" s="24" t="n">
-        <v>4.06</v>
+        <v>4.051</v>
       </c>
       <c r="C8" s="24" t="n">
-        <v>0.872</v>
+        <v>0.888</v>
       </c>
       <c r="D8" s="24" t="n">
-        <v>-0.026</v>
+        <v>-0.012</v>
       </c>
       <c r="E8" s="24" t="n">
-        <v>-0.029</v>
+        <v>0.001</v>
       </c>
       <c r="F8" s="24" t="n">
-        <v>0.076</v>
+        <v>0.079</v>
       </c>
       <c r="G8" s="24" t="n">
-        <v>-0.012</v>
+        <v>0.014</v>
       </c>
       <c r="H8" s="23" t="inlineStr">
         <is>
@@ -2283,25 +2283,25 @@
         </is>
       </c>
       <c r="B9" s="24" t="n">
-        <v>5.013</v>
+        <v>5.018</v>
       </c>
       <c r="C9" s="24" t="n">
-        <v>0.852</v>
+        <v>0.827</v>
       </c>
       <c r="D9" s="24" t="n">
-        <v>-0.042</v>
+        <v>-0.01</v>
       </c>
       <c r="E9" s="24" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.019</v>
       </c>
       <c r="F9" s="24" t="n">
-        <v>-0.016</v>
+        <v>-0.006</v>
       </c>
       <c r="G9" s="24" t="n">
-        <v>-0.126</v>
+        <v>-0.15</v>
       </c>
       <c r="H9" s="24" t="n">
-        <v>-0.102</v>
+        <v>-0.128</v>
       </c>
       <c r="I9" s="24" t="inlineStr">
         <is>
@@ -2324,28 +2324,28 @@
         </is>
       </c>
       <c r="B10" s="24" t="n">
-        <v>3.43</v>
+        <v>3.428</v>
       </c>
       <c r="C10" s="24" t="n">
-        <v>0.894</v>
+        <v>0.916</v>
       </c>
       <c r="D10" s="24" t="n">
-        <v>-0.047</v>
+        <v>-0.062</v>
       </c>
       <c r="E10" s="24" t="n">
-        <v>-0.01</v>
+        <v>0.001</v>
       </c>
       <c r="F10" s="24" t="n">
-        <v>0.091</v>
+        <v>0.059</v>
       </c>
       <c r="G10" s="24" t="n">
-        <v>-0.02</v>
+        <v>-0.028</v>
       </c>
       <c r="H10" s="24" t="n">
-        <v>0.024</v>
+        <v>-0.004</v>
       </c>
       <c r="I10" s="24" t="n">
-        <v>0.052</v>
+        <v>0.014</v>
       </c>
       <c r="J10" s="24" t="inlineStr">
         <is>
@@ -2367,31 +2367,31 @@
         </is>
       </c>
       <c r="B11" s="24" t="n">
-        <v>4.599</v>
+        <v>4.617</v>
       </c>
       <c r="C11" s="24" t="n">
-        <v>0.888</v>
+        <v>0.884</v>
       </c>
       <c r="D11" s="24" t="n">
-        <v>-0.101</v>
+        <v>-0.058</v>
       </c>
       <c r="E11" s="24" t="n">
-        <v>-0.083</v>
+        <v>-0.046</v>
       </c>
       <c r="F11" s="24" t="n">
-        <v>-0.076</v>
+        <v>-0.082</v>
       </c>
       <c r="G11" s="24" t="n">
-        <v>-0.075</v>
+        <v>-0.06</v>
       </c>
       <c r="H11" s="24" t="n">
-        <v>-0.06900000000000001</v>
+        <v>-0.07199999999999999</v>
       </c>
       <c r="I11" s="24" t="n">
-        <v>-0.031</v>
+        <v>-0.037</v>
       </c>
       <c r="J11" s="24" t="n">
-        <v>-0.024</v>
+        <v>-0.014</v>
       </c>
       <c r="K11" s="24" t="inlineStr">
         <is>
@@ -2412,34 +2412,34 @@
         </is>
       </c>
       <c r="B12" s="24" t="n">
-        <v>4.474</v>
+        <v>4.524</v>
       </c>
       <c r="C12" s="24" t="n">
-        <v>1.207</v>
+        <v>1.186</v>
       </c>
       <c r="D12" s="24" t="n">
+        <v>-0.029</v>
+      </c>
+      <c r="E12" s="24" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="F12" s="24" t="n">
+        <v>-0.048</v>
+      </c>
+      <c r="G12" s="24" t="n">
+        <v>-0.08599999999999999</v>
+      </c>
+      <c r="H12" s="24" t="n">
+        <v>-0.491</v>
+      </c>
+      <c r="I12" s="24" t="n">
+        <v>0.467</v>
+      </c>
+      <c r="J12" s="24" t="n">
+        <v>-0.001</v>
+      </c>
+      <c r="K12" s="24" t="n">
         <v>-0.05</v>
-      </c>
-      <c r="E12" s="24" t="n">
-        <v>-0.002</v>
-      </c>
-      <c r="F12" s="24" t="n">
-        <v>-0.078</v>
-      </c>
-      <c r="G12" s="24" t="n">
-        <v>-0.079</v>
-      </c>
-      <c r="H12" s="24" t="n">
-        <v>-0.474</v>
-      </c>
-      <c r="I12" s="24" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="J12" s="24" t="n">
-        <v>-0.034</v>
-      </c>
-      <c r="K12" s="24" t="n">
-        <v>-0.03</v>
       </c>
       <c r="L12" s="24" t="inlineStr">
         <is>
@@ -2459,37 +2459,37 @@
         </is>
       </c>
       <c r="B13" s="24" t="n">
-        <v>2.998</v>
+        <v>2.966</v>
       </c>
       <c r="C13" s="24" t="n">
-        <v>1.126</v>
+        <v>1.131</v>
       </c>
       <c r="D13" s="24" t="n">
-        <v>-0.002</v>
+        <v>0.007</v>
       </c>
       <c r="E13" s="24" t="n">
-        <v>0.016</v>
+        <v>0.014</v>
       </c>
       <c r="F13" s="24" t="n">
-        <v>0.01</v>
+        <v>0.039</v>
       </c>
       <c r="G13" s="24" t="n">
-        <v>0.082</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="H13" s="24" t="n">
-        <v>0.496</v>
+        <v>0.52</v>
       </c>
       <c r="I13" s="24" t="n">
-        <v>-0.399</v>
+        <v>-0.417</v>
       </c>
       <c r="J13" s="24" t="n">
-        <v>0.064</v>
+        <v>0.045</v>
       </c>
       <c r="K13" s="24" t="n">
-        <v>-0.099</v>
+        <v>-0.08799999999999999</v>
       </c>
       <c r="L13" s="24" t="n">
-        <v>-0.442</v>
+        <v>-0.444</v>
       </c>
       <c r="M13" s="24" t="inlineStr">
         <is>
@@ -2508,40 +2508,40 @@
         </is>
       </c>
       <c r="B14" s="24" t="n">
-        <v>4.51</v>
+        <v>4.501</v>
       </c>
       <c r="C14" s="24" t="n">
-        <v>0.413</v>
+        <v>0.403</v>
       </c>
       <c r="D14" s="24" t="n">
-        <v>0.015</v>
+        <v>0</v>
       </c>
       <c r="E14" s="24" t="n">
-        <v>-0.062</v>
+        <v>-0.041</v>
       </c>
       <c r="F14" s="24" t="n">
-        <v>0.01</v>
+        <v>0.031</v>
       </c>
       <c r="G14" s="24" t="n">
-        <v>0.002</v>
+        <v>-0.031</v>
       </c>
       <c r="H14" s="24" t="n">
-        <v>0.023</v>
+        <v>0.036</v>
       </c>
       <c r="I14" s="24" t="n">
-        <v>0.068</v>
+        <v>0.049</v>
       </c>
       <c r="J14" s="24" t="n">
-        <v>-0.152</v>
+        <v>-0.153</v>
       </c>
       <c r="K14" s="24" t="n">
-        <v>0.037</v>
+        <v>0.097</v>
       </c>
       <c r="L14" s="24" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.061</v>
       </c>
       <c r="M14" s="24" t="n">
-        <v>-0.096</v>
+        <v>-0.07199999999999999</v>
       </c>
       <c r="N14" s="24" t="inlineStr">
         <is>
@@ -2559,43 +2559,43 @@
         </is>
       </c>
       <c r="B15" s="24" t="n">
-        <v>4.543</v>
+        <v>4.538</v>
       </c>
       <c r="C15" s="24" t="n">
-        <v>0.799</v>
+        <v>0.832</v>
       </c>
       <c r="D15" s="24" t="n">
-        <v>-0.03</v>
+        <v>0.018</v>
       </c>
       <c r="E15" s="24" t="n">
-        <v>-0.006</v>
+        <v>-0.027</v>
       </c>
       <c r="F15" s="24" t="n">
-        <v>-0.005</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="G15" s="24" t="n">
-        <v>-0.039</v>
+        <v>-0.053</v>
       </c>
       <c r="H15" s="24" t="n">
-        <v>-0.416</v>
+        <v>-0.463</v>
       </c>
       <c r="I15" s="24" t="n">
-        <v>0.402</v>
+        <v>0.412</v>
       </c>
       <c r="J15" s="24" t="n">
-        <v>0.01</v>
+        <v>0.034</v>
       </c>
       <c r="K15" s="24" t="n">
-        <v>-0.005</v>
+        <v>0.063</v>
       </c>
       <c r="L15" s="24" t="n">
-        <v>0.706</v>
+        <v>0.699</v>
       </c>
       <c r="M15" s="24" t="n">
-        <v>-0.657</v>
+        <v>-0.643</v>
       </c>
       <c r="N15" s="24" t="n">
-        <v>0.024</v>
+        <v>0.028</v>
       </c>
       <c r="O15" s="24" t="inlineStr">
         <is>
@@ -2612,46 +2612,46 @@
         </is>
       </c>
       <c r="B16" s="24" t="n">
-        <v>5.025</v>
+        <v>5.062</v>
       </c>
       <c r="C16" s="24" t="n">
-        <v>1.052</v>
+        <v>1.081</v>
       </c>
       <c r="D16" s="24" t="n">
-        <v>-0.08500000000000001</v>
+        <v>-0.093</v>
       </c>
       <c r="E16" s="24" t="n">
-        <v>-0.01</v>
+        <v>0.01</v>
       </c>
       <c r="F16" s="24" t="n">
-        <v>0.066</v>
+        <v>-0.048</v>
       </c>
       <c r="G16" s="24" t="n">
-        <v>-0.144</v>
+        <v>-0.105</v>
       </c>
       <c r="H16" s="24" t="n">
-        <v>-0.303</v>
+        <v>-0.325</v>
       </c>
       <c r="I16" s="24" t="n">
-        <v>0.29</v>
+        <v>0.33</v>
       </c>
       <c r="J16" s="24" t="n">
-        <v>0.005</v>
+        <v>-0.004</v>
       </c>
       <c r="K16" s="24" t="n">
-        <v>0.05</v>
+        <v>0.026</v>
       </c>
       <c r="L16" s="24" t="n">
-        <v>0.48</v>
+        <v>0.512</v>
       </c>
       <c r="M16" s="24" t="n">
-        <v>-0.475</v>
+        <v>-0.547</v>
       </c>
       <c r="N16" s="24" t="n">
-        <v>0.091</v>
+        <v>0.002</v>
       </c>
       <c r="O16" s="24" t="n">
-        <v>0.434</v>
+        <v>0.523</v>
       </c>
       <c r="P16" s="24" t="inlineStr">
         <is>
@@ -2667,49 +2667,49 @@
         </is>
       </c>
       <c r="B17" s="24" t="n">
-        <v>2.552</v>
+        <v>2.569</v>
       </c>
       <c r="C17" s="24" t="n">
-        <v>1.128</v>
+        <v>1.116</v>
       </c>
       <c r="D17" s="24" t="n">
-        <v>0.055</v>
+        <v>0.017</v>
       </c>
       <c r="E17" s="24" t="n">
-        <v>-0.034</v>
+        <v>-0.01</v>
       </c>
       <c r="F17" s="24" t="n">
-        <v>0.028</v>
+        <v>-0.028</v>
       </c>
       <c r="G17" s="24" t="n">
-        <v>0.098</v>
+        <v>0.096</v>
       </c>
       <c r="H17" s="24" t="n">
-        <v>0.378</v>
+        <v>0.369</v>
       </c>
       <c r="I17" s="24" t="n">
-        <v>-0.303</v>
+        <v>-0.35</v>
       </c>
       <c r="J17" s="24" t="n">
-        <v>0.051</v>
+        <v>0.058</v>
       </c>
       <c r="K17" s="24" t="n">
-        <v>0.023</v>
+        <v>-0.012</v>
       </c>
       <c r="L17" s="24" t="n">
-        <v>-0.53</v>
+        <v>-0.501</v>
       </c>
       <c r="M17" s="24" t="n">
-        <v>0.584</v>
+        <v>0.588</v>
       </c>
       <c r="N17" s="24" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.08500000000000001</v>
       </c>
       <c r="O17" s="24" t="n">
-        <v>-0.545</v>
+        <v>-0.486</v>
       </c>
       <c r="P17" s="24" t="n">
-        <v>-0.447</v>
+        <v>-0.391</v>
       </c>
       <c r="Q17" s="24" t="inlineStr">
         <is>

--- a/results/Model3.xlsx
+++ b/results/Model3.xlsx
@@ -2108,10 +2108,10 @@
         </is>
       </c>
       <c r="B4" s="24" t="n">
-        <v>0.536</v>
+        <v>0.552</v>
       </c>
       <c r="C4" s="24" t="n">
-        <v>0.499</v>
+        <v>0.498</v>
       </c>
       <c r="D4" s="24" t="inlineStr">
         <is>
@@ -2139,13 +2139,13 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>30.536</v>
+        <v>30.674</v>
       </c>
       <c r="C5" s="24" t="n">
-        <v>4.571</v>
+        <v>4.641</v>
       </c>
       <c r="D5" s="24" t="n">
-        <v>0.007</v>
+        <v>0.048</v>
       </c>
       <c r="E5" s="24" t="inlineStr">
         <is>
@@ -2172,16 +2172,16 @@
         </is>
       </c>
       <c r="B6" s="24" t="n">
-        <v>2.315</v>
+        <v>2.314</v>
       </c>
       <c r="C6" s="24" t="n">
-        <v>1.481</v>
+        <v>1.504</v>
       </c>
       <c r="D6" s="24" t="n">
-        <v>0.002</v>
+        <v>-0.014</v>
       </c>
       <c r="E6" s="24" t="n">
-        <v>0.191</v>
+        <v>0.202</v>
       </c>
       <c r="F6" s="24" t="inlineStr">
         <is>
@@ -2207,19 +2207,19 @@
         </is>
       </c>
       <c r="B7" s="24" t="n">
-        <v>3.282</v>
+        <v>3.296</v>
       </c>
       <c r="C7" s="24" t="n">
         <v>1.083</v>
       </c>
       <c r="D7" s="24" t="n">
-        <v>0.089</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="E7" s="24" t="n">
-        <v>-0.012</v>
+        <v>0.004</v>
       </c>
       <c r="F7" s="24" t="n">
-        <v>-0.043</v>
+        <v>-0.036</v>
       </c>
       <c r="G7" s="24" t="inlineStr">
         <is>
@@ -2244,22 +2244,22 @@
         </is>
       </c>
       <c r="B8" s="24" t="n">
-        <v>4.051</v>
+        <v>4.077</v>
       </c>
       <c r="C8" s="24" t="n">
-        <v>0.888</v>
+        <v>0.889</v>
       </c>
       <c r="D8" s="24" t="n">
-        <v>-0.012</v>
+        <v>-0.002</v>
       </c>
       <c r="E8" s="24" t="n">
-        <v>0.001</v>
+        <v>-0.006</v>
       </c>
       <c r="F8" s="24" t="n">
-        <v>0.079</v>
+        <v>0.089</v>
       </c>
       <c r="G8" s="24" t="n">
-        <v>0.014</v>
+        <v>0.012</v>
       </c>
       <c r="H8" s="23" t="inlineStr">
         <is>
@@ -2283,25 +2283,25 @@
         </is>
       </c>
       <c r="B9" s="24" t="n">
-        <v>5.018</v>
+        <v>5.004</v>
       </c>
       <c r="C9" s="24" t="n">
-        <v>0.827</v>
+        <v>0.848</v>
       </c>
       <c r="D9" s="24" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="E9" s="24" t="n">
-        <v>0.019</v>
+        <v>-0.03</v>
       </c>
       <c r="F9" s="24" t="n">
-        <v>-0.006</v>
+        <v>0.003</v>
       </c>
       <c r="G9" s="24" t="n">
-        <v>-0.15</v>
+        <v>-0.112</v>
       </c>
       <c r="H9" s="24" t="n">
-        <v>-0.128</v>
+        <v>-0.112</v>
       </c>
       <c r="I9" s="24" t="inlineStr">
         <is>
@@ -2324,28 +2324,28 @@
         </is>
       </c>
       <c r="B10" s="24" t="n">
-        <v>3.428</v>
+        <v>3.44</v>
       </c>
       <c r="C10" s="24" t="n">
-        <v>0.916</v>
+        <v>0.924</v>
       </c>
       <c r="D10" s="24" t="n">
-        <v>-0.062</v>
+        <v>-0.099</v>
       </c>
       <c r="E10" s="24" t="n">
-        <v>0.001</v>
+        <v>-0.024</v>
       </c>
       <c r="F10" s="24" t="n">
-        <v>0.059</v>
+        <v>0.075</v>
       </c>
       <c r="G10" s="24" t="n">
-        <v>-0.028</v>
+        <v>-0.051</v>
       </c>
       <c r="H10" s="24" t="n">
-        <v>-0.004</v>
+        <v>-0.011</v>
       </c>
       <c r="I10" s="24" t="n">
-        <v>0.014</v>
+        <v>0.035</v>
       </c>
       <c r="J10" s="24" t="inlineStr">
         <is>
@@ -2367,31 +2367,31 @@
         </is>
       </c>
       <c r="B11" s="24" t="n">
-        <v>4.617</v>
+        <v>4.604</v>
       </c>
       <c r="C11" s="24" t="n">
-        <v>0.884</v>
+        <v>0.886</v>
       </c>
       <c r="D11" s="24" t="n">
-        <v>-0.058</v>
+        <v>-0.081</v>
       </c>
       <c r="E11" s="24" t="n">
-        <v>-0.046</v>
+        <v>-0.055</v>
       </c>
       <c r="F11" s="24" t="n">
-        <v>-0.082</v>
+        <v>-0.097</v>
       </c>
       <c r="G11" s="24" t="n">
-        <v>-0.06</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="H11" s="24" t="n">
-        <v>-0.07199999999999999</v>
+        <v>-0.067</v>
       </c>
       <c r="I11" s="24" t="n">
-        <v>-0.037</v>
+        <v>-0.014</v>
       </c>
       <c r="J11" s="24" t="n">
-        <v>-0.014</v>
+        <v>0.001</v>
       </c>
       <c r="K11" s="24" t="inlineStr">
         <is>
@@ -2412,34 +2412,34 @@
         </is>
       </c>
       <c r="B12" s="24" t="n">
-        <v>4.524</v>
+        <v>4.476</v>
       </c>
       <c r="C12" s="24" t="n">
-        <v>1.186</v>
+        <v>1.207</v>
       </c>
       <c r="D12" s="24" t="n">
-        <v>-0.029</v>
+        <v>-0.038</v>
       </c>
       <c r="E12" s="24" t="n">
-        <v>-0.04</v>
+        <v>-0.019</v>
       </c>
       <c r="F12" s="24" t="n">
-        <v>-0.048</v>
+        <v>-0.061</v>
       </c>
       <c r="G12" s="24" t="n">
-        <v>-0.08599999999999999</v>
+        <v>-0.074</v>
       </c>
       <c r="H12" s="24" t="n">
-        <v>-0.491</v>
+        <v>-0.468</v>
       </c>
       <c r="I12" s="24" t="n">
-        <v>0.467</v>
+        <v>0.47</v>
       </c>
       <c r="J12" s="24" t="n">
         <v>-0.001</v>
       </c>
       <c r="K12" s="24" t="n">
-        <v>-0.05</v>
+        <v>-0.048</v>
       </c>
       <c r="L12" s="24" t="inlineStr">
         <is>
@@ -2459,37 +2459,37 @@
         </is>
       </c>
       <c r="B13" s="24" t="n">
-        <v>2.966</v>
+        <v>3.013</v>
       </c>
       <c r="C13" s="24" t="n">
-        <v>1.131</v>
+        <v>1.128</v>
       </c>
       <c r="D13" s="24" t="n">
         <v>0.007</v>
       </c>
       <c r="E13" s="24" t="n">
-        <v>0.014</v>
+        <v>0.018</v>
       </c>
       <c r="F13" s="24" t="n">
-        <v>0.039</v>
+        <v>0.022</v>
       </c>
       <c r="G13" s="24" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.065</v>
       </c>
       <c r="H13" s="24" t="n">
-        <v>0.52</v>
+        <v>0.483</v>
       </c>
       <c r="I13" s="24" t="n">
-        <v>-0.417</v>
+        <v>-0.427</v>
       </c>
       <c r="J13" s="24" t="n">
-        <v>0.045</v>
+        <v>0.025</v>
       </c>
       <c r="K13" s="24" t="n">
-        <v>-0.08799999999999999</v>
+        <v>-0.101</v>
       </c>
       <c r="L13" s="24" t="n">
-        <v>-0.444</v>
+        <v>-0.43</v>
       </c>
       <c r="M13" s="24" t="inlineStr">
         <is>
@@ -2508,40 +2508,40 @@
         </is>
       </c>
       <c r="B14" s="24" t="n">
-        <v>4.501</v>
+        <v>4.495</v>
       </c>
       <c r="C14" s="24" t="n">
-        <v>0.403</v>
+        <v>0.404</v>
       </c>
       <c r="D14" s="24" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="E14" s="24" t="n">
-        <v>-0.041</v>
+        <v>-0.022</v>
       </c>
       <c r="F14" s="24" t="n">
-        <v>0.031</v>
+        <v>0.018</v>
       </c>
       <c r="G14" s="24" t="n">
-        <v>-0.031</v>
+        <v>-0.02</v>
       </c>
       <c r="H14" s="24" t="n">
-        <v>0.036</v>
+        <v>0.005</v>
       </c>
       <c r="I14" s="24" t="n">
-        <v>0.049</v>
+        <v>0.074</v>
       </c>
       <c r="J14" s="24" t="n">
-        <v>-0.153</v>
+        <v>-0.16</v>
       </c>
       <c r="K14" s="24" t="n">
-        <v>0.097</v>
+        <v>0.024</v>
       </c>
       <c r="L14" s="24" t="n">
-        <v>0.061</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="M14" s="24" t="n">
-        <v>-0.07199999999999999</v>
+        <v>-0.094</v>
       </c>
       <c r="N14" s="24" t="inlineStr">
         <is>
@@ -2559,43 +2559,43 @@
         </is>
       </c>
       <c r="B15" s="24" t="n">
-        <v>4.538</v>
+        <v>4.554</v>
       </c>
       <c r="C15" s="24" t="n">
-        <v>0.832</v>
+        <v>0.806</v>
       </c>
       <c r="D15" s="24" t="n">
+        <v>-0.042</v>
+      </c>
+      <c r="E15" s="24" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="F15" s="24" t="n">
         <v>0.018</v>
       </c>
-      <c r="E15" s="24" t="n">
-        <v>-0.027</v>
-      </c>
-      <c r="F15" s="24" t="n">
-        <v>-0.008999999999999999</v>
-      </c>
       <c r="G15" s="24" t="n">
-        <v>-0.053</v>
+        <v>-0.063</v>
       </c>
       <c r="H15" s="24" t="n">
-        <v>-0.463</v>
+        <v>-0.381</v>
       </c>
       <c r="I15" s="24" t="n">
-        <v>0.412</v>
+        <v>0.449</v>
       </c>
       <c r="J15" s="24" t="n">
-        <v>0.034</v>
+        <v>-0.001</v>
       </c>
       <c r="K15" s="24" t="n">
-        <v>0.063</v>
+        <v>0.003</v>
       </c>
       <c r="L15" s="24" t="n">
-        <v>0.699</v>
+        <v>0.708</v>
       </c>
       <c r="M15" s="24" t="n">
-        <v>-0.643</v>
+        <v>-0.619</v>
       </c>
       <c r="N15" s="24" t="n">
-        <v>0.028</v>
+        <v>0.117</v>
       </c>
       <c r="O15" s="24" t="inlineStr">
         <is>
@@ -2612,46 +2612,46 @@
         </is>
       </c>
       <c r="B16" s="24" t="n">
-        <v>5.062</v>
+        <v>5.077</v>
       </c>
       <c r="C16" s="24" t="n">
-        <v>1.081</v>
+        <v>1.049</v>
       </c>
       <c r="D16" s="24" t="n">
-        <v>-0.093</v>
+        <v>-0.078</v>
       </c>
       <c r="E16" s="24" t="n">
-        <v>0.01</v>
+        <v>-0.056</v>
       </c>
       <c r="F16" s="24" t="n">
-        <v>-0.048</v>
+        <v>-0.029</v>
       </c>
       <c r="G16" s="24" t="n">
-        <v>-0.105</v>
+        <v>-0.07199999999999999</v>
       </c>
       <c r="H16" s="24" t="n">
-        <v>-0.325</v>
+        <v>-0.26</v>
       </c>
       <c r="I16" s="24" t="n">
-        <v>0.33</v>
+        <v>0.321</v>
       </c>
       <c r="J16" s="24" t="n">
-        <v>-0.004</v>
+        <v>0.038</v>
       </c>
       <c r="K16" s="24" t="n">
-        <v>0.026</v>
+        <v>0.056</v>
       </c>
       <c r="L16" s="24" t="n">
-        <v>0.512</v>
+        <v>0.463</v>
       </c>
       <c r="M16" s="24" t="n">
-        <v>-0.547</v>
+        <v>-0.538</v>
       </c>
       <c r="N16" s="24" t="n">
-        <v>0.002</v>
+        <v>0.107</v>
       </c>
       <c r="O16" s="24" t="n">
-        <v>0.523</v>
+        <v>0.499</v>
       </c>
       <c r="P16" s="24" t="inlineStr">
         <is>
@@ -2667,49 +2667,49 @@
         </is>
       </c>
       <c r="B17" s="24" t="n">
-        <v>2.569</v>
+        <v>2.543</v>
       </c>
       <c r="C17" s="24" t="n">
-        <v>1.116</v>
+        <v>1.121</v>
       </c>
       <c r="D17" s="24" t="n">
-        <v>0.017</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="E17" s="24" t="n">
-        <v>-0.01</v>
+        <v>-0.022</v>
       </c>
       <c r="F17" s="24" t="n">
-        <v>-0.028</v>
+        <v>0.032</v>
       </c>
       <c r="G17" s="24" t="n">
-        <v>0.096</v>
+        <v>0.03</v>
       </c>
       <c r="H17" s="24" t="n">
-        <v>0.369</v>
+        <v>0.318</v>
       </c>
       <c r="I17" s="24" t="n">
-        <v>-0.35</v>
+        <v>-0.294</v>
       </c>
       <c r="J17" s="24" t="n">
-        <v>0.058</v>
+        <v>0.065</v>
       </c>
       <c r="K17" s="24" t="n">
-        <v>-0.012</v>
+        <v>-0.056</v>
       </c>
       <c r="L17" s="24" t="n">
-        <v>-0.501</v>
+        <v>-0.428</v>
       </c>
       <c r="M17" s="24" t="n">
-        <v>0.588</v>
+        <v>0.597</v>
       </c>
       <c r="N17" s="24" t="n">
-        <v>-0.08500000000000001</v>
+        <v>-0.024</v>
       </c>
       <c r="O17" s="24" t="n">
-        <v>-0.486</v>
+        <v>-0.47</v>
       </c>
       <c r="P17" s="24" t="n">
-        <v>-0.391</v>
+        <v>-0.394</v>
       </c>
       <c r="Q17" s="24" t="inlineStr">
         <is>
@@ -3287,16 +3287,16 @@
         <v>0.041</v>
       </c>
       <c r="L14" s="24" t="n">
-        <v>-0.067</v>
+        <v>-0.078</v>
       </c>
       <c r="M14" s="24" t="n">
-        <v>0.04</v>
+        <v>0.041</v>
       </c>
       <c r="N14" s="24" t="n">
-        <v>0.075</v>
+        <v>0.118</v>
       </c>
       <c r="O14" s="24" t="n">
-        <v>0.042</v>
+        <v>0.045</v>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1" s="37">
@@ -3336,16 +3336,16 @@
         <v>0.043</v>
       </c>
       <c r="L15" s="24" t="n">
-        <v>0.094</v>
+        <v>0.108</v>
       </c>
       <c r="M15" s="24" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="N15" s="24" t="n">
+        <v>-0.08400000000000001</v>
+      </c>
+      <c r="O15" s="24" t="n">
         <v>0.041</v>
-      </c>
-      <c r="N15" s="24" t="n">
-        <v>-0.058</v>
-      </c>
-      <c r="O15" s="24" t="n">
-        <v>0.04</v>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1" s="37">
@@ -3416,22 +3416,22 @@
         </is>
       </c>
       <c r="J17" s="24" t="n">
-        <v>0.234</v>
+        <v>0.248</v>
       </c>
       <c r="K17" s="24" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="L17" s="24" t="n">
+        <v>0.235</v>
+      </c>
+      <c r="M17" s="24" t="n">
         <v>0.046</v>
       </c>
-      <c r="L17" s="24" t="n">
-        <v>0.203</v>
-      </c>
-      <c r="M17" s="24" t="n">
-        <v>0.048</v>
-      </c>
       <c r="N17" s="24" t="n">
-        <v>-0.112</v>
+        <v>-0.08500000000000001</v>
       </c>
       <c r="O17" s="24" t="n">
-        <v>0.044</v>
+        <v>0.043</v>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1" s="37">
@@ -3481,22 +3481,22 @@
         </is>
       </c>
       <c r="J18" s="24" t="n">
-        <v>-0.198</v>
+        <v>-0.212</v>
       </c>
       <c r="K18" s="24" t="n">
-        <v>0.051</v>
+        <v>0.05</v>
       </c>
       <c r="L18" s="24" t="n">
-        <v>-0.156</v>
+        <v>-0.118</v>
       </c>
       <c r="M18" s="24" t="n">
-        <v>0.053</v>
+        <v>0.052</v>
       </c>
       <c r="N18" s="24" t="n">
-        <v>0.278</v>
+        <v>0.318</v>
       </c>
       <c r="O18" s="24" t="n">
-        <v>0.055</v>
+        <v>0.054</v>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1" s="37">
@@ -3527,46 +3527,46 @@
         </is>
       </c>
       <c r="B20" s="24" t="n">
-        <v>-0.054</v>
+        <v>-0.118</v>
       </c>
       <c r="C20" s="24" t="n">
-        <v>0.044</v>
+        <v>0.046</v>
       </c>
       <c r="D20" s="24" t="n">
-        <v>-0.054</v>
+        <v>-0.118</v>
       </c>
       <c r="E20" s="24" t="n">
-        <v>0.044</v>
+        <v>0.046</v>
       </c>
       <c r="F20" s="24" t="n">
-        <v>0.082</v>
+        <v>0.214</v>
       </c>
       <c r="G20" s="24" t="n">
+        <v>0.047</v>
+      </c>
+      <c r="H20" s="24" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="I20" s="24" t="n">
+        <v>0.047</v>
+      </c>
+      <c r="J20" s="24" t="n">
+        <v>-0.118</v>
+      </c>
+      <c r="K20" s="24" t="n">
         <v>0.046</v>
       </c>
-      <c r="H20" s="24" t="n">
-        <v>0.082</v>
-      </c>
-      <c r="I20" s="24" t="n">
+      <c r="L20" s="24" t="n">
+        <v>-0.118</v>
+      </c>
+      <c r="M20" s="24" t="n">
         <v>0.046</v>
       </c>
-      <c r="J20" s="24" t="n">
-        <v>-0.054</v>
-      </c>
-      <c r="K20" s="24" t="n">
-        <v>0.044</v>
-      </c>
-      <c r="L20" s="24" t="n">
-        <v>-0.054</v>
-      </c>
-      <c r="M20" s="24" t="n">
-        <v>0.044</v>
-      </c>
       <c r="N20" s="24" t="n">
-        <v>-0.054</v>
+        <v>-0.118</v>
       </c>
       <c r="O20" s="24" t="n">
-        <v>0.044</v>
+        <v>0.046</v>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1" s="37">

--- a/results/Model3.xlsx
+++ b/results/Model3.xlsx
@@ -2108,10 +2108,10 @@
         </is>
       </c>
       <c r="B4" s="24" t="n">
-        <v>0.552</v>
+        <v>0.546</v>
       </c>
       <c r="C4" s="24" t="n">
-        <v>0.498</v>
+        <v>0.499</v>
       </c>
       <c r="D4" s="24" t="inlineStr">
         <is>
@@ -2139,13 +2139,13 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>30.674</v>
+        <v>30.609</v>
       </c>
       <c r="C5" s="24" t="n">
-        <v>4.641</v>
+        <v>4.651</v>
       </c>
       <c r="D5" s="24" t="n">
-        <v>0.048</v>
+        <v>0.042</v>
       </c>
       <c r="E5" s="24" t="inlineStr">
         <is>
@@ -2172,16 +2172,16 @@
         </is>
       </c>
       <c r="B6" s="24" t="n">
-        <v>2.314</v>
+        <v>2.269</v>
       </c>
       <c r="C6" s="24" t="n">
-        <v>1.504</v>
+        <v>1.437</v>
       </c>
       <c r="D6" s="24" t="n">
-        <v>-0.014</v>
+        <v>-0.002</v>
       </c>
       <c r="E6" s="24" t="n">
-        <v>0.202</v>
+        <v>0.183</v>
       </c>
       <c r="F6" s="24" t="inlineStr">
         <is>
@@ -2207,19 +2207,19 @@
         </is>
       </c>
       <c r="B7" s="24" t="n">
-        <v>3.296</v>
+        <v>3.283</v>
       </c>
       <c r="C7" s="24" t="n">
-        <v>1.083</v>
+        <v>1.082</v>
       </c>
       <c r="D7" s="24" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.115</v>
       </c>
       <c r="E7" s="24" t="n">
-        <v>0.004</v>
+        <v>-0.024</v>
       </c>
       <c r="F7" s="24" t="n">
-        <v>-0.036</v>
+        <v>-0.058</v>
       </c>
       <c r="G7" s="24" t="inlineStr">
         <is>
@@ -2244,22 +2244,22 @@
         </is>
       </c>
       <c r="B8" s="24" t="n">
-        <v>4.077</v>
+        <v>4.029</v>
       </c>
       <c r="C8" s="24" t="n">
-        <v>0.889</v>
+        <v>0.879</v>
       </c>
       <c r="D8" s="24" t="n">
-        <v>-0.002</v>
+        <v>-0.016</v>
       </c>
       <c r="E8" s="24" t="n">
-        <v>-0.006</v>
+        <v>-0.033</v>
       </c>
       <c r="F8" s="24" t="n">
-        <v>0.089</v>
+        <v>0.043</v>
       </c>
       <c r="G8" s="24" t="n">
-        <v>0.012</v>
+        <v>0.011</v>
       </c>
       <c r="H8" s="23" t="inlineStr">
         <is>
@@ -2283,25 +2283,25 @@
         </is>
       </c>
       <c r="B9" s="24" t="n">
-        <v>5.004</v>
+        <v>5</v>
       </c>
       <c r="C9" s="24" t="n">
-        <v>0.848</v>
+        <v>0.837</v>
       </c>
       <c r="D9" s="24" t="n">
-        <v>0</v>
+        <v>-0.043</v>
       </c>
       <c r="E9" s="24" t="n">
-        <v>-0.03</v>
+        <v>0.026</v>
       </c>
       <c r="F9" s="24" t="n">
-        <v>0.003</v>
+        <v>-0.023</v>
       </c>
       <c r="G9" s="24" t="n">
-        <v>-0.112</v>
+        <v>-0.125</v>
       </c>
       <c r="H9" s="24" t="n">
-        <v>-0.112</v>
+        <v>-0.129</v>
       </c>
       <c r="I9" s="24" t="inlineStr">
         <is>
@@ -2324,28 +2324,28 @@
         </is>
       </c>
       <c r="B10" s="24" t="n">
-        <v>3.44</v>
+        <v>3.438</v>
       </c>
       <c r="C10" s="24" t="n">
-        <v>0.924</v>
+        <v>0.906</v>
       </c>
       <c r="D10" s="24" t="n">
-        <v>-0.099</v>
+        <v>-0.041</v>
       </c>
       <c r="E10" s="24" t="n">
-        <v>-0.024</v>
+        <v>-0.038</v>
       </c>
       <c r="F10" s="24" t="n">
-        <v>0.075</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="G10" s="24" t="n">
-        <v>-0.051</v>
+        <v>-0.045</v>
       </c>
       <c r="H10" s="24" t="n">
-        <v>-0.011</v>
+        <v>-0.023</v>
       </c>
       <c r="I10" s="24" t="n">
-        <v>0.035</v>
+        <v>0.029</v>
       </c>
       <c r="J10" s="24" t="inlineStr">
         <is>
@@ -2367,31 +2367,31 @@
         </is>
       </c>
       <c r="B11" s="24" t="n">
-        <v>4.604</v>
+        <v>4.575</v>
       </c>
       <c r="C11" s="24" t="n">
-        <v>0.886</v>
+        <v>0.897</v>
       </c>
       <c r="D11" s="24" t="n">
-        <v>-0.081</v>
+        <v>-0.107</v>
       </c>
       <c r="E11" s="24" t="n">
-        <v>-0.055</v>
+        <v>-0.079</v>
       </c>
       <c r="F11" s="24" t="n">
-        <v>-0.097</v>
+        <v>-0.056</v>
       </c>
       <c r="G11" s="24" t="n">
-        <v>-0.06900000000000001</v>
+        <v>-0.08500000000000001</v>
       </c>
       <c r="H11" s="24" t="n">
-        <v>-0.067</v>
+        <v>-0.041</v>
       </c>
       <c r="I11" s="24" t="n">
-        <v>-0.014</v>
+        <v>-0.036</v>
       </c>
       <c r="J11" s="24" t="n">
-        <v>0.001</v>
+        <v>-0.018</v>
       </c>
       <c r="K11" s="24" t="inlineStr">
         <is>
@@ -2412,34 +2412,34 @@
         </is>
       </c>
       <c r="B12" s="24" t="n">
-        <v>4.476</v>
+        <v>4.471</v>
       </c>
       <c r="C12" s="24" t="n">
-        <v>1.207</v>
+        <v>1.194</v>
       </c>
       <c r="D12" s="24" t="n">
-        <v>-0.038</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E12" s="24" t="n">
-        <v>-0.019</v>
+        <v>0.003</v>
       </c>
       <c r="F12" s="24" t="n">
-        <v>-0.061</v>
+        <v>-0.053</v>
       </c>
       <c r="G12" s="24" t="n">
-        <v>-0.074</v>
+        <v>-0.048</v>
       </c>
       <c r="H12" s="24" t="n">
-        <v>-0.468</v>
+        <v>-0.477</v>
       </c>
       <c r="I12" s="24" t="n">
-        <v>0.47</v>
+        <v>0.463</v>
       </c>
       <c r="J12" s="24" t="n">
-        <v>-0.001</v>
+        <v>-0.008</v>
       </c>
       <c r="K12" s="24" t="n">
-        <v>-0.048</v>
+        <v>-0.051</v>
       </c>
       <c r="L12" s="24" t="inlineStr">
         <is>
@@ -2459,37 +2459,37 @@
         </is>
       </c>
       <c r="B13" s="24" t="n">
-        <v>3.013</v>
+        <v>2.977</v>
       </c>
       <c r="C13" s="24" t="n">
-        <v>1.128</v>
+        <v>1.137</v>
       </c>
       <c r="D13" s="24" t="n">
-        <v>0.007</v>
+        <v>0.025</v>
       </c>
       <c r="E13" s="24" t="n">
-        <v>0.018</v>
+        <v>0.016</v>
       </c>
       <c r="F13" s="24" t="n">
-        <v>0.022</v>
+        <v>0.047</v>
       </c>
       <c r="G13" s="24" t="n">
-        <v>0.065</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="H13" s="24" t="n">
-        <v>0.483</v>
+        <v>0.525</v>
       </c>
       <c r="I13" s="24" t="n">
-        <v>-0.427</v>
+        <v>-0.435</v>
       </c>
       <c r="J13" s="24" t="n">
-        <v>0.025</v>
+        <v>0.049</v>
       </c>
       <c r="K13" s="24" t="n">
-        <v>-0.101</v>
+        <v>-0.092</v>
       </c>
       <c r="L13" s="24" t="n">
-        <v>-0.43</v>
+        <v>-0.457</v>
       </c>
       <c r="M13" s="24" t="inlineStr">
         <is>
@@ -2508,40 +2508,40 @@
         </is>
       </c>
       <c r="B14" s="24" t="n">
-        <v>4.495</v>
+        <v>4.505</v>
       </c>
       <c r="C14" s="24" t="n">
-        <v>0.404</v>
+        <v>0.403</v>
       </c>
       <c r="D14" s="24" t="n">
-        <v>0.001</v>
+        <v>0.004</v>
       </c>
       <c r="E14" s="24" t="n">
-        <v>-0.022</v>
+        <v>-0.036</v>
       </c>
       <c r="F14" s="24" t="n">
-        <v>0.018</v>
+        <v>0.015</v>
       </c>
       <c r="G14" s="24" t="n">
-        <v>-0.02</v>
+        <v>0.022</v>
       </c>
       <c r="H14" s="24" t="n">
-        <v>0.005</v>
+        <v>-0</v>
       </c>
       <c r="I14" s="24" t="n">
-        <v>0.074</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J14" s="24" t="n">
-        <v>-0.16</v>
+        <v>-0.175</v>
       </c>
       <c r="K14" s="24" t="n">
-        <v>0.024</v>
+        <v>0.073</v>
       </c>
       <c r="L14" s="24" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.075</v>
       </c>
       <c r="M14" s="24" t="n">
-        <v>-0.094</v>
+        <v>-0.095</v>
       </c>
       <c r="N14" s="24" t="inlineStr">
         <is>
@@ -2559,43 +2559,43 @@
         </is>
       </c>
       <c r="B15" s="24" t="n">
-        <v>4.554</v>
+        <v>4.548</v>
       </c>
       <c r="C15" s="24" t="n">
         <v>0.806</v>
       </c>
       <c r="D15" s="24" t="n">
-        <v>-0.042</v>
+        <v>0.011</v>
       </c>
       <c r="E15" s="24" t="n">
-        <v>0.004</v>
+        <v>0.015</v>
       </c>
       <c r="F15" s="24" t="n">
-        <v>0.018</v>
+        <v>0.028</v>
       </c>
       <c r="G15" s="24" t="n">
-        <v>-0.063</v>
+        <v>-0.081</v>
       </c>
       <c r="H15" s="24" t="n">
-        <v>-0.381</v>
+        <v>-0.514</v>
       </c>
       <c r="I15" s="24" t="n">
-        <v>0.449</v>
+        <v>0.409</v>
       </c>
       <c r="J15" s="24" t="n">
-        <v>-0.001</v>
+        <v>-0.052</v>
       </c>
       <c r="K15" s="24" t="n">
-        <v>0.003</v>
+        <v>0.04</v>
       </c>
       <c r="L15" s="24" t="n">
-        <v>0.708</v>
+        <v>0.677</v>
       </c>
       <c r="M15" s="24" t="n">
-        <v>-0.619</v>
+        <v>-0.6870000000000001</v>
       </c>
       <c r="N15" s="24" t="n">
-        <v>0.117</v>
+        <v>0.083</v>
       </c>
       <c r="O15" s="24" t="inlineStr">
         <is>
@@ -2612,46 +2612,46 @@
         </is>
       </c>
       <c r="B16" s="24" t="n">
-        <v>5.077</v>
+        <v>5.046</v>
       </c>
       <c r="C16" s="24" t="n">
-        <v>1.049</v>
+        <v>1.113</v>
       </c>
       <c r="D16" s="24" t="n">
-        <v>-0.078</v>
+        <v>-0.051</v>
       </c>
       <c r="E16" s="24" t="n">
-        <v>-0.056</v>
+        <v>0.076</v>
       </c>
       <c r="F16" s="24" t="n">
-        <v>-0.029</v>
+        <v>0.005</v>
       </c>
       <c r="G16" s="24" t="n">
-        <v>-0.07199999999999999</v>
+        <v>-0.008</v>
       </c>
       <c r="H16" s="24" t="n">
-        <v>-0.26</v>
+        <v>-0.36</v>
       </c>
       <c r="I16" s="24" t="n">
-        <v>0.321</v>
+        <v>0.299</v>
       </c>
       <c r="J16" s="24" t="n">
-        <v>0.038</v>
+        <v>0.016</v>
       </c>
       <c r="K16" s="24" t="n">
-        <v>0.056</v>
+        <v>0.061</v>
       </c>
       <c r="L16" s="24" t="n">
-        <v>0.463</v>
+        <v>0.512</v>
       </c>
       <c r="M16" s="24" t="n">
-        <v>-0.538</v>
+        <v>-0.512</v>
       </c>
       <c r="N16" s="24" t="n">
-        <v>0.107</v>
+        <v>0.051</v>
       </c>
       <c r="O16" s="24" t="n">
-        <v>0.499</v>
+        <v>0.413</v>
       </c>
       <c r="P16" s="24" t="inlineStr">
         <is>
@@ -2667,49 +2667,49 @@
         </is>
       </c>
       <c r="B17" s="24" t="n">
-        <v>2.543</v>
+        <v>2.551</v>
       </c>
       <c r="C17" s="24" t="n">
-        <v>1.121</v>
+        <v>1.116</v>
       </c>
       <c r="D17" s="24" t="n">
-        <v>-0.008999999999999999</v>
+        <v>0.023</v>
       </c>
       <c r="E17" s="24" t="n">
-        <v>-0.022</v>
+        <v>-0.08500000000000001</v>
       </c>
       <c r="F17" s="24" t="n">
-        <v>0.032</v>
+        <v>0.047</v>
       </c>
       <c r="G17" s="24" t="n">
-        <v>0.03</v>
+        <v>0.059</v>
       </c>
       <c r="H17" s="24" t="n">
-        <v>0.318</v>
+        <v>0.426</v>
       </c>
       <c r="I17" s="24" t="n">
-        <v>-0.294</v>
+        <v>-0.343</v>
       </c>
       <c r="J17" s="24" t="n">
-        <v>0.065</v>
+        <v>-0.031</v>
       </c>
       <c r="K17" s="24" t="n">
-        <v>-0.056</v>
+        <v>0.026</v>
       </c>
       <c r="L17" s="24" t="n">
-        <v>-0.428</v>
+        <v>-0.522</v>
       </c>
       <c r="M17" s="24" t="n">
-        <v>0.597</v>
+        <v>0.602</v>
       </c>
       <c r="N17" s="24" t="n">
-        <v>-0.024</v>
+        <v>-0.102</v>
       </c>
       <c r="O17" s="24" t="n">
-        <v>-0.47</v>
+        <v>-0.532</v>
       </c>
       <c r="P17" s="24" t="n">
-        <v>-0.394</v>
+        <v>-0.453</v>
       </c>
       <c r="Q17" s="24" t="inlineStr">
         <is>

--- a/results/Model3.xlsx
+++ b/results/Model3.xlsx
@@ -1608,22 +1608,22 @@
         </is>
       </c>
       <c r="B3" s="35" t="n">
-        <v>1183.4</v>
+        <v>1893.4</v>
       </c>
       <c r="C3" s="35" t="n">
-        <v>542</v>
+        <v>873</v>
       </c>
       <c r="D3" s="35" t="n">
-        <v>0.952</v>
+        <v>0.9429999999999999</v>
       </c>
       <c r="E3" s="35" t="n">
-        <v>0.948</v>
+        <v>0.9370000000000001</v>
       </c>
       <c r="F3" s="35" t="n">
-        <v>0.043</v>
+        <v>0.045</v>
       </c>
       <c r="G3" s="35" t="n">
-        <v>0.038</v>
+        <v>0.041</v>
       </c>
       <c r="H3" s="35" t="n"/>
       <c r="I3" s="35" t="n"/>
@@ -1642,28 +1642,28 @@
         </is>
       </c>
       <c r="B4" s="35" t="n">
-        <v>1098.6</v>
+        <v>1815.9</v>
       </c>
       <c r="C4" s="35" t="n">
-        <v>521</v>
+        <v>852</v>
       </c>
       <c r="D4" s="35" t="n">
-        <v>0.961</v>
+        <v>0.948</v>
       </c>
       <c r="E4" s="35" t="n">
-        <v>0.954</v>
+        <v>0.9389999999999999</v>
       </c>
       <c r="F4" s="35" t="n">
-        <v>0.041</v>
+        <v>0.044</v>
       </c>
       <c r="G4" s="35" t="n">
-        <v>0.036</v>
+        <v>0.04</v>
       </c>
       <c r="H4" s="35" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.005</v>
       </c>
       <c r="I4" s="35" t="n">
-        <v>-0.002</v>
+        <v>-0.001</v>
       </c>
       <c r="J4" s="36" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
       <c r="I5" s="35" t="n"/>
       <c r="J5" s="35" t="inlineStr">
         <is>
-          <t>Method factor explains 12%</t>
+          <t>Method factor explains 9.4%</t>
         </is>
       </c>
       <c r="K5" s="35" t="n"/>
@@ -1816,28 +1816,28 @@
         </is>
       </c>
       <c r="D3" s="32" t="n">
-        <v>1183.4</v>
+        <v>1893.4</v>
       </c>
       <c r="E3" s="32" t="n">
-        <v>542</v>
+        <v>873</v>
       </c>
       <c r="F3" s="32" t="n">
-        <v>0.952</v>
+        <v>0.9429999999999999</v>
       </c>
       <c r="G3" s="32" t="n">
-        <v>0.948</v>
+        <v>0.9370000000000001</v>
       </c>
       <c r="H3" s="32" t="n">
-        <v>0.043</v>
+        <v>0.045</v>
       </c>
       <c r="I3" s="32" t="n">
-        <v>0.038</v>
+        <v>0.041</v>
       </c>
       <c r="J3" s="32" t="n">
-        <v>0.046</v>
+        <v>0.058</v>
       </c>
       <c r="K3" s="32" t="n">
-        <v>22456.3</v>
+        <v>31207.8</v>
       </c>
     </row>
     <row r="4" ht="46.5" customHeight="1" s="37">
@@ -1857,28 +1857,28 @@
         </is>
       </c>
       <c r="D4" s="32" t="n">
-        <v>1392.7</v>
+        <v>2108.2</v>
       </c>
       <c r="E4" s="32" t="n">
-        <v>547</v>
+        <v>877</v>
       </c>
       <c r="F4" s="32" t="n">
-        <v>0.928</v>
+        <v>0.926</v>
       </c>
       <c r="G4" s="32" t="n">
-        <v>0.922</v>
+        <v>0.918</v>
       </c>
       <c r="H4" s="32" t="n">
-        <v>0.054</v>
+        <v>0.052</v>
       </c>
       <c r="I4" s="32" t="n">
-        <v>0.044</v>
+        <v>0.048</v>
       </c>
       <c r="J4" s="32" t="n">
-        <v>0.051</v>
+        <v>0.061</v>
       </c>
       <c r="K4" s="32" t="n">
-        <v>22612.5</v>
+        <v>31398.5</v>
       </c>
     </row>
     <row r="5" ht="46.5" customHeight="1" s="37">
@@ -1898,28 +1898,28 @@
         </is>
       </c>
       <c r="D5" s="32" t="n">
-        <v>1518.3</v>
+        <v>2287.6</v>
       </c>
       <c r="E5" s="32" t="n">
-        <v>547</v>
+        <v>877</v>
       </c>
       <c r="F5" s="32" t="n">
-        <v>0.918</v>
+        <v>0.913</v>
       </c>
       <c r="G5" s="32" t="n">
-        <v>0.911</v>
+        <v>0.904</v>
       </c>
       <c r="H5" s="32" t="n">
-        <v>0.058</v>
+        <v>0.057</v>
       </c>
       <c r="I5" s="32" t="n">
-        <v>0.047</v>
+        <v>0.05</v>
       </c>
       <c r="J5" s="32" t="n">
-        <v>0.053</v>
+        <v>0.075</v>
       </c>
       <c r="K5" s="32" t="n">
-        <v>22789.6</v>
+        <v>31573.9</v>
       </c>
     </row>
     <row r="6" ht="69.75" customHeight="1" s="37">
@@ -1939,28 +1939,28 @@
         </is>
       </c>
       <c r="D6" s="32" t="n">
-        <v>2034.1</v>
+        <v>2541.3</v>
       </c>
       <c r="E6" s="32" t="n">
-        <v>552</v>
+        <v>882</v>
       </c>
       <c r="F6" s="32" t="n">
-        <v>0.876</v>
+        <v>0.892</v>
       </c>
       <c r="G6" s="32" t="n">
-        <v>0.866</v>
+        <v>0.881</v>
       </c>
       <c r="H6" s="32" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.064</v>
       </c>
       <c r="I6" s="32" t="n">
-        <v>0.052</v>
+        <v>0.057</v>
       </c>
       <c r="J6" s="32" t="n">
-        <v>0.058</v>
+        <v>0.073</v>
       </c>
       <c r="K6" s="32" t="n">
-        <v>23156.2</v>
+        <v>31814.2</v>
       </c>
     </row>
     <row r="7" ht="46.5" customHeight="1" s="37">
@@ -1980,28 +1980,28 @@
         </is>
       </c>
       <c r="D7" s="32" t="n">
-        <v>2789.5</v>
+        <v>3294.7</v>
       </c>
       <c r="E7" s="32" t="n">
-        <v>556</v>
+        <v>887</v>
       </c>
       <c r="F7" s="32" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.821</v>
       </c>
       <c r="G7" s="32" t="n">
-        <v>0.798</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="H7" s="32" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.083</v>
       </c>
       <c r="I7" s="32" t="n">
-        <v>0.064</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="J7" s="32" t="n">
-        <v>0.078</v>
+        <v>0.097</v>
       </c>
       <c r="K7" s="32" t="n">
-        <v>23598.7</v>
+        <v>32508.6</v>
       </c>
     </row>
   </sheetData>
@@ -2108,10 +2108,10 @@
         </is>
       </c>
       <c r="B4" s="24" t="n">
-        <v>0.546</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="C4" s="24" t="n">
-        <v>0.499</v>
+        <v>0.497</v>
       </c>
       <c r="D4" s="24" t="inlineStr">
         <is>
@@ -2139,13 +2139,13 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>30.609</v>
+        <v>30.699</v>
       </c>
       <c r="C5" s="24" t="n">
-        <v>4.651</v>
+        <v>4.675</v>
       </c>
       <c r="D5" s="24" t="n">
-        <v>0.042</v>
+        <v>0.022</v>
       </c>
       <c r="E5" s="24" t="inlineStr">
         <is>
@@ -2172,16 +2172,16 @@
         </is>
       </c>
       <c r="B6" s="24" t="n">
-        <v>2.269</v>
+        <v>2.297</v>
       </c>
       <c r="C6" s="24" t="n">
-        <v>1.437</v>
+        <v>1.468</v>
       </c>
       <c r="D6" s="24" t="n">
-        <v>-0.002</v>
+        <v>-0.025</v>
       </c>
       <c r="E6" s="24" t="n">
-        <v>0.183</v>
+        <v>0.203</v>
       </c>
       <c r="F6" s="24" t="inlineStr">
         <is>
@@ -2207,19 +2207,19 @@
         </is>
       </c>
       <c r="B7" s="24" t="n">
-        <v>3.283</v>
+        <v>3.249</v>
       </c>
       <c r="C7" s="24" t="n">
-        <v>1.082</v>
+        <v>1.06</v>
       </c>
       <c r="D7" s="24" t="n">
-        <v>0.115</v>
+        <v>0.096</v>
       </c>
       <c r="E7" s="24" t="n">
-        <v>-0.024</v>
+        <v>-0.014</v>
       </c>
       <c r="F7" s="24" t="n">
-        <v>-0.058</v>
+        <v>-0.049</v>
       </c>
       <c r="G7" s="24" t="inlineStr">
         <is>
@@ -2244,26 +2244,26 @@
         </is>
       </c>
       <c r="B8" s="24" t="n">
-        <v>4.029</v>
+        <v>4.04</v>
       </c>
       <c r="C8" s="24" t="n">
-        <v>0.879</v>
+        <v>0.901</v>
       </c>
       <c r="D8" s="24" t="n">
+        <v>-0.058</v>
+      </c>
+      <c r="E8" s="24" t="n">
+        <v>-0.008</v>
+      </c>
+      <c r="F8" s="24" t="n">
+        <v>0.082</v>
+      </c>
+      <c r="G8" s="24" t="n">
         <v>-0.016</v>
       </c>
-      <c r="E8" s="24" t="n">
-        <v>-0.033</v>
-      </c>
-      <c r="F8" s="24" t="n">
-        <v>0.043</v>
-      </c>
-      <c r="G8" s="24" t="n">
-        <v>0.011</v>
-      </c>
       <c r="H8" s="23" t="inlineStr">
         <is>
-          <t>(0.91)</t>
+          <t>(0.86)</t>
         </is>
       </c>
       <c r="I8" s="24" t="n"/>
@@ -2283,29 +2283,29 @@
         </is>
       </c>
       <c r="B9" s="24" t="n">
-        <v>5</v>
+        <v>4.999</v>
       </c>
       <c r="C9" s="24" t="n">
-        <v>0.837</v>
+        <v>0.997</v>
       </c>
       <c r="D9" s="24" t="n">
-        <v>-0.043</v>
+        <v>-0</v>
       </c>
       <c r="E9" s="24" t="n">
-        <v>0.026</v>
+        <v>-0.027</v>
       </c>
       <c r="F9" s="24" t="n">
-        <v>-0.023</v>
+        <v>0.028</v>
       </c>
       <c r="G9" s="24" t="n">
-        <v>-0.125</v>
+        <v>-0.119</v>
       </c>
       <c r="H9" s="24" t="n">
-        <v>-0.129</v>
+        <v>-0.354</v>
       </c>
       <c r="I9" s="24" t="inlineStr">
         <is>
-          <t>(0.93)</t>
+          <t>(0.87)</t>
         </is>
       </c>
       <c r="J9" s="24" t="n"/>
@@ -2324,32 +2324,32 @@
         </is>
       </c>
       <c r="B10" s="24" t="n">
-        <v>3.438</v>
+        <v>3.463</v>
       </c>
       <c r="C10" s="24" t="n">
-        <v>0.906</v>
+        <v>0.921</v>
       </c>
       <c r="D10" s="24" t="n">
-        <v>-0.041</v>
+        <v>-0.062</v>
       </c>
       <c r="E10" s="24" t="n">
-        <v>-0.038</v>
+        <v>-0</v>
       </c>
       <c r="F10" s="24" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.076</v>
       </c>
       <c r="G10" s="24" t="n">
-        <v>-0.045</v>
+        <v>-0.06</v>
       </c>
       <c r="H10" s="24" t="n">
-        <v>-0.023</v>
+        <v>0.021</v>
       </c>
       <c r="I10" s="24" t="n">
-        <v>0.029</v>
+        <v>-0.004</v>
       </c>
       <c r="J10" s="24" t="inlineStr">
         <is>
-          <t>(0.86)</t>
+          <t>(0.79)</t>
         </is>
       </c>
       <c r="K10" s="24" t="n"/>
@@ -2367,35 +2367,35 @@
         </is>
       </c>
       <c r="B11" s="24" t="n">
-        <v>4.575</v>
+        <v>4.597</v>
       </c>
       <c r="C11" s="24" t="n">
-        <v>0.897</v>
+        <v>0.887</v>
       </c>
       <c r="D11" s="24" t="n">
-        <v>-0.107</v>
+        <v>-0.07199999999999999</v>
       </c>
       <c r="E11" s="24" t="n">
-        <v>-0.079</v>
+        <v>-0.091</v>
       </c>
       <c r="F11" s="24" t="n">
-        <v>-0.056</v>
+        <v>-0.046</v>
       </c>
       <c r="G11" s="24" t="n">
-        <v>-0.08500000000000001</v>
+        <v>-0.049</v>
       </c>
       <c r="H11" s="24" t="n">
-        <v>-0.041</v>
+        <v>-0.031</v>
       </c>
       <c r="I11" s="24" t="n">
-        <v>-0.036</v>
+        <v>-0.039</v>
       </c>
       <c r="J11" s="24" t="n">
-        <v>-0.018</v>
+        <v>0.02</v>
       </c>
       <c r="K11" s="24" t="inlineStr">
         <is>
-          <t>(0.84)</t>
+          <t>(0.78)</t>
         </is>
       </c>
       <c r="L11" s="24" t="n"/>
@@ -2412,38 +2412,38 @@
         </is>
       </c>
       <c r="B12" s="24" t="n">
-        <v>4.471</v>
+        <v>4.533</v>
       </c>
       <c r="C12" s="24" t="n">
-        <v>1.194</v>
+        <v>1.266</v>
       </c>
       <c r="D12" s="24" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.03</v>
       </c>
       <c r="E12" s="24" t="n">
-        <v>0.003</v>
+        <v>-0.038</v>
       </c>
       <c r="F12" s="24" t="n">
-        <v>-0.053</v>
+        <v>-0.016</v>
       </c>
       <c r="G12" s="24" t="n">
-        <v>-0.048</v>
+        <v>-0.059</v>
       </c>
       <c r="H12" s="24" t="n">
-        <v>-0.477</v>
+        <v>-0.5679999999999999</v>
       </c>
       <c r="I12" s="24" t="n">
-        <v>0.463</v>
+        <v>0.569</v>
       </c>
       <c r="J12" s="24" t="n">
-        <v>-0.008</v>
+        <v>-0.059</v>
       </c>
       <c r="K12" s="24" t="n">
-        <v>-0.051</v>
+        <v>-0.081</v>
       </c>
       <c r="L12" s="24" t="inlineStr">
         <is>
-          <t>(0.88)</t>
+          <t>(0.84)</t>
         </is>
       </c>
       <c r="M12" s="24" t="n"/>
@@ -2459,41 +2459,41 @@
         </is>
       </c>
       <c r="B13" s="24" t="n">
-        <v>2.977</v>
+        <v>2.971</v>
       </c>
       <c r="C13" s="24" t="n">
-        <v>1.137</v>
+        <v>1.201</v>
       </c>
       <c r="D13" s="24" t="n">
-        <v>0.025</v>
+        <v>-0.011</v>
       </c>
       <c r="E13" s="24" t="n">
-        <v>0.016</v>
+        <v>0.05</v>
       </c>
       <c r="F13" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="24" t="n">
         <v>0.047</v>
       </c>
-      <c r="G13" s="24" t="n">
-        <v>0.08599999999999999</v>
-      </c>
       <c r="H13" s="24" t="n">
-        <v>0.525</v>
+        <v>0.539</v>
       </c>
       <c r="I13" s="24" t="n">
-        <v>-0.435</v>
+        <v>-0.52</v>
       </c>
       <c r="J13" s="24" t="n">
-        <v>0.049</v>
+        <v>0.039</v>
       </c>
       <c r="K13" s="24" t="n">
-        <v>-0.092</v>
+        <v>-0.026</v>
       </c>
       <c r="L13" s="24" t="n">
-        <v>-0.457</v>
+        <v>-0.456</v>
       </c>
       <c r="M13" s="24" t="inlineStr">
         <is>
-          <t>(0.87)</t>
+          <t>(0.81)</t>
         </is>
       </c>
       <c r="N13" s="24" t="n"/>
@@ -2508,44 +2508,44 @@
         </is>
       </c>
       <c r="B14" s="24" t="n">
-        <v>4.505</v>
+        <v>4.42</v>
       </c>
       <c r="C14" s="24" t="n">
-        <v>0.403</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="D14" s="24" t="n">
-        <v>0.004</v>
+        <v>-0.005</v>
       </c>
       <c r="E14" s="24" t="n">
-        <v>-0.036</v>
+        <v>-0.025</v>
       </c>
       <c r="F14" s="24" t="n">
-        <v>0.015</v>
+        <v>-0.013</v>
       </c>
       <c r="G14" s="24" t="n">
-        <v>0.022</v>
+        <v>0.001</v>
       </c>
       <c r="H14" s="24" t="n">
-        <v>-0</v>
+        <v>-0.022</v>
       </c>
       <c r="I14" s="24" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.024</v>
       </c>
       <c r="J14" s="24" t="n">
-        <v>-0.175</v>
+        <v>-0.13</v>
       </c>
       <c r="K14" s="24" t="n">
-        <v>0.073</v>
+        <v>0.034</v>
       </c>
       <c r="L14" s="24" t="n">
-        <v>0.075</v>
+        <v>-0.005</v>
       </c>
       <c r="M14" s="24" t="n">
-        <v>-0.095</v>
+        <v>-0.065</v>
       </c>
       <c r="N14" s="24" t="inlineStr">
         <is>
-          <t>(0.90)</t>
+          <t>(0.83)</t>
         </is>
       </c>
       <c r="O14" s="24" t="n"/>
@@ -2559,47 +2559,47 @@
         </is>
       </c>
       <c r="B15" s="24" t="n">
-        <v>4.548</v>
+        <v>4.524</v>
       </c>
       <c r="C15" s="24" t="n">
-        <v>0.806</v>
+        <v>0.829</v>
       </c>
       <c r="D15" s="24" t="n">
-        <v>0.011</v>
+        <v>0.033</v>
       </c>
       <c r="E15" s="24" t="n">
-        <v>0.015</v>
+        <v>-0.08599999999999999</v>
       </c>
       <c r="F15" s="24" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G15" s="24" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="H15" s="24" t="n">
+        <v>-0.456</v>
+      </c>
+      <c r="I15" s="24" t="n">
+        <v>0.426</v>
+      </c>
+      <c r="J15" s="24" t="n">
+        <v>-0.094</v>
+      </c>
+      <c r="K15" s="24" t="n">
         <v>0.028</v>
       </c>
-      <c r="G15" s="24" t="n">
-        <v>-0.081</v>
-      </c>
-      <c r="H15" s="24" t="n">
-        <v>-0.514</v>
-      </c>
-      <c r="I15" s="24" t="n">
-        <v>0.409</v>
-      </c>
-      <c r="J15" s="24" t="n">
-        <v>-0.052</v>
-      </c>
-      <c r="K15" s="24" t="n">
-        <v>0.04</v>
-      </c>
       <c r="L15" s="24" t="n">
-        <v>0.677</v>
+        <v>0.576</v>
       </c>
       <c r="M15" s="24" t="n">
-        <v>-0.6870000000000001</v>
+        <v>-0.615</v>
       </c>
       <c r="N15" s="24" t="n">
-        <v>0.083</v>
+        <v>0.433</v>
       </c>
       <c r="O15" s="24" t="inlineStr">
         <is>
-          <t>(0.90)</t>
+          <t>(0.85)</t>
         </is>
       </c>
       <c r="P15" s="24" t="n"/>
@@ -2612,50 +2612,50 @@
         </is>
       </c>
       <c r="B16" s="24" t="n">
-        <v>5.046</v>
+        <v>5.073</v>
       </c>
       <c r="C16" s="24" t="n">
-        <v>1.113</v>
+        <v>1.066</v>
       </c>
       <c r="D16" s="24" t="n">
-        <v>-0.051</v>
+        <v>-0.055</v>
       </c>
       <c r="E16" s="24" t="n">
-        <v>0.076</v>
+        <v>-0.03</v>
       </c>
       <c r="F16" s="24" t="n">
-        <v>0.005</v>
+        <v>0.031</v>
       </c>
       <c r="G16" s="24" t="n">
-        <v>-0.008</v>
+        <v>-0.041</v>
       </c>
       <c r="H16" s="24" t="n">
-        <v>-0.36</v>
+        <v>-0.366</v>
       </c>
       <c r="I16" s="24" t="n">
-        <v>0.299</v>
+        <v>0.322</v>
       </c>
       <c r="J16" s="24" t="n">
-        <v>0.016</v>
+        <v>0.027</v>
       </c>
       <c r="K16" s="24" t="n">
-        <v>0.061</v>
+        <v>-0.023</v>
       </c>
       <c r="L16" s="24" t="n">
-        <v>0.512</v>
+        <v>0.488</v>
       </c>
       <c r="M16" s="24" t="n">
-        <v>-0.512</v>
+        <v>-0.542</v>
       </c>
       <c r="N16" s="24" t="n">
-        <v>0.051</v>
+        <v>-0.048</v>
       </c>
       <c r="O16" s="24" t="n">
-        <v>0.413</v>
+        <v>0.426</v>
       </c>
       <c r="P16" s="24" t="inlineStr">
         <is>
-          <t>(0.88)</t>
+          <t>(0.81)</t>
         </is>
       </c>
       <c r="Q16" s="24" t="n"/>
@@ -2667,53 +2667,53 @@
         </is>
       </c>
       <c r="B17" s="24" t="n">
-        <v>2.551</v>
+        <v>2.582</v>
       </c>
       <c r="C17" s="24" t="n">
-        <v>1.116</v>
+        <v>1.08</v>
       </c>
       <c r="D17" s="24" t="n">
-        <v>0.023</v>
+        <v>0.024</v>
       </c>
       <c r="E17" s="24" t="n">
-        <v>-0.08500000000000001</v>
+        <v>-0.029</v>
       </c>
       <c r="F17" s="24" t="n">
-        <v>0.047</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="G17" s="24" t="n">
-        <v>0.059</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="H17" s="24" t="n">
-        <v>0.426</v>
+        <v>0.444</v>
       </c>
       <c r="I17" s="24" t="n">
-        <v>-0.343</v>
+        <v>-0.382</v>
       </c>
       <c r="J17" s="24" t="n">
-        <v>-0.031</v>
+        <v>-0.027</v>
       </c>
       <c r="K17" s="24" t="n">
-        <v>0.026</v>
+        <v>0.1</v>
       </c>
       <c r="L17" s="24" t="n">
-        <v>-0.522</v>
+        <v>-0.495</v>
       </c>
       <c r="M17" s="24" t="n">
-        <v>0.602</v>
+        <v>0.569</v>
       </c>
       <c r="N17" s="24" t="n">
-        <v>-0.102</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="O17" s="24" t="n">
-        <v>-0.532</v>
+        <v>-0.427</v>
       </c>
       <c r="P17" s="24" t="n">
-        <v>-0.453</v>
+        <v>-0.433</v>
       </c>
       <c r="Q17" s="24" t="inlineStr">
         <is>
-          <t>(0.85)</t>
+          <t>(0.79)</t>
         </is>
       </c>
     </row>
@@ -3659,7 +3659,7 @@
         <v>-0.012</v>
       </c>
       <c r="E23" s="24" t="n">
-        <v>0.04</v>
+        <v>0.044</v>
       </c>
       <c r="F23" s="24" t="inlineStr">
         <is>
@@ -3675,7 +3675,7 @@
         <v>0.024</v>
       </c>
       <c r="I23" s="24" t="n">
-        <v>0.043</v>
+        <v>0.046</v>
       </c>
       <c r="J23" s="24" t="inlineStr">
         <is>
@@ -3728,7 +3728,7 @@
         <v>0.018</v>
       </c>
       <c r="E24" s="24" t="n">
-        <v>0.039</v>
+        <v>0.037</v>
       </c>
       <c r="F24" s="24" t="inlineStr">
         <is>
@@ -3744,7 +3744,7 @@
         <v>-0.019</v>
       </c>
       <c r="I24" s="24" t="n">
-        <v>0.041</v>
+        <v>0.048</v>
       </c>
       <c r="J24" s="24" t="inlineStr">
         <is>
@@ -3794,10 +3794,10 @@
         </is>
       </c>
       <c r="D25" s="24" t="n">
-        <v>0.078</v>
+        <v>0.046</v>
       </c>
       <c r="E25" s="24" t="n">
-        <v>0.038</v>
+        <v>0.041</v>
       </c>
       <c r="F25" s="24" t="inlineStr">
         <is>
@@ -3813,7 +3813,7 @@
         <v>-0.111</v>
       </c>
       <c r="I25" s="24" t="n">
-        <v>0.041</v>
+        <v>0.039</v>
       </c>
       <c r="J25" s="24" t="inlineStr">
         <is>
@@ -3866,7 +3866,7 @@
         <v>-0.098</v>
       </c>
       <c r="E26" s="24" t="n">
-        <v>0.039</v>
+        <v>0.045</v>
       </c>
       <c r="F26" s="24" t="inlineStr">
         <is>
@@ -3882,7 +3882,7 @@
         <v>0.067</v>
       </c>
       <c r="I26" s="24" t="n">
-        <v>0.038</v>
+        <v>0.052</v>
       </c>
       <c r="J26" s="24" t="inlineStr">
         <is>
@@ -3934,13 +3934,13 @@
         <v>0.198</v>
       </c>
       <c r="J27" s="24" t="n">
-        <v>0.342</v>
+        <v>0.358</v>
       </c>
       <c r="L27" s="24" t="n">
-        <v>0.281</v>
+        <v>0.247</v>
       </c>
       <c r="N27" s="24" t="n">
-        <v>0.253</v>
+        <v>0.218</v>
       </c>
     </row>
     <row r="28" ht="21" customHeight="1" s="37">
@@ -3962,13 +3962,13 @@
         <v>0.118</v>
       </c>
       <c r="J28" s="27" t="n">
-        <v>0.218</v>
+        <v>0.231</v>
       </c>
       <c r="L28" s="27" t="n">
-        <v>0.184</v>
+        <v>0.149</v>
       </c>
       <c r="N28" s="27" t="n">
-        <v>0.162</v>
+        <v>0.131</v>
       </c>
     </row>
   </sheetData>
@@ -4130,27 +4130,27 @@
         </is>
       </c>
       <c r="B8" s="14" t="n">
+        <v>-0.035</v>
+      </c>
+      <c r="C8" s="14" t="inlineStr">
+        <is>
+          <t>[-0.066, -0.014]</t>
+        </is>
+      </c>
+      <c r="D8" s="14" t="n">
         <v>-0.033</v>
       </c>
-      <c r="C8" s="14" t="inlineStr">
-        <is>
-          <t>[-0.063, -0.012]</t>
-        </is>
-      </c>
-      <c r="D8" s="14" t="n">
-        <v>-0.029</v>
-      </c>
       <c r="E8" s="14" t="inlineStr">
         <is>
-          <t>[-0.056, -0.010]</t>
+          <t>[-0.063, -0.013]</t>
         </is>
       </c>
       <c r="F8" s="14" t="n">
-        <v>0.016</v>
+        <v>0.012</v>
       </c>
       <c r="G8" s="14" t="inlineStr">
         <is>
-          <t>[0.005, 0.032]</t>
+          <t>[0.001, 0.024]</t>
         </is>
       </c>
     </row>
@@ -4174,27 +4174,27 @@
         </is>
       </c>
       <c r="B10" s="14" t="n">
+        <v>-0.032</v>
+      </c>
+      <c r="C10" s="14" t="inlineStr">
+        <is>
+          <t>[-0.067, 0.003]</t>
+        </is>
+      </c>
+      <c r="D10" s="14" t="n">
         <v>-0.03</v>
       </c>
-      <c r="C10" s="14" t="inlineStr">
+      <c r="E10" s="14" t="inlineStr">
         <is>
           <t>[-0.064, 0.004]</t>
         </is>
       </c>
-      <c r="D10" s="14" t="n">
-        <v>-0.026</v>
-      </c>
-      <c r="E10" s="14" t="inlineStr">
-        <is>
-          <t>[-0.058, 0.006]</t>
-        </is>
-      </c>
       <c r="F10" s="14" t="n">
-        <v>0.014</v>
+        <v>0.011</v>
       </c>
       <c r="G10" s="14" t="inlineStr">
         <is>
-          <t>[-0.012, 0.040]</t>
+          <t>[-0.014, 0.036]</t>
         </is>
       </c>
     </row>
@@ -4205,27 +4205,27 @@
         </is>
       </c>
       <c r="B11" s="14" t="n">
+        <v>-0.038</v>
+      </c>
+      <c r="C11" s="14" t="inlineStr">
+        <is>
+          <t>[-0.076, 0.000]</t>
+        </is>
+      </c>
+      <c r="D11" s="14" t="n">
         <v>-0.036</v>
       </c>
-      <c r="C11" s="14" t="inlineStr">
+      <c r="E11" s="14" t="inlineStr">
         <is>
           <t>[-0.073, 0.001]</t>
         </is>
       </c>
-      <c r="D11" s="14" t="n">
-        <v>-0.032</v>
-      </c>
-      <c r="E11" s="14" t="inlineStr">
-        <is>
-          <t>[-0.067, 0.003]</t>
-        </is>
-      </c>
       <c r="F11" s="14" t="n">
-        <v>0.018</v>
+        <v>0.013</v>
       </c>
       <c r="G11" s="14" t="inlineStr">
         <is>
-          <t>[-0.010, 0.046]</t>
+          <t>[-0.013, 0.039]</t>
         </is>
       </c>
     </row>
@@ -4244,19 +4244,19 @@
         </is>
       </c>
       <c r="D12" s="14" t="n">
-        <v>0.006</v>
+        <v>0.007</v>
       </c>
       <c r="E12" s="14" t="inlineStr">
         <is>
-          <t>[-0.018, 0.030]</t>
+          <t>[-0.017, 0.031]</t>
         </is>
       </c>
       <c r="F12" s="14" t="n">
-        <v>-0.004</v>
+        <v>-0.003</v>
       </c>
       <c r="G12" s="14" t="inlineStr">
         <is>
-          <t>[-0.028, 0.020]</t>
+          <t>[-0.027, 0.021]</t>
         </is>
       </c>
     </row>
@@ -4280,27 +4280,27 @@
         </is>
       </c>
       <c r="B14" s="14" t="n">
+        <v>-0.014</v>
+      </c>
+      <c r="C14" s="14" t="inlineStr">
+        <is>
+          <t>[-0.040, 0.012]</t>
+        </is>
+      </c>
+      <c r="D14" s="14" t="n">
         <v>-0.013</v>
       </c>
-      <c r="C14" s="14" t="inlineStr">
+      <c r="E14" s="14" t="inlineStr">
         <is>
           <t>[-0.039, 0.013]</t>
         </is>
       </c>
-      <c r="D14" s="14" t="n">
-        <v>-0.011</v>
-      </c>
-      <c r="E14" s="14" t="inlineStr">
-        <is>
-          <t>[-0.036, 0.014]</t>
-        </is>
-      </c>
       <c r="F14" s="14" t="n">
-        <v>0.006</v>
+        <v>0.005</v>
       </c>
       <c r="G14" s="14" t="inlineStr">
         <is>
-          <t>[-0.018, 0.030]</t>
+          <t>[-0.019, 0.029]</t>
         </is>
       </c>
     </row>
@@ -4311,27 +4311,27 @@
         </is>
       </c>
       <c r="B15" s="14" t="n">
-        <v>-0.053</v>
+        <v>-0.056</v>
       </c>
       <c r="C15" s="14" t="inlineStr">
         <is>
-          <t>[-0.099, -0.007]</t>
+          <t>[-0.103, -0.009]</t>
         </is>
       </c>
       <c r="D15" s="14" t="n">
-        <v>-0.046</v>
+        <v>-0.052</v>
       </c>
       <c r="E15" s="14" t="inlineStr">
         <is>
-          <t>[-0.088, -0.004]</t>
+          <t>[-0.097, -0.007]</t>
         </is>
       </c>
       <c r="F15" s="14" t="n">
-        <v>0.026</v>
+        <v>0.019</v>
       </c>
       <c r="G15" s="14" t="inlineStr">
         <is>
-          <t>[-0.006, 0.058]</t>
+          <t>[-0.010, 0.048]</t>
         </is>
       </c>
     </row>
@@ -4342,27 +4342,27 @@
         </is>
       </c>
       <c r="B16" s="14" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="C16" s="14" t="inlineStr">
+        <is>
+          <t>[0.002, 0.082]</t>
+        </is>
+      </c>
+      <c r="D16" s="14" t="n">
         <v>0.04</v>
       </c>
-      <c r="C16" s="14" t="inlineStr">
+      <c r="E16" s="14" t="inlineStr">
         <is>
           <t>[0.001, 0.079]</t>
         </is>
       </c>
-      <c r="D16" s="14" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="E16" s="14" t="inlineStr">
-        <is>
-          <t>[-0.002, 0.072]</t>
-        </is>
-      </c>
       <c r="F16" s="14" t="n">
-        <v>-0.02</v>
+        <v>-0.015</v>
       </c>
       <c r="G16" s="14" t="inlineStr">
         <is>
-          <t>[-0.049, 0.009]</t>
+          <t>[-0.042, 0.012]</t>
         </is>
       </c>
     </row>
@@ -4386,27 +4386,27 @@
         </is>
       </c>
       <c r="B18" s="16" t="n">
-        <v>0.062</v>
+        <v>0.066</v>
       </c>
       <c r="C18" s="16" t="inlineStr">
         <is>
-          <t>[0.034, 0.094]</t>
+          <t>[0.038, 0.099]</t>
         </is>
       </c>
       <c r="D18" s="16" t="n">
-        <v>0.054</v>
+        <v>0.063</v>
       </c>
       <c r="E18" s="16" t="inlineStr">
         <is>
-          <t>[0.028, 0.084]</t>
+          <t>[0.034, 0.093]</t>
         </is>
       </c>
       <c r="F18" s="16" t="n">
-        <v>-0.03</v>
+        <v>-0.023</v>
       </c>
       <c r="G18" s="16" t="inlineStr">
         <is>
-          <t>[-0.056, -0.011]</t>
+          <t>[-0.046, -0.005]</t>
         </is>
       </c>
     </row>
@@ -4430,27 +4430,27 @@
         </is>
       </c>
       <c r="B20" s="16" t="n">
-        <v>0.066</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="C20" s="16" t="inlineStr">
         <is>
-          <t>[0.014, 0.118]</t>
+          <t>[0.016, 0.124]</t>
         </is>
       </c>
       <c r="D20" s="16" t="n">
-        <v>0.058</v>
+        <v>0.068</v>
       </c>
       <c r="E20" s="16" t="inlineStr">
         <is>
-          <t>[0.010, 0.106]</t>
+          <t>[0.015, 0.121]</t>
         </is>
       </c>
       <c r="F20" s="16" t="n">
-        <v>-0.032</v>
+        <v>-0.025</v>
       </c>
       <c r="G20" s="16" t="inlineStr">
         <is>
-          <t>[-0.067, 0.003]</t>
+          <t>[-0.057, 0.007]</t>
         </is>
       </c>
     </row>
@@ -4461,27 +4461,27 @@
         </is>
       </c>
       <c r="B21" s="16" t="n">
+        <v>0.061</v>
+      </c>
+      <c r="C21" s="16" t="inlineStr">
+        <is>
+          <t>[0.012, 0.110]</t>
+        </is>
+      </c>
+      <c r="D21" s="16" t="n">
         <v>0.058</v>
       </c>
-      <c r="C21" s="16" t="inlineStr">
+      <c r="E21" s="16" t="inlineStr">
         <is>
           <t>[0.010, 0.106]</t>
         </is>
       </c>
-      <c r="D21" s="16" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="E21" s="16" t="inlineStr">
-        <is>
-          <t>[0.006, 0.094]</t>
-        </is>
-      </c>
       <c r="F21" s="16" t="n">
-        <v>-0.028</v>
+        <v>-0.021</v>
       </c>
       <c r="G21" s="16" t="inlineStr">
         <is>
-          <t>[-0.061, 0.005]</t>
+          <t>[-0.051, 0.009]</t>
         </is>
       </c>
     </row>
@@ -4500,19 +4500,19 @@
         </is>
       </c>
       <c r="D22" s="16" t="n">
-        <v>0.008</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="E22" s="16" t="inlineStr">
         <is>
-          <t>[-0.016, 0.032]</t>
+          <t>[-0.015, 0.033]</t>
         </is>
       </c>
       <c r="F22" s="16" t="n">
-        <v>-0.004</v>
+        <v>-0.003</v>
       </c>
       <c r="G22" s="16" t="inlineStr">
         <is>
-          <t>[-0.028, 0.020]</t>
+          <t>[-0.027, 0.021]</t>
         </is>
       </c>
     </row>
@@ -4523,27 +4523,27 @@
         </is>
       </c>
       <c r="B23" s="16" t="n">
+        <v>0.038</v>
+      </c>
+      <c r="C23" s="16" t="inlineStr">
+        <is>
+          <t>[-0.000, 0.076]</t>
+        </is>
+      </c>
+      <c r="D23" s="16" t="n">
         <v>0.036</v>
       </c>
-      <c r="C23" s="16" t="inlineStr">
+      <c r="E23" s="16" t="inlineStr">
         <is>
           <t>[-0.001, 0.073]</t>
         </is>
       </c>
-      <c r="D23" s="16" t="n">
-        <v>0.031</v>
-      </c>
-      <c r="E23" s="16" t="inlineStr">
-        <is>
-          <t>[-0.004, 0.066]</t>
-        </is>
-      </c>
       <c r="F23" s="16" t="n">
-        <v>-0.017</v>
+        <v>-0.013</v>
       </c>
       <c r="G23" s="16" t="inlineStr">
         <is>
-          <t>[-0.045, 0.011]</t>
+          <t>[-0.039, 0.013]</t>
         </is>
       </c>
     </row>
@@ -4554,27 +4554,27 @@
         </is>
       </c>
       <c r="B24" s="16" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.093</v>
       </c>
       <c r="C24" s="16" t="inlineStr">
         <is>
-          <t>[0.025, 0.151]</t>
+          <t>[0.028, 0.158]</t>
         </is>
       </c>
       <c r="D24" s="16" t="n">
-        <v>0.077</v>
+        <v>0.09</v>
       </c>
       <c r="E24" s="16" t="inlineStr">
         <is>
-          <t>[0.020, 0.134]</t>
+          <t>[0.026, 0.154]</t>
         </is>
       </c>
       <c r="F24" s="16" t="n">
-        <v>-0.043</v>
+        <v>-0.033</v>
       </c>
       <c r="G24" s="16" t="inlineStr">
         <is>
-          <t>[-0.084, -0.002]</t>
+          <t>[-0.069, 0.003]</t>
         </is>
       </c>
     </row>
@@ -4585,27 +4585,27 @@
         </is>
       </c>
       <c r="B25" s="16" t="n">
-        <v>-0.052</v>
+        <v>-0.055</v>
       </c>
       <c r="C25" s="16" t="inlineStr">
         <is>
-          <t>[-0.097, -0.007]</t>
+          <t>[-0.102, -0.008]</t>
         </is>
       </c>
       <c r="D25" s="16" t="n">
-        <v>-0.046</v>
+        <v>-0.054</v>
       </c>
       <c r="E25" s="16" t="inlineStr">
         <is>
-          <t>[-0.088, -0.004]</t>
+          <t>[-0.100, -0.008]</t>
         </is>
       </c>
       <c r="F25" s="16" t="n">
-        <v>0.026</v>
+        <v>0.02</v>
       </c>
       <c r="G25" s="16" t="inlineStr">
         <is>
-          <t>[-0.006, 0.058]</t>
+          <t>[-0.009, 0.049]</t>
         </is>
       </c>
     </row>
@@ -4642,27 +4642,27 @@
         </is>
       </c>
       <c r="B28" s="18" t="n">
-        <v>-0.062</v>
+        <v>-0.066</v>
       </c>
       <c r="C28" s="18" t="inlineStr">
         <is>
-          <t>[-0.098, -0.034]</t>
+          <t>[-0.103, -0.038]</t>
         </is>
       </c>
       <c r="D28" s="18" t="n">
-        <v>-0.049</v>
+        <v>-0.037</v>
       </c>
       <c r="E28" s="18" t="inlineStr">
         <is>
-          <t>[-0.082, -0.024]</t>
+          <t>[-0.069, -0.013]</t>
         </is>
       </c>
       <c r="F28" s="18" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.099</v>
       </c>
       <c r="G28" s="18" t="inlineStr">
         <is>
-          <t>[0.054, 0.124]</t>
+          <t>[0.063, 0.140]</t>
         </is>
       </c>
     </row>
@@ -4673,27 +4673,27 @@
         </is>
       </c>
       <c r="B29" s="18" t="n">
-        <v>-0.067</v>
+        <v>-0.07099999999999999</v>
       </c>
       <c r="C29" s="18" t="inlineStr">
         <is>
-          <t>[-0.119, -0.015]</t>
+          <t>[-0.125, -0.017]</t>
         </is>
       </c>
       <c r="D29" s="18" t="n">
-        <v>-0.053</v>
+        <v>-0.04</v>
       </c>
       <c r="E29" s="18" t="inlineStr">
         <is>
-          <t>[-0.099, -0.007]</t>
+          <t>[-0.079, -0.001]</t>
         </is>
       </c>
       <c r="F29" s="18" t="n">
-        <v>0.093</v>
+        <v>0.106</v>
       </c>
       <c r="G29" s="18" t="inlineStr">
         <is>
-          <t>[0.028, 0.158]</t>
+          <t>[0.034, 0.178]</t>
         </is>
       </c>
     </row>
@@ -4704,27 +4704,27 @@
         </is>
       </c>
       <c r="B30" s="18" t="n">
-        <v>-0.057</v>
+        <v>-0.06</v>
       </c>
       <c r="C30" s="18" t="inlineStr">
         <is>
-          <t>[-0.105, -0.009]</t>
+          <t>[-0.109, -0.011]</t>
         </is>
       </c>
       <c r="D30" s="18" t="n">
-        <v>-0.045</v>
+        <v>-0.034</v>
       </c>
       <c r="E30" s="18" t="inlineStr">
         <is>
-          <t>[-0.087, -0.003]</t>
+          <t>[-0.070, 0.002]</t>
         </is>
       </c>
       <c r="F30" s="18" t="n">
-        <v>0.081</v>
+        <v>0.092</v>
       </c>
       <c r="G30" s="18" t="inlineStr">
         <is>
-          <t>[0.022, 0.140]</t>
+          <t>[0.027, 0.157]</t>
         </is>
       </c>
     </row>
@@ -4735,27 +4735,27 @@
         </is>
       </c>
       <c r="B31" s="18" t="n">
-        <v>-0.01</v>
+        <v>-0.011</v>
       </c>
       <c r="C31" s="18" t="inlineStr">
         <is>
-          <t>[-0.035, 0.015]</t>
+          <t>[-0.036, 0.014]</t>
         </is>
       </c>
       <c r="D31" s="18" t="n">
-        <v>-0.008</v>
+        <v>-0.006</v>
       </c>
       <c r="E31" s="18" t="inlineStr">
         <is>
-          <t>[-0.032, 0.016]</t>
+          <t>[-0.030, 0.018]</t>
         </is>
       </c>
       <c r="F31" s="18" t="n">
-        <v>0.012</v>
+        <v>0.014</v>
       </c>
       <c r="G31" s="18" t="inlineStr">
         <is>
-          <t>[-0.013, 0.037]</t>
+          <t>[-0.012, 0.040]</t>
         </is>
       </c>
     </row>
@@ -4766,27 +4766,27 @@
         </is>
       </c>
       <c r="B32" s="18" t="n">
-        <v>-0.04</v>
+        <v>-0.042</v>
       </c>
       <c r="C32" s="18" t="inlineStr">
         <is>
-          <t>[-0.079, -0.001]</t>
+          <t>[-0.082, -0.002]</t>
         </is>
       </c>
       <c r="D32" s="18" t="n">
-        <v>-0.031</v>
+        <v>-0.023</v>
       </c>
       <c r="E32" s="18" t="inlineStr">
         <is>
-          <t>[-0.066, 0.004]</t>
+          <t>[-0.054, 0.008]</t>
         </is>
       </c>
       <c r="F32" s="18" t="n">
-        <v>0.055</v>
+        <v>0.063</v>
       </c>
       <c r="G32" s="18" t="inlineStr">
         <is>
-          <t>[0.008, 0.102]</t>
+          <t>[0.013, 0.113]</t>
         </is>
       </c>
     </row>
@@ -4797,27 +4797,27 @@
         </is>
       </c>
       <c r="B33" s="18" t="n">
-        <v>-0.08400000000000001</v>
+        <v>-0.089</v>
       </c>
       <c r="C33" s="18" t="inlineStr">
         <is>
-          <t>[-0.145, -0.023]</t>
+          <t>[-0.152, -0.026]</t>
         </is>
       </c>
       <c r="D33" s="18" t="n">
-        <v>-0.067</v>
+        <v>-0.051</v>
       </c>
       <c r="E33" s="18" t="inlineStr">
         <is>
-          <t>[-0.119, -0.015]</t>
+          <t>[-0.096, -0.006]</t>
         </is>
       </c>
       <c r="F33" s="18" t="n">
-        <v>0.118</v>
+        <v>0.134</v>
       </c>
       <c r="G33" s="18" t="inlineStr">
         <is>
-          <t>[0.041, 0.195]</t>
+          <t>[0.049, 0.219]</t>
         </is>
       </c>
     </row>
@@ -4828,27 +4828,27 @@
         </is>
       </c>
       <c r="B34" s="18" t="n">
-        <v>0.044</v>
+        <v>0.047</v>
       </c>
       <c r="C34" s="18" t="inlineStr">
         <is>
-          <t>[0.003, 0.085]</t>
+          <t>[0.004, 0.090]</t>
         </is>
       </c>
       <c r="D34" s="18" t="n">
-        <v>0.036</v>
+        <v>0.027</v>
       </c>
       <c r="E34" s="18" t="inlineStr">
         <is>
-          <t>[-0.001, 0.073]</t>
+          <t>[-0.006, 0.060]</t>
         </is>
       </c>
       <c r="F34" s="18" t="n">
-        <v>-0.063</v>
+        <v>-0.07199999999999999</v>
       </c>
       <c r="G34" s="18" t="inlineStr">
         <is>
-          <t>[-0.113, -0.013]</t>
+          <t>[-0.127, -0.017]</t>
         </is>
       </c>
     </row>
@@ -4872,27 +4872,27 @@
         </is>
       </c>
       <c r="B36" s="20" t="n">
-        <v>0.029</v>
+        <v>0.031</v>
       </c>
       <c r="C36" s="20" t="inlineStr">
         <is>
-          <t>[0.011, 0.052]</t>
+          <t>[0.012, 0.055]</t>
         </is>
       </c>
       <c r="D36" s="20" t="n">
-        <v>0.023</v>
+        <v>0.017</v>
       </c>
       <c r="E36" s="20" t="inlineStr">
         <is>
-          <t>[0.008, 0.044]</t>
+          <t>[0.005, 0.034]</t>
         </is>
       </c>
       <c r="F36" s="20" t="n">
-        <v>-0.04</v>
+        <v>-0.046</v>
       </c>
       <c r="G36" s="20" t="inlineStr">
         <is>
-          <t>[-0.072, -0.015]</t>
+          <t>[-0.078, -0.018]</t>
         </is>
       </c>
     </row>
@@ -4903,27 +4903,27 @@
         </is>
       </c>
       <c r="B37" s="20" t="n">
-        <v>0.026</v>
+        <v>0.028</v>
       </c>
       <c r="C37" s="20" t="inlineStr">
         <is>
-          <t>[-0.006, 0.058]</t>
+          <t>[-0.005, 0.061]</t>
         </is>
       </c>
       <c r="D37" s="20" t="n">
-        <v>0.02</v>
+        <v>0.015</v>
       </c>
       <c r="E37" s="20" t="inlineStr">
         <is>
-          <t>[-0.009, 0.049]</t>
+          <t>[-0.012, 0.042]</t>
         </is>
       </c>
       <c r="F37" s="20" t="n">
-        <v>-0.036</v>
+        <v>-0.041</v>
       </c>
       <c r="G37" s="20" t="inlineStr">
         <is>
-          <t>[-0.073, 0.001]</t>
+          <t>[-0.081, -0.001]</t>
         </is>
       </c>
     </row>
@@ -4934,27 +4934,27 @@
         </is>
       </c>
       <c r="B38" s="20" t="n">
-        <v>0.032</v>
+        <v>0.034</v>
       </c>
       <c r="C38" s="20" t="inlineStr">
         <is>
-          <t>[-0.003, 0.067]</t>
+          <t>[-0.002, 0.070]</t>
         </is>
       </c>
       <c r="D38" s="20" t="n">
-        <v>0.026</v>
+        <v>0.019</v>
       </c>
       <c r="E38" s="20" t="inlineStr">
         <is>
-          <t>[-0.006, 0.058]</t>
+          <t>[-0.010, 0.048]</t>
         </is>
       </c>
       <c r="F38" s="20" t="n">
-        <v>-0.044</v>
+        <v>-0.051</v>
       </c>
       <c r="G38" s="20" t="inlineStr">
         <is>
-          <t>[-0.085, -0.003]</t>
+          <t>[-0.096, -0.006]</t>
         </is>
       </c>
     </row>
@@ -4973,19 +4973,19 @@
         </is>
       </c>
       <c r="D39" s="20" t="n">
-        <v>-0.006</v>
+        <v>-0.004</v>
       </c>
       <c r="E39" s="20" t="inlineStr">
         <is>
-          <t>[-0.030, 0.018]</t>
+          <t>[-0.028, 0.020]</t>
         </is>
       </c>
       <c r="F39" s="20" t="n">
-        <v>0.008</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="G39" s="20" t="inlineStr">
         <is>
-          <t>[-0.016, 0.032]</t>
+          <t>[-0.015, 0.033]</t>
         </is>
       </c>
     </row>
@@ -4996,27 +4996,27 @@
         </is>
       </c>
       <c r="B40" s="20" t="n">
-        <v>0.046</v>
+        <v>0.049</v>
       </c>
       <c r="C40" s="20" t="inlineStr">
         <is>
-          <t>[0.004, 0.088]</t>
+          <t>[0.005, 0.093]</t>
         </is>
       </c>
       <c r="D40" s="20" t="n">
-        <v>0.037</v>
+        <v>0.027</v>
       </c>
       <c r="E40" s="20" t="inlineStr">
         <is>
-          <t>[-0.001, 0.075]</t>
+          <t>[-0.006, 0.060]</t>
         </is>
       </c>
       <c r="F40" s="20" t="n">
-        <v>-0.063</v>
+        <v>-0.07199999999999999</v>
       </c>
       <c r="G40" s="20" t="inlineStr">
         <is>
-          <t>[-0.113, -0.013]</t>
+          <t>[-0.127, -0.017]</t>
         </is>
       </c>
     </row>
@@ -5027,27 +5027,27 @@
         </is>
       </c>
       <c r="B41" s="20" t="n">
-        <v>0.012</v>
+        <v>0.013</v>
       </c>
       <c r="C41" s="20" t="inlineStr">
         <is>
-          <t>[-0.013, 0.037]</t>
+          <t>[-0.013, 0.039]</t>
         </is>
       </c>
       <c r="D41" s="20" t="n">
-        <v>0.01</v>
+        <v>0.007</v>
       </c>
       <c r="E41" s="20" t="inlineStr">
         <is>
-          <t>[-0.015, 0.035]</t>
+          <t>[-0.017, 0.031]</t>
         </is>
       </c>
       <c r="F41" s="20" t="n">
-        <v>-0.018</v>
+        <v>-0.021</v>
       </c>
       <c r="G41" s="20" t="inlineStr">
         <is>
-          <t>[-0.046, 0.010]</t>
+          <t>[-0.051, 0.009]</t>
         </is>
       </c>
     </row>
@@ -5058,27 +5058,27 @@
         </is>
       </c>
       <c r="B42" s="20" t="n">
-        <v>0.034</v>
+        <v>0.036</v>
       </c>
       <c r="C42" s="20" t="inlineStr">
         <is>
-          <t>[-0.002, 0.070]</t>
+          <t>[-0.001, 0.073]</t>
         </is>
       </c>
       <c r="D42" s="20" t="n">
-        <v>0.027</v>
+        <v>0.02</v>
       </c>
       <c r="E42" s="20" t="inlineStr">
         <is>
-          <t>[-0.006, 0.060]</t>
+          <t>[-0.009, 0.049]</t>
         </is>
       </c>
       <c r="F42" s="20" t="n">
-        <v>-0.045</v>
+        <v>-0.052</v>
       </c>
       <c r="G42" s="20" t="inlineStr">
         <is>
-          <t>[-0.087, -0.003]</t>
+          <t>[-0.097, -0.007]</t>
         </is>
       </c>
     </row>
@@ -5306,49 +5306,49 @@
         </is>
       </c>
       <c r="D5" s="4" t="n">
-        <v>-0.012</v>
+        <v>-0.013</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>0.04</v>
+        <v>0.038</v>
       </c>
       <c r="F5" s="4" t="n">
         <v>0.764</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>-0.091</v>
+        <v>-0.092</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>0.067</v>
+        <v>0.068</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>-0.154</v>
+        <v>-0.16</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>0.062</v>
+        <v>0.06</v>
       </c>
       <c r="K5" s="4" t="n">
         <v>0.013</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>-0.276</v>
+        <v>-0.283</v>
       </c>
       <c r="M5" s="4" t="n">
-        <v>-0.032</v>
+        <v>-0.031</v>
       </c>
       <c r="N5" s="4" t="n">
-        <v>-0.13</v>
+        <v>-0.135</v>
       </c>
       <c r="O5" s="4" t="n">
-        <v>0.064</v>
+        <v>0.066</v>
       </c>
       <c r="P5" s="4" t="n">
         <v>0.042</v>
       </c>
       <c r="Q5" s="4" t="n">
-        <v>-0.255</v>
+        <v>-0.251</v>
       </c>
       <c r="R5" s="4" t="n">
-        <v>-0.005</v>
+        <v>-0.006</v>
       </c>
       <c r="S5" s="4" t="n">
         <v>-0.024</v>
@@ -5360,10 +5360,10 @@
         <v>0.764</v>
       </c>
       <c r="V5" s="4" t="n">
-        <v>-0.181</v>
+        <v>-0.183</v>
       </c>
       <c r="W5" s="4" t="n">
-        <v>0.133</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1" s="37">
@@ -5383,64 +5383,64 @@
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.018</v>
+        <v>0.017</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.039</v>
+        <v>0.037</v>
       </c>
       <c r="F6" s="4" t="n">
         <v>0.645</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.058</v>
+        <v>-0.055</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.094</v>
+        <v>0.093</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.285</v>
+        <v>0.276</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.059</v>
+        <v>0.058</v>
       </c>
       <c r="K6" s="4" t="n">
         <v>0</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.169</v>
+        <v>0.167</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.401</v>
+        <v>0.419</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.249</v>
+        <v>0.242</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.06</v>
+        <v>0.058</v>
       </c>
       <c r="P6" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>0.131</v>
+        <v>0.132</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>0.367</v>
+        <v>0.369</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>0.036</v>
+        <v>0.038</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>0.078</v>
+        <v>0.081</v>
       </c>
       <c r="U6" s="4" t="n">
         <v>0.645</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>-0.117</v>
+        <v>-0.119</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>0.189</v>
+        <v>0.183</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" s="37">
@@ -5460,64 +5460,64 @@
         </is>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.078</v>
+        <v>0.048</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.038</v>
+        <v>0.043</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.041</v>
+        <v>0.263</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.003</v>
+        <v>-0.036</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.153</v>
+        <v>0.129</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-0.064</v>
+        <v>-0.038</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>0.062</v>
+        <v>0.064</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.301</v>
+        <v>0.535</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-0.186</v>
+        <v>-0.167</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0.058</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-0.22</v>
+        <v>-0.152</v>
       </c>
       <c r="O7" s="4" t="n">
         <v>0.065</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.001</v>
+        <v>0.02</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>-0.347</v>
+        <v>-0.284</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>-0.093</v>
+        <v>-0.025</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>0.156</v>
+        <v>0.112</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>0.076</v>
+        <v>0.081</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>0.041</v>
+        <v>0.155</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>0.007</v>
+        <v>-0.044</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>0.305</v>
+        <v>0.274</v>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1" s="37">
@@ -5537,37 +5537,37 @@
         </is>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.098</v>
+        <v>-0.097</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.039</v>
+        <v>0.04</v>
       </c>
       <c r="F8" s="4" t="n">
         <v>0.012</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.174</v>
+        <v>-0.166</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.022</v>
+        <v>-0.021</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0.169</v>
+        <v>0.177</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>0.059</v>
+        <v>0.061</v>
       </c>
       <c r="K8" s="4" t="n">
         <v>0.004</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.053</v>
+        <v>0.052</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.285</v>
+        <v>0.276</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.365</v>
+        <v>0.37</v>
       </c>
       <c r="O8" s="4" t="n">
         <v>0.062</v>
@@ -5576,25 +5576,25 @@
         <v>0</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>0.243</v>
+        <v>0.247</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>0.487</v>
+        <v>0.467</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>-0.196</v>
+        <v>-0.202</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>0.078</v>
+        <v>0.081</v>
       </c>
       <c r="U8" s="4" t="n">
         <v>0.012</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>-0.349</v>
+        <v>-0.345</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>-0.043</v>
+        <v>-0.042</v>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" s="37">
@@ -5614,7 +5614,7 @@
         </is>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.024</v>
+        <v>0.023</v>
       </c>
       <c r="E9" s="4" t="n">
         <v>0.043</v>
@@ -5623,55 +5623,55 @@
         <v>0.577</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.06</v>
+        <v>-0.058</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.108</v>
+        <v>0.11</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.336</v>
+        <v>0.353</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.067</v>
       </c>
       <c r="K9" s="4" t="n">
         <v>0</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.201</v>
+        <v>0.2</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.471</v>
+        <v>0.485</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>0.288</v>
+        <v>0.286</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.073</v>
       </c>
       <c r="P9" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>0.149</v>
+        <v>0.15</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>0.427</v>
+        <v>0.411</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>0.048</v>
+        <v>0.046</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.09</v>
       </c>
       <c r="U9" s="4" t="n">
         <v>0.577</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>-0.121</v>
+        <v>-0.126</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>0.217</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" s="37">
@@ -5694,13 +5694,13 @@
         <v>-0.019</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.041</v>
+        <v>0.042</v>
       </c>
       <c r="F10" s="4" t="n">
         <v>0.643</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.099</v>
+        <v>-0.095</v>
       </c>
       <c r="H10" s="4" t="n">
         <v>0.061</v>
@@ -5709,46 +5709,46 @@
         <v>-0.164</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.06</v>
+        <v>0.062</v>
       </c>
       <c r="K10" s="4" t="n">
         <v>0.006</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-0.282</v>
+        <v>-0.288</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-0.046</v>
+        <v>-0.047</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-0.126</v>
+        <v>-0.125</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>0.063</v>
+        <v>0.064</v>
       </c>
       <c r="P10" s="4" t="n">
         <v>0.045</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>-0.249</v>
+        <v>-0.261</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>-0.003</v>
+        <v>-0.004</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>-0.038</v>
+        <v>-0.039</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>0.082</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="U10" s="4" t="n">
         <v>0.643</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>-0.199</v>
+        <v>-0.195</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>0.123</v>
+        <v>0.129</v>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" s="37">
@@ -5768,64 +5768,64 @@
         </is>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.111</v>
+        <v>-0.108</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.041</v>
+        <v>0.04</v>
       </c>
       <c r="F11" s="4" t="n">
         <v>0.007</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.191</v>
+        <v>-0.186</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.031</v>
+        <v>-0.029</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.201</v>
+        <v>0.198</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.066</v>
+        <v>0.063</v>
       </c>
       <c r="K11" s="4" t="n">
         <v>0.002</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.33</v>
+        <v>0.323</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.423</v>
+        <v>0.409</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.066</v>
       </c>
       <c r="P11" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>0.288</v>
+        <v>0.277</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>0.5580000000000001</v>
+        <v>0.578</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>-0.222</v>
+        <v>-0.232</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>0.082</v>
+        <v>0.083</v>
       </c>
       <c r="U11" s="4" t="n">
         <v>0.007</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>-0.383</v>
+        <v>-0.394</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>-0.061</v>
+        <v>-0.063</v>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1" s="37">
@@ -5845,22 +5845,22 @@
         </is>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.067</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.038</v>
+        <v>0.037</v>
       </c>
       <c r="F12" s="4" t="n">
         <v>0.078</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.008</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.142</v>
+        <v>0.141</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-0.078</v>
+        <v>-0.076</v>
       </c>
       <c r="J12" s="4" t="n">
         <v>0.06</v>
@@ -5869,40 +5869,40 @@
         <v>0.193</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-0.196</v>
+        <v>-0.189</v>
       </c>
       <c r="M12" s="4" t="n">
         <v>0.04</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-0.212</v>
+        <v>-0.211</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0.062</v>
+        <v>0.063</v>
       </c>
       <c r="P12" s="4" t="n">
         <v>0.001</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>-0.334</v>
+        <v>-0.335</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>-0.09</v>
+        <v>-0.08799999999999999</v>
       </c>
       <c r="S12" s="4" t="n">
         <v>0.134</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>0.076</v>
+        <v>0.073</v>
       </c>
       <c r="U12" s="4" t="n">
         <v>0.078</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>-0.015</v>
+        <v>-0.016</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>0.283</v>
+        <v>0.291</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="37">

--- a/results/Model3.xlsx
+++ b/results/Model3.xlsx
@@ -1642,28 +1642,28 @@
         </is>
       </c>
       <c r="B4" s="35" t="n">
-        <v>1815.9</v>
+        <v>1771.6</v>
       </c>
       <c r="C4" s="35" t="n">
         <v>852</v>
       </c>
       <c r="D4" s="35" t="n">
-        <v>0.948</v>
+        <v>0.953</v>
       </c>
       <c r="E4" s="35" t="n">
-        <v>0.9389999999999999</v>
+        <v>0.945</v>
       </c>
       <c r="F4" s="35" t="n">
-        <v>0.044</v>
+        <v>0.043</v>
       </c>
       <c r="G4" s="35" t="n">
-        <v>0.04</v>
+        <v>0.039</v>
       </c>
       <c r="H4" s="35" t="n">
-        <v>0.005</v>
+        <v>0.01</v>
       </c>
       <c r="I4" s="35" t="n">
-        <v>-0.001</v>
+        <v>-0.002</v>
       </c>
       <c r="J4" s="36" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
       <c r="I5" s="35" t="n"/>
       <c r="J5" s="35" t="inlineStr">
         <is>
-          <t>Method factor explains 9.4%</t>
+          <t>Method factor explains 11.6%</t>
         </is>
       </c>
       <c r="K5" s="35" t="n"/>
@@ -2108,10 +2108,10 @@
         </is>
       </c>
       <c r="B4" s="24" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.551</v>
       </c>
       <c r="C4" s="24" t="n">
-        <v>0.497</v>
+        <v>0.498</v>
       </c>
       <c r="D4" s="24" t="inlineStr">
         <is>
@@ -2139,13 +2139,13 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>30.699</v>
+        <v>30.654</v>
       </c>
       <c r="C5" s="24" t="n">
-        <v>4.675</v>
+        <v>4.636</v>
       </c>
       <c r="D5" s="24" t="n">
-        <v>0.022</v>
+        <v>0.041</v>
       </c>
       <c r="E5" s="24" t="inlineStr">
         <is>
@@ -2172,16 +2172,16 @@
         </is>
       </c>
       <c r="B6" s="24" t="n">
-        <v>2.297</v>
+        <v>2.307</v>
       </c>
       <c r="C6" s="24" t="n">
-        <v>1.468</v>
+        <v>1.49</v>
       </c>
       <c r="D6" s="24" t="n">
-        <v>-0.025</v>
+        <v>-0.004</v>
       </c>
       <c r="E6" s="24" t="n">
-        <v>0.203</v>
+        <v>0.191</v>
       </c>
       <c r="F6" s="24" t="inlineStr">
         <is>
@@ -2207,19 +2207,19 @@
         </is>
       </c>
       <c r="B7" s="24" t="n">
-        <v>3.249</v>
+        <v>3.302</v>
       </c>
       <c r="C7" s="24" t="n">
-        <v>1.06</v>
+        <v>1.078</v>
       </c>
       <c r="D7" s="24" t="n">
-        <v>0.096</v>
+        <v>0.103</v>
       </c>
       <c r="E7" s="24" t="n">
-        <v>-0.014</v>
+        <v>-0.034</v>
       </c>
       <c r="F7" s="24" t="n">
-        <v>-0.049</v>
+        <v>-0.061</v>
       </c>
       <c r="G7" s="24" t="inlineStr">
         <is>
@@ -2244,22 +2244,22 @@
         </is>
       </c>
       <c r="B8" s="24" t="n">
-        <v>4.04</v>
+        <v>4.055</v>
       </c>
       <c r="C8" s="24" t="n">
-        <v>0.901</v>
+        <v>0.87</v>
       </c>
       <c r="D8" s="24" t="n">
-        <v>-0.058</v>
+        <v>-0.002</v>
       </c>
       <c r="E8" s="24" t="n">
-        <v>-0.008</v>
+        <v>-0.012</v>
       </c>
       <c r="F8" s="24" t="n">
-        <v>0.082</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="G8" s="24" t="n">
-        <v>-0.016</v>
+        <v>0.023</v>
       </c>
       <c r="H8" s="23" t="inlineStr">
         <is>
@@ -2283,25 +2283,25 @@
         </is>
       </c>
       <c r="B9" s="24" t="n">
-        <v>4.999</v>
+        <v>4.998</v>
       </c>
       <c r="C9" s="24" t="n">
-        <v>0.997</v>
+        <v>1.001</v>
       </c>
       <c r="D9" s="24" t="n">
-        <v>-0</v>
+        <v>-0.055</v>
       </c>
       <c r="E9" s="24" t="n">
-        <v>-0.027</v>
+        <v>0.011</v>
       </c>
       <c r="F9" s="24" t="n">
-        <v>0.028</v>
+        <v>0.022</v>
       </c>
       <c r="G9" s="24" t="n">
-        <v>-0.119</v>
+        <v>-0.147</v>
       </c>
       <c r="H9" s="24" t="n">
-        <v>-0.354</v>
+        <v>-0.351</v>
       </c>
       <c r="I9" s="24" t="inlineStr">
         <is>
@@ -2324,28 +2324,28 @@
         </is>
       </c>
       <c r="B10" s="24" t="n">
-        <v>3.463</v>
+        <v>3.445</v>
       </c>
       <c r="C10" s="24" t="n">
-        <v>0.921</v>
+        <v>0.905</v>
       </c>
       <c r="D10" s="24" t="n">
-        <v>-0.062</v>
+        <v>-0.055</v>
       </c>
       <c r="E10" s="24" t="n">
-        <v>-0</v>
+        <v>-0.041</v>
       </c>
       <c r="F10" s="24" t="n">
-        <v>0.076</v>
+        <v>0.057</v>
       </c>
       <c r="G10" s="24" t="n">
-        <v>-0.06</v>
+        <v>-0.066</v>
       </c>
       <c r="H10" s="24" t="n">
-        <v>0.021</v>
+        <v>-0.026</v>
       </c>
       <c r="I10" s="24" t="n">
-        <v>-0.004</v>
+        <v>0.044</v>
       </c>
       <c r="J10" s="24" t="inlineStr">
         <is>
@@ -2367,31 +2367,31 @@
         </is>
       </c>
       <c r="B11" s="24" t="n">
-        <v>4.597</v>
+        <v>4.556</v>
       </c>
       <c r="C11" s="24" t="n">
-        <v>0.887</v>
+        <v>0.878</v>
       </c>
       <c r="D11" s="24" t="n">
-        <v>-0.07199999999999999</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E11" s="24" t="n">
-        <v>-0.091</v>
+        <v>-0.092</v>
       </c>
       <c r="F11" s="24" t="n">
-        <v>-0.046</v>
+        <v>-0.092</v>
       </c>
       <c r="G11" s="24" t="n">
-        <v>-0.049</v>
+        <v>-0.044</v>
       </c>
       <c r="H11" s="24" t="n">
-        <v>-0.031</v>
+        <v>-0.08</v>
       </c>
       <c r="I11" s="24" t="n">
-        <v>-0.039</v>
+        <v>0.027</v>
       </c>
       <c r="J11" s="24" t="n">
-        <v>0.02</v>
+        <v>-0.003</v>
       </c>
       <c r="K11" s="24" t="inlineStr">
         <is>
@@ -2412,34 +2412,34 @@
         </is>
       </c>
       <c r="B12" s="24" t="n">
-        <v>4.533</v>
+        <v>4.546</v>
       </c>
       <c r="C12" s="24" t="n">
-        <v>1.266</v>
+        <v>1.248</v>
       </c>
       <c r="D12" s="24" t="n">
-        <v>0.03</v>
+        <v>-0.026</v>
       </c>
       <c r="E12" s="24" t="n">
-        <v>-0.038</v>
+        <v>-0.018</v>
       </c>
       <c r="F12" s="24" t="n">
-        <v>-0.016</v>
+        <v>-0.006</v>
       </c>
       <c r="G12" s="24" t="n">
-        <v>-0.059</v>
+        <v>-0.08</v>
       </c>
       <c r="H12" s="24" t="n">
-        <v>-0.5679999999999999</v>
+        <v>-0.537</v>
       </c>
       <c r="I12" s="24" t="n">
-        <v>0.569</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="J12" s="24" t="n">
-        <v>-0.059</v>
+        <v>-0.017</v>
       </c>
       <c r="K12" s="24" t="n">
-        <v>-0.081</v>
+        <v>-0.036</v>
       </c>
       <c r="L12" s="24" t="inlineStr">
         <is>
@@ -2459,37 +2459,37 @@
         </is>
       </c>
       <c r="B13" s="24" t="n">
-        <v>2.971</v>
+        <v>2.961</v>
       </c>
       <c r="C13" s="24" t="n">
-        <v>1.201</v>
+        <v>1.182</v>
       </c>
       <c r="D13" s="24" t="n">
-        <v>-0.011</v>
+        <v>0.032</v>
       </c>
       <c r="E13" s="24" t="n">
-        <v>0.05</v>
+        <v>0.036</v>
       </c>
       <c r="F13" s="24" t="n">
-        <v>0</v>
+        <v>0.008</v>
       </c>
       <c r="G13" s="24" t="n">
-        <v>0.047</v>
+        <v>0.074</v>
       </c>
       <c r="H13" s="24" t="n">
-        <v>0.539</v>
+        <v>0.552</v>
       </c>
       <c r="I13" s="24" t="n">
-        <v>-0.52</v>
+        <v>-0.525</v>
       </c>
       <c r="J13" s="24" t="n">
-        <v>0.039</v>
+        <v>-0.008</v>
       </c>
       <c r="K13" s="24" t="n">
-        <v>-0.026</v>
+        <v>-0.08</v>
       </c>
       <c r="L13" s="24" t="n">
-        <v>-0.456</v>
+        <v>-0.454</v>
       </c>
       <c r="M13" s="24" t="inlineStr">
         <is>
@@ -2508,40 +2508,40 @@
         </is>
       </c>
       <c r="B14" s="24" t="n">
-        <v>4.42</v>
+        <v>4.402</v>
       </c>
       <c r="C14" s="24" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.639</v>
       </c>
       <c r="D14" s="24" t="n">
-        <v>-0.005</v>
+        <v>-0.026</v>
       </c>
       <c r="E14" s="24" t="n">
+        <v>-0.013</v>
+      </c>
+      <c r="F14" s="24" t="n">
+        <v>-0.052</v>
+      </c>
+      <c r="G14" s="24" t="n">
+        <v>-0.008</v>
+      </c>
+      <c r="H14" s="24" t="n">
         <v>-0.025</v>
       </c>
-      <c r="F14" s="24" t="n">
-        <v>-0.013</v>
-      </c>
-      <c r="G14" s="24" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="H14" s="24" t="n">
-        <v>-0.022</v>
-      </c>
       <c r="I14" s="24" t="n">
-        <v>-0.024</v>
+        <v>0.005</v>
       </c>
       <c r="J14" s="24" t="n">
-        <v>-0.13</v>
+        <v>-0.125</v>
       </c>
       <c r="K14" s="24" t="n">
-        <v>0.034</v>
+        <v>-0.045</v>
       </c>
       <c r="L14" s="24" t="n">
-        <v>-0.005</v>
+        <v>0.041</v>
       </c>
       <c r="M14" s="24" t="n">
-        <v>-0.065</v>
+        <v>-0.068</v>
       </c>
       <c r="N14" s="24" t="inlineStr">
         <is>
@@ -2559,43 +2559,43 @@
         </is>
       </c>
       <c r="B15" s="24" t="n">
-        <v>4.524</v>
+        <v>4.518</v>
       </c>
       <c r="C15" s="24" t="n">
-        <v>0.829</v>
+        <v>0.828</v>
       </c>
       <c r="D15" s="24" t="n">
-        <v>0.033</v>
+        <v>-0.06</v>
       </c>
       <c r="E15" s="24" t="n">
-        <v>-0.08599999999999999</v>
+        <v>-0.029</v>
       </c>
       <c r="F15" s="24" t="n">
-        <v>0.03</v>
+        <v>-0.042</v>
       </c>
       <c r="G15" s="24" t="n">
-        <v>-0.06</v>
+        <v>-0.108</v>
       </c>
       <c r="H15" s="24" t="n">
-        <v>-0.456</v>
+        <v>-0.419</v>
       </c>
       <c r="I15" s="24" t="n">
-        <v>0.426</v>
+        <v>0.451</v>
       </c>
       <c r="J15" s="24" t="n">
-        <v>-0.094</v>
+        <v>-0.025</v>
       </c>
       <c r="K15" s="24" t="n">
-        <v>0.028</v>
+        <v>0.013</v>
       </c>
       <c r="L15" s="24" t="n">
-        <v>0.576</v>
+        <v>0.602</v>
       </c>
       <c r="M15" s="24" t="n">
-        <v>-0.615</v>
+        <v>-0.663</v>
       </c>
       <c r="N15" s="24" t="n">
-        <v>0.433</v>
+        <v>0.394</v>
       </c>
       <c r="O15" s="24" t="inlineStr">
         <is>
@@ -2612,46 +2612,46 @@
         </is>
       </c>
       <c r="B16" s="24" t="n">
-        <v>5.073</v>
+        <v>5.048</v>
       </c>
       <c r="C16" s="24" t="n">
-        <v>1.066</v>
+        <v>1.135</v>
       </c>
       <c r="D16" s="24" t="n">
-        <v>-0.055</v>
+        <v>0.003</v>
       </c>
       <c r="E16" s="24" t="n">
-        <v>-0.03</v>
+        <v>-0.012</v>
       </c>
       <c r="F16" s="24" t="n">
-        <v>0.031</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="G16" s="24" t="n">
-        <v>-0.041</v>
+        <v>-0.095</v>
       </c>
       <c r="H16" s="24" t="n">
-        <v>-0.366</v>
+        <v>-0.327</v>
       </c>
       <c r="I16" s="24" t="n">
-        <v>0.322</v>
+        <v>0.415</v>
       </c>
       <c r="J16" s="24" t="n">
-        <v>0.027</v>
+        <v>-0.013</v>
       </c>
       <c r="K16" s="24" t="n">
-        <v>-0.023</v>
+        <v>0.044</v>
       </c>
       <c r="L16" s="24" t="n">
-        <v>0.488</v>
+        <v>0.499</v>
       </c>
       <c r="M16" s="24" t="n">
-        <v>-0.542</v>
+        <v>-0.53</v>
       </c>
       <c r="N16" s="24" t="n">
-        <v>-0.048</v>
+        <v>0.045</v>
       </c>
       <c r="O16" s="24" t="n">
-        <v>0.426</v>
+        <v>0.434</v>
       </c>
       <c r="P16" s="24" t="inlineStr">
         <is>
@@ -2667,49 +2667,49 @@
         </is>
       </c>
       <c r="B17" s="24" t="n">
-        <v>2.582</v>
+        <v>2.586</v>
       </c>
       <c r="C17" s="24" t="n">
-        <v>1.08</v>
+        <v>1.144</v>
       </c>
       <c r="D17" s="24" t="n">
-        <v>0.024</v>
+        <v>-0.02</v>
       </c>
       <c r="E17" s="24" t="n">
-        <v>-0.029</v>
+        <v>-0.066</v>
       </c>
       <c r="F17" s="24" t="n">
-        <v>-0.008999999999999999</v>
+        <v>-0.02</v>
       </c>
       <c r="G17" s="24" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.076</v>
       </c>
       <c r="H17" s="24" t="n">
-        <v>0.444</v>
+        <v>0.379</v>
       </c>
       <c r="I17" s="24" t="n">
-        <v>-0.382</v>
+        <v>-0.349</v>
       </c>
       <c r="J17" s="24" t="n">
-        <v>-0.027</v>
+        <v>-0.136</v>
       </c>
       <c r="K17" s="24" t="n">
-        <v>0.1</v>
+        <v>0.089</v>
       </c>
       <c r="L17" s="24" t="n">
-        <v>-0.495</v>
+        <v>-0.496</v>
       </c>
       <c r="M17" s="24" t="n">
-        <v>0.569</v>
+        <v>0.527</v>
       </c>
       <c r="N17" s="24" t="n">
-        <v>-0.008999999999999999</v>
+        <v>-0.016</v>
       </c>
       <c r="O17" s="24" t="n">
-        <v>-0.427</v>
+        <v>-0.484</v>
       </c>
       <c r="P17" s="24" t="n">
-        <v>-0.433</v>
+        <v>-0.409</v>
       </c>
       <c r="Q17" s="24" t="inlineStr">
         <is>

--- a/results/Model3.xlsx
+++ b/results/Model3.xlsx
@@ -2139,13 +2139,13 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>30.654</v>
+        <v>30.834</v>
       </c>
       <c r="C5" s="24" t="n">
-        <v>4.636</v>
+        <v>4.634</v>
       </c>
       <c r="D5" s="24" t="n">
-        <v>0.041</v>
+        <v>0.027</v>
       </c>
       <c r="E5" s="24" t="inlineStr">
         <is>
@@ -2172,16 +2172,16 @@
         </is>
       </c>
       <c r="B6" s="24" t="n">
-        <v>2.307</v>
+        <v>2.331</v>
       </c>
       <c r="C6" s="24" t="n">
-        <v>1.49</v>
+        <v>1.474</v>
       </c>
       <c r="D6" s="24" t="n">
-        <v>-0.004</v>
+        <v>-0.013</v>
       </c>
       <c r="E6" s="24" t="n">
-        <v>0.191</v>
+        <v>0.187</v>
       </c>
       <c r="F6" s="24" t="inlineStr">
         <is>
@@ -2207,19 +2207,19 @@
         </is>
       </c>
       <c r="B7" s="24" t="n">
-        <v>3.302</v>
+        <v>3.271</v>
       </c>
       <c r="C7" s="24" t="n">
-        <v>1.078</v>
+        <v>1.061</v>
       </c>
       <c r="D7" s="24" t="n">
-        <v>0.103</v>
+        <v>0.031</v>
       </c>
       <c r="E7" s="24" t="n">
-        <v>-0.034</v>
+        <v>-0.024</v>
       </c>
       <c r="F7" s="24" t="n">
-        <v>-0.061</v>
+        <v>-0.068</v>
       </c>
       <c r="G7" s="24" t="inlineStr">
         <is>
@@ -2244,22 +2244,22 @@
         </is>
       </c>
       <c r="B8" s="24" t="n">
-        <v>4.055</v>
+        <v>4.031</v>
       </c>
       <c r="C8" s="24" t="n">
         <v>0.87</v>
       </c>
       <c r="D8" s="24" t="n">
-        <v>-0.002</v>
+        <v>-0.03</v>
       </c>
       <c r="E8" s="24" t="n">
-        <v>-0.012</v>
+        <v>0</v>
       </c>
       <c r="F8" s="24" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.068</v>
       </c>
       <c r="G8" s="24" t="n">
-        <v>0.023</v>
+        <v>-0.005</v>
       </c>
       <c r="H8" s="23" t="inlineStr">
         <is>
@@ -2283,25 +2283,25 @@
         </is>
       </c>
       <c r="B9" s="24" t="n">
-        <v>4.998</v>
+        <v>4.913</v>
       </c>
       <c r="C9" s="24" t="n">
-        <v>1.001</v>
+        <v>0.958</v>
       </c>
       <c r="D9" s="24" t="n">
-        <v>-0.055</v>
+        <v>-0.005</v>
       </c>
       <c r="E9" s="24" t="n">
-        <v>0.011</v>
+        <v>-0.023</v>
       </c>
       <c r="F9" s="24" t="n">
-        <v>0.022</v>
+        <v>0.017</v>
       </c>
       <c r="G9" s="24" t="n">
-        <v>-0.147</v>
+        <v>-0.07199999999999999</v>
       </c>
       <c r="H9" s="24" t="n">
-        <v>-0.351</v>
+        <v>-0.331</v>
       </c>
       <c r="I9" s="24" t="inlineStr">
         <is>
@@ -2324,28 +2324,28 @@
         </is>
       </c>
       <c r="B10" s="24" t="n">
-        <v>3.445</v>
+        <v>3.433</v>
       </c>
       <c r="C10" s="24" t="n">
-        <v>0.905</v>
+        <v>0.889</v>
       </c>
       <c r="D10" s="24" t="n">
-        <v>-0.055</v>
+        <v>-0.041</v>
       </c>
       <c r="E10" s="24" t="n">
-        <v>-0.041</v>
+        <v>-0.025</v>
       </c>
       <c r="F10" s="24" t="n">
-        <v>0.057</v>
+        <v>0.056</v>
       </c>
       <c r="G10" s="24" t="n">
-        <v>-0.066</v>
+        <v>0.015</v>
       </c>
       <c r="H10" s="24" t="n">
-        <v>-0.026</v>
+        <v>-0.011</v>
       </c>
       <c r="I10" s="24" t="n">
-        <v>0.044</v>
+        <v>0.045</v>
       </c>
       <c r="J10" s="24" t="inlineStr">
         <is>
@@ -2367,31 +2367,31 @@
         </is>
       </c>
       <c r="B11" s="24" t="n">
-        <v>4.556</v>
+        <v>4.585</v>
       </c>
       <c r="C11" s="24" t="n">
-        <v>0.878</v>
+        <v>0.887</v>
       </c>
       <c r="D11" s="24" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.101</v>
       </c>
       <c r="E11" s="24" t="n">
-        <v>-0.092</v>
+        <v>-0.059</v>
       </c>
       <c r="F11" s="24" t="n">
-        <v>-0.092</v>
+        <v>-0.056</v>
       </c>
       <c r="G11" s="24" t="n">
-        <v>-0.044</v>
+        <v>-0.068</v>
       </c>
       <c r="H11" s="24" t="n">
-        <v>-0.08</v>
+        <v>-0.063</v>
       </c>
       <c r="I11" s="24" t="n">
-        <v>0.027</v>
+        <v>-0.028</v>
       </c>
       <c r="J11" s="24" t="n">
-        <v>-0.003</v>
+        <v>-0.007</v>
       </c>
       <c r="K11" s="24" t="inlineStr">
         <is>
@@ -2412,34 +2412,34 @@
         </is>
       </c>
       <c r="B12" s="24" t="n">
-        <v>4.546</v>
+        <v>4.512</v>
       </c>
       <c r="C12" s="24" t="n">
-        <v>1.248</v>
+        <v>1.214</v>
       </c>
       <c r="D12" s="24" t="n">
-        <v>-0.026</v>
+        <v>-0.04</v>
       </c>
       <c r="E12" s="24" t="n">
-        <v>-0.018</v>
+        <v>-0.013</v>
       </c>
       <c r="F12" s="24" t="n">
-        <v>-0.006</v>
+        <v>-0.022</v>
       </c>
       <c r="G12" s="24" t="n">
-        <v>-0.08</v>
+        <v>-0.058</v>
       </c>
       <c r="H12" s="24" t="n">
-        <v>-0.537</v>
+        <v>-0.506</v>
       </c>
       <c r="I12" s="24" t="n">
-        <v>0.5580000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="J12" s="24" t="n">
-        <v>-0.017</v>
+        <v>-0.004</v>
       </c>
       <c r="K12" s="24" t="n">
-        <v>-0.036</v>
+        <v>-0.021</v>
       </c>
       <c r="L12" s="24" t="inlineStr">
         <is>
@@ -2459,37 +2459,37 @@
         </is>
       </c>
       <c r="B13" s="24" t="n">
-        <v>2.961</v>
+        <v>3.064</v>
       </c>
       <c r="C13" s="24" t="n">
-        <v>1.182</v>
+        <v>1.179</v>
       </c>
       <c r="D13" s="24" t="n">
-        <v>0.032</v>
+        <v>0.011</v>
       </c>
       <c r="E13" s="24" t="n">
-        <v>0.036</v>
+        <v>0.001</v>
       </c>
       <c r="F13" s="24" t="n">
-        <v>0.008</v>
+        <v>-0.07199999999999999</v>
       </c>
       <c r="G13" s="24" t="n">
-        <v>0.074</v>
+        <v>0.024</v>
       </c>
       <c r="H13" s="24" t="n">
-        <v>0.552</v>
+        <v>0.514</v>
       </c>
       <c r="I13" s="24" t="n">
-        <v>-0.525</v>
+        <v>-0.499</v>
       </c>
       <c r="J13" s="24" t="n">
-        <v>-0.008</v>
+        <v>0.017</v>
       </c>
       <c r="K13" s="24" t="n">
-        <v>-0.08</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="L13" s="24" t="n">
-        <v>-0.454</v>
+        <v>-0.448</v>
       </c>
       <c r="M13" s="24" t="inlineStr">
         <is>
@@ -2508,44 +2508,44 @@
         </is>
       </c>
       <c r="B14" s="24" t="n">
-        <v>4.402</v>
+        <v>4.379</v>
       </c>
       <c r="C14" s="24" t="n">
-        <v>0.639</v>
+        <v>0.649</v>
       </c>
       <c r="D14" s="24" t="n">
-        <v>-0.026</v>
+        <v>0.034</v>
       </c>
       <c r="E14" s="24" t="n">
-        <v>-0.013</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="F14" s="24" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="G14" s="24" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="H14" s="24" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I14" s="24" t="n">
         <v>-0.052</v>
       </c>
-      <c r="G14" s="24" t="n">
-        <v>-0.008</v>
-      </c>
-      <c r="H14" s="24" t="n">
-        <v>-0.025</v>
-      </c>
-      <c r="I14" s="24" t="n">
-        <v>0.005</v>
-      </c>
       <c r="J14" s="24" t="n">
-        <v>-0.125</v>
+        <v>-0.153</v>
       </c>
       <c r="K14" s="24" t="n">
-        <v>-0.045</v>
+        <v>-0.074</v>
       </c>
       <c r="L14" s="24" t="n">
-        <v>0.041</v>
+        <v>-0.005</v>
       </c>
       <c r="M14" s="24" t="n">
-        <v>-0.068</v>
+        <v>0.067</v>
       </c>
       <c r="N14" s="24" t="inlineStr">
         <is>
-          <t>(0.83)</t>
+          <t>(0.79)</t>
         </is>
       </c>
       <c r="O14" s="24" t="n"/>
@@ -2559,43 +2559,43 @@
         </is>
       </c>
       <c r="B15" s="24" t="n">
-        <v>4.518</v>
+        <v>4.525</v>
       </c>
       <c r="C15" s="24" t="n">
-        <v>0.828</v>
+        <v>0.742</v>
       </c>
       <c r="D15" s="24" t="n">
-        <v>-0.06</v>
+        <v>0.028</v>
       </c>
       <c r="E15" s="24" t="n">
-        <v>-0.029</v>
+        <v>-0.028</v>
       </c>
       <c r="F15" s="24" t="n">
-        <v>-0.042</v>
+        <v>-0.006</v>
       </c>
       <c r="G15" s="24" t="n">
-        <v>-0.108</v>
+        <v>-0.051</v>
       </c>
       <c r="H15" s="24" t="n">
-        <v>-0.419</v>
+        <v>-0.426</v>
       </c>
       <c r="I15" s="24" t="n">
-        <v>0.451</v>
+        <v>0.406</v>
       </c>
       <c r="J15" s="24" t="n">
-        <v>-0.025</v>
+        <v>-0.105</v>
       </c>
       <c r="K15" s="24" t="n">
-        <v>0.013</v>
+        <v>-0.011</v>
       </c>
       <c r="L15" s="24" t="n">
-        <v>0.602</v>
+        <v>0.603</v>
       </c>
       <c r="M15" s="24" t="n">
-        <v>-0.663</v>
+        <v>-0.634</v>
       </c>
       <c r="N15" s="24" t="n">
-        <v>0.394</v>
+        <v>0.318</v>
       </c>
       <c r="O15" s="24" t="inlineStr">
         <is>
@@ -2612,46 +2612,46 @@
         </is>
       </c>
       <c r="B16" s="24" t="n">
-        <v>5.048</v>
+        <v>4.988</v>
       </c>
       <c r="C16" s="24" t="n">
-        <v>1.135</v>
+        <v>1.019</v>
       </c>
       <c r="D16" s="24" t="n">
-        <v>0.003</v>
+        <v>0.004</v>
       </c>
       <c r="E16" s="24" t="n">
-        <v>-0.012</v>
+        <v>0.014</v>
       </c>
       <c r="F16" s="24" t="n">
-        <v>0.008999999999999999</v>
+        <v>-0.039</v>
       </c>
       <c r="G16" s="24" t="n">
-        <v>-0.095</v>
+        <v>-0.058</v>
       </c>
       <c r="H16" s="24" t="n">
-        <v>-0.327</v>
+        <v>-0.358</v>
       </c>
       <c r="I16" s="24" t="n">
-        <v>0.415</v>
+        <v>0.33</v>
       </c>
       <c r="J16" s="24" t="n">
-        <v>-0.013</v>
+        <v>0.046</v>
       </c>
       <c r="K16" s="24" t="n">
-        <v>0.044</v>
+        <v>0.066</v>
       </c>
       <c r="L16" s="24" t="n">
-        <v>0.499</v>
+        <v>0.469</v>
       </c>
       <c r="M16" s="24" t="n">
-        <v>-0.53</v>
+        <v>-0.47</v>
       </c>
       <c r="N16" s="24" t="n">
-        <v>0.045</v>
+        <v>-0.021</v>
       </c>
       <c r="O16" s="24" t="n">
-        <v>0.434</v>
+        <v>0.343</v>
       </c>
       <c r="P16" s="24" t="inlineStr">
         <is>
@@ -2667,49 +2667,49 @@
         </is>
       </c>
       <c r="B17" s="24" t="n">
-        <v>2.586</v>
+        <v>2.661</v>
       </c>
       <c r="C17" s="24" t="n">
-        <v>1.144</v>
+        <v>1.169</v>
       </c>
       <c r="D17" s="24" t="n">
-        <v>-0.02</v>
+        <v>-0.043</v>
       </c>
       <c r="E17" s="24" t="n">
-        <v>-0.066</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="F17" s="24" t="n">
-        <v>-0.02</v>
+        <v>0.002</v>
       </c>
       <c r="G17" s="24" t="n">
         <v>0.076</v>
       </c>
       <c r="H17" s="24" t="n">
-        <v>0.379</v>
+        <v>0.345</v>
       </c>
       <c r="I17" s="24" t="n">
-        <v>-0.349</v>
+        <v>-0.468</v>
       </c>
       <c r="J17" s="24" t="n">
-        <v>-0.136</v>
+        <v>-0</v>
       </c>
       <c r="K17" s="24" t="n">
-        <v>0.089</v>
+        <v>-0.004</v>
       </c>
       <c r="L17" s="24" t="n">
-        <v>-0.496</v>
+        <v>-0.475</v>
       </c>
       <c r="M17" s="24" t="n">
-        <v>0.527</v>
+        <v>0.599</v>
       </c>
       <c r="N17" s="24" t="n">
-        <v>-0.016</v>
+        <v>0.106</v>
       </c>
       <c r="O17" s="24" t="n">
-        <v>-0.484</v>
+        <v>-0.429</v>
       </c>
       <c r="P17" s="24" t="n">
-        <v>-0.409</v>
+        <v>-0.347</v>
       </c>
       <c r="Q17" s="24" t="inlineStr">
         <is>

--- a/results/Model3.xlsx
+++ b/results/Model3.xlsx
@@ -2108,10 +2108,10 @@
         </is>
       </c>
       <c r="B4" s="24" t="n">
-        <v>0.551</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="C4" s="24" t="n">
-        <v>0.498</v>
+        <v>0.497</v>
       </c>
       <c r="D4" s="24" t="inlineStr">
         <is>
@@ -2139,13 +2139,13 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>30.834</v>
+        <v>30.756</v>
       </c>
       <c r="C5" s="24" t="n">
-        <v>4.634</v>
+        <v>4.688</v>
       </c>
       <c r="D5" s="24" t="n">
-        <v>0.027</v>
+        <v>0.028</v>
       </c>
       <c r="E5" s="24" t="inlineStr">
         <is>
@@ -2172,13 +2172,13 @@
         </is>
       </c>
       <c r="B6" s="24" t="n">
-        <v>2.331</v>
+        <v>2.328</v>
       </c>
       <c r="C6" s="24" t="n">
-        <v>1.474</v>
+        <v>1.481</v>
       </c>
       <c r="D6" s="24" t="n">
-        <v>-0.013</v>
+        <v>0.01</v>
       </c>
       <c r="E6" s="24" t="n">
         <v>0.187</v>
@@ -2207,19 +2207,19 @@
         </is>
       </c>
       <c r="B7" s="24" t="n">
-        <v>3.271</v>
+        <v>3.297</v>
       </c>
       <c r="C7" s="24" t="n">
-        <v>1.061</v>
+        <v>1.07</v>
       </c>
       <c r="D7" s="24" t="n">
-        <v>0.031</v>
+        <v>0.122</v>
       </c>
       <c r="E7" s="24" t="n">
-        <v>-0.024</v>
+        <v>-0.034</v>
       </c>
       <c r="F7" s="24" t="n">
-        <v>-0.068</v>
+        <v>-0.07199999999999999</v>
       </c>
       <c r="G7" s="24" t="inlineStr">
         <is>
@@ -2244,22 +2244,22 @@
         </is>
       </c>
       <c r="B8" s="24" t="n">
-        <v>4.031</v>
+        <v>4.054</v>
       </c>
       <c r="C8" s="24" t="n">
-        <v>0.87</v>
+        <v>0.894</v>
       </c>
       <c r="D8" s="24" t="n">
-        <v>-0.03</v>
+        <v>-0.023</v>
       </c>
       <c r="E8" s="24" t="n">
         <v>0</v>
       </c>
       <c r="F8" s="24" t="n">
-        <v>0.068</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="G8" s="24" t="n">
-        <v>-0.005</v>
+        <v>-0.012</v>
       </c>
       <c r="H8" s="23" t="inlineStr">
         <is>
@@ -2283,25 +2283,25 @@
         </is>
       </c>
       <c r="B9" s="24" t="n">
-        <v>4.913</v>
+        <v>4.869</v>
       </c>
       <c r="C9" s="24" t="n">
-        <v>0.958</v>
+        <v>0.972</v>
       </c>
       <c r="D9" s="24" t="n">
-        <v>-0.005</v>
+        <v>-0.01</v>
       </c>
       <c r="E9" s="24" t="n">
-        <v>-0.023</v>
+        <v>-0.019</v>
       </c>
       <c r="F9" s="24" t="n">
-        <v>0.017</v>
+        <v>0.019</v>
       </c>
       <c r="G9" s="24" t="n">
-        <v>-0.07199999999999999</v>
+        <v>-0.082</v>
       </c>
       <c r="H9" s="24" t="n">
-        <v>-0.331</v>
+        <v>-0.363</v>
       </c>
       <c r="I9" s="24" t="inlineStr">
         <is>
@@ -2324,28 +2324,28 @@
         </is>
       </c>
       <c r="B10" s="24" t="n">
-        <v>3.433</v>
+        <v>3.45</v>
       </c>
       <c r="C10" s="24" t="n">
-        <v>0.889</v>
+        <v>0.893</v>
       </c>
       <c r="D10" s="24" t="n">
-        <v>-0.041</v>
+        <v>-0.063</v>
       </c>
       <c r="E10" s="24" t="n">
-        <v>-0.025</v>
+        <v>-0.027</v>
       </c>
       <c r="F10" s="24" t="n">
-        <v>0.056</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="G10" s="24" t="n">
-        <v>0.015</v>
+        <v>-0.063</v>
       </c>
       <c r="H10" s="24" t="n">
-        <v>-0.011</v>
+        <v>0.018</v>
       </c>
       <c r="I10" s="24" t="n">
-        <v>0.045</v>
+        <v>0.058</v>
       </c>
       <c r="J10" s="24" t="inlineStr">
         <is>
@@ -2367,31 +2367,31 @@
         </is>
       </c>
       <c r="B11" s="24" t="n">
-        <v>4.585</v>
+        <v>4.622</v>
       </c>
       <c r="C11" s="24" t="n">
-        <v>0.887</v>
+        <v>0.881</v>
       </c>
       <c r="D11" s="24" t="n">
-        <v>-0.101</v>
+        <v>-0.113</v>
       </c>
       <c r="E11" s="24" t="n">
-        <v>-0.059</v>
+        <v>-0.047</v>
       </c>
       <c r="F11" s="24" t="n">
-        <v>-0.056</v>
+        <v>-0.08599999999999999</v>
       </c>
       <c r="G11" s="24" t="n">
-        <v>-0.068</v>
+        <v>-0.1</v>
       </c>
       <c r="H11" s="24" t="n">
-        <v>-0.063</v>
+        <v>-0.06</v>
       </c>
       <c r="I11" s="24" t="n">
-        <v>-0.028</v>
+        <v>-0.022</v>
       </c>
       <c r="J11" s="24" t="n">
-        <v>-0.007</v>
+        <v>0.015</v>
       </c>
       <c r="K11" s="24" t="inlineStr">
         <is>
@@ -2412,34 +2412,34 @@
         </is>
       </c>
       <c r="B12" s="24" t="n">
-        <v>4.512</v>
+        <v>4.45</v>
       </c>
       <c r="C12" s="24" t="n">
-        <v>1.214</v>
+        <v>1.246</v>
       </c>
       <c r="D12" s="24" t="n">
-        <v>-0.04</v>
+        <v>-0.044</v>
       </c>
       <c r="E12" s="24" t="n">
-        <v>-0.013</v>
+        <v>-0.006</v>
       </c>
       <c r="F12" s="24" t="n">
-        <v>-0.022</v>
+        <v>-0.012</v>
       </c>
       <c r="G12" s="24" t="n">
-        <v>-0.058</v>
+        <v>-0.065</v>
       </c>
       <c r="H12" s="24" t="n">
-        <v>-0.506</v>
+        <v>-0.53</v>
       </c>
       <c r="I12" s="24" t="n">
-        <v>0.53</v>
+        <v>0.528</v>
       </c>
       <c r="J12" s="24" t="n">
-        <v>-0.004</v>
+        <v>0.004</v>
       </c>
       <c r="K12" s="24" t="n">
-        <v>-0.021</v>
+        <v>-0.029</v>
       </c>
       <c r="L12" s="24" t="inlineStr">
         <is>
@@ -2459,37 +2459,37 @@
         </is>
       </c>
       <c r="B13" s="24" t="n">
-        <v>3.064</v>
+        <v>3.084</v>
       </c>
       <c r="C13" s="24" t="n">
-        <v>1.179</v>
+        <v>1.215</v>
       </c>
       <c r="D13" s="24" t="n">
-        <v>0.011</v>
+        <v>0.031</v>
       </c>
       <c r="E13" s="24" t="n">
-        <v>0.001</v>
+        <v>0.026</v>
       </c>
       <c r="F13" s="24" t="n">
-        <v>-0.07199999999999999</v>
+        <v>-0.02</v>
       </c>
       <c r="G13" s="24" t="n">
-        <v>0.024</v>
+        <v>0.026</v>
       </c>
       <c r="H13" s="24" t="n">
-        <v>0.514</v>
+        <v>0.543</v>
       </c>
       <c r="I13" s="24" t="n">
-        <v>-0.499</v>
+        <v>-0.508</v>
       </c>
       <c r="J13" s="24" t="n">
-        <v>0.017</v>
+        <v>0.022</v>
       </c>
       <c r="K13" s="24" t="n">
-        <v>-0.06900000000000001</v>
+        <v>-0.062</v>
       </c>
       <c r="L13" s="24" t="n">
-        <v>-0.448</v>
+        <v>-0.438</v>
       </c>
       <c r="M13" s="24" t="inlineStr">
         <is>
@@ -2508,40 +2508,40 @@
         </is>
       </c>
       <c r="B14" s="24" t="n">
-        <v>4.379</v>
+        <v>4.382</v>
       </c>
       <c r="C14" s="24" t="n">
-        <v>0.649</v>
+        <v>0.655</v>
       </c>
       <c r="D14" s="24" t="n">
-        <v>0.034</v>
+        <v>0.036</v>
       </c>
       <c r="E14" s="24" t="n">
         <v>0.008999999999999999</v>
       </c>
       <c r="F14" s="24" t="n">
-        <v>-0.02</v>
+        <v>-0.024</v>
       </c>
       <c r="G14" s="24" t="n">
-        <v>-0.03</v>
+        <v>-0.021</v>
       </c>
       <c r="H14" s="24" t="n">
-        <v>0.05</v>
+        <v>0.058</v>
       </c>
       <c r="I14" s="24" t="n">
-        <v>-0.052</v>
+        <v>-0.058</v>
       </c>
       <c r="J14" s="24" t="n">
-        <v>-0.153</v>
+        <v>-0.115</v>
       </c>
       <c r="K14" s="24" t="n">
-        <v>-0.074</v>
+        <v>-0.057</v>
       </c>
       <c r="L14" s="24" t="n">
-        <v>-0.005</v>
+        <v>-0</v>
       </c>
       <c r="M14" s="24" t="n">
-        <v>0.067</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="N14" s="24" t="inlineStr">
         <is>
@@ -2559,43 +2559,43 @@
         </is>
       </c>
       <c r="B15" s="24" t="n">
-        <v>4.525</v>
+        <v>4.509</v>
       </c>
       <c r="C15" s="24" t="n">
-        <v>0.742</v>
+        <v>0.744</v>
       </c>
       <c r="D15" s="24" t="n">
-        <v>0.028</v>
+        <v>0.008</v>
       </c>
       <c r="E15" s="24" t="n">
-        <v>-0.028</v>
+        <v>-0.024</v>
       </c>
       <c r="F15" s="24" t="n">
-        <v>-0.006</v>
+        <v>0.005</v>
       </c>
       <c r="G15" s="24" t="n">
-        <v>-0.051</v>
+        <v>-0.031</v>
       </c>
       <c r="H15" s="24" t="n">
-        <v>-0.426</v>
+        <v>-0.41</v>
       </c>
       <c r="I15" s="24" t="n">
-        <v>0.406</v>
+        <v>0.415</v>
       </c>
       <c r="J15" s="24" t="n">
-        <v>-0.105</v>
+        <v>-0.095</v>
       </c>
       <c r="K15" s="24" t="n">
-        <v>-0.011</v>
+        <v>-0.032</v>
       </c>
       <c r="L15" s="24" t="n">
         <v>0.603</v>
       </c>
       <c r="M15" s="24" t="n">
-        <v>-0.634</v>
+        <v>-0.578</v>
       </c>
       <c r="N15" s="24" t="n">
-        <v>0.318</v>
+        <v>0.313</v>
       </c>
       <c r="O15" s="24" t="inlineStr">
         <is>
@@ -2612,46 +2612,46 @@
         </is>
       </c>
       <c r="B16" s="24" t="n">
-        <v>4.988</v>
+        <v>4.989</v>
       </c>
       <c r="C16" s="24" t="n">
-        <v>1.019</v>
+        <v>1.064</v>
       </c>
       <c r="D16" s="24" t="n">
-        <v>0.004</v>
+        <v>-0.046</v>
       </c>
       <c r="E16" s="24" t="n">
-        <v>0.014</v>
+        <v>0.028</v>
       </c>
       <c r="F16" s="24" t="n">
-        <v>-0.039</v>
+        <v>-0.025</v>
       </c>
       <c r="G16" s="24" t="n">
-        <v>-0.058</v>
+        <v>-0.05</v>
       </c>
       <c r="H16" s="24" t="n">
-        <v>-0.358</v>
+        <v>-0.299</v>
       </c>
       <c r="I16" s="24" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="J16" s="24" t="n">
-        <v>0.046</v>
+        <v>-0.079</v>
       </c>
       <c r="K16" s="24" t="n">
-        <v>0.066</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="L16" s="24" t="n">
-        <v>0.469</v>
+        <v>0.417</v>
       </c>
       <c r="M16" s="24" t="n">
-        <v>-0.47</v>
+        <v>-0.521</v>
       </c>
       <c r="N16" s="24" t="n">
-        <v>-0.021</v>
+        <v>-0.016</v>
       </c>
       <c r="O16" s="24" t="n">
-        <v>0.343</v>
+        <v>0.449</v>
       </c>
       <c r="P16" s="24" t="inlineStr">
         <is>
@@ -2667,49 +2667,49 @@
         </is>
       </c>
       <c r="B17" s="24" t="n">
-        <v>2.661</v>
+        <v>2.68</v>
       </c>
       <c r="C17" s="24" t="n">
-        <v>1.169</v>
+        <v>1.115</v>
       </c>
       <c r="D17" s="24" t="n">
-        <v>-0.043</v>
+        <v>0.004</v>
       </c>
       <c r="E17" s="24" t="n">
-        <v>-0.008999999999999999</v>
+        <v>0.051</v>
       </c>
       <c r="F17" s="24" t="n">
-        <v>0.002</v>
+        <v>-0.005</v>
       </c>
       <c r="G17" s="24" t="n">
-        <v>0.076</v>
+        <v>0.037</v>
       </c>
       <c r="H17" s="24" t="n">
-        <v>0.345</v>
+        <v>0.421</v>
       </c>
       <c r="I17" s="24" t="n">
-        <v>-0.468</v>
+        <v>-0.459</v>
       </c>
       <c r="J17" s="24" t="n">
-        <v>-0</v>
+        <v>-0.033</v>
       </c>
       <c r="K17" s="24" t="n">
-        <v>-0.004</v>
+        <v>0.022</v>
       </c>
       <c r="L17" s="24" t="n">
-        <v>-0.475</v>
+        <v>-0.496</v>
       </c>
       <c r="M17" s="24" t="n">
-        <v>0.599</v>
+        <v>0.552</v>
       </c>
       <c r="N17" s="24" t="n">
-        <v>0.106</v>
+        <v>0.082</v>
       </c>
       <c r="O17" s="24" t="n">
-        <v>-0.429</v>
+        <v>-0.376</v>
       </c>
       <c r="P17" s="24" t="n">
-        <v>-0.347</v>
+        <v>-0.296</v>
       </c>
       <c r="Q17" s="24" t="inlineStr">
         <is>
@@ -2921,46 +2921,46 @@
         </is>
       </c>
       <c r="B6" s="24" t="n">
-        <v>3.821</v>
+        <v>3.793</v>
       </c>
       <c r="C6" s="24" t="n">
-        <v>0.094</v>
+        <v>0.092</v>
       </c>
       <c r="D6" s="24" t="n">
-        <v>3.821</v>
+        <v>3.793</v>
       </c>
       <c r="E6" s="24" t="n">
-        <v>0.094</v>
+        <v>0.092</v>
       </c>
       <c r="F6" s="24" t="n">
-        <v>3.821</v>
+        <v>3.793</v>
       </c>
       <c r="G6" s="24" t="n">
-        <v>0.094</v>
+        <v>0.092</v>
       </c>
       <c r="H6" s="24" t="n">
-        <v>3.821</v>
+        <v>3.793</v>
       </c>
       <c r="I6" s="24" t="n">
-        <v>0.094</v>
+        <v>0.092</v>
       </c>
       <c r="J6" s="24" t="n">
-        <v>3.821</v>
+        <v>3.793</v>
       </c>
       <c r="K6" s="24" t="n">
-        <v>0.094</v>
+        <v>0.092</v>
       </c>
       <c r="L6" s="24" t="n">
-        <v>3.821</v>
+        <v>3.793</v>
       </c>
       <c r="M6" s="24" t="n">
-        <v>0.094</v>
+        <v>0.092</v>
       </c>
       <c r="N6" s="24" t="n">
-        <v>3.821</v>
+        <v>3.793</v>
       </c>
       <c r="O6" s="24" t="n">
-        <v>0.094</v>
+        <v>0.092</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" s="37">
@@ -2991,43 +2991,43 @@
         </is>
       </c>
       <c r="B8" s="24" t="n">
-        <v>-0.018</v>
+        <v>-0.021</v>
       </c>
       <c r="C8" s="24" t="n">
         <v>0.022</v>
       </c>
       <c r="D8" s="24" t="n">
-        <v>-0.018</v>
+        <v>-0.021</v>
       </c>
       <c r="E8" s="24" t="n">
         <v>0.022</v>
       </c>
       <c r="F8" s="24" t="n">
-        <v>-0.018</v>
+        <v>-0.021</v>
       </c>
       <c r="G8" s="24" t="n">
         <v>0.022</v>
       </c>
       <c r="H8" s="24" t="n">
-        <v>-0.018</v>
+        <v>-0.021</v>
       </c>
       <c r="I8" s="24" t="n">
         <v>0.022</v>
       </c>
       <c r="J8" s="24" t="n">
-        <v>-0.018</v>
+        <v>-0.021</v>
       </c>
       <c r="K8" s="24" t="n">
         <v>0.022</v>
       </c>
       <c r="L8" s="24" t="n">
-        <v>-0.018</v>
+        <v>-0.021</v>
       </c>
       <c r="M8" s="24" t="n">
         <v>0.022</v>
       </c>
       <c r="N8" s="24" t="n">
-        <v>-0.018</v>
+        <v>-0.021</v>
       </c>
       <c r="O8" s="24" t="n">
         <v>0.022</v>
@@ -3040,43 +3040,43 @@
         </is>
       </c>
       <c r="B9" s="24" t="n">
-        <v>0.034</v>
+        <v>0.038</v>
       </c>
       <c r="C9" s="24" t="n">
         <v>0.041</v>
       </c>
       <c r="D9" s="24" t="n">
-        <v>0.034</v>
+        <v>0.038</v>
       </c>
       <c r="E9" s="24" t="n">
         <v>0.041</v>
       </c>
       <c r="F9" s="24" t="n">
-        <v>0.034</v>
+        <v>0.038</v>
       </c>
       <c r="G9" s="24" t="n">
         <v>0.041</v>
       </c>
       <c r="H9" s="24" t="n">
-        <v>0.034</v>
+        <v>0.038</v>
       </c>
       <c r="I9" s="24" t="n">
         <v>0.041</v>
       </c>
       <c r="J9" s="24" t="n">
-        <v>0.034</v>
+        <v>0.038</v>
       </c>
       <c r="K9" s="24" t="n">
         <v>0.041</v>
       </c>
       <c r="L9" s="24" t="n">
-        <v>0.034</v>
+        <v>0.038</v>
       </c>
       <c r="M9" s="24" t="n">
         <v>0.041</v>
       </c>
       <c r="N9" s="24" t="n">
-        <v>0.034</v>
+        <v>0.038</v>
       </c>
       <c r="O9" s="24" t="n">
         <v>0.041</v>
@@ -3089,43 +3089,43 @@
         </is>
       </c>
       <c r="B10" s="24" t="n">
-        <v>0.012</v>
+        <v>0.015</v>
       </c>
       <c r="C10" s="24" t="n">
         <v>0.018</v>
       </c>
       <c r="D10" s="24" t="n">
-        <v>0.012</v>
+        <v>0.015</v>
       </c>
       <c r="E10" s="24" t="n">
         <v>0.018</v>
       </c>
       <c r="F10" s="24" t="n">
-        <v>0.012</v>
+        <v>0.015</v>
       </c>
       <c r="G10" s="24" t="n">
         <v>0.018</v>
       </c>
       <c r="H10" s="24" t="n">
-        <v>0.012</v>
+        <v>0.015</v>
       </c>
       <c r="I10" s="24" t="n">
         <v>0.018</v>
       </c>
       <c r="J10" s="24" t="n">
-        <v>0.012</v>
+        <v>0.015</v>
       </c>
       <c r="K10" s="24" t="n">
         <v>0.018</v>
       </c>
       <c r="L10" s="24" t="n">
-        <v>0.012</v>
+        <v>0.015</v>
       </c>
       <c r="M10" s="24" t="n">
         <v>0.018</v>
       </c>
       <c r="N10" s="24" t="n">
-        <v>0.012</v>
+        <v>0.015</v>
       </c>
       <c r="O10" s="24" t="n">
         <v>0.018</v>
@@ -3138,43 +3138,43 @@
         </is>
       </c>
       <c r="B11" s="24" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.091</v>
       </c>
       <c r="C11" s="24" t="n">
         <v>0.034</v>
       </c>
       <c r="D11" s="24" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.091</v>
       </c>
       <c r="E11" s="24" t="n">
         <v>0.034</v>
       </c>
       <c r="F11" s="24" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.091</v>
       </c>
       <c r="G11" s="24" t="n">
         <v>0.034</v>
       </c>
       <c r="H11" s="24" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.091</v>
       </c>
       <c r="I11" s="24" t="n">
         <v>0.034</v>
       </c>
       <c r="J11" s="24" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.091</v>
       </c>
       <c r="K11" s="24" t="n">
         <v>0.034</v>
       </c>
       <c r="L11" s="24" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.091</v>
       </c>
       <c r="M11" s="24" t="n">
         <v>0.034</v>
       </c>
       <c r="N11" s="24" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.091</v>
       </c>
       <c r="O11" s="24" t="n">
         <v>0.034</v>
@@ -3187,46 +3187,46 @@
         </is>
       </c>
       <c r="B12" s="24" t="n">
-        <v>0.412</v>
+        <v>0.428</v>
       </c>
       <c r="C12" s="24" t="n">
-        <v>0.048</v>
+        <v>0.047</v>
       </c>
       <c r="D12" s="24" t="n">
-        <v>0.412</v>
+        <v>0.428</v>
       </c>
       <c r="E12" s="24" t="n">
-        <v>0.048</v>
+        <v>0.047</v>
       </c>
       <c r="F12" s="24" t="n">
-        <v>0.412</v>
+        <v>0.428</v>
       </c>
       <c r="G12" s="24" t="n">
-        <v>0.048</v>
+        <v>0.047</v>
       </c>
       <c r="H12" s="24" t="n">
-        <v>0.412</v>
+        <v>0.428</v>
       </c>
       <c r="I12" s="24" t="n">
-        <v>0.048</v>
+        <v>0.047</v>
       </c>
       <c r="J12" s="24" t="n">
-        <v>0.412</v>
+        <v>0.428</v>
       </c>
       <c r="K12" s="24" t="n">
-        <v>0.048</v>
+        <v>0.047</v>
       </c>
       <c r="L12" s="24" t="n">
-        <v>0.412</v>
+        <v>0.428</v>
       </c>
       <c r="M12" s="24" t="n">
-        <v>0.048</v>
+        <v>0.047</v>
       </c>
       <c r="N12" s="24" t="n">
-        <v>0.412</v>
+        <v>0.428</v>
       </c>
       <c r="O12" s="24" t="n">
-        <v>0.048</v>
+        <v>0.047</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="37">
@@ -3257,28 +3257,28 @@
         </is>
       </c>
       <c r="B14" s="24" t="n">
-        <v>-0.142</v>
+        <v>-0.146</v>
       </c>
       <c r="C14" s="24" t="n">
-        <v>0.052</v>
+        <v>0.051</v>
       </c>
       <c r="D14" s="24" t="n">
-        <v>-0.14</v>
+        <v>-0.144</v>
       </c>
       <c r="E14" s="24" t="n">
-        <v>0.052</v>
+        <v>0.051</v>
       </c>
       <c r="F14" s="24" t="n">
-        <v>0.312</v>
+        <v>0.321</v>
       </c>
       <c r="G14" s="24" t="n">
-        <v>0.058</v>
+        <v>0.057</v>
       </c>
       <c r="H14" s="24" t="n">
-        <v>0.309</v>
+        <v>0.318</v>
       </c>
       <c r="I14" s="24" t="n">
-        <v>0.058</v>
+        <v>0.057</v>
       </c>
       <c r="J14" s="24" t="n">
         <v>-0.082</v>
@@ -3306,28 +3306,28 @@
         </is>
       </c>
       <c r="B15" s="24" t="n">
-        <v>0.267</v>
+        <v>0.275</v>
       </c>
       <c r="C15" s="24" t="n">
-        <v>0.049</v>
+        <v>0.048</v>
       </c>
       <c r="D15" s="24" t="n">
-        <v>0.26</v>
+        <v>0.268</v>
       </c>
       <c r="E15" s="24" t="n">
-        <v>0.049</v>
+        <v>0.048</v>
       </c>
       <c r="F15" s="24" t="n">
-        <v>-0.145</v>
+        <v>-0.149</v>
       </c>
       <c r="G15" s="24" t="n">
-        <v>0.052</v>
+        <v>0.051</v>
       </c>
       <c r="H15" s="24" t="n">
-        <v>-0.14</v>
+        <v>-0.144</v>
       </c>
       <c r="I15" s="24" t="n">
-        <v>0.052</v>
+        <v>0.051</v>
       </c>
       <c r="J15" s="24" t="n">
         <v>0.118</v>
@@ -3527,46 +3527,46 @@
         </is>
       </c>
       <c r="B20" s="24" t="n">
-        <v>-0.118</v>
+        <v>-0.122</v>
       </c>
       <c r="C20" s="24" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="D20" s="24" t="n">
+        <v>-0.122</v>
+      </c>
+      <c r="E20" s="24" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="F20" s="24" t="n">
+        <v>0.221</v>
+      </c>
+      <c r="G20" s="24" t="n">
         <v>0.046</v>
       </c>
-      <c r="D20" s="24" t="n">
-        <v>-0.118</v>
-      </c>
-      <c r="E20" s="24" t="n">
+      <c r="H20" s="24" t="n">
+        <v>0.221</v>
+      </c>
+      <c r="I20" s="24" t="n">
         <v>0.046</v>
       </c>
-      <c r="F20" s="24" t="n">
-        <v>0.214</v>
-      </c>
-      <c r="G20" s="24" t="n">
-        <v>0.047</v>
-      </c>
-      <c r="H20" s="24" t="n">
-        <v>0.214</v>
-      </c>
-      <c r="I20" s="24" t="n">
-        <v>0.047</v>
-      </c>
       <c r="J20" s="24" t="n">
-        <v>-0.118</v>
+        <v>-0.122</v>
       </c>
       <c r="K20" s="24" t="n">
-        <v>0.046</v>
+        <v>0.045</v>
       </c>
       <c r="L20" s="24" t="n">
-        <v>-0.118</v>
+        <v>-0.122</v>
       </c>
       <c r="M20" s="24" t="n">
-        <v>0.046</v>
+        <v>0.045</v>
       </c>
       <c r="N20" s="24" t="n">
-        <v>-0.118</v>
+        <v>-0.122</v>
       </c>
       <c r="O20" s="24" t="n">
-        <v>0.046</v>
+        <v>0.045</v>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1" s="37">
@@ -3576,46 +3576,46 @@
         </is>
       </c>
       <c r="B21" s="24" t="n">
-        <v>-0.062</v>
+        <v>-0.064</v>
       </c>
       <c r="C21" s="24" t="n">
-        <v>0.039</v>
+        <v>0.038</v>
       </c>
       <c r="D21" s="24" t="n">
-        <v>-0.062</v>
+        <v>-0.064</v>
       </c>
       <c r="E21" s="24" t="n">
-        <v>0.039</v>
+        <v>0.038</v>
       </c>
       <c r="F21" s="24" t="n">
-        <v>0.135</v>
+        <v>0.139</v>
       </c>
       <c r="G21" s="24" t="n">
-        <v>0.045</v>
+        <v>0.044</v>
       </c>
       <c r="H21" s="24" t="n">
-        <v>0.135</v>
+        <v>0.139</v>
       </c>
       <c r="I21" s="24" t="n">
-        <v>0.045</v>
+        <v>0.044</v>
       </c>
       <c r="J21" s="24" t="n">
-        <v>-0.062</v>
+        <v>-0.064</v>
       </c>
       <c r="K21" s="24" t="n">
-        <v>0.039</v>
+        <v>0.038</v>
       </c>
       <c r="L21" s="24" t="n">
-        <v>-0.062</v>
+        <v>-0.064</v>
       </c>
       <c r="M21" s="24" t="n">
-        <v>0.039</v>
+        <v>0.038</v>
       </c>
       <c r="N21" s="24" t="n">
-        <v>-0.062</v>
+        <v>-0.064</v>
       </c>
       <c r="O21" s="24" t="n">
-        <v>0.039</v>
+        <v>0.038</v>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1" s="37">
@@ -3656,10 +3656,10 @@
         </is>
       </c>
       <c r="D23" s="24" t="n">
-        <v>-0.012</v>
+        <v>-0.014</v>
       </c>
       <c r="E23" s="24" t="n">
-        <v>0.044</v>
+        <v>0.043</v>
       </c>
       <c r="F23" s="24" t="inlineStr">
         <is>
@@ -3672,10 +3672,10 @@
         </is>
       </c>
       <c r="H23" s="24" t="n">
-        <v>0.024</v>
+        <v>0.027</v>
       </c>
       <c r="I23" s="24" t="n">
-        <v>0.046</v>
+        <v>0.045</v>
       </c>
       <c r="J23" s="24" t="inlineStr">
         <is>
@@ -3725,10 +3725,10 @@
         </is>
       </c>
       <c r="D24" s="24" t="n">
-        <v>0.018</v>
+        <v>0.021</v>
       </c>
       <c r="E24" s="24" t="n">
-        <v>0.037</v>
+        <v>0.036</v>
       </c>
       <c r="F24" s="24" t="inlineStr">
         <is>
@@ -3741,10 +3741,10 @@
         </is>
       </c>
       <c r="H24" s="24" t="n">
-        <v>-0.019</v>
+        <v>-0.022</v>
       </c>
       <c r="I24" s="24" t="n">
-        <v>0.048</v>
+        <v>0.047</v>
       </c>
       <c r="J24" s="24" t="inlineStr">
         <is>
@@ -3794,10 +3794,10 @@
         </is>
       </c>
       <c r="D25" s="24" t="n">
-        <v>0.046</v>
+        <v>0.049</v>
       </c>
       <c r="E25" s="24" t="n">
-        <v>0.041</v>
+        <v>0.04</v>
       </c>
       <c r="F25" s="24" t="inlineStr">
         <is>
@@ -3810,10 +3810,10 @@
         </is>
       </c>
       <c r="H25" s="24" t="n">
-        <v>-0.111</v>
+        <v>-0.116</v>
       </c>
       <c r="I25" s="24" t="n">
-        <v>0.039</v>
+        <v>0.038</v>
       </c>
       <c r="J25" s="24" t="inlineStr">
         <is>
@@ -3863,10 +3863,10 @@
         </is>
       </c>
       <c r="D26" s="24" t="n">
-        <v>-0.098</v>
+        <v>-0.101</v>
       </c>
       <c r="E26" s="24" t="n">
-        <v>0.045</v>
+        <v>0.044</v>
       </c>
       <c r="F26" s="24" t="inlineStr">
         <is>
@@ -3879,10 +3879,10 @@
         </is>
       </c>
       <c r="H26" s="24" t="n">
-        <v>0.067</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="I26" s="24" t="n">
-        <v>0.052</v>
+        <v>0.051</v>
       </c>
       <c r="J26" s="24" t="inlineStr">
         <is>

--- a/results/Model3.xlsx
+++ b/results/Model3.xlsx
@@ -2108,10 +2108,10 @@
         </is>
       </c>
       <c r="B4" s="24" t="n">
-        <v>0.5580000000000001</v>
+        <v>0.551</v>
       </c>
       <c r="C4" s="24" t="n">
-        <v>0.497</v>
+        <v>0.498</v>
       </c>
       <c r="D4" s="24" t="inlineStr">
         <is>
@@ -2139,13 +2139,13 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>30.756</v>
+        <v>30.74</v>
       </c>
       <c r="C5" s="24" t="n">
-        <v>4.688</v>
+        <v>4.596</v>
       </c>
       <c r="D5" s="24" t="n">
-        <v>0.028</v>
+        <v>0.04</v>
       </c>
       <c r="E5" s="24" t="inlineStr">
         <is>
@@ -2172,16 +2172,16 @@
         </is>
       </c>
       <c r="B6" s="24" t="n">
-        <v>2.328</v>
+        <v>2.305</v>
       </c>
       <c r="C6" s="24" t="n">
-        <v>1.481</v>
+        <v>1.458</v>
       </c>
       <c r="D6" s="24" t="n">
-        <v>0.01</v>
+        <v>0.006</v>
       </c>
       <c r="E6" s="24" t="n">
-        <v>0.187</v>
+        <v>0.184</v>
       </c>
       <c r="F6" s="24" t="inlineStr">
         <is>
@@ -2207,19 +2207,19 @@
         </is>
       </c>
       <c r="B7" s="24" t="n">
-        <v>3.297</v>
+        <v>3.307</v>
       </c>
       <c r="C7" s="24" t="n">
-        <v>1.07</v>
+        <v>1.081</v>
       </c>
       <c r="D7" s="24" t="n">
-        <v>0.122</v>
+        <v>0.063</v>
       </c>
       <c r="E7" s="24" t="n">
-        <v>-0.034</v>
+        <v>-0.038</v>
       </c>
       <c r="F7" s="24" t="n">
-        <v>-0.07199999999999999</v>
+        <v>-0.027</v>
       </c>
       <c r="G7" s="24" t="inlineStr">
         <is>
@@ -2244,22 +2244,22 @@
         </is>
       </c>
       <c r="B8" s="24" t="n">
-        <v>4.054</v>
+        <v>4.062</v>
       </c>
       <c r="C8" s="24" t="n">
-        <v>0.894</v>
+        <v>0.91</v>
       </c>
       <c r="D8" s="24" t="n">
-        <v>-0.023</v>
+        <v>-0.031</v>
       </c>
       <c r="E8" s="24" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="F8" s="24" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.099</v>
       </c>
       <c r="G8" s="24" t="n">
-        <v>-0.012</v>
+        <v>-0.016</v>
       </c>
       <c r="H8" s="23" t="inlineStr">
         <is>
@@ -2283,25 +2283,25 @@
         </is>
       </c>
       <c r="B9" s="24" t="n">
-        <v>4.869</v>
+        <v>4.916</v>
       </c>
       <c r="C9" s="24" t="n">
-        <v>0.972</v>
+        <v>0.957</v>
       </c>
       <c r="D9" s="24" t="n">
-        <v>-0.01</v>
+        <v>-0.027</v>
       </c>
       <c r="E9" s="24" t="n">
-        <v>-0.019</v>
+        <v>0.015</v>
       </c>
       <c r="F9" s="24" t="n">
-        <v>0.019</v>
+        <v>0</v>
       </c>
       <c r="G9" s="24" t="n">
-        <v>-0.082</v>
+        <v>-0.095</v>
       </c>
       <c r="H9" s="24" t="n">
-        <v>-0.363</v>
+        <v>-0.353</v>
       </c>
       <c r="I9" s="24" t="inlineStr">
         <is>
@@ -2324,28 +2324,28 @@
         </is>
       </c>
       <c r="B10" s="24" t="n">
-        <v>3.45</v>
+        <v>3.456</v>
       </c>
       <c r="C10" s="24" t="n">
-        <v>0.893</v>
+        <v>0.918</v>
       </c>
       <c r="D10" s="24" t="n">
-        <v>-0.063</v>
+        <v>-0.08</v>
       </c>
       <c r="E10" s="24" t="n">
-        <v>-0.027</v>
+        <v>-0.002</v>
       </c>
       <c r="F10" s="24" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="G10" s="24" t="n">
-        <v>-0.063</v>
+        <v>-0.04</v>
       </c>
       <c r="H10" s="24" t="n">
-        <v>0.018</v>
+        <v>0.003</v>
       </c>
       <c r="I10" s="24" t="n">
-        <v>0.058</v>
+        <v>0.054</v>
       </c>
       <c r="J10" s="24" t="inlineStr">
         <is>
@@ -2367,35 +2367,35 @@
         </is>
       </c>
       <c r="B11" s="24" t="n">
-        <v>4.622</v>
+        <v>4.57</v>
       </c>
       <c r="C11" s="24" t="n">
-        <v>0.881</v>
+        <v>0.901</v>
       </c>
       <c r="D11" s="24" t="n">
-        <v>-0.113</v>
+        <v>-0.065</v>
       </c>
       <c r="E11" s="24" t="n">
-        <v>-0.047</v>
+        <v>-0.078</v>
       </c>
       <c r="F11" s="24" t="n">
-        <v>-0.08599999999999999</v>
+        <v>-0.08699999999999999</v>
       </c>
       <c r="G11" s="24" t="n">
-        <v>-0.1</v>
+        <v>-0.07099999999999999</v>
       </c>
       <c r="H11" s="24" t="n">
-        <v>-0.06</v>
+        <v>-0.04</v>
       </c>
       <c r="I11" s="24" t="n">
-        <v>-0.022</v>
+        <v>-0.035</v>
       </c>
       <c r="J11" s="24" t="n">
-        <v>0.015</v>
+        <v>-0.008</v>
       </c>
       <c r="K11" s="24" t="inlineStr">
         <is>
-          <t>(0.78)</t>
+          <t>(0.74)</t>
         </is>
       </c>
       <c r="L11" s="24" t="n"/>
@@ -2412,34 +2412,34 @@
         </is>
       </c>
       <c r="B12" s="24" t="n">
-        <v>4.45</v>
+        <v>4.51</v>
       </c>
       <c r="C12" s="24" t="n">
-        <v>1.246</v>
+        <v>1.234</v>
       </c>
       <c r="D12" s="24" t="n">
-        <v>-0.044</v>
+        <v>-0.03</v>
       </c>
       <c r="E12" s="24" t="n">
-        <v>-0.006</v>
+        <v>0.002</v>
       </c>
       <c r="F12" s="24" t="n">
-        <v>-0.012</v>
+        <v>-0.067</v>
       </c>
       <c r="G12" s="24" t="n">
-        <v>-0.065</v>
+        <v>-0.045</v>
       </c>
       <c r="H12" s="24" t="n">
-        <v>-0.53</v>
+        <v>-0.535</v>
       </c>
       <c r="I12" s="24" t="n">
-        <v>0.528</v>
+        <v>0.532</v>
       </c>
       <c r="J12" s="24" t="n">
-        <v>0.004</v>
+        <v>0.002</v>
       </c>
       <c r="K12" s="24" t="n">
-        <v>-0.029</v>
+        <v>-0.025</v>
       </c>
       <c r="L12" s="24" t="inlineStr">
         <is>
@@ -2459,37 +2459,37 @@
         </is>
       </c>
       <c r="B13" s="24" t="n">
-        <v>3.084</v>
+        <v>3.046</v>
       </c>
       <c r="C13" s="24" t="n">
-        <v>1.215</v>
+        <v>1.217</v>
       </c>
       <c r="D13" s="24" t="n">
-        <v>0.031</v>
+        <v>0.019</v>
       </c>
       <c r="E13" s="24" t="n">
-        <v>0.026</v>
+        <v>-0.004</v>
       </c>
       <c r="F13" s="24" t="n">
-        <v>-0.02</v>
+        <v>-0.005</v>
       </c>
       <c r="G13" s="24" t="n">
-        <v>0.026</v>
+        <v>0.046</v>
       </c>
       <c r="H13" s="24" t="n">
-        <v>0.543</v>
+        <v>0.545</v>
       </c>
       <c r="I13" s="24" t="n">
-        <v>-0.508</v>
+        <v>-0.52</v>
       </c>
       <c r="J13" s="24" t="n">
-        <v>0.022</v>
+        <v>0.041</v>
       </c>
       <c r="K13" s="24" t="n">
-        <v>-0.062</v>
+        <v>-0.066</v>
       </c>
       <c r="L13" s="24" t="n">
-        <v>-0.438</v>
+        <v>-0.431</v>
       </c>
       <c r="M13" s="24" t="inlineStr">
         <is>
@@ -2508,44 +2508,44 @@
         </is>
       </c>
       <c r="B14" s="24" t="n">
-        <v>4.382</v>
+        <v>4.372</v>
       </c>
       <c r="C14" s="24" t="n">
-        <v>0.655</v>
+        <v>0.647</v>
       </c>
       <c r="D14" s="24" t="n">
-        <v>0.036</v>
+        <v>0.007</v>
       </c>
       <c r="E14" s="24" t="n">
-        <v>0.008999999999999999</v>
+        <v>-0</v>
       </c>
       <c r="F14" s="24" t="n">
         <v>-0.024</v>
       </c>
       <c r="G14" s="24" t="n">
-        <v>-0.021</v>
+        <v>-0.032</v>
       </c>
       <c r="H14" s="24" t="n">
-        <v>0.058</v>
+        <v>0.061</v>
       </c>
       <c r="I14" s="24" t="n">
-        <v>-0.058</v>
+        <v>-0.053</v>
       </c>
       <c r="J14" s="24" t="n">
-        <v>-0.115</v>
+        <v>-0.117</v>
       </c>
       <c r="K14" s="24" t="n">
-        <v>-0.057</v>
+        <v>-0.075</v>
       </c>
       <c r="L14" s="24" t="n">
         <v>-0</v>
       </c>
       <c r="M14" s="24" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.061</v>
       </c>
       <c r="N14" s="24" t="inlineStr">
         <is>
-          <t>(0.79)</t>
+          <t>(0.75)</t>
         </is>
       </c>
       <c r="O14" s="24" t="n"/>
@@ -2559,43 +2559,43 @@
         </is>
       </c>
       <c r="B15" s="24" t="n">
-        <v>4.509</v>
+        <v>4.521</v>
       </c>
       <c r="C15" s="24" t="n">
-        <v>0.744</v>
+        <v>0.741</v>
       </c>
       <c r="D15" s="24" t="n">
-        <v>0.008</v>
+        <v>0.01</v>
       </c>
       <c r="E15" s="24" t="n">
+        <v>0.041</v>
+      </c>
+      <c r="F15" s="24" t="n">
         <v>-0.024</v>
       </c>
-      <c r="F15" s="24" t="n">
-        <v>0.005</v>
-      </c>
       <c r="G15" s="24" t="n">
-        <v>-0.031</v>
+        <v>-0.082</v>
       </c>
       <c r="H15" s="24" t="n">
-        <v>-0.41</v>
+        <v>-0.417</v>
       </c>
       <c r="I15" s="24" t="n">
-        <v>0.415</v>
+        <v>0.4</v>
       </c>
       <c r="J15" s="24" t="n">
-        <v>-0.095</v>
+        <v>-0.064</v>
       </c>
       <c r="K15" s="24" t="n">
-        <v>-0.032</v>
+        <v>-0.005</v>
       </c>
       <c r="L15" s="24" t="n">
-        <v>0.603</v>
+        <v>0.57</v>
       </c>
       <c r="M15" s="24" t="n">
-        <v>-0.578</v>
+        <v>-0.592</v>
       </c>
       <c r="N15" s="24" t="n">
-        <v>0.313</v>
+        <v>0.375</v>
       </c>
       <c r="O15" s="24" t="inlineStr">
         <is>
@@ -2612,46 +2612,46 @@
         </is>
       </c>
       <c r="B16" s="24" t="n">
-        <v>4.989</v>
+        <v>5.007</v>
       </c>
       <c r="C16" s="24" t="n">
-        <v>1.064</v>
+        <v>0.989</v>
       </c>
       <c r="D16" s="24" t="n">
-        <v>-0.046</v>
+        <v>0.032</v>
       </c>
       <c r="E16" s="24" t="n">
-        <v>0.028</v>
+        <v>-0.073</v>
       </c>
       <c r="F16" s="24" t="n">
-        <v>-0.025</v>
+        <v>-0.081</v>
       </c>
       <c r="G16" s="24" t="n">
-        <v>-0.05</v>
+        <v>-0.019</v>
       </c>
       <c r="H16" s="24" t="n">
-        <v>-0.299</v>
+        <v>-0.352</v>
       </c>
       <c r="I16" s="24" t="n">
-        <v>0.32</v>
+        <v>0.302</v>
       </c>
       <c r="J16" s="24" t="n">
-        <v>-0.079</v>
+        <v>-0.061</v>
       </c>
       <c r="K16" s="24" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.038</v>
       </c>
       <c r="L16" s="24" t="n">
-        <v>0.417</v>
+        <v>0.414</v>
       </c>
       <c r="M16" s="24" t="n">
-        <v>-0.521</v>
+        <v>-0.502</v>
       </c>
       <c r="N16" s="24" t="n">
-        <v>-0.016</v>
+        <v>-0.083</v>
       </c>
       <c r="O16" s="24" t="n">
-        <v>0.449</v>
+        <v>0.36</v>
       </c>
       <c r="P16" s="24" t="inlineStr">
         <is>
@@ -2667,49 +2667,49 @@
         </is>
       </c>
       <c r="B17" s="24" t="n">
-        <v>2.68</v>
+        <v>2.659</v>
       </c>
       <c r="C17" s="24" t="n">
-        <v>1.115</v>
+        <v>1.128</v>
       </c>
       <c r="D17" s="24" t="n">
-        <v>0.004</v>
+        <v>-0.028</v>
       </c>
       <c r="E17" s="24" t="n">
+        <v>-0.047</v>
+      </c>
+      <c r="F17" s="24" t="n">
+        <v>-0.022</v>
+      </c>
+      <c r="G17" s="24" t="n">
+        <v>0.08400000000000001</v>
+      </c>
+      <c r="H17" s="24" t="n">
+        <v>0.392</v>
+      </c>
+      <c r="I17" s="24" t="n">
+        <v>-0.429</v>
+      </c>
+      <c r="J17" s="24" t="n">
         <v>0.051</v>
       </c>
-      <c r="F17" s="24" t="n">
-        <v>-0.005</v>
-      </c>
-      <c r="G17" s="24" t="n">
-        <v>0.037</v>
-      </c>
-      <c r="H17" s="24" t="n">
-        <v>0.421</v>
-      </c>
-      <c r="I17" s="24" t="n">
-        <v>-0.459</v>
-      </c>
-      <c r="J17" s="24" t="n">
-        <v>-0.033</v>
-      </c>
       <c r="K17" s="24" t="n">
-        <v>0.022</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="L17" s="24" t="n">
-        <v>-0.496</v>
+        <v>-0.5620000000000001</v>
       </c>
       <c r="M17" s="24" t="n">
-        <v>0.552</v>
+        <v>0.527</v>
       </c>
       <c r="N17" s="24" t="n">
-        <v>0.082</v>
+        <v>-0.026</v>
       </c>
       <c r="O17" s="24" t="n">
-        <v>-0.376</v>
+        <v>-0.456</v>
       </c>
       <c r="P17" s="24" t="n">
-        <v>-0.296</v>
+        <v>-0.331</v>
       </c>
       <c r="Q17" s="24" t="inlineStr">
         <is>

--- a/results/Model3.xlsx
+++ b/results/Model3.xlsx
@@ -2108,10 +2108,10 @@
         </is>
       </c>
       <c r="B4" s="24" t="n">
-        <v>0.551</v>
+        <v>0.553</v>
       </c>
       <c r="C4" s="24" t="n">
-        <v>0.498</v>
+        <v>0.487</v>
       </c>
       <c r="D4" s="24" t="inlineStr">
         <is>
@@ -2139,13 +2139,13 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>30.74</v>
+        <v>30.869</v>
       </c>
       <c r="C5" s="24" t="n">
         <v>4.596</v>
       </c>
       <c r="D5" s="24" t="n">
-        <v>0.04</v>
+        <v>0.028</v>
       </c>
       <c r="E5" s="24" t="inlineStr">
         <is>
@@ -2172,16 +2172,16 @@
         </is>
       </c>
       <c r="B6" s="24" t="n">
-        <v>2.305</v>
+        <v>2.332</v>
       </c>
       <c r="C6" s="24" t="n">
-        <v>1.458</v>
+        <v>1.466</v>
       </c>
       <c r="D6" s="24" t="n">
-        <v>0.006</v>
+        <v>0.01</v>
       </c>
       <c r="E6" s="24" t="n">
-        <v>0.184</v>
+        <v>0.18</v>
       </c>
       <c r="F6" s="24" t="inlineStr">
         <is>
@@ -2207,19 +2207,19 @@
         </is>
       </c>
       <c r="B7" s="24" t="n">
-        <v>3.307</v>
+        <v>3.337</v>
       </c>
       <c r="C7" s="24" t="n">
-        <v>1.081</v>
+        <v>1.071</v>
       </c>
       <c r="D7" s="24" t="n">
-        <v>0.063</v>
+        <v>0.06</v>
       </c>
       <c r="E7" s="24" t="n">
-        <v>-0.038</v>
+        <v>-0.037</v>
       </c>
       <c r="F7" s="24" t="n">
-        <v>-0.027</v>
+        <v>-0.032</v>
       </c>
       <c r="G7" s="24" t="inlineStr">
         <is>
@@ -2244,22 +2244,22 @@
         </is>
       </c>
       <c r="B8" s="24" t="n">
-        <v>4.062</v>
+        <v>4.102</v>
       </c>
       <c r="C8" s="24" t="n">
-        <v>0.91</v>
+        <v>0.903</v>
       </c>
       <c r="D8" s="24" t="n">
-        <v>-0.031</v>
+        <v>-0.038</v>
       </c>
       <c r="E8" s="24" t="n">
-        <v>-0.01</v>
+        <v>-0.001</v>
       </c>
       <c r="F8" s="24" t="n">
-        <v>0.099</v>
+        <v>0.097</v>
       </c>
       <c r="G8" s="24" t="n">
-        <v>-0.016</v>
+        <v>-0.011</v>
       </c>
       <c r="H8" s="23" t="inlineStr">
         <is>
@@ -2283,25 +2283,25 @@
         </is>
       </c>
       <c r="B9" s="24" t="n">
-        <v>4.916</v>
+        <v>4.954</v>
       </c>
       <c r="C9" s="24" t="n">
-        <v>0.957</v>
+        <v>0.9419999999999999</v>
       </c>
       <c r="D9" s="24" t="n">
-        <v>-0.027</v>
+        <v>-0.024</v>
       </c>
       <c r="E9" s="24" t="n">
-        <v>0.015</v>
+        <v>0.006</v>
       </c>
       <c r="F9" s="24" t="n">
-        <v>0</v>
+        <v>0.004</v>
       </c>
       <c r="G9" s="24" t="n">
-        <v>-0.095</v>
+        <v>-0.08799999999999999</v>
       </c>
       <c r="H9" s="24" t="n">
-        <v>-0.353</v>
+        <v>-0.343</v>
       </c>
       <c r="I9" s="24" t="inlineStr">
         <is>
@@ -2324,28 +2324,28 @@
         </is>
       </c>
       <c r="B10" s="24" t="n">
-        <v>3.456</v>
+        <v>3.455</v>
       </c>
       <c r="C10" s="24" t="n">
-        <v>0.918</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="D10" s="24" t="n">
-        <v>-0.08</v>
+        <v>-0.08799999999999999</v>
       </c>
       <c r="E10" s="24" t="n">
-        <v>-0.002</v>
+        <v>0.005</v>
       </c>
       <c r="F10" s="24" t="n">
-        <v>0.09</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="G10" s="24" t="n">
-        <v>-0.04</v>
+        <v>-0.051</v>
       </c>
       <c r="H10" s="24" t="n">
-        <v>0.003</v>
+        <v>-0.003</v>
       </c>
       <c r="I10" s="24" t="n">
-        <v>0.054</v>
+        <v>0.057</v>
       </c>
       <c r="J10" s="24" t="inlineStr">
         <is>
@@ -2367,31 +2367,31 @@
         </is>
       </c>
       <c r="B11" s="24" t="n">
-        <v>4.57</v>
+        <v>4.584</v>
       </c>
       <c r="C11" s="24" t="n">
-        <v>0.901</v>
+        <v>0.91</v>
       </c>
       <c r="D11" s="24" t="n">
-        <v>-0.065</v>
+        <v>-0.07099999999999999</v>
       </c>
       <c r="E11" s="24" t="n">
-        <v>-0.078</v>
+        <v>-0.07199999999999999</v>
       </c>
       <c r="F11" s="24" t="n">
-        <v>-0.08699999999999999</v>
+        <v>-0.095</v>
       </c>
       <c r="G11" s="24" t="n">
-        <v>-0.07099999999999999</v>
+        <v>-0.07199999999999999</v>
       </c>
       <c r="H11" s="24" t="n">
-        <v>-0.04</v>
+        <v>-0.046</v>
       </c>
       <c r="I11" s="24" t="n">
-        <v>-0.035</v>
+        <v>-0.044</v>
       </c>
       <c r="J11" s="24" t="n">
-        <v>-0.008</v>
+        <v>-0.002</v>
       </c>
       <c r="K11" s="24" t="inlineStr">
         <is>
@@ -2412,34 +2412,34 @@
         </is>
       </c>
       <c r="B12" s="24" t="n">
-        <v>4.51</v>
+        <v>4.525</v>
       </c>
       <c r="C12" s="24" t="n">
-        <v>1.234</v>
+        <v>1.21</v>
       </c>
       <c r="D12" s="24" t="n">
-        <v>-0.03</v>
+        <v>-0.037</v>
       </c>
       <c r="E12" s="24" t="n">
-        <v>0.002</v>
+        <v>0.015</v>
       </c>
       <c r="F12" s="24" t="n">
-        <v>-0.067</v>
+        <v>-0.07199999999999999</v>
       </c>
       <c r="G12" s="24" t="n">
-        <v>-0.045</v>
+        <v>-0.038</v>
       </c>
       <c r="H12" s="24" t="n">
-        <v>-0.535</v>
+        <v>-0.532</v>
       </c>
       <c r="I12" s="24" t="n">
-        <v>0.532</v>
+        <v>0.53</v>
       </c>
       <c r="J12" s="24" t="n">
-        <v>0.002</v>
+        <v>-0.005</v>
       </c>
       <c r="K12" s="24" t="n">
-        <v>-0.025</v>
+        <v>-0.036</v>
       </c>
       <c r="L12" s="24" t="inlineStr">
         <is>
@@ -2459,37 +2459,37 @@
         </is>
       </c>
       <c r="B13" s="24" t="n">
-        <v>3.046</v>
+        <v>3.039</v>
       </c>
       <c r="C13" s="24" t="n">
-        <v>1.217</v>
+        <v>1.243</v>
       </c>
       <c r="D13" s="24" t="n">
-        <v>0.019</v>
+        <v>0.01</v>
       </c>
       <c r="E13" s="24" t="n">
-        <v>-0.004</v>
+        <v>-0.011</v>
       </c>
       <c r="F13" s="24" t="n">
-        <v>-0.005</v>
+        <v>-0.007</v>
       </c>
       <c r="G13" s="24" t="n">
-        <v>0.046</v>
+        <v>0.051</v>
       </c>
       <c r="H13" s="24" t="n">
-        <v>0.545</v>
+        <v>0.539</v>
       </c>
       <c r="I13" s="24" t="n">
-        <v>-0.52</v>
+        <v>-0.522</v>
       </c>
       <c r="J13" s="24" t="n">
-        <v>0.041</v>
+        <v>0.039</v>
       </c>
       <c r="K13" s="24" t="n">
-        <v>-0.066</v>
+        <v>-0.077</v>
       </c>
       <c r="L13" s="24" t="n">
-        <v>-0.431</v>
+        <v>-0.43</v>
       </c>
       <c r="M13" s="24" t="inlineStr">
         <is>
@@ -2508,40 +2508,40 @@
         </is>
       </c>
       <c r="B14" s="24" t="n">
-        <v>4.372</v>
+        <v>4.412</v>
       </c>
       <c r="C14" s="24" t="n">
-        <v>0.647</v>
+        <v>0.631</v>
       </c>
       <c r="D14" s="24" t="n">
-        <v>0.007</v>
+        <v>0.016</v>
       </c>
       <c r="E14" s="24" t="n">
-        <v>-0</v>
+        <v>-0.01</v>
       </c>
       <c r="F14" s="24" t="n">
-        <v>-0.024</v>
+        <v>-0.033</v>
       </c>
       <c r="G14" s="24" t="n">
-        <v>-0.032</v>
+        <v>-0.038</v>
       </c>
       <c r="H14" s="24" t="n">
-        <v>0.061</v>
+        <v>0.062</v>
       </c>
       <c r="I14" s="24" t="n">
-        <v>-0.053</v>
+        <v>-0.04</v>
       </c>
       <c r="J14" s="24" t="n">
-        <v>-0.117</v>
+        <v>-0.106</v>
       </c>
       <c r="K14" s="24" t="n">
-        <v>-0.075</v>
+        <v>-0.081</v>
       </c>
       <c r="L14" s="24" t="n">
-        <v>-0</v>
+        <v>-0.01</v>
       </c>
       <c r="M14" s="24" t="n">
-        <v>0.061</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="N14" s="24" t="inlineStr">
         <is>
@@ -2559,43 +2559,43 @@
         </is>
       </c>
       <c r="B15" s="24" t="n">
-        <v>4.521</v>
+        <v>4.533</v>
       </c>
       <c r="C15" s="24" t="n">
-        <v>0.741</v>
+        <v>0.757</v>
       </c>
       <c r="D15" s="24" t="n">
-        <v>0.01</v>
+        <v>0.002</v>
       </c>
       <c r="E15" s="24" t="n">
-        <v>0.041</v>
+        <v>0.034</v>
       </c>
       <c r="F15" s="24" t="n">
-        <v>-0.024</v>
+        <v>-0.036</v>
       </c>
       <c r="G15" s="24" t="n">
-        <v>-0.082</v>
+        <v>-0.083</v>
       </c>
       <c r="H15" s="24" t="n">
-        <v>-0.417</v>
+        <v>-0.427</v>
       </c>
       <c r="I15" s="24" t="n">
-        <v>0.4</v>
+        <v>0.387</v>
       </c>
       <c r="J15" s="24" t="n">
-        <v>-0.064</v>
+        <v>-0.077</v>
       </c>
       <c r="K15" s="24" t="n">
-        <v>-0.005</v>
+        <v>-0.011</v>
       </c>
       <c r="L15" s="24" t="n">
-        <v>0.57</v>
+        <v>0.572</v>
       </c>
       <c r="M15" s="24" t="n">
-        <v>-0.592</v>
+        <v>-0.579</v>
       </c>
       <c r="N15" s="24" t="n">
-        <v>0.375</v>
+        <v>0.37</v>
       </c>
       <c r="O15" s="24" t="inlineStr">
         <is>

--- a/results/Model3.xlsx
+++ b/results/Model3.xlsx
@@ -2108,7 +2108,7 @@
         </is>
       </c>
       <c r="B4" s="24" t="n">
-        <v>0.553</v>
+        <v>0.545</v>
       </c>
       <c r="C4" s="24" t="n">
         <v>0.487</v>
@@ -2139,13 +2139,13 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>30.869</v>
+        <v>30.765</v>
       </c>
       <c r="C5" s="24" t="n">
-        <v>4.596</v>
+        <v>4.537</v>
       </c>
       <c r="D5" s="24" t="n">
-        <v>0.028</v>
+        <v>0.02</v>
       </c>
       <c r="E5" s="24" t="inlineStr">
         <is>
@@ -2172,16 +2172,16 @@
         </is>
       </c>
       <c r="B6" s="24" t="n">
-        <v>2.332</v>
+        <v>2.333</v>
       </c>
       <c r="C6" s="24" t="n">
-        <v>1.466</v>
+        <v>1.459</v>
       </c>
       <c r="D6" s="24" t="n">
-        <v>0.01</v>
+        <v>0.005</v>
       </c>
       <c r="E6" s="24" t="n">
-        <v>0.18</v>
+        <v>0.196</v>
       </c>
       <c r="F6" s="24" t="inlineStr">
         <is>
@@ -2207,19 +2207,19 @@
         </is>
       </c>
       <c r="B7" s="24" t="n">
-        <v>3.337</v>
+        <v>3.32</v>
       </c>
       <c r="C7" s="24" t="n">
-        <v>1.071</v>
+        <v>1.078</v>
       </c>
       <c r="D7" s="24" t="n">
-        <v>0.06</v>
+        <v>0.059</v>
       </c>
       <c r="E7" s="24" t="n">
-        <v>-0.037</v>
+        <v>-0.022</v>
       </c>
       <c r="F7" s="24" t="n">
-        <v>-0.032</v>
+        <v>-0.052</v>
       </c>
       <c r="G7" s="24" t="inlineStr">
         <is>
@@ -2244,22 +2244,22 @@
         </is>
       </c>
       <c r="B8" s="24" t="n">
-        <v>4.102</v>
+        <v>4.08</v>
       </c>
       <c r="C8" s="24" t="n">
-        <v>0.903</v>
+        <v>0.879</v>
       </c>
       <c r="D8" s="24" t="n">
-        <v>-0.038</v>
+        <v>-0.034</v>
       </c>
       <c r="E8" s="24" t="n">
-        <v>-0.001</v>
+        <v>0.006</v>
       </c>
       <c r="F8" s="24" t="n">
-        <v>0.097</v>
+        <v>0.075</v>
       </c>
       <c r="G8" s="24" t="n">
-        <v>-0.011</v>
+        <v>0.002</v>
       </c>
       <c r="H8" s="23" t="inlineStr">
         <is>
@@ -2283,25 +2283,25 @@
         </is>
       </c>
       <c r="B9" s="24" t="n">
-        <v>4.954</v>
+        <v>4.969</v>
       </c>
       <c r="C9" s="24" t="n">
-        <v>0.9419999999999999</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="D9" s="24" t="n">
-        <v>-0.024</v>
+        <v>-0.007</v>
       </c>
       <c r="E9" s="24" t="n">
-        <v>0.006</v>
+        <v>-0.003</v>
       </c>
       <c r="F9" s="24" t="n">
-        <v>0.004</v>
+        <v>0.012</v>
       </c>
       <c r="G9" s="24" t="n">
-        <v>-0.08799999999999999</v>
+        <v>-0.101</v>
       </c>
       <c r="H9" s="24" t="n">
-        <v>-0.343</v>
+        <v>-0.36</v>
       </c>
       <c r="I9" s="24" t="inlineStr">
         <is>
@@ -2324,28 +2324,28 @@
         </is>
       </c>
       <c r="B10" s="24" t="n">
-        <v>3.455</v>
+        <v>3.448</v>
       </c>
       <c r="C10" s="24" t="n">
-        <v>0.9409999999999999</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="D10" s="24" t="n">
-        <v>-0.08799999999999999</v>
+        <v>-0.093</v>
       </c>
       <c r="E10" s="24" t="n">
-        <v>0.005</v>
+        <v>0.016</v>
       </c>
       <c r="F10" s="24" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.033</v>
       </c>
       <c r="G10" s="24" t="n">
-        <v>-0.051</v>
+        <v>-0.047</v>
       </c>
       <c r="H10" s="24" t="n">
-        <v>-0.003</v>
+        <v>-0.025</v>
       </c>
       <c r="I10" s="24" t="n">
-        <v>0.057</v>
+        <v>0.078</v>
       </c>
       <c r="J10" s="24" t="inlineStr">
         <is>
@@ -2367,31 +2367,31 @@
         </is>
       </c>
       <c r="B11" s="24" t="n">
-        <v>4.584</v>
+        <v>4.606</v>
       </c>
       <c r="C11" s="24" t="n">
-        <v>0.91</v>
+        <v>0.88</v>
       </c>
       <c r="D11" s="24" t="n">
-        <v>-0.07099999999999999</v>
+        <v>-0.08799999999999999</v>
       </c>
       <c r="E11" s="24" t="n">
-        <v>-0.07199999999999999</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="F11" s="24" t="n">
-        <v>-0.095</v>
+        <v>-0.053</v>
       </c>
       <c r="G11" s="24" t="n">
-        <v>-0.07199999999999999</v>
+        <v>-0.101</v>
       </c>
       <c r="H11" s="24" t="n">
-        <v>-0.046</v>
+        <v>-0.049</v>
       </c>
       <c r="I11" s="24" t="n">
-        <v>-0.044</v>
+        <v>-0.031</v>
       </c>
       <c r="J11" s="24" t="n">
-        <v>-0.002</v>
+        <v>0.01</v>
       </c>
       <c r="K11" s="24" t="inlineStr">
         <is>
@@ -2412,34 +2412,34 @@
         </is>
       </c>
       <c r="B12" s="24" t="n">
-        <v>4.525</v>
+        <v>4.541</v>
       </c>
       <c r="C12" s="24" t="n">
-        <v>1.21</v>
+        <v>1.229</v>
       </c>
       <c r="D12" s="24" t="n">
-        <v>-0.037</v>
+        <v>-0.039</v>
       </c>
       <c r="E12" s="24" t="n">
-        <v>0.015</v>
+        <v>0.007</v>
       </c>
       <c r="F12" s="24" t="n">
-        <v>-0.07199999999999999</v>
+        <v>-0.039</v>
       </c>
       <c r="G12" s="24" t="n">
-        <v>-0.038</v>
+        <v>-0.048</v>
       </c>
       <c r="H12" s="24" t="n">
-        <v>-0.532</v>
+        <v>-0.509</v>
       </c>
       <c r="I12" s="24" t="n">
-        <v>0.53</v>
+        <v>0.534</v>
       </c>
       <c r="J12" s="24" t="n">
-        <v>-0.005</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="K12" s="24" t="n">
-        <v>-0.036</v>
+        <v>-0.053</v>
       </c>
       <c r="L12" s="24" t="inlineStr">
         <is>
@@ -2459,37 +2459,37 @@
         </is>
       </c>
       <c r="B13" s="24" t="n">
-        <v>3.039</v>
+        <v>3.028</v>
       </c>
       <c r="C13" s="24" t="n">
-        <v>1.243</v>
+        <v>1.231</v>
       </c>
       <c r="D13" s="24" t="n">
-        <v>0.01</v>
+        <v>0.001</v>
       </c>
       <c r="E13" s="24" t="n">
-        <v>-0.011</v>
+        <v>-0.012</v>
       </c>
       <c r="F13" s="24" t="n">
-        <v>-0.007</v>
+        <v>-0.022</v>
       </c>
       <c r="G13" s="24" t="n">
-        <v>0.051</v>
+        <v>0.065</v>
       </c>
       <c r="H13" s="24" t="n">
-        <v>0.539</v>
+        <v>0.537</v>
       </c>
       <c r="I13" s="24" t="n">
-        <v>-0.522</v>
+        <v>-0.533</v>
       </c>
       <c r="J13" s="24" t="n">
-        <v>0.039</v>
+        <v>0.008</v>
       </c>
       <c r="K13" s="24" t="n">
-        <v>-0.077</v>
+        <v>-0.07199999999999999</v>
       </c>
       <c r="L13" s="24" t="n">
-        <v>-0.43</v>
+        <v>-0.45</v>
       </c>
       <c r="M13" s="24" t="inlineStr">
         <is>
@@ -2511,37 +2511,37 @@
         <v>4.412</v>
       </c>
       <c r="C14" s="24" t="n">
-        <v>0.631</v>
+        <v>0.638</v>
       </c>
       <c r="D14" s="24" t="n">
-        <v>0.016</v>
+        <v>0.054</v>
       </c>
       <c r="E14" s="24" t="n">
-        <v>-0.01</v>
+        <v>-0.029</v>
       </c>
       <c r="F14" s="24" t="n">
-        <v>-0.033</v>
+        <v>-0.046</v>
       </c>
       <c r="G14" s="24" t="n">
-        <v>-0.038</v>
+        <v>-0.032</v>
       </c>
       <c r="H14" s="24" t="n">
-        <v>0.062</v>
+        <v>0.065</v>
       </c>
       <c r="I14" s="24" t="n">
-        <v>-0.04</v>
+        <v>-0.041</v>
       </c>
       <c r="J14" s="24" t="n">
-        <v>-0.106</v>
+        <v>-0.092</v>
       </c>
       <c r="K14" s="24" t="n">
-        <v>-0.081</v>
+        <v>-0.082</v>
       </c>
       <c r="L14" s="24" t="n">
-        <v>-0.01</v>
+        <v>-0.023</v>
       </c>
       <c r="M14" s="24" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.078</v>
       </c>
       <c r="N14" s="24" t="inlineStr">
         <is>
@@ -2559,43 +2559,43 @@
         </is>
       </c>
       <c r="B15" s="24" t="n">
-        <v>4.533</v>
+        <v>4.527</v>
       </c>
       <c r="C15" s="24" t="n">
-        <v>0.757</v>
+        <v>0.799</v>
       </c>
       <c r="D15" s="24" t="n">
-        <v>0.002</v>
+        <v>-0.022</v>
       </c>
       <c r="E15" s="24" t="n">
-        <v>0.034</v>
+        <v>-0.008</v>
       </c>
       <c r="F15" s="24" t="n">
-        <v>-0.036</v>
+        <v>0.035</v>
       </c>
       <c r="G15" s="24" t="n">
-        <v>-0.083</v>
+        <v>-0.08500000000000001</v>
       </c>
       <c r="H15" s="24" t="n">
-        <v>-0.427</v>
+        <v>-0.446</v>
       </c>
       <c r="I15" s="24" t="n">
-        <v>0.387</v>
+        <v>0.444</v>
       </c>
       <c r="J15" s="24" t="n">
-        <v>-0.077</v>
+        <v>-0.043</v>
       </c>
       <c r="K15" s="24" t="n">
-        <v>-0.011</v>
+        <v>-0.053</v>
       </c>
       <c r="L15" s="24" t="n">
-        <v>0.572</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="M15" s="24" t="n">
-        <v>-0.579</v>
+        <v>-0.578</v>
       </c>
       <c r="N15" s="24" t="n">
-        <v>0.37</v>
+        <v>0.286</v>
       </c>
       <c r="O15" s="24" t="inlineStr">
         <is>
@@ -2612,46 +2612,46 @@
         </is>
       </c>
       <c r="B16" s="24" t="n">
-        <v>5.007</v>
+        <v>4.996</v>
       </c>
       <c r="C16" s="24" t="n">
-        <v>0.989</v>
+        <v>1.032</v>
       </c>
       <c r="D16" s="24" t="n">
-        <v>0.032</v>
+        <v>-0.044</v>
       </c>
       <c r="E16" s="24" t="n">
-        <v>-0.073</v>
+        <v>-0.034</v>
       </c>
       <c r="F16" s="24" t="n">
-        <v>-0.081</v>
+        <v>-0.032</v>
       </c>
       <c r="G16" s="24" t="n">
-        <v>-0.019</v>
+        <v>-0.07199999999999999</v>
       </c>
       <c r="H16" s="24" t="n">
-        <v>-0.352</v>
+        <v>-0.35</v>
       </c>
       <c r="I16" s="24" t="n">
-        <v>0.302</v>
+        <v>0.377</v>
       </c>
       <c r="J16" s="24" t="n">
-        <v>-0.061</v>
+        <v>-0.018</v>
       </c>
       <c r="K16" s="24" t="n">
         <v>0.038</v>
       </c>
       <c r="L16" s="24" t="n">
-        <v>0.414</v>
+        <v>0.547</v>
       </c>
       <c r="M16" s="24" t="n">
-        <v>-0.502</v>
+        <v>-0.507</v>
       </c>
       <c r="N16" s="24" t="n">
-        <v>-0.083</v>
+        <v>-0.031</v>
       </c>
       <c r="O16" s="24" t="n">
-        <v>0.36</v>
+        <v>0.468</v>
       </c>
       <c r="P16" s="24" t="inlineStr">
         <is>
@@ -2667,49 +2667,49 @@
         </is>
       </c>
       <c r="B17" s="24" t="n">
-        <v>2.659</v>
+        <v>2.604</v>
       </c>
       <c r="C17" s="24" t="n">
-        <v>1.128</v>
+        <v>1.076</v>
       </c>
       <c r="D17" s="24" t="n">
-        <v>-0.028</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="E17" s="24" t="n">
-        <v>-0.047</v>
+        <v>-0.002</v>
       </c>
       <c r="F17" s="24" t="n">
-        <v>-0.022</v>
+        <v>-0.04</v>
       </c>
       <c r="G17" s="24" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.007</v>
       </c>
       <c r="H17" s="24" t="n">
-        <v>0.392</v>
+        <v>0.445</v>
       </c>
       <c r="I17" s="24" t="n">
-        <v>-0.429</v>
+        <v>-0.418</v>
       </c>
       <c r="J17" s="24" t="n">
-        <v>0.051</v>
+        <v>-0.058</v>
       </c>
       <c r="K17" s="24" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.005</v>
       </c>
       <c r="L17" s="24" t="n">
-        <v>-0.5620000000000001</v>
+        <v>-0.554</v>
       </c>
       <c r="M17" s="24" t="n">
-        <v>0.527</v>
+        <v>0.552</v>
       </c>
       <c r="N17" s="24" t="n">
-        <v>-0.026</v>
+        <v>0.06</v>
       </c>
       <c r="O17" s="24" t="n">
-        <v>-0.456</v>
+        <v>-0.485</v>
       </c>
       <c r="P17" s="24" t="n">
-        <v>-0.331</v>
+        <v>-0.478</v>
       </c>
       <c r="Q17" s="24" t="inlineStr">
         <is>

--- a/results/Model3.xlsx
+++ b/results/Model3.xlsx
@@ -2108,10 +2108,10 @@
         </is>
       </c>
       <c r="B4" s="24" t="n">
-        <v>0.545</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="C4" s="24" t="n">
-        <v>0.487</v>
+        <v>0.486</v>
       </c>
       <c r="D4" s="24" t="inlineStr">
         <is>
@@ -2139,13 +2139,13 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>30.765</v>
+        <v>30.752</v>
       </c>
       <c r="C5" s="24" t="n">
-        <v>4.537</v>
+        <v>4.613</v>
       </c>
       <c r="D5" s="24" t="n">
-        <v>0.02</v>
+        <v>0.004</v>
       </c>
       <c r="E5" s="24" t="inlineStr">
         <is>
@@ -2172,16 +2172,16 @@
         </is>
       </c>
       <c r="B6" s="24" t="n">
-        <v>2.333</v>
+        <v>2.341</v>
       </c>
       <c r="C6" s="24" t="n">
-        <v>1.459</v>
+        <v>1.475</v>
       </c>
       <c r="D6" s="24" t="n">
-        <v>0.005</v>
+        <v>-0.043</v>
       </c>
       <c r="E6" s="24" t="n">
-        <v>0.196</v>
+        <v>0.216</v>
       </c>
       <c r="F6" s="24" t="inlineStr">
         <is>
@@ -2207,19 +2207,19 @@
         </is>
       </c>
       <c r="B7" s="24" t="n">
-        <v>3.32</v>
+        <v>3.33</v>
       </c>
       <c r="C7" s="24" t="n">
-        <v>1.078</v>
+        <v>1.075</v>
       </c>
       <c r="D7" s="24" t="n">
-        <v>0.059</v>
+        <v>0.079</v>
       </c>
       <c r="E7" s="24" t="n">
-        <v>-0.022</v>
+        <v>0.004</v>
       </c>
       <c r="F7" s="24" t="n">
-        <v>-0.052</v>
+        <v>-0.06</v>
       </c>
       <c r="G7" s="24" t="inlineStr">
         <is>
@@ -2244,22 +2244,22 @@
         </is>
       </c>
       <c r="B8" s="24" t="n">
-        <v>4.08</v>
+        <v>4.128</v>
       </c>
       <c r="C8" s="24" t="n">
-        <v>0.879</v>
+        <v>0.878</v>
       </c>
       <c r="D8" s="24" t="n">
-        <v>-0.034</v>
+        <v>-0.055</v>
       </c>
       <c r="E8" s="24" t="n">
-        <v>0.006</v>
+        <v>-0.003</v>
       </c>
       <c r="F8" s="24" t="n">
-        <v>0.075</v>
+        <v>0.077</v>
       </c>
       <c r="G8" s="24" t="n">
-        <v>0.002</v>
+        <v>0.01</v>
       </c>
       <c r="H8" s="23" t="inlineStr">
         <is>
@@ -2283,25 +2283,25 @@
         </is>
       </c>
       <c r="B9" s="24" t="n">
-        <v>4.969</v>
+        <v>4.929</v>
       </c>
       <c r="C9" s="24" t="n">
-        <v>0.9409999999999999</v>
+        <v>0.95</v>
       </c>
       <c r="D9" s="24" t="n">
-        <v>-0.007</v>
+        <v>-0.002</v>
       </c>
       <c r="E9" s="24" t="n">
-        <v>-0.003</v>
+        <v>-0.036</v>
       </c>
       <c r="F9" s="24" t="n">
-        <v>0.012</v>
+        <v>0.032</v>
       </c>
       <c r="G9" s="24" t="n">
-        <v>-0.101</v>
+        <v>-0.093</v>
       </c>
       <c r="H9" s="24" t="n">
-        <v>-0.36</v>
+        <v>-0.34</v>
       </c>
       <c r="I9" s="24" t="inlineStr">
         <is>
@@ -2324,28 +2324,28 @@
         </is>
       </c>
       <c r="B10" s="24" t="n">
-        <v>3.448</v>
+        <v>3.479</v>
       </c>
       <c r="C10" s="24" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.913</v>
       </c>
       <c r="D10" s="24" t="n">
-        <v>-0.093</v>
+        <v>-0.051</v>
       </c>
       <c r="E10" s="24" t="n">
-        <v>0.016</v>
+        <v>-0.029</v>
       </c>
       <c r="F10" s="24" t="n">
-        <v>0.033</v>
+        <v>0.102</v>
       </c>
       <c r="G10" s="24" t="n">
-        <v>-0.047</v>
+        <v>-0.057</v>
       </c>
       <c r="H10" s="24" t="n">
-        <v>-0.025</v>
+        <v>0</v>
       </c>
       <c r="I10" s="24" t="n">
-        <v>0.078</v>
+        <v>0.059</v>
       </c>
       <c r="J10" s="24" t="inlineStr">
         <is>
@@ -2367,31 +2367,31 @@
         </is>
       </c>
       <c r="B11" s="24" t="n">
-        <v>4.606</v>
+        <v>4.582</v>
       </c>
       <c r="C11" s="24" t="n">
-        <v>0.88</v>
+        <v>0.892</v>
       </c>
       <c r="D11" s="24" t="n">
-        <v>-0.08799999999999999</v>
+        <v>-0.078</v>
       </c>
       <c r="E11" s="24" t="n">
-        <v>-0.06900000000000001</v>
+        <v>-0.092</v>
       </c>
       <c r="F11" s="24" t="n">
-        <v>-0.053</v>
+        <v>-0.11</v>
       </c>
       <c r="G11" s="24" t="n">
-        <v>-0.101</v>
+        <v>-0.067</v>
       </c>
       <c r="H11" s="24" t="n">
-        <v>-0.049</v>
+        <v>-0.019</v>
       </c>
       <c r="I11" s="24" t="n">
-        <v>-0.031</v>
+        <v>-0.048</v>
       </c>
       <c r="J11" s="24" t="n">
-        <v>0.01</v>
+        <v>-0.037</v>
       </c>
       <c r="K11" s="24" t="inlineStr">
         <is>
@@ -2412,34 +2412,34 @@
         </is>
       </c>
       <c r="B12" s="24" t="n">
-        <v>4.541</v>
+        <v>4.46</v>
       </c>
       <c r="C12" s="24" t="n">
-        <v>1.229</v>
+        <v>1.207</v>
       </c>
       <c r="D12" s="24" t="n">
-        <v>-0.039</v>
+        <v>-0.045</v>
       </c>
       <c r="E12" s="24" t="n">
-        <v>0.007</v>
+        <v>-0.022</v>
       </c>
       <c r="F12" s="24" t="n">
-        <v>-0.039</v>
+        <v>-0.033</v>
       </c>
       <c r="G12" s="24" t="n">
-        <v>-0.048</v>
+        <v>-0.05</v>
       </c>
       <c r="H12" s="24" t="n">
-        <v>-0.509</v>
+        <v>-0.531</v>
       </c>
       <c r="I12" s="24" t="n">
-        <v>0.534</v>
+        <v>0.542</v>
       </c>
       <c r="J12" s="24" t="n">
-        <v>0.008999999999999999</v>
+        <v>-0.017</v>
       </c>
       <c r="K12" s="24" t="n">
-        <v>-0.053</v>
+        <v>-0.032</v>
       </c>
       <c r="L12" s="24" t="inlineStr">
         <is>
@@ -2459,37 +2459,37 @@
         </is>
       </c>
       <c r="B13" s="24" t="n">
-        <v>3.028</v>
+        <v>3.061</v>
       </c>
       <c r="C13" s="24" t="n">
-        <v>1.231</v>
+        <v>1.197</v>
       </c>
       <c r="D13" s="24" t="n">
-        <v>0.001</v>
+        <v>0.008</v>
       </c>
       <c r="E13" s="24" t="n">
-        <v>-0.012</v>
+        <v>-0.029</v>
       </c>
       <c r="F13" s="24" t="n">
-        <v>-0.022</v>
+        <v>0.006</v>
       </c>
       <c r="G13" s="24" t="n">
-        <v>0.065</v>
+        <v>0.056</v>
       </c>
       <c r="H13" s="24" t="n">
-        <v>0.537</v>
+        <v>0.526</v>
       </c>
       <c r="I13" s="24" t="n">
-        <v>-0.533</v>
+        <v>-0.514</v>
       </c>
       <c r="J13" s="24" t="n">
-        <v>0.008</v>
+        <v>0.03</v>
       </c>
       <c r="K13" s="24" t="n">
-        <v>-0.07199999999999999</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="L13" s="24" t="n">
-        <v>-0.45</v>
+        <v>-0.466</v>
       </c>
       <c r="M13" s="24" t="inlineStr">
         <is>
@@ -2508,40 +2508,40 @@
         </is>
       </c>
       <c r="B14" s="24" t="n">
-        <v>4.412</v>
+        <v>4.432</v>
       </c>
       <c r="C14" s="24" t="n">
-        <v>0.638</v>
+        <v>0.623</v>
       </c>
       <c r="D14" s="24" t="n">
         <v>0.054</v>
       </c>
       <c r="E14" s="24" t="n">
-        <v>-0.029</v>
+        <v>-0.026</v>
       </c>
       <c r="F14" s="24" t="n">
-        <v>-0.046</v>
+        <v>-0.011</v>
       </c>
       <c r="G14" s="24" t="n">
-        <v>-0.032</v>
+        <v>-0.023</v>
       </c>
       <c r="H14" s="24" t="n">
-        <v>0.065</v>
+        <v>0.054</v>
       </c>
       <c r="I14" s="24" t="n">
-        <v>-0.041</v>
+        <v>-0.053</v>
       </c>
       <c r="J14" s="24" t="n">
-        <v>-0.092</v>
+        <v>-0.107</v>
       </c>
       <c r="K14" s="24" t="n">
-        <v>-0.082</v>
+        <v>-0.074</v>
       </c>
       <c r="L14" s="24" t="n">
-        <v>-0.023</v>
+        <v>-0.04</v>
       </c>
       <c r="M14" s="24" t="n">
-        <v>0.078</v>
+        <v>0.053</v>
       </c>
       <c r="N14" s="24" t="inlineStr">
         <is>
@@ -2559,43 +2559,43 @@
         </is>
       </c>
       <c r="B15" s="24" t="n">
-        <v>4.527</v>
+        <v>4.532</v>
       </c>
       <c r="C15" s="24" t="n">
-        <v>0.799</v>
+        <v>0.795</v>
       </c>
       <c r="D15" s="24" t="n">
-        <v>-0.022</v>
+        <v>-0.033</v>
       </c>
       <c r="E15" s="24" t="n">
-        <v>-0.008</v>
+        <v>-0.007</v>
       </c>
       <c r="F15" s="24" t="n">
-        <v>0.035</v>
+        <v>-0.005</v>
       </c>
       <c r="G15" s="24" t="n">
-        <v>-0.08500000000000001</v>
+        <v>-0.092</v>
       </c>
       <c r="H15" s="24" t="n">
-        <v>-0.446</v>
+        <v>-0.455</v>
       </c>
       <c r="I15" s="24" t="n">
-        <v>0.444</v>
+        <v>0.445</v>
       </c>
       <c r="J15" s="24" t="n">
-        <v>-0.043</v>
+        <v>-0.07099999999999999</v>
       </c>
       <c r="K15" s="24" t="n">
-        <v>-0.053</v>
+        <v>-0.023</v>
       </c>
       <c r="L15" s="24" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.617</v>
       </c>
       <c r="M15" s="24" t="n">
-        <v>-0.578</v>
+        <v>-0.596</v>
       </c>
       <c r="N15" s="24" t="n">
-        <v>0.286</v>
+        <v>0.351</v>
       </c>
       <c r="O15" s="24" t="inlineStr">
         <is>
@@ -2612,46 +2612,46 @@
         </is>
       </c>
       <c r="B16" s="24" t="n">
-        <v>4.996</v>
+        <v>4.973</v>
       </c>
       <c r="C16" s="24" t="n">
-        <v>1.032</v>
+        <v>1.115</v>
       </c>
       <c r="D16" s="24" t="n">
-        <v>-0.044</v>
+        <v>-0.045</v>
       </c>
       <c r="E16" s="24" t="n">
-        <v>-0.034</v>
+        <v>0.05</v>
       </c>
       <c r="F16" s="24" t="n">
-        <v>-0.032</v>
+        <v>0.112</v>
       </c>
       <c r="G16" s="24" t="n">
-        <v>-0.07199999999999999</v>
+        <v>-0.05</v>
       </c>
       <c r="H16" s="24" t="n">
-        <v>-0.35</v>
+        <v>-0.423</v>
       </c>
       <c r="I16" s="24" t="n">
-        <v>0.377</v>
+        <v>0.389</v>
       </c>
       <c r="J16" s="24" t="n">
-        <v>-0.018</v>
+        <v>0.051</v>
       </c>
       <c r="K16" s="24" t="n">
-        <v>0.038</v>
+        <v>-0.013</v>
       </c>
       <c r="L16" s="24" t="n">
-        <v>0.547</v>
+        <v>0.486</v>
       </c>
       <c r="M16" s="24" t="n">
-        <v>-0.507</v>
+        <v>-0.5669999999999999</v>
       </c>
       <c r="N16" s="24" t="n">
-        <v>-0.031</v>
+        <v>-0.043</v>
       </c>
       <c r="O16" s="24" t="n">
-        <v>0.468</v>
+        <v>0.372</v>
       </c>
       <c r="P16" s="24" t="inlineStr">
         <is>
@@ -2667,49 +2667,49 @@
         </is>
       </c>
       <c r="B17" s="24" t="n">
-        <v>2.604</v>
+        <v>2.663</v>
       </c>
       <c r="C17" s="24" t="n">
-        <v>1.076</v>
+        <v>1.139</v>
       </c>
       <c r="D17" s="24" t="n">
-        <v>0.008999999999999999</v>
+        <v>-0.008</v>
       </c>
       <c r="E17" s="24" t="n">
-        <v>-0.002</v>
+        <v>-0.027</v>
       </c>
       <c r="F17" s="24" t="n">
-        <v>-0.04</v>
+        <v>0.028</v>
       </c>
       <c r="G17" s="24" t="n">
-        <v>0.007</v>
+        <v>0.032</v>
       </c>
       <c r="H17" s="24" t="n">
-        <v>0.445</v>
+        <v>0.383</v>
       </c>
       <c r="I17" s="24" t="n">
-        <v>-0.418</v>
+        <v>-0.375</v>
       </c>
       <c r="J17" s="24" t="n">
-        <v>-0.058</v>
+        <v>-0.039</v>
       </c>
       <c r="K17" s="24" t="n">
-        <v>0.005</v>
+        <v>-0.016</v>
       </c>
       <c r="L17" s="24" t="n">
-        <v>-0.554</v>
+        <v>-0.498</v>
       </c>
       <c r="M17" s="24" t="n">
-        <v>0.552</v>
+        <v>0.587</v>
       </c>
       <c r="N17" s="24" t="n">
-        <v>0.06</v>
+        <v>-0.024</v>
       </c>
       <c r="O17" s="24" t="n">
-        <v>-0.485</v>
+        <v>-0.433</v>
       </c>
       <c r="P17" s="24" t="n">
-        <v>-0.478</v>
+        <v>-0.4</v>
       </c>
       <c r="Q17" s="24" t="inlineStr">
         <is>

--- a/results/Model3.xlsx
+++ b/results/Model3.xlsx
@@ -1608,22 +1608,22 @@
         </is>
       </c>
       <c r="B3" s="35" t="n">
-        <v>1893.4</v>
+        <v>1881.6</v>
       </c>
       <c r="C3" s="35" t="n">
-        <v>873</v>
+        <v>871</v>
       </c>
       <c r="D3" s="35" t="n">
-        <v>0.9429999999999999</v>
+        <v>0.945</v>
       </c>
       <c r="E3" s="35" t="n">
-        <v>0.9370000000000001</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="F3" s="35" t="n">
-        <v>0.045</v>
+        <v>0.044</v>
       </c>
       <c r="G3" s="35" t="n">
-        <v>0.041</v>
+        <v>0.04</v>
       </c>
       <c r="H3" s="35" t="n"/>
       <c r="I3" s="35" t="n"/>
@@ -1642,22 +1642,22 @@
         </is>
       </c>
       <c r="B4" s="35" t="n">
-        <v>1771.6</v>
+        <v>1758.4</v>
       </c>
       <c r="C4" s="35" t="n">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="D4" s="35" t="n">
-        <v>0.953</v>
+        <v>0.955</v>
       </c>
       <c r="E4" s="35" t="n">
-        <v>0.945</v>
+        <v>0.946</v>
       </c>
       <c r="F4" s="35" t="n">
-        <v>0.043</v>
+        <v>0.042</v>
       </c>
       <c r="G4" s="35" t="n">
-        <v>0.039</v>
+        <v>0.038</v>
       </c>
       <c r="H4" s="35" t="n">
         <v>0.01</v>

--- a/results/Model3.xlsx
+++ b/results/Model3.xlsx
@@ -2180,8 +2180,10 @@
       <c r="D6" s="24" t="n">
         <v>-0.043</v>
       </c>
-      <c r="E6" s="24" t="n">
-        <v>0.216</v>
+      <c r="E6" s="24" t="inlineStr">
+        <is>
+          <t>0.216***</t>
+        </is>
       </c>
       <c r="F6" s="24" t="inlineStr">
         <is>
@@ -2300,8 +2302,10 @@
       <c r="G9" s="24" t="n">
         <v>-0.093</v>
       </c>
-      <c r="H9" s="24" t="n">
-        <v>-0.34</v>
+      <c r="H9" s="24" t="inlineStr">
+        <is>
+          <t>-0.34***</t>
+        </is>
       </c>
       <c r="I9" s="24" t="inlineStr">
         <is>
@@ -2378,8 +2382,10 @@
       <c r="E11" s="24" t="n">
         <v>-0.092</v>
       </c>
-      <c r="F11" s="24" t="n">
-        <v>-0.11</v>
+      <c r="F11" s="24" t="inlineStr">
+        <is>
+          <t>-0.11*</t>
+        </is>
       </c>
       <c r="G11" s="24" t="n">
         <v>-0.067</v>
@@ -2429,11 +2435,15 @@
       <c r="G12" s="24" t="n">
         <v>-0.05</v>
       </c>
-      <c r="H12" s="24" t="n">
-        <v>-0.531</v>
-      </c>
-      <c r="I12" s="24" t="n">
-        <v>0.542</v>
+      <c r="H12" s="24" t="inlineStr">
+        <is>
+          <t>-0.531***</t>
+        </is>
+      </c>
+      <c r="I12" s="24" t="inlineStr">
+        <is>
+          <t>0.542***</t>
+        </is>
       </c>
       <c r="J12" s="24" t="n">
         <v>-0.017</v>
@@ -2476,11 +2486,15 @@
       <c r="G13" s="24" t="n">
         <v>0.056</v>
       </c>
-      <c r="H13" s="24" t="n">
-        <v>0.526</v>
-      </c>
-      <c r="I13" s="24" t="n">
-        <v>-0.514</v>
+      <c r="H13" s="24" t="inlineStr">
+        <is>
+          <t>0.526***</t>
+        </is>
+      </c>
+      <c r="I13" s="24" t="inlineStr">
+        <is>
+          <t>-0.514***</t>
+        </is>
       </c>
       <c r="J13" s="24" t="n">
         <v>0.03</v>
@@ -2488,8 +2502,10 @@
       <c r="K13" s="24" t="n">
         <v>-0.07000000000000001</v>
       </c>
-      <c r="L13" s="24" t="n">
-        <v>-0.466</v>
+      <c r="L13" s="24" t="inlineStr">
+        <is>
+          <t>-0.466***</t>
+        </is>
       </c>
       <c r="M13" s="24" t="inlineStr">
         <is>
@@ -2531,8 +2547,10 @@
       <c r="I14" s="24" t="n">
         <v>-0.053</v>
       </c>
-      <c r="J14" s="24" t="n">
-        <v>-0.107</v>
+      <c r="J14" s="24" t="inlineStr">
+        <is>
+          <t>-0.107*</t>
+        </is>
       </c>
       <c r="K14" s="24" t="n">
         <v>-0.074</v>
@@ -2576,11 +2594,15 @@
       <c r="G15" s="24" t="n">
         <v>-0.092</v>
       </c>
-      <c r="H15" s="24" t="n">
-        <v>-0.455</v>
-      </c>
-      <c r="I15" s="24" t="n">
-        <v>0.445</v>
+      <c r="H15" s="24" t="inlineStr">
+        <is>
+          <t>-0.455***</t>
+        </is>
+      </c>
+      <c r="I15" s="24" t="inlineStr">
+        <is>
+          <t>0.445***</t>
+        </is>
       </c>
       <c r="J15" s="24" t="n">
         <v>-0.07099999999999999</v>
@@ -2588,14 +2610,20 @@
       <c r="K15" s="24" t="n">
         <v>-0.023</v>
       </c>
-      <c r="L15" s="24" t="n">
-        <v>0.617</v>
-      </c>
-      <c r="M15" s="24" t="n">
-        <v>-0.596</v>
-      </c>
-      <c r="N15" s="24" t="n">
-        <v>0.351</v>
+      <c r="L15" s="24" t="inlineStr">
+        <is>
+          <t>0.617***</t>
+        </is>
+      </c>
+      <c r="M15" s="24" t="inlineStr">
+        <is>
+          <t>-0.596***</t>
+        </is>
+      </c>
+      <c r="N15" s="24" t="inlineStr">
+        <is>
+          <t>0.351***</t>
+        </is>
       </c>
       <c r="O15" s="24" t="inlineStr">
         <is>
@@ -2623,17 +2651,23 @@
       <c r="E16" s="24" t="n">
         <v>0.05</v>
       </c>
-      <c r="F16" s="24" t="n">
-        <v>0.112</v>
+      <c r="F16" s="24" t="inlineStr">
+        <is>
+          <t>0.112*</t>
+        </is>
       </c>
       <c r="G16" s="24" t="n">
         <v>-0.05</v>
       </c>
-      <c r="H16" s="24" t="n">
-        <v>-0.423</v>
-      </c>
-      <c r="I16" s="24" t="n">
-        <v>0.389</v>
+      <c r="H16" s="24" t="inlineStr">
+        <is>
+          <t>-0.423***</t>
+        </is>
+      </c>
+      <c r="I16" s="24" t="inlineStr">
+        <is>
+          <t>0.389***</t>
+        </is>
       </c>
       <c r="J16" s="24" t="n">
         <v>0.051</v>
@@ -2641,17 +2675,23 @@
       <c r="K16" s="24" t="n">
         <v>-0.013</v>
       </c>
-      <c r="L16" s="24" t="n">
-        <v>0.486</v>
-      </c>
-      <c r="M16" s="24" t="n">
-        <v>-0.5669999999999999</v>
+      <c r="L16" s="24" t="inlineStr">
+        <is>
+          <t>0.486***</t>
+        </is>
+      </c>
+      <c r="M16" s="24" t="inlineStr">
+        <is>
+          <t>-0.567***</t>
+        </is>
       </c>
       <c r="N16" s="24" t="n">
         <v>-0.043</v>
       </c>
-      <c r="O16" s="24" t="n">
-        <v>0.372</v>
+      <c r="O16" s="24" t="inlineStr">
+        <is>
+          <t>0.372***</t>
+        </is>
       </c>
       <c r="P16" s="24" t="inlineStr">
         <is>
@@ -2684,11 +2724,15 @@
       <c r="G17" s="24" t="n">
         <v>0.032</v>
       </c>
-      <c r="H17" s="24" t="n">
-        <v>0.383</v>
-      </c>
-      <c r="I17" s="24" t="n">
-        <v>-0.375</v>
+      <c r="H17" s="24" t="inlineStr">
+        <is>
+          <t>0.383***</t>
+        </is>
+      </c>
+      <c r="I17" s="24" t="inlineStr">
+        <is>
+          <t>-0.375***</t>
+        </is>
       </c>
       <c r="J17" s="24" t="n">
         <v>-0.039</v>
@@ -2696,20 +2740,28 @@
       <c r="K17" s="24" t="n">
         <v>-0.016</v>
       </c>
-      <c r="L17" s="24" t="n">
-        <v>-0.498</v>
-      </c>
-      <c r="M17" s="24" t="n">
-        <v>0.587</v>
+      <c r="L17" s="24" t="inlineStr">
+        <is>
+          <t>-0.498***</t>
+        </is>
+      </c>
+      <c r="M17" s="24" t="inlineStr">
+        <is>
+          <t>0.587***</t>
+        </is>
       </c>
       <c r="N17" s="24" t="n">
         <v>-0.024</v>
       </c>
-      <c r="O17" s="24" t="n">
-        <v>-0.433</v>
-      </c>
-      <c r="P17" s="24" t="n">
-        <v>-0.4</v>
+      <c r="O17" s="24" t="inlineStr">
+        <is>
+          <t>-0.433***</t>
+        </is>
+      </c>
+      <c r="P17" s="24" t="inlineStr">
+        <is>
+          <t>-0.4***</t>
+        </is>
       </c>
       <c r="Q17" s="24" t="inlineStr">
         <is>
@@ -2920,44 +2972,58 @@
           <t>Intercept</t>
         </is>
       </c>
-      <c r="B6" s="24" t="n">
-        <v>3.793</v>
+      <c r="B6" s="24" t="inlineStr">
+        <is>
+          <t>3.793***</t>
+        </is>
       </c>
       <c r="C6" s="24" t="n">
         <v>0.092</v>
       </c>
-      <c r="D6" s="24" t="n">
-        <v>3.793</v>
+      <c r="D6" s="24" t="inlineStr">
+        <is>
+          <t>3.793***</t>
+        </is>
       </c>
       <c r="E6" s="24" t="n">
         <v>0.092</v>
       </c>
-      <c r="F6" s="24" t="n">
-        <v>3.793</v>
+      <c r="F6" s="24" t="inlineStr">
+        <is>
+          <t>3.793***</t>
+        </is>
       </c>
       <c r="G6" s="24" t="n">
         <v>0.092</v>
       </c>
-      <c r="H6" s="24" t="n">
-        <v>3.793</v>
+      <c r="H6" s="24" t="inlineStr">
+        <is>
+          <t>3.793***</t>
+        </is>
       </c>
       <c r="I6" s="24" t="n">
         <v>0.092</v>
       </c>
-      <c r="J6" s="24" t="n">
-        <v>3.793</v>
+      <c r="J6" s="24" t="inlineStr">
+        <is>
+          <t>3.793***</t>
+        </is>
       </c>
       <c r="K6" s="24" t="n">
         <v>0.092</v>
       </c>
-      <c r="L6" s="24" t="n">
-        <v>3.793</v>
+      <c r="L6" s="24" t="inlineStr">
+        <is>
+          <t>3.793***</t>
+        </is>
       </c>
       <c r="M6" s="24" t="n">
         <v>0.092</v>
       </c>
-      <c r="N6" s="24" t="n">
-        <v>3.793</v>
+      <c r="N6" s="24" t="inlineStr">
+        <is>
+          <t>3.793***</t>
+        </is>
       </c>
       <c r="O6" s="24" t="n">
         <v>0.092</v>
@@ -3137,44 +3203,58 @@
           <t xml:space="preserve">Interaction frequency with leader </t>
         </is>
       </c>
-      <c r="B11" s="24" t="n">
-        <v>0.091</v>
+      <c r="B11" s="24" t="inlineStr">
+        <is>
+          <t>0.091**</t>
+        </is>
       </c>
       <c r="C11" s="24" t="n">
         <v>0.034</v>
       </c>
-      <c r="D11" s="24" t="n">
-        <v>0.091</v>
+      <c r="D11" s="24" t="inlineStr">
+        <is>
+          <t>0.091**</t>
+        </is>
       </c>
       <c r="E11" s="24" t="n">
         <v>0.034</v>
       </c>
-      <c r="F11" s="24" t="n">
-        <v>0.091</v>
+      <c r="F11" s="24" t="inlineStr">
+        <is>
+          <t>0.091**</t>
+        </is>
       </c>
       <c r="G11" s="24" t="n">
         <v>0.034</v>
       </c>
-      <c r="H11" s="24" t="n">
-        <v>0.091</v>
+      <c r="H11" s="24" t="inlineStr">
+        <is>
+          <t>0.091**</t>
+        </is>
       </c>
       <c r="I11" s="24" t="n">
         <v>0.034</v>
       </c>
-      <c r="J11" s="24" t="n">
-        <v>0.091</v>
+      <c r="J11" s="24" t="inlineStr">
+        <is>
+          <t>0.091**</t>
+        </is>
       </c>
       <c r="K11" s="24" t="n">
         <v>0.034</v>
       </c>
-      <c r="L11" s="24" t="n">
-        <v>0.091</v>
+      <c r="L11" s="24" t="inlineStr">
+        <is>
+          <t>0.091**</t>
+        </is>
       </c>
       <c r="M11" s="24" t="n">
         <v>0.034</v>
       </c>
-      <c r="N11" s="24" t="n">
-        <v>0.091</v>
+      <c r="N11" s="24" t="inlineStr">
+        <is>
+          <t>0.091**</t>
+        </is>
       </c>
       <c r="O11" s="24" t="n">
         <v>0.034</v>
@@ -3186,44 +3266,58 @@
           <t>Thriving (T1) baseline</t>
         </is>
       </c>
-      <c r="B12" s="24" t="n">
-        <v>0.428</v>
+      <c r="B12" s="24" t="inlineStr">
+        <is>
+          <t>0.428***</t>
+        </is>
       </c>
       <c r="C12" s="24" t="n">
         <v>0.047</v>
       </c>
-      <c r="D12" s="24" t="n">
-        <v>0.428</v>
+      <c r="D12" s="24" t="inlineStr">
+        <is>
+          <t>0.428***</t>
+        </is>
       </c>
       <c r="E12" s="24" t="n">
         <v>0.047</v>
       </c>
-      <c r="F12" s="24" t="n">
-        <v>0.428</v>
+      <c r="F12" s="24" t="inlineStr">
+        <is>
+          <t>0.428***</t>
+        </is>
       </c>
       <c r="G12" s="24" t="n">
         <v>0.047</v>
       </c>
-      <c r="H12" s="24" t="n">
-        <v>0.428</v>
+      <c r="H12" s="24" t="inlineStr">
+        <is>
+          <t>0.428***</t>
+        </is>
       </c>
       <c r="I12" s="24" t="n">
         <v>0.047</v>
       </c>
-      <c r="J12" s="24" t="n">
-        <v>0.428</v>
+      <c r="J12" s="24" t="inlineStr">
+        <is>
+          <t>0.428***</t>
+        </is>
       </c>
       <c r="K12" s="24" t="n">
         <v>0.047</v>
       </c>
-      <c r="L12" s="24" t="n">
-        <v>0.428</v>
+      <c r="L12" s="24" t="inlineStr">
+        <is>
+          <t>0.428***</t>
+        </is>
       </c>
       <c r="M12" s="24" t="n">
         <v>0.047</v>
       </c>
-      <c r="N12" s="24" t="n">
-        <v>0.428</v>
+      <c r="N12" s="24" t="inlineStr">
+        <is>
+          <t>0.428***</t>
+        </is>
       </c>
       <c r="O12" s="24" t="n">
         <v>0.047</v>
@@ -3256,44 +3350,58 @@
           <t>Autocratic leadership (T1)</t>
         </is>
       </c>
-      <c r="B14" s="24" t="n">
-        <v>-0.146</v>
+      <c r="B14" s="24" t="inlineStr">
+        <is>
+          <t>-0.146**</t>
+        </is>
       </c>
       <c r="C14" s="24" t="n">
         <v>0.051</v>
       </c>
-      <c r="D14" s="24" t="n">
-        <v>-0.144</v>
+      <c r="D14" s="24" t="inlineStr">
+        <is>
+          <t>-0.144**</t>
+        </is>
       </c>
       <c r="E14" s="24" t="n">
         <v>0.051</v>
       </c>
-      <c r="F14" s="24" t="n">
-        <v>0.321</v>
+      <c r="F14" s="24" t="inlineStr">
+        <is>
+          <t>0.321***</t>
+        </is>
       </c>
       <c r="G14" s="24" t="n">
         <v>0.057</v>
       </c>
-      <c r="H14" s="24" t="n">
-        <v>0.318</v>
+      <c r="H14" s="24" t="inlineStr">
+        <is>
+          <t>0.318***</t>
+        </is>
       </c>
       <c r="I14" s="24" t="n">
         <v>0.057</v>
       </c>
-      <c r="J14" s="24" t="n">
-        <v>-0.082</v>
+      <c r="J14" s="24" t="inlineStr">
+        <is>
+          <t>-0.082*</t>
+        </is>
       </c>
       <c r="K14" s="24" t="n">
         <v>0.041</v>
       </c>
-      <c r="L14" s="24" t="n">
-        <v>-0.078</v>
+      <c r="L14" s="24" t="inlineStr">
+        <is>
+          <t>-0.078†</t>
+        </is>
       </c>
       <c r="M14" s="24" t="n">
         <v>0.041</v>
       </c>
-      <c r="N14" s="24" t="n">
-        <v>0.118</v>
+      <c r="N14" s="24" t="inlineStr">
+        <is>
+          <t>0.118**</t>
+        </is>
       </c>
       <c r="O14" s="24" t="n">
         <v>0.045</v>
@@ -3305,44 +3413,58 @@
           <t>Empowering leadership (T1)</t>
         </is>
       </c>
-      <c r="B15" s="24" t="n">
-        <v>0.275</v>
+      <c r="B15" s="24" t="inlineStr">
+        <is>
+          <t>0.275***</t>
+        </is>
       </c>
       <c r="C15" s="24" t="n">
         <v>0.048</v>
       </c>
-      <c r="D15" s="24" t="n">
-        <v>0.268</v>
+      <c r="D15" s="24" t="inlineStr">
+        <is>
+          <t>0.268***</t>
+        </is>
       </c>
       <c r="E15" s="24" t="n">
         <v>0.048</v>
       </c>
-      <c r="F15" s="24" t="n">
-        <v>-0.149</v>
+      <c r="F15" s="24" t="inlineStr">
+        <is>
+          <t>-0.149**</t>
+        </is>
       </c>
       <c r="G15" s="24" t="n">
         <v>0.051</v>
       </c>
-      <c r="H15" s="24" t="n">
-        <v>-0.144</v>
+      <c r="H15" s="24" t="inlineStr">
+        <is>
+          <t>-0.144**</t>
+        </is>
       </c>
       <c r="I15" s="24" t="n">
         <v>0.051</v>
       </c>
-      <c r="J15" s="24" t="n">
-        <v>0.118</v>
+      <c r="J15" s="24" t="inlineStr">
+        <is>
+          <t>0.118**</t>
+        </is>
       </c>
       <c r="K15" s="24" t="n">
         <v>0.043</v>
       </c>
-      <c r="L15" s="24" t="n">
-        <v>0.108</v>
+      <c r="L15" s="24" t="inlineStr">
+        <is>
+          <t>0.108*</t>
+        </is>
       </c>
       <c r="M15" s="24" t="n">
         <v>0.042</v>
       </c>
-      <c r="N15" s="24" t="n">
-        <v>-0.08400000000000001</v>
+      <c r="N15" s="24" t="inlineStr">
+        <is>
+          <t>-0.084*</t>
+        </is>
       </c>
       <c r="O15" s="24" t="n">
         <v>0.041</v>
@@ -3415,20 +3537,26 @@
           <t>—</t>
         </is>
       </c>
-      <c r="J17" s="24" t="n">
-        <v>0.248</v>
+      <c r="J17" s="24" t="inlineStr">
+        <is>
+          <t>0.248***</t>
+        </is>
       </c>
       <c r="K17" s="24" t="n">
         <v>0.045</v>
       </c>
-      <c r="L17" s="24" t="n">
-        <v>0.235</v>
+      <c r="L17" s="24" t="inlineStr">
+        <is>
+          <t>0.235***</t>
+        </is>
       </c>
       <c r="M17" s="24" t="n">
         <v>0.046</v>
       </c>
-      <c r="N17" s="24" t="n">
-        <v>-0.08500000000000001</v>
+      <c r="N17" s="24" t="inlineStr">
+        <is>
+          <t>-0.085*</t>
+        </is>
       </c>
       <c r="O17" s="24" t="n">
         <v>0.043</v>
@@ -3480,20 +3608,26 @@
           <t>—</t>
         </is>
       </c>
-      <c r="J18" s="24" t="n">
-        <v>-0.212</v>
+      <c r="J18" s="24" t="inlineStr">
+        <is>
+          <t>-0.212***</t>
+        </is>
       </c>
       <c r="K18" s="24" t="n">
         <v>0.05</v>
       </c>
-      <c r="L18" s="24" t="n">
-        <v>-0.118</v>
+      <c r="L18" s="24" t="inlineStr">
+        <is>
+          <t>-0.118*</t>
+        </is>
       </c>
       <c r="M18" s="24" t="n">
         <v>0.052</v>
       </c>
-      <c r="N18" s="24" t="n">
-        <v>0.318</v>
+      <c r="N18" s="24" t="inlineStr">
+        <is>
+          <t>0.318***</t>
+        </is>
       </c>
       <c r="O18" s="24" t="n">
         <v>0.054</v>
@@ -3526,44 +3660,58 @@
           <t>Narcissism (T1)</t>
         </is>
       </c>
-      <c r="B20" s="24" t="n">
-        <v>-0.122</v>
+      <c r="B20" s="24" t="inlineStr">
+        <is>
+          <t>-0.122**</t>
+        </is>
       </c>
       <c r="C20" s="24" t="n">
         <v>0.045</v>
       </c>
-      <c r="D20" s="24" t="n">
-        <v>-0.122</v>
+      <c r="D20" s="24" t="inlineStr">
+        <is>
+          <t>-0.122**</t>
+        </is>
       </c>
       <c r="E20" s="24" t="n">
         <v>0.045</v>
       </c>
-      <c r="F20" s="24" t="n">
-        <v>0.221</v>
+      <c r="F20" s="24" t="inlineStr">
+        <is>
+          <t>0.221***</t>
+        </is>
       </c>
       <c r="G20" s="24" t="n">
         <v>0.046</v>
       </c>
-      <c r="H20" s="24" t="n">
-        <v>0.221</v>
+      <c r="H20" s="24" t="inlineStr">
+        <is>
+          <t>0.221***</t>
+        </is>
       </c>
       <c r="I20" s="24" t="n">
         <v>0.046</v>
       </c>
-      <c r="J20" s="24" t="n">
-        <v>-0.122</v>
+      <c r="J20" s="24" t="inlineStr">
+        <is>
+          <t>-0.122**</t>
+        </is>
       </c>
       <c r="K20" s="24" t="n">
         <v>0.045</v>
       </c>
-      <c r="L20" s="24" t="n">
-        <v>-0.122</v>
+      <c r="L20" s="24" t="inlineStr">
+        <is>
+          <t>-0.122**</t>
+        </is>
       </c>
       <c r="M20" s="24" t="n">
         <v>0.045</v>
       </c>
-      <c r="N20" s="24" t="n">
-        <v>-0.122</v>
+      <c r="N20" s="24" t="inlineStr">
+        <is>
+          <t>-0.122**</t>
+        </is>
       </c>
       <c r="O20" s="24" t="n">
         <v>0.045</v>
@@ -3575,44 +3723,58 @@
           <t>Power distance (T1)</t>
         </is>
       </c>
-      <c r="B21" s="24" t="n">
-        <v>-0.064</v>
+      <c r="B21" s="24" t="inlineStr">
+        <is>
+          <t>-0.064†</t>
+        </is>
       </c>
       <c r="C21" s="24" t="n">
         <v>0.038</v>
       </c>
-      <c r="D21" s="24" t="n">
-        <v>-0.064</v>
+      <c r="D21" s="24" t="inlineStr">
+        <is>
+          <t>-0.064†</t>
+        </is>
       </c>
       <c r="E21" s="24" t="n">
         <v>0.038</v>
       </c>
-      <c r="F21" s="24" t="n">
-        <v>0.139</v>
+      <c r="F21" s="24" t="inlineStr">
+        <is>
+          <t>0.139**</t>
+        </is>
       </c>
       <c r="G21" s="24" t="n">
         <v>0.044</v>
       </c>
-      <c r="H21" s="24" t="n">
-        <v>0.139</v>
+      <c r="H21" s="24" t="inlineStr">
+        <is>
+          <t>0.139**</t>
+        </is>
       </c>
       <c r="I21" s="24" t="n">
         <v>0.044</v>
       </c>
-      <c r="J21" s="24" t="n">
-        <v>-0.064</v>
+      <c r="J21" s="24" t="inlineStr">
+        <is>
+          <t>-0.064†</t>
+        </is>
       </c>
       <c r="K21" s="24" t="n">
         <v>0.038</v>
       </c>
-      <c r="L21" s="24" t="n">
-        <v>-0.064</v>
+      <c r="L21" s="24" t="inlineStr">
+        <is>
+          <t>-0.064†</t>
+        </is>
       </c>
       <c r="M21" s="24" t="n">
         <v>0.038</v>
       </c>
-      <c r="N21" s="24" t="n">
-        <v>-0.064</v>
+      <c r="N21" s="24" t="inlineStr">
+        <is>
+          <t>-0.064†</t>
+        </is>
       </c>
       <c r="O21" s="24" t="n">
         <v>0.038</v>
@@ -3809,8 +3971,10 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H25" s="24" t="n">
-        <v>-0.116</v>
+      <c r="H25" s="24" t="inlineStr">
+        <is>
+          <t>-0.116**</t>
+        </is>
       </c>
       <c r="I25" s="24" t="n">
         <v>0.038</v>
@@ -3862,8 +4026,10 @@
           <t>—</t>
         </is>
       </c>
-      <c r="D26" s="24" t="n">
-        <v>-0.101</v>
+      <c r="D26" s="24" t="inlineStr">
+        <is>
+          <t>-0.101*</t>
+        </is>
       </c>
       <c r="E26" s="24" t="n">
         <v>0.044</v>
@@ -4129,24 +4295,30 @@
           <t>Mediation</t>
         </is>
       </c>
-      <c r="B8" s="14" t="n">
-        <v>-0.035</v>
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>-0.035*</t>
+        </is>
       </c>
       <c r="C8" s="14" t="inlineStr">
         <is>
           <t>[-0.066, -0.014]</t>
         </is>
       </c>
-      <c r="D8" s="14" t="n">
-        <v>-0.033</v>
+      <c r="D8" s="14" t="inlineStr">
+        <is>
+          <t>-0.033*</t>
+        </is>
       </c>
       <c r="E8" s="14" t="inlineStr">
         <is>
           <t>[-0.063, -0.013]</t>
         </is>
       </c>
-      <c r="F8" s="14" t="n">
-        <v>0.012</v>
+      <c r="F8" s="14" t="inlineStr">
+        <is>
+          <t>0.012*</t>
+        </is>
       </c>
       <c r="G8" s="14" t="inlineStr">
         <is>
@@ -4310,16 +4482,20 @@
           <t>Low power distance (−1 SD)</t>
         </is>
       </c>
-      <c r="B15" s="14" t="n">
-        <v>-0.056</v>
+      <c r="B15" s="14" t="inlineStr">
+        <is>
+          <t>-0.056*</t>
+        </is>
       </c>
       <c r="C15" s="14" t="inlineStr">
         <is>
           <t>[-0.103, -0.009]</t>
         </is>
       </c>
-      <c r="D15" s="14" t="n">
-        <v>-0.052</v>
+      <c r="D15" s="14" t="inlineStr">
+        <is>
+          <t>-0.052*</t>
+        </is>
       </c>
       <c r="E15" s="14" t="inlineStr">
         <is>
@@ -4341,16 +4517,20 @@
           <t>Difference</t>
         </is>
       </c>
-      <c r="B16" s="14" t="n">
-        <v>0.042</v>
+      <c r="B16" s="14" t="inlineStr">
+        <is>
+          <t>0.042*</t>
+        </is>
       </c>
       <c r="C16" s="14" t="inlineStr">
         <is>
           <t>[0.002, 0.082]</t>
         </is>
       </c>
-      <c r="D16" s="14" t="n">
-        <v>0.04</v>
+      <c r="D16" s="14" t="inlineStr">
+        <is>
+          <t>0.04*</t>
+        </is>
       </c>
       <c r="E16" s="14" t="inlineStr">
         <is>
@@ -4385,24 +4565,30 @@
           <t>Mediation</t>
         </is>
       </c>
-      <c r="B18" s="16" t="n">
-        <v>0.066</v>
+      <c r="B18" s="16" t="inlineStr">
+        <is>
+          <t>0.066*</t>
+        </is>
       </c>
       <c r="C18" s="16" t="inlineStr">
         <is>
           <t>[0.038, 0.099]</t>
         </is>
       </c>
-      <c r="D18" s="16" t="n">
-        <v>0.063</v>
+      <c r="D18" s="16" t="inlineStr">
+        <is>
+          <t>0.063*</t>
+        </is>
       </c>
       <c r="E18" s="16" t="inlineStr">
         <is>
           <t>[0.034, 0.093]</t>
         </is>
       </c>
-      <c r="F18" s="16" t="n">
-        <v>-0.023</v>
+      <c r="F18" s="16" t="inlineStr">
+        <is>
+          <t>-0.023*</t>
+        </is>
       </c>
       <c r="G18" s="16" t="inlineStr">
         <is>
@@ -4429,16 +4615,20 @@
           <t>High narcissism (+1 SD)</t>
         </is>
       </c>
-      <c r="B20" s="16" t="n">
-        <v>0.07000000000000001</v>
+      <c r="B20" s="16" t="inlineStr">
+        <is>
+          <t>0.07*</t>
+        </is>
       </c>
       <c r="C20" s="16" t="inlineStr">
         <is>
           <t>[0.016, 0.124]</t>
         </is>
       </c>
-      <c r="D20" s="16" t="n">
-        <v>0.068</v>
+      <c r="D20" s="16" t="inlineStr">
+        <is>
+          <t>0.068*</t>
+        </is>
       </c>
       <c r="E20" s="16" t="inlineStr">
         <is>
@@ -4460,16 +4650,20 @@
           <t>Low narcissism (−1 SD)</t>
         </is>
       </c>
-      <c r="B21" s="16" t="n">
-        <v>0.061</v>
+      <c r="B21" s="16" t="inlineStr">
+        <is>
+          <t>0.061*</t>
+        </is>
       </c>
       <c r="C21" s="16" t="inlineStr">
         <is>
           <t>[0.012, 0.110]</t>
         </is>
       </c>
-      <c r="D21" s="16" t="n">
-        <v>0.058</v>
+      <c r="D21" s="16" t="inlineStr">
+        <is>
+          <t>0.058*</t>
+        </is>
       </c>
       <c r="E21" s="16" t="inlineStr">
         <is>
@@ -4553,16 +4747,20 @@
           <t>Low power distance (−1 SD)</t>
         </is>
       </c>
-      <c r="B24" s="16" t="n">
-        <v>0.093</v>
+      <c r="B24" s="16" t="inlineStr">
+        <is>
+          <t>0.093*</t>
+        </is>
       </c>
       <c r="C24" s="16" t="inlineStr">
         <is>
           <t>[0.028, 0.158]</t>
         </is>
       </c>
-      <c r="D24" s="16" t="n">
-        <v>0.09</v>
+      <c r="D24" s="16" t="inlineStr">
+        <is>
+          <t>0.09*</t>
+        </is>
       </c>
       <c r="E24" s="16" t="inlineStr">
         <is>
@@ -4584,16 +4782,20 @@
           <t>Difference</t>
         </is>
       </c>
-      <c r="B25" s="16" t="n">
-        <v>-0.055</v>
+      <c r="B25" s="16" t="inlineStr">
+        <is>
+          <t>-0.055*</t>
+        </is>
       </c>
       <c r="C25" s="16" t="inlineStr">
         <is>
           <t>[-0.102, -0.008]</t>
         </is>
       </c>
-      <c r="D25" s="16" t="n">
-        <v>-0.054</v>
+      <c r="D25" s="16" t="inlineStr">
+        <is>
+          <t>-0.054*</t>
+        </is>
       </c>
       <c r="E25" s="16" t="inlineStr">
         <is>
@@ -4641,24 +4843,30 @@
           <t>Indirect effect</t>
         </is>
       </c>
-      <c r="B28" s="18" t="n">
-        <v>-0.066</v>
+      <c r="B28" s="18" t="inlineStr">
+        <is>
+          <t>-0.066*</t>
+        </is>
       </c>
       <c r="C28" s="18" t="inlineStr">
         <is>
           <t>[-0.103, -0.038]</t>
         </is>
       </c>
-      <c r="D28" s="18" t="n">
-        <v>-0.037</v>
+      <c r="D28" s="18" t="inlineStr">
+        <is>
+          <t>-0.037*</t>
+        </is>
       </c>
       <c r="E28" s="18" t="inlineStr">
         <is>
           <t>[-0.069, -0.013]</t>
         </is>
       </c>
-      <c r="F28" s="18" t="n">
-        <v>0.099</v>
+      <c r="F28" s="18" t="inlineStr">
+        <is>
+          <t>0.099*</t>
+        </is>
       </c>
       <c r="G28" s="18" t="inlineStr">
         <is>
@@ -4672,24 +4880,30 @@
           <t>High narcissism (+1 SD)</t>
         </is>
       </c>
-      <c r="B29" s="18" t="n">
-        <v>-0.07099999999999999</v>
+      <c r="B29" s="18" t="inlineStr">
+        <is>
+          <t>-0.071*</t>
+        </is>
       </c>
       <c r="C29" s="18" t="inlineStr">
         <is>
           <t>[-0.125, -0.017]</t>
         </is>
       </c>
-      <c r="D29" s="18" t="n">
-        <v>-0.04</v>
+      <c r="D29" s="18" t="inlineStr">
+        <is>
+          <t>-0.04*</t>
+        </is>
       </c>
       <c r="E29" s="18" t="inlineStr">
         <is>
           <t>[-0.079, -0.001]</t>
         </is>
       </c>
-      <c r="F29" s="18" t="n">
-        <v>0.106</v>
+      <c r="F29" s="18" t="inlineStr">
+        <is>
+          <t>0.106*</t>
+        </is>
       </c>
       <c r="G29" s="18" t="inlineStr">
         <is>
@@ -4703,8 +4917,10 @@
           <t>Low narcissism (−1 SD)</t>
         </is>
       </c>
-      <c r="B30" s="18" t="n">
-        <v>-0.06</v>
+      <c r="B30" s="18" t="inlineStr">
+        <is>
+          <t>-0.06*</t>
+        </is>
       </c>
       <c r="C30" s="18" t="inlineStr">
         <is>
@@ -4719,8 +4935,10 @@
           <t>[-0.070, 0.002]</t>
         </is>
       </c>
-      <c r="F30" s="18" t="n">
-        <v>0.092</v>
+      <c r="F30" s="18" t="inlineStr">
+        <is>
+          <t>0.092*</t>
+        </is>
       </c>
       <c r="G30" s="18" t="inlineStr">
         <is>
@@ -4765,8 +4983,10 @@
           <t>High power distance (+1 SD)</t>
         </is>
       </c>
-      <c r="B32" s="18" t="n">
-        <v>-0.042</v>
+      <c r="B32" s="18" t="inlineStr">
+        <is>
+          <t>-0.042*</t>
+        </is>
       </c>
       <c r="C32" s="18" t="inlineStr">
         <is>
@@ -4781,8 +5001,10 @@
           <t>[-0.054, 0.008]</t>
         </is>
       </c>
-      <c r="F32" s="18" t="n">
-        <v>0.063</v>
+      <c r="F32" s="18" t="inlineStr">
+        <is>
+          <t>0.063*</t>
+        </is>
       </c>
       <c r="G32" s="18" t="inlineStr">
         <is>
@@ -4796,24 +5018,30 @@
           <t>Low power distance (−1 SD)</t>
         </is>
       </c>
-      <c r="B33" s="18" t="n">
-        <v>-0.089</v>
+      <c r="B33" s="18" t="inlineStr">
+        <is>
+          <t>-0.089*</t>
+        </is>
       </c>
       <c r="C33" s="18" t="inlineStr">
         <is>
           <t>[-0.152, -0.026]</t>
         </is>
       </c>
-      <c r="D33" s="18" t="n">
-        <v>-0.051</v>
+      <c r="D33" s="18" t="inlineStr">
+        <is>
+          <t>-0.051*</t>
+        </is>
       </c>
       <c r="E33" s="18" t="inlineStr">
         <is>
           <t>[-0.096, -0.006]</t>
         </is>
       </c>
-      <c r="F33" s="18" t="n">
-        <v>0.134</v>
+      <c r="F33" s="18" t="inlineStr">
+        <is>
+          <t>0.134*</t>
+        </is>
       </c>
       <c r="G33" s="18" t="inlineStr">
         <is>
@@ -4827,8 +5055,10 @@
           <t>Difference</t>
         </is>
       </c>
-      <c r="B34" s="18" t="n">
-        <v>0.047</v>
+      <c r="B34" s="18" t="inlineStr">
+        <is>
+          <t>0.047*</t>
+        </is>
       </c>
       <c r="C34" s="18" t="inlineStr">
         <is>
@@ -4843,8 +5073,10 @@
           <t>[-0.006, 0.060]</t>
         </is>
       </c>
-      <c r="F34" s="18" t="n">
-        <v>-0.07199999999999999</v>
+      <c r="F34" s="18" t="inlineStr">
+        <is>
+          <t>-0.072*</t>
+        </is>
       </c>
       <c r="G34" s="18" t="inlineStr">
         <is>
@@ -4871,24 +5103,30 @@
           <t>Indirect effect</t>
         </is>
       </c>
-      <c r="B36" s="20" t="n">
-        <v>0.031</v>
+      <c r="B36" s="20" t="inlineStr">
+        <is>
+          <t>0.031*</t>
+        </is>
       </c>
       <c r="C36" s="20" t="inlineStr">
         <is>
           <t>[0.012, 0.055]</t>
         </is>
       </c>
-      <c r="D36" s="20" t="n">
-        <v>0.017</v>
+      <c r="D36" s="20" t="inlineStr">
+        <is>
+          <t>0.017*</t>
+        </is>
       </c>
       <c r="E36" s="20" t="inlineStr">
         <is>
           <t>[0.005, 0.034]</t>
         </is>
       </c>
-      <c r="F36" s="20" t="n">
-        <v>-0.046</v>
+      <c r="F36" s="20" t="inlineStr">
+        <is>
+          <t>-0.046*</t>
+        </is>
       </c>
       <c r="G36" s="20" t="inlineStr">
         <is>
@@ -4918,8 +5156,10 @@
           <t>[-0.012, 0.042]</t>
         </is>
       </c>
-      <c r="F37" s="20" t="n">
-        <v>-0.041</v>
+      <c r="F37" s="20" t="inlineStr">
+        <is>
+          <t>-0.041*</t>
+        </is>
       </c>
       <c r="G37" s="20" t="inlineStr">
         <is>
@@ -4949,8 +5189,10 @@
           <t>[-0.010, 0.048]</t>
         </is>
       </c>
-      <c r="F38" s="20" t="n">
-        <v>-0.051</v>
+      <c r="F38" s="20" t="inlineStr">
+        <is>
+          <t>-0.051*</t>
+        </is>
       </c>
       <c r="G38" s="20" t="inlineStr">
         <is>
@@ -4995,8 +5237,10 @@
           <t>High power distance (+1 SD)</t>
         </is>
       </c>
-      <c r="B40" s="20" t="n">
-        <v>0.049</v>
+      <c r="B40" s="20" t="inlineStr">
+        <is>
+          <t>0.049*</t>
+        </is>
       </c>
       <c r="C40" s="20" t="inlineStr">
         <is>
@@ -5011,8 +5255,10 @@
           <t>[-0.006, 0.060]</t>
         </is>
       </c>
-      <c r="F40" s="20" t="n">
-        <v>-0.07199999999999999</v>
+      <c r="F40" s="20" t="inlineStr">
+        <is>
+          <t>-0.072*</t>
+        </is>
       </c>
       <c r="G40" s="20" t="inlineStr">
         <is>
@@ -5073,8 +5319,10 @@
           <t>[-0.009, 0.049]</t>
         </is>
       </c>
-      <c r="F42" s="20" t="n">
-        <v>-0.052</v>
+      <c r="F42" s="20" t="inlineStr">
+        <is>
+          <t>-0.052*</t>
+        </is>
       </c>
       <c r="G42" s="20" t="inlineStr">
         <is>
@@ -5320,8 +5568,10 @@
       <c r="H5" s="4" t="n">
         <v>0.068</v>
       </c>
-      <c r="I5" s="4" t="n">
-        <v>-0.16</v>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>-0.16*</t>
+        </is>
       </c>
       <c r="J5" s="4" t="n">
         <v>0.06</v>
@@ -5335,8 +5585,10 @@
       <c r="M5" s="4" t="n">
         <v>-0.031</v>
       </c>
-      <c r="N5" s="4" t="n">
-        <v>-0.135</v>
+      <c r="N5" s="4" t="inlineStr">
+        <is>
+          <t>-0.135*</t>
+        </is>
       </c>
       <c r="O5" s="4" t="n">
         <v>0.066</v>
@@ -5397,8 +5649,10 @@
       <c r="H6" s="4" t="n">
         <v>0.093</v>
       </c>
-      <c r="I6" s="4" t="n">
-        <v>0.276</v>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>0.276***</t>
+        </is>
       </c>
       <c r="J6" s="4" t="n">
         <v>0.058</v>
@@ -5412,8 +5666,10 @@
       <c r="M6" s="4" t="n">
         <v>0.419</v>
       </c>
-      <c r="N6" s="4" t="n">
-        <v>0.242</v>
+      <c r="N6" s="4" t="inlineStr">
+        <is>
+          <t>0.242***</t>
+        </is>
       </c>
       <c r="O6" s="4" t="n">
         <v>0.058</v>
@@ -5489,8 +5745,10 @@
       <c r="M7" s="4" t="n">
         <v>0.08599999999999999</v>
       </c>
-      <c r="N7" s="4" t="n">
-        <v>-0.152</v>
+      <c r="N7" s="4" t="inlineStr">
+        <is>
+          <t>-0.152*</t>
+        </is>
       </c>
       <c r="O7" s="4" t="n">
         <v>0.065</v>
@@ -5536,8 +5794,10 @@
           <t>Power distance</t>
         </is>
       </c>
-      <c r="D8" s="4" t="n">
-        <v>-0.097</v>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>-0.097*</t>
+        </is>
       </c>
       <c r="E8" s="4" t="n">
         <v>0.04</v>
@@ -5551,8 +5811,10 @@
       <c r="H8" s="4" t="n">
         <v>-0.021</v>
       </c>
-      <c r="I8" s="4" t="n">
-        <v>0.177</v>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>0.177**</t>
+        </is>
       </c>
       <c r="J8" s="4" t="n">
         <v>0.061</v>
@@ -5566,8 +5828,10 @@
       <c r="M8" s="4" t="n">
         <v>0.276</v>
       </c>
-      <c r="N8" s="4" t="n">
-        <v>0.37</v>
+      <c r="N8" s="4" t="inlineStr">
+        <is>
+          <t>0.37***</t>
+        </is>
       </c>
       <c r="O8" s="4" t="n">
         <v>0.062</v>
@@ -5581,8 +5845,10 @@
       <c r="R8" s="4" t="n">
         <v>0.467</v>
       </c>
-      <c r="S8" s="4" t="n">
-        <v>-0.202</v>
+      <c r="S8" s="4" t="inlineStr">
+        <is>
+          <t>-0.202*</t>
+        </is>
       </c>
       <c r="T8" s="4" t="n">
         <v>0.081</v>
@@ -5628,8 +5894,10 @@
       <c r="H9" s="4" t="n">
         <v>0.11</v>
       </c>
-      <c r="I9" s="4" t="n">
-        <v>0.353</v>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>0.353***</t>
+        </is>
       </c>
       <c r="J9" s="4" t="n">
         <v>0.067</v>
@@ -5643,8 +5911,10 @@
       <c r="M9" s="4" t="n">
         <v>0.485</v>
       </c>
-      <c r="N9" s="4" t="n">
-        <v>0.286</v>
+      <c r="N9" s="4" t="inlineStr">
+        <is>
+          <t>0.286***</t>
+        </is>
       </c>
       <c r="O9" s="4" t="n">
         <v>0.073</v>
@@ -5705,8 +5975,10 @@
       <c r="H10" s="4" t="n">
         <v>0.061</v>
       </c>
-      <c r="I10" s="4" t="n">
-        <v>-0.164</v>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>-0.164**</t>
+        </is>
       </c>
       <c r="J10" s="4" t="n">
         <v>0.062</v>
@@ -5720,8 +5992,10 @@
       <c r="M10" s="4" t="n">
         <v>-0.047</v>
       </c>
-      <c r="N10" s="4" t="n">
-        <v>-0.125</v>
+      <c r="N10" s="4" t="inlineStr">
+        <is>
+          <t>-0.125*</t>
+        </is>
       </c>
       <c r="O10" s="4" t="n">
         <v>0.064</v>
@@ -5767,8 +6041,10 @@
           <t>Power distance</t>
         </is>
       </c>
-      <c r="D11" s="4" t="n">
-        <v>-0.108</v>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>-0.108**</t>
+        </is>
       </c>
       <c r="E11" s="4" t="n">
         <v>0.04</v>
@@ -5782,8 +6058,10 @@
       <c r="H11" s="4" t="n">
         <v>-0.029</v>
       </c>
-      <c r="I11" s="4" t="n">
-        <v>0.198</v>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>0.198**</t>
+        </is>
       </c>
       <c r="J11" s="4" t="n">
         <v>0.063</v>
@@ -5797,8 +6075,10 @@
       <c r="M11" s="4" t="n">
         <v>0.323</v>
       </c>
-      <c r="N11" s="4" t="n">
-        <v>0.409</v>
+      <c r="N11" s="4" t="inlineStr">
+        <is>
+          <t>0.409***</t>
+        </is>
       </c>
       <c r="O11" s="4" t="n">
         <v>0.066</v>
@@ -5812,8 +6092,10 @@
       <c r="R11" s="4" t="n">
         <v>0.578</v>
       </c>
-      <c r="S11" s="4" t="n">
-        <v>-0.232</v>
+      <c r="S11" s="4" t="inlineStr">
+        <is>
+          <t>-0.232**</t>
+        </is>
       </c>
       <c r="T11" s="4" t="n">
         <v>0.083</v>
@@ -5844,8 +6126,10 @@
           <t>Power distance</t>
         </is>
       </c>
-      <c r="D12" s="4" t="n">
-        <v>0.06900000000000001</v>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>0.069†</t>
+        </is>
       </c>
       <c r="E12" s="4" t="n">
         <v>0.037</v>
@@ -5874,8 +6158,10 @@
       <c r="M12" s="4" t="n">
         <v>0.04</v>
       </c>
-      <c r="N12" s="4" t="n">
-        <v>-0.211</v>
+      <c r="N12" s="4" t="inlineStr">
+        <is>
+          <t>-0.211**</t>
+        </is>
       </c>
       <c r="O12" s="4" t="n">
         <v>0.063</v>
@@ -5889,8 +6175,10 @@
       <c r="R12" s="4" t="n">
         <v>-0.08799999999999999</v>
       </c>
-      <c r="S12" s="4" t="n">
-        <v>0.134</v>
+      <c r="S12" s="4" t="inlineStr">
+        <is>
+          <t>0.134†</t>
+        </is>
       </c>
       <c r="T12" s="4" t="n">
         <v>0.073</v>

--- a/results/Model3.xlsx
+++ b/results/Model3.xlsx
@@ -2108,7 +2108,7 @@
         </is>
       </c>
       <c r="B4" s="24" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="C4" s="24" t="n">
         <v>0.486</v>
@@ -2139,13 +2139,13 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>30.752</v>
+        <v>30.767</v>
       </c>
       <c r="C5" s="24" t="n">
-        <v>4.613</v>
+        <v>4.607</v>
       </c>
       <c r="D5" s="24" t="n">
-        <v>0.004</v>
+        <v>0.028</v>
       </c>
       <c r="E5" s="24" t="inlineStr">
         <is>
@@ -2172,17 +2172,17 @@
         </is>
       </c>
       <c r="B6" s="24" t="n">
-        <v>2.341</v>
+        <v>2.376</v>
       </c>
       <c r="C6" s="24" t="n">
-        <v>1.475</v>
+        <v>1.52</v>
       </c>
       <c r="D6" s="24" t="n">
-        <v>-0.043</v>
+        <v>-0.021</v>
       </c>
       <c r="E6" s="24" t="inlineStr">
         <is>
-          <t>0.216***</t>
+          <t>0.194***</t>
         </is>
       </c>
       <c r="F6" s="24" t="inlineStr">
@@ -2209,19 +2209,19 @@
         </is>
       </c>
       <c r="B7" s="24" t="n">
-        <v>3.33</v>
+        <v>3.279</v>
       </c>
       <c r="C7" s="24" t="n">
-        <v>1.075</v>
+        <v>1.066</v>
       </c>
       <c r="D7" s="24" t="n">
-        <v>0.079</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="E7" s="24" t="n">
-        <v>0.004</v>
+        <v>-0.001</v>
       </c>
       <c r="F7" s="24" t="n">
-        <v>-0.06</v>
+        <v>-0.052</v>
       </c>
       <c r="G7" s="24" t="inlineStr">
         <is>
@@ -2246,22 +2246,22 @@
         </is>
       </c>
       <c r="B8" s="24" t="n">
-        <v>4.128</v>
+        <v>4.048</v>
       </c>
       <c r="C8" s="24" t="n">
-        <v>0.878</v>
+        <v>0.854</v>
       </c>
       <c r="D8" s="24" t="n">
-        <v>-0.055</v>
+        <v>-0.017</v>
       </c>
       <c r="E8" s="24" t="n">
-        <v>-0.003</v>
+        <v>-0.001</v>
       </c>
       <c r="F8" s="24" t="n">
-        <v>0.077</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="G8" s="24" t="n">
-        <v>0.01</v>
+        <v>-0.034</v>
       </c>
       <c r="H8" s="23" t="inlineStr">
         <is>
@@ -2285,26 +2285,26 @@
         </is>
       </c>
       <c r="B9" s="24" t="n">
-        <v>4.929</v>
+        <v>4.959</v>
       </c>
       <c r="C9" s="24" t="n">
-        <v>0.95</v>
+        <v>0.9389999999999999</v>
       </c>
       <c r="D9" s="24" t="n">
-        <v>-0.002</v>
+        <v>-0.027</v>
       </c>
       <c r="E9" s="24" t="n">
-        <v>-0.036</v>
+        <v>-0.056</v>
       </c>
       <c r="F9" s="24" t="n">
-        <v>0.032</v>
+        <v>0.025</v>
       </c>
       <c r="G9" s="24" t="n">
-        <v>-0.093</v>
+        <v>-0.079</v>
       </c>
       <c r="H9" s="24" t="inlineStr">
         <is>
-          <t>-0.34***</t>
+          <t>-0.315***</t>
         </is>
       </c>
       <c r="I9" s="24" t="inlineStr">
@@ -2328,28 +2328,28 @@
         </is>
       </c>
       <c r="B10" s="24" t="n">
-        <v>3.479</v>
+        <v>3.465</v>
       </c>
       <c r="C10" s="24" t="n">
-        <v>0.913</v>
+        <v>0.916</v>
       </c>
       <c r="D10" s="24" t="n">
-        <v>-0.051</v>
+        <v>-0.077</v>
       </c>
       <c r="E10" s="24" t="n">
-        <v>-0.029</v>
+        <v>-0.026</v>
       </c>
       <c r="F10" s="24" t="n">
-        <v>0.102</v>
+        <v>0.038</v>
       </c>
       <c r="G10" s="24" t="n">
-        <v>-0.057</v>
+        <v>-0.033</v>
       </c>
       <c r="H10" s="24" t="n">
-        <v>0</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="I10" s="24" t="n">
-        <v>0.059</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J10" s="24" t="inlineStr">
         <is>
@@ -2371,33 +2371,31 @@
         </is>
       </c>
       <c r="B11" s="24" t="n">
-        <v>4.582</v>
+        <v>4.597</v>
       </c>
       <c r="C11" s="24" t="n">
-        <v>0.892</v>
+        <v>0.902</v>
       </c>
       <c r="D11" s="24" t="n">
-        <v>-0.078</v>
+        <v>-0.09</v>
       </c>
       <c r="E11" s="24" t="n">
-        <v>-0.092</v>
-      </c>
-      <c r="F11" s="24" t="inlineStr">
-        <is>
-          <t>-0.11*</t>
-        </is>
+        <v>-0.089</v>
+      </c>
+      <c r="F11" s="24" t="n">
+        <v>-0.08699999999999999</v>
       </c>
       <c r="G11" s="24" t="n">
-        <v>-0.067</v>
+        <v>-0.099</v>
       </c>
       <c r="H11" s="24" t="n">
-        <v>-0.019</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="I11" s="24" t="n">
-        <v>-0.048</v>
+        <v>-0.039</v>
       </c>
       <c r="J11" s="24" t="n">
-        <v>-0.037</v>
+        <v>-0.002</v>
       </c>
       <c r="K11" s="24" t="inlineStr">
         <is>
@@ -2418,38 +2416,38 @@
         </is>
       </c>
       <c r="B12" s="24" t="n">
-        <v>4.46</v>
+        <v>4.542</v>
       </c>
       <c r="C12" s="24" t="n">
-        <v>1.207</v>
+        <v>1.214</v>
       </c>
       <c r="D12" s="24" t="n">
-        <v>-0.045</v>
+        <v>-0.06</v>
       </c>
       <c r="E12" s="24" t="n">
-        <v>-0.022</v>
+        <v>-0.014</v>
       </c>
       <c r="F12" s="24" t="n">
-        <v>-0.033</v>
+        <v>-0.049</v>
       </c>
       <c r="G12" s="24" t="n">
-        <v>-0.05</v>
+        <v>-0.061</v>
       </c>
       <c r="H12" s="24" t="inlineStr">
         <is>
-          <t>-0.531***</t>
+          <t>-0.519***</t>
         </is>
       </c>
       <c r="I12" s="24" t="inlineStr">
         <is>
-          <t>0.542***</t>
+          <t>0.523***</t>
         </is>
       </c>
       <c r="J12" s="24" t="n">
-        <v>-0.017</v>
+        <v>-0.003</v>
       </c>
       <c r="K12" s="24" t="n">
-        <v>-0.032</v>
+        <v>-0.035</v>
       </c>
       <c r="L12" s="24" t="inlineStr">
         <is>
@@ -2469,42 +2467,42 @@
         </is>
       </c>
       <c r="B13" s="24" t="n">
-        <v>3.061</v>
+        <v>3.017</v>
       </c>
       <c r="C13" s="24" t="n">
-        <v>1.197</v>
+        <v>1.181</v>
       </c>
       <c r="D13" s="24" t="n">
-        <v>0.008</v>
+        <v>0.034</v>
       </c>
       <c r="E13" s="24" t="n">
-        <v>-0.029</v>
+        <v>0.001</v>
       </c>
       <c r="F13" s="24" t="n">
-        <v>0.006</v>
+        <v>-0.014</v>
       </c>
       <c r="G13" s="24" t="n">
-        <v>0.056</v>
+        <v>0.038</v>
       </c>
       <c r="H13" s="24" t="inlineStr">
         <is>
-          <t>0.526***</t>
+          <t>0.505***</t>
         </is>
       </c>
       <c r="I13" s="24" t="inlineStr">
         <is>
-          <t>-0.514***</t>
+          <t>-0.516***</t>
         </is>
       </c>
       <c r="J13" s="24" t="n">
-        <v>0.03</v>
+        <v>0.032</v>
       </c>
       <c r="K13" s="24" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.082</v>
       </c>
       <c r="L13" s="24" t="inlineStr">
         <is>
-          <t>-0.466***</t>
+          <t>-0.46***</t>
         </is>
       </c>
       <c r="M13" s="24" t="inlineStr">
@@ -2524,39 +2522,37 @@
         </is>
       </c>
       <c r="B14" s="24" t="n">
-        <v>4.432</v>
+        <v>4.428</v>
       </c>
       <c r="C14" s="24" t="n">
-        <v>0.623</v>
+        <v>0.605</v>
       </c>
       <c r="D14" s="24" t="n">
-        <v>0.054</v>
+        <v>0.028</v>
       </c>
       <c r="E14" s="24" t="n">
-        <v>-0.026</v>
+        <v>0.034</v>
       </c>
       <c r="F14" s="24" t="n">
-        <v>-0.011</v>
+        <v>-0.03</v>
       </c>
       <c r="G14" s="24" t="n">
-        <v>-0.023</v>
+        <v>0.007</v>
       </c>
       <c r="H14" s="24" t="n">
-        <v>0.054</v>
+        <v>0.055</v>
       </c>
       <c r="I14" s="24" t="n">
-        <v>-0.053</v>
-      </c>
-      <c r="J14" s="24" t="inlineStr">
-        <is>
-          <t>-0.107*</t>
-        </is>
+        <v>-0.022</v>
+      </c>
+      <c r="J14" s="24" t="n">
+        <v>-0.091</v>
       </c>
       <c r="K14" s="24" t="n">
-        <v>-0.074</v>
+        <v>-0.034</v>
       </c>
       <c r="L14" s="24" t="n">
-        <v>-0.04</v>
+        <v>-0.013</v>
       </c>
       <c r="M14" s="24" t="n">
         <v>0.053</v>
@@ -2577,52 +2573,52 @@
         </is>
       </c>
       <c r="B15" s="24" t="n">
-        <v>4.532</v>
+        <v>4.521</v>
       </c>
       <c r="C15" s="24" t="n">
-        <v>0.795</v>
+        <v>0.821</v>
       </c>
       <c r="D15" s="24" t="n">
-        <v>-0.033</v>
+        <v>-0.016</v>
       </c>
       <c r="E15" s="24" t="n">
-        <v>-0.007</v>
+        <v>-0.028</v>
       </c>
       <c r="F15" s="24" t="n">
-        <v>-0.005</v>
+        <v>-0.038</v>
       </c>
       <c r="G15" s="24" t="n">
-        <v>-0.092</v>
+        <v>-0.045</v>
       </c>
       <c r="H15" s="24" t="inlineStr">
         <is>
-          <t>-0.455***</t>
+          <t>-0.404***</t>
         </is>
       </c>
       <c r="I15" s="24" t="inlineStr">
         <is>
-          <t>0.445***</t>
+          <t>0.408***</t>
         </is>
       </c>
       <c r="J15" s="24" t="n">
-        <v>-0.07099999999999999</v>
+        <v>-0.054</v>
       </c>
       <c r="K15" s="24" t="n">
-        <v>-0.023</v>
+        <v>-0.008</v>
       </c>
       <c r="L15" s="24" t="inlineStr">
         <is>
-          <t>0.617***</t>
+          <t>0.574***</t>
         </is>
       </c>
       <c r="M15" s="24" t="inlineStr">
         <is>
-          <t>-0.596***</t>
+          <t>-0.583***</t>
         </is>
       </c>
       <c r="N15" s="24" t="inlineStr">
         <is>
-          <t>0.351***</t>
+          <t>0.425***</t>
         </is>
       </c>
       <c r="O15" s="24" t="inlineStr">
@@ -2640,57 +2636,55 @@
         </is>
       </c>
       <c r="B16" s="24" t="n">
-        <v>4.973</v>
+        <v>4.987</v>
       </c>
       <c r="C16" s="24" t="n">
-        <v>1.115</v>
+        <v>1.097</v>
       </c>
       <c r="D16" s="24" t="n">
-        <v>-0.045</v>
+        <v>-0.08500000000000001</v>
       </c>
       <c r="E16" s="24" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="F16" s="24" t="inlineStr">
-        <is>
-          <t>0.112*</t>
-        </is>
+        <v>0.011</v>
+      </c>
+      <c r="F16" s="24" t="n">
+        <v>-0.007</v>
       </c>
       <c r="G16" s="24" t="n">
-        <v>-0.05</v>
+        <v>-0.041</v>
       </c>
       <c r="H16" s="24" t="inlineStr">
         <is>
-          <t>-0.423***</t>
+          <t>-0.338***</t>
         </is>
       </c>
       <c r="I16" s="24" t="inlineStr">
         <is>
-          <t>0.389***</t>
+          <t>0.326***</t>
         </is>
       </c>
       <c r="J16" s="24" t="n">
-        <v>0.051</v>
+        <v>-0.03</v>
       </c>
       <c r="K16" s="24" t="n">
-        <v>-0.013</v>
+        <v>0.066</v>
       </c>
       <c r="L16" s="24" t="inlineStr">
         <is>
-          <t>0.486***</t>
+          <t>0.516***</t>
         </is>
       </c>
       <c r="M16" s="24" t="inlineStr">
         <is>
-          <t>-0.567***</t>
+          <t>-0.573***</t>
         </is>
       </c>
       <c r="N16" s="24" t="n">
-        <v>-0.043</v>
+        <v>0.016</v>
       </c>
       <c r="O16" s="24" t="inlineStr">
         <is>
-          <t>0.372***</t>
+          <t>0.481***</t>
         </is>
       </c>
       <c r="P16" s="24" t="inlineStr">
@@ -2707,60 +2701,60 @@
         </is>
       </c>
       <c r="B17" s="24" t="n">
-        <v>2.663</v>
+        <v>2.674</v>
       </c>
       <c r="C17" s="24" t="n">
-        <v>1.139</v>
+        <v>1.14</v>
       </c>
       <c r="D17" s="24" t="n">
-        <v>-0.008</v>
+        <v>0.078</v>
       </c>
       <c r="E17" s="24" t="n">
-        <v>-0.027</v>
+        <v>0.011</v>
       </c>
       <c r="F17" s="24" t="n">
-        <v>0.028</v>
+        <v>-0.014</v>
       </c>
       <c r="G17" s="24" t="n">
-        <v>0.032</v>
+        <v>0.05</v>
       </c>
       <c r="H17" s="24" t="inlineStr">
         <is>
-          <t>0.383***</t>
+          <t>0.421***</t>
         </is>
       </c>
       <c r="I17" s="24" t="inlineStr">
         <is>
-          <t>-0.375***</t>
+          <t>-0.441***</t>
         </is>
       </c>
       <c r="J17" s="24" t="n">
-        <v>-0.039</v>
+        <v>-0.047</v>
       </c>
       <c r="K17" s="24" t="n">
-        <v>-0.016</v>
+        <v>0.046</v>
       </c>
       <c r="L17" s="24" t="inlineStr">
         <is>
-          <t>-0.498***</t>
+          <t>-0.519***</t>
         </is>
       </c>
       <c r="M17" s="24" t="inlineStr">
         <is>
-          <t>0.587***</t>
+          <t>0.642***</t>
         </is>
       </c>
       <c r="N17" s="24" t="n">
-        <v>-0.024</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="O17" s="24" t="inlineStr">
         <is>
-          <t>-0.433***</t>
+          <t>-0.425***</t>
         </is>
       </c>
       <c r="P17" s="24" t="inlineStr">
         <is>
-          <t>-0.4***</t>
+          <t>-0.473***</t>
         </is>
       </c>
       <c r="Q17" s="24" t="inlineStr">
@@ -2990,43 +2984,43 @@
       </c>
       <c r="F6" s="24" t="inlineStr">
         <is>
-          <t>3.793***</t>
+          <t>3.785***</t>
         </is>
       </c>
       <c r="G6" s="24" t="n">
-        <v>0.092</v>
+        <v>0.094</v>
       </c>
       <c r="H6" s="24" t="inlineStr">
         <is>
-          <t>3.793***</t>
+          <t>3.785***</t>
         </is>
       </c>
       <c r="I6" s="24" t="n">
-        <v>0.092</v>
+        <v>0.094</v>
       </c>
       <c r="J6" s="24" t="inlineStr">
         <is>
-          <t>3.793***</t>
+          <t>4.412***</t>
         </is>
       </c>
       <c r="K6" s="24" t="n">
-        <v>0.092</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="L6" s="24" t="inlineStr">
         <is>
-          <t>3.793***</t>
+          <t>4.952***</t>
         </is>
       </c>
       <c r="M6" s="24" t="n">
-        <v>0.092</v>
+        <v>0.102</v>
       </c>
       <c r="N6" s="24" t="inlineStr">
         <is>
-          <t>3.793***</t>
+          <t>2.654***</t>
         </is>
       </c>
       <c r="O6" s="24" t="n">
-        <v>0.092</v>
+        <v>0.097</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" s="37">
@@ -3063,40 +3057,40 @@
         <v>0.022</v>
       </c>
       <c r="D8" s="24" t="n">
-        <v>-0.021</v>
+        <v>-0.022</v>
       </c>
       <c r="E8" s="24" t="n">
         <v>0.022</v>
       </c>
       <c r="F8" s="24" t="n">
-        <v>-0.021</v>
+        <v>-0.017</v>
       </c>
       <c r="G8" s="24" t="n">
-        <v>0.022</v>
+        <v>0.023</v>
       </c>
       <c r="H8" s="24" t="n">
-        <v>-0.021</v>
+        <v>-0.018</v>
       </c>
       <c r="I8" s="24" t="n">
-        <v>0.022</v>
+        <v>0.023</v>
       </c>
       <c r="J8" s="24" t="n">
-        <v>-0.021</v>
+        <v>-0.014</v>
       </c>
       <c r="K8" s="24" t="n">
-        <v>0.022</v>
+        <v>0.021</v>
       </c>
       <c r="L8" s="24" t="n">
-        <v>-0.021</v>
+        <v>-0.027</v>
       </c>
       <c r="M8" s="24" t="n">
-        <v>0.022</v>
+        <v>0.025</v>
       </c>
       <c r="N8" s="24" t="n">
-        <v>-0.021</v>
+        <v>-0.012</v>
       </c>
       <c r="O8" s="24" t="n">
-        <v>0.022</v>
+        <v>0.023</v>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" s="37">
@@ -3112,37 +3106,37 @@
         <v>0.041</v>
       </c>
       <c r="D9" s="24" t="n">
-        <v>0.038</v>
+        <v>0.041</v>
       </c>
       <c r="E9" s="24" t="n">
         <v>0.041</v>
       </c>
       <c r="F9" s="24" t="n">
-        <v>0.038</v>
+        <v>0.032</v>
       </c>
       <c r="G9" s="24" t="n">
-        <v>0.041</v>
+        <v>0.043</v>
       </c>
       <c r="H9" s="24" t="n">
-        <v>0.038</v>
+        <v>0.033</v>
       </c>
       <c r="I9" s="24" t="n">
-        <v>0.041</v>
+        <v>0.043</v>
       </c>
       <c r="J9" s="24" t="n">
-        <v>0.038</v>
+        <v>0.046</v>
       </c>
       <c r="K9" s="24" t="n">
-        <v>0.041</v>
+        <v>0.039</v>
       </c>
       <c r="L9" s="24" t="n">
-        <v>0.038</v>
+        <v>0.018</v>
       </c>
       <c r="M9" s="24" t="n">
-        <v>0.041</v>
+        <v>0.045</v>
       </c>
       <c r="N9" s="24" t="n">
-        <v>0.038</v>
+        <v>0.057</v>
       </c>
       <c r="O9" s="24" t="n">
         <v>0.041</v>
@@ -3161,40 +3155,40 @@
         <v>0.018</v>
       </c>
       <c r="D10" s="24" t="n">
-        <v>0.015</v>
+        <v>0.017</v>
       </c>
       <c r="E10" s="24" t="n">
         <v>0.018</v>
       </c>
       <c r="F10" s="24" t="n">
-        <v>0.015</v>
+        <v>0.011</v>
       </c>
       <c r="G10" s="24" t="n">
-        <v>0.018</v>
+        <v>0.019</v>
       </c>
       <c r="H10" s="24" t="n">
-        <v>0.015</v>
+        <v>0.012</v>
       </c>
       <c r="I10" s="24" t="n">
-        <v>0.018</v>
+        <v>0.019</v>
       </c>
       <c r="J10" s="24" t="n">
-        <v>0.015</v>
+        <v>0.02</v>
       </c>
       <c r="K10" s="24" t="n">
-        <v>0.018</v>
+        <v>0.017</v>
       </c>
       <c r="L10" s="24" t="n">
-        <v>0.015</v>
+        <v>0.003</v>
       </c>
       <c r="M10" s="24" t="n">
-        <v>0.018</v>
+        <v>0.021</v>
       </c>
       <c r="N10" s="24" t="n">
-        <v>0.015</v>
+        <v>0.025</v>
       </c>
       <c r="O10" s="24" t="n">
-        <v>0.018</v>
+        <v>0.019</v>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" s="37">
@@ -3213,7 +3207,7 @@
       </c>
       <c r="D11" s="24" t="inlineStr">
         <is>
-          <t>0.091**</t>
+          <t>0.09**</t>
         </is>
       </c>
       <c r="E11" s="24" t="n">
@@ -3221,39 +3215,39 @@
       </c>
       <c r="F11" s="24" t="inlineStr">
         <is>
-          <t>0.091**</t>
+          <t>0.095**</t>
         </is>
       </c>
       <c r="G11" s="24" t="n">
-        <v>0.034</v>
+        <v>0.035</v>
       </c>
       <c r="H11" s="24" t="inlineStr">
         <is>
-          <t>0.091**</t>
+          <t>0.094**</t>
         </is>
       </c>
       <c r="I11" s="24" t="n">
-        <v>0.034</v>
+        <v>0.035</v>
       </c>
       <c r="J11" s="24" t="inlineStr">
         <is>
-          <t>0.091**</t>
+          <t>0.081*</t>
         </is>
       </c>
       <c r="K11" s="24" t="n">
-        <v>0.034</v>
+        <v>0.033</v>
       </c>
       <c r="L11" s="24" t="inlineStr">
         <is>
-          <t>0.091**</t>
+          <t>0.114**</t>
         </is>
       </c>
       <c r="M11" s="24" t="n">
-        <v>0.034</v>
+        <v>0.037</v>
       </c>
       <c r="N11" s="24" t="inlineStr">
         <is>
-          <t>0.091**</t>
+          <t>0.066†</t>
         </is>
       </c>
       <c r="O11" s="24" t="n">
@@ -3268,35 +3262,43 @@
       </c>
       <c r="B12" s="24" t="inlineStr">
         <is>
-          <t>0.428***</t>
-        </is>
-      </c>
-      <c r="C12" s="24" t="n">
-        <v>0.047</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C12" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="D12" s="24" t="inlineStr">
         <is>
-          <t>0.428***</t>
-        </is>
-      </c>
-      <c r="E12" s="24" t="n">
-        <v>0.047</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E12" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="F12" s="24" t="inlineStr">
         <is>
-          <t>0.428***</t>
-        </is>
-      </c>
-      <c r="G12" s="24" t="n">
-        <v>0.047</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="H12" s="24" t="inlineStr">
         <is>
-          <t>0.428***</t>
-        </is>
-      </c>
-      <c r="I12" s="24" t="n">
-        <v>0.047</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I12" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="J12" s="24" t="inlineStr">
         <is>
@@ -3308,19 +3310,23 @@
       </c>
       <c r="L12" s="24" t="inlineStr">
         <is>
-          <t>0.428***</t>
-        </is>
-      </c>
-      <c r="M12" s="24" t="n">
-        <v>0.047</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M12" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="N12" s="24" t="inlineStr">
         <is>
-          <t>0.428***</t>
-        </is>
-      </c>
-      <c r="O12" s="24" t="n">
-        <v>0.047</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O12" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="37">

--- a/results/Model3.xlsx
+++ b/results/Model3.xlsx
@@ -1642,28 +1642,28 @@
         </is>
       </c>
       <c r="B4" s="35" t="n">
-        <v>1758.4</v>
+        <v>1762.4</v>
       </c>
       <c r="C4" s="35" t="n">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="D4" s="35" t="n">
-        <v>0.955</v>
+        <v>0.954</v>
       </c>
       <c r="E4" s="35" t="n">
-        <v>0.946</v>
+        <v>0.945</v>
       </c>
       <c r="F4" s="35" t="n">
-        <v>0.042</v>
+        <v>0.043</v>
       </c>
       <c r="G4" s="35" t="n">
-        <v>0.038</v>
+        <v>0.039</v>
       </c>
       <c r="H4" s="35" t="n">
-        <v>0.01</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="I4" s="35" t="n">
-        <v>-0.002</v>
+        <v>-0.001</v>
       </c>
       <c r="J4" s="36" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
       <c r="I5" s="35" t="n"/>
       <c r="J5" s="35" t="inlineStr">
         <is>
-          <t>Method factor explains 11.6%</t>
+          <t>Method factor explains 10.8%</t>
         </is>
       </c>
       <c r="K5" s="35" t="n"/>
@@ -1857,28 +1857,28 @@
         </is>
       </c>
       <c r="D4" s="32" t="n">
-        <v>2108.2</v>
+        <v>2189.7</v>
       </c>
       <c r="E4" s="32" t="n">
         <v>877</v>
       </c>
       <c r="F4" s="32" t="n">
-        <v>0.926</v>
+        <v>0.921</v>
       </c>
       <c r="G4" s="32" t="n">
-        <v>0.918</v>
+        <v>0.913</v>
       </c>
       <c r="H4" s="32" t="n">
-        <v>0.052</v>
+        <v>0.056</v>
       </c>
       <c r="I4" s="32" t="n">
-        <v>0.048</v>
+        <v>0.049</v>
       </c>
       <c r="J4" s="32" t="n">
-        <v>0.061</v>
+        <v>0.063</v>
       </c>
       <c r="K4" s="32" t="n">
-        <v>31398.5</v>
+        <v>31472.1</v>
       </c>
     </row>
     <row r="5" ht="46.5" customHeight="1" s="37">
@@ -1898,28 +1898,28 @@
         </is>
       </c>
       <c r="D5" s="32" t="n">
-        <v>2287.6</v>
+        <v>2378.4</v>
       </c>
       <c r="E5" s="32" t="n">
         <v>877</v>
       </c>
       <c r="F5" s="32" t="n">
-        <v>0.913</v>
+        <v>0.906</v>
       </c>
       <c r="G5" s="32" t="n">
-        <v>0.904</v>
+        <v>0.897</v>
       </c>
       <c r="H5" s="32" t="n">
-        <v>0.057</v>
+        <v>0.062</v>
       </c>
       <c r="I5" s="32" t="n">
-        <v>0.05</v>
+        <v>0.053</v>
       </c>
       <c r="J5" s="32" t="n">
-        <v>0.075</v>
+        <v>0.077</v>
       </c>
       <c r="K5" s="32" t="n">
-        <v>31573.9</v>
+        <v>31654.6</v>
       </c>
     </row>
     <row r="6" ht="69.75" customHeight="1" s="37">
@@ -1939,28 +1939,28 @@
         </is>
       </c>
       <c r="D6" s="32" t="n">
-        <v>2541.3</v>
+        <v>2614.9</v>
       </c>
       <c r="E6" s="32" t="n">
         <v>882</v>
       </c>
       <c r="F6" s="32" t="n">
-        <v>0.892</v>
+        <v>0.89</v>
       </c>
       <c r="G6" s="32" t="n">
-        <v>0.881</v>
+        <v>0.878</v>
       </c>
       <c r="H6" s="32" t="n">
-        <v>0.064</v>
+        <v>0.066</v>
       </c>
       <c r="I6" s="32" t="n">
-        <v>0.057</v>
+        <v>0.058</v>
       </c>
       <c r="J6" s="32" t="n">
-        <v>0.073</v>
+        <v>0.076</v>
       </c>
       <c r="K6" s="32" t="n">
-        <v>31814.2</v>
+        <v>31881.3</v>
       </c>
     </row>
     <row r="7" ht="46.5" customHeight="1" s="37">
@@ -1980,28 +1980,28 @@
         </is>
       </c>
       <c r="D7" s="32" t="n">
-        <v>3294.7</v>
+        <v>3413.1</v>
       </c>
       <c r="E7" s="32" t="n">
         <v>887</v>
       </c>
       <c r="F7" s="32" t="n">
-        <v>0.821</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="G7" s="32" t="n">
-        <v>0.8080000000000001</v>
+        <v>0.798</v>
       </c>
       <c r="H7" s="32" t="n">
-        <v>0.083</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="I7" s="32" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="J7" s="32" t="n">
-        <v>0.097</v>
+        <v>0.099</v>
       </c>
       <c r="K7" s="32" t="n">
-        <v>32508.6</v>
+        <v>32622.4</v>
       </c>
     </row>
   </sheetData>
@@ -2108,10 +2108,10 @@
         </is>
       </c>
       <c r="B4" s="24" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.531</v>
       </c>
       <c r="C4" s="24" t="n">
-        <v>0.486</v>
+        <v>0.488</v>
       </c>
       <c r="D4" s="24" t="inlineStr">
         <is>
@@ -2139,13 +2139,13 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>30.767</v>
+        <v>30.962</v>
       </c>
       <c r="C5" s="24" t="n">
-        <v>4.607</v>
+        <v>4.55</v>
       </c>
       <c r="D5" s="24" t="n">
-        <v>0.028</v>
+        <v>0.032</v>
       </c>
       <c r="E5" s="24" t="inlineStr">
         <is>
@@ -2172,17 +2172,17 @@
         </is>
       </c>
       <c r="B6" s="24" t="n">
-        <v>2.376</v>
+        <v>2.374</v>
       </c>
       <c r="C6" s="24" t="n">
-        <v>1.52</v>
+        <v>1.496</v>
       </c>
       <c r="D6" s="24" t="n">
-        <v>-0.021</v>
+        <v>-0.001</v>
       </c>
       <c r="E6" s="24" t="inlineStr">
         <is>
-          <t>0.194***</t>
+          <t>0.171**</t>
         </is>
       </c>
       <c r="F6" s="24" t="inlineStr">
@@ -2209,19 +2209,19 @@
         </is>
       </c>
       <c r="B7" s="24" t="n">
-        <v>3.279</v>
+        <v>3.328</v>
       </c>
       <c r="C7" s="24" t="n">
-        <v>1.066</v>
+        <v>1.072</v>
       </c>
       <c r="D7" s="24" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.079</v>
       </c>
       <c r="E7" s="24" t="n">
-        <v>-0.001</v>
+        <v>-0.011</v>
       </c>
       <c r="F7" s="24" t="n">
-        <v>-0.052</v>
+        <v>-0.08599999999999999</v>
       </c>
       <c r="G7" s="24" t="inlineStr">
         <is>
@@ -2246,22 +2246,24 @@
         </is>
       </c>
       <c r="B8" s="24" t="n">
-        <v>4.048</v>
+        <v>4.115</v>
       </c>
       <c r="C8" s="24" t="n">
-        <v>0.854</v>
+        <v>0.886</v>
       </c>
       <c r="D8" s="24" t="n">
-        <v>-0.017</v>
+        <v>-0.019</v>
       </c>
       <c r="E8" s="24" t="n">
-        <v>-0.001</v>
-      </c>
-      <c r="F8" s="24" t="n">
-        <v>0.08500000000000001</v>
+        <v>-0.005</v>
+      </c>
+      <c r="F8" s="24" t="inlineStr">
+        <is>
+          <t>0.109*</t>
+        </is>
       </c>
       <c r="G8" s="24" t="n">
-        <v>-0.034</v>
+        <v>-0.007</v>
       </c>
       <c r="H8" s="23" t="inlineStr">
         <is>
@@ -2285,26 +2287,26 @@
         </is>
       </c>
       <c r="B9" s="24" t="n">
-        <v>4.959</v>
+        <v>4.919</v>
       </c>
       <c r="C9" s="24" t="n">
-        <v>0.9389999999999999</v>
+        <v>0.921</v>
       </c>
       <c r="D9" s="24" t="n">
-        <v>-0.027</v>
+        <v>-0.02</v>
       </c>
       <c r="E9" s="24" t="n">
-        <v>-0.056</v>
+        <v>-0.013</v>
       </c>
       <c r="F9" s="24" t="n">
-        <v>0.025</v>
+        <v>0.028</v>
       </c>
       <c r="G9" s="24" t="n">
-        <v>-0.079</v>
+        <v>-0.053</v>
       </c>
       <c r="H9" s="24" t="inlineStr">
         <is>
-          <t>-0.315***</t>
+          <t>-0.33***</t>
         </is>
       </c>
       <c r="I9" s="24" t="inlineStr">
@@ -2328,28 +2330,28 @@
         </is>
       </c>
       <c r="B10" s="24" t="n">
-        <v>3.465</v>
+        <v>3.484</v>
       </c>
       <c r="C10" s="24" t="n">
-        <v>0.916</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="D10" s="24" t="n">
-        <v>-0.077</v>
+        <v>-0.08500000000000001</v>
       </c>
       <c r="E10" s="24" t="n">
-        <v>-0.026</v>
+        <v>-0.062</v>
       </c>
       <c r="F10" s="24" t="n">
-        <v>0.038</v>
+        <v>0.044</v>
       </c>
       <c r="G10" s="24" t="n">
-        <v>-0.033</v>
+        <v>-0.068</v>
       </c>
       <c r="H10" s="24" t="n">
-        <v>-0.008999999999999999</v>
+        <v>-0.014</v>
       </c>
       <c r="I10" s="24" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.091</v>
       </c>
       <c r="J10" s="24" t="inlineStr">
         <is>
@@ -2371,31 +2373,33 @@
         </is>
       </c>
       <c r="B11" s="24" t="n">
-        <v>4.597</v>
+        <v>4.639</v>
       </c>
       <c r="C11" s="24" t="n">
-        <v>0.902</v>
+        <v>0.892</v>
       </c>
       <c r="D11" s="24" t="n">
-        <v>-0.09</v>
+        <v>-0.068</v>
       </c>
       <c r="E11" s="24" t="n">
-        <v>-0.089</v>
-      </c>
-      <c r="F11" s="24" t="n">
-        <v>-0.08699999999999999</v>
+        <v>-0.08</v>
+      </c>
+      <c r="F11" s="24" t="inlineStr">
+        <is>
+          <t>-0.12*</t>
+        </is>
       </c>
       <c r="G11" s="24" t="n">
-        <v>-0.099</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="H11" s="24" t="n">
-        <v>-0.06900000000000001</v>
+        <v>-0.078</v>
       </c>
       <c r="I11" s="24" t="n">
-        <v>-0.039</v>
+        <v>-0.024</v>
       </c>
       <c r="J11" s="24" t="n">
-        <v>-0.002</v>
+        <v>0.007</v>
       </c>
       <c r="K11" s="24" t="inlineStr">
         <is>
@@ -2416,38 +2420,38 @@
         </is>
       </c>
       <c r="B12" s="24" t="n">
-        <v>4.542</v>
+        <v>4.483</v>
       </c>
       <c r="C12" s="24" t="n">
-        <v>1.214</v>
+        <v>1.205</v>
       </c>
       <c r="D12" s="24" t="n">
-        <v>-0.06</v>
+        <v>-0.07099999999999999</v>
       </c>
       <c r="E12" s="24" t="n">
-        <v>-0.014</v>
+        <v>0.031</v>
       </c>
       <c r="F12" s="24" t="n">
-        <v>-0.049</v>
+        <v>-0.037</v>
       </c>
       <c r="G12" s="24" t="n">
-        <v>-0.061</v>
+        <v>-0.037</v>
       </c>
       <c r="H12" s="24" t="inlineStr">
         <is>
-          <t>-0.519***</t>
+          <t>-0.524***</t>
         </is>
       </c>
       <c r="I12" s="24" t="inlineStr">
         <is>
-          <t>0.523***</t>
+          <t>0.498***</t>
         </is>
       </c>
       <c r="J12" s="24" t="n">
-        <v>-0.003</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="K12" s="24" t="n">
-        <v>-0.035</v>
+        <v>-0.023</v>
       </c>
       <c r="L12" s="24" t="inlineStr">
         <is>
@@ -2467,42 +2471,44 @@
         </is>
       </c>
       <c r="B13" s="24" t="n">
-        <v>3.017</v>
+        <v>3.07</v>
       </c>
       <c r="C13" s="24" t="n">
-        <v>1.181</v>
+        <v>1.213</v>
       </c>
       <c r="D13" s="24" t="n">
-        <v>0.034</v>
+        <v>0.031</v>
       </c>
       <c r="E13" s="24" t="n">
-        <v>0.001</v>
+        <v>0.013</v>
       </c>
       <c r="F13" s="24" t="n">
-        <v>-0.014</v>
+        <v>0.008</v>
       </c>
       <c r="G13" s="24" t="n">
-        <v>0.038</v>
+        <v>0.031</v>
       </c>
       <c r="H13" s="24" t="inlineStr">
         <is>
-          <t>0.505***</t>
+          <t>0.52***</t>
         </is>
       </c>
       <c r="I13" s="24" t="inlineStr">
         <is>
-          <t>-0.516***</t>
+          <t>-0.506***</t>
         </is>
       </c>
       <c r="J13" s="24" t="n">
-        <v>0.032</v>
-      </c>
-      <c r="K13" s="24" t="n">
-        <v>-0.082</v>
+        <v>0.025</v>
+      </c>
+      <c r="K13" s="24" t="inlineStr">
+        <is>
+          <t>-0.106*</t>
+        </is>
       </c>
       <c r="L13" s="24" t="inlineStr">
         <is>
-          <t>-0.46***</t>
+          <t>-0.446***</t>
         </is>
       </c>
       <c r="M13" s="24" t="inlineStr">
@@ -2522,44 +2528,46 @@
         </is>
       </c>
       <c r="B14" s="24" t="n">
-        <v>4.428</v>
+        <v>4.419</v>
       </c>
       <c r="C14" s="24" t="n">
-        <v>0.605</v>
+        <v>0.61</v>
       </c>
       <c r="D14" s="24" t="n">
-        <v>0.028</v>
+        <v>0.021</v>
       </c>
       <c r="E14" s="24" t="n">
-        <v>0.034</v>
+        <v>-0.031</v>
       </c>
       <c r="F14" s="24" t="n">
-        <v>-0.03</v>
+        <v>0.006</v>
       </c>
       <c r="G14" s="24" t="n">
-        <v>0.007</v>
+        <v>-0.042</v>
       </c>
       <c r="H14" s="24" t="n">
-        <v>0.055</v>
+        <v>0.031</v>
       </c>
       <c r="I14" s="24" t="n">
-        <v>-0.022</v>
-      </c>
-      <c r="J14" s="24" t="n">
-        <v>-0.091</v>
+        <v>-0.043</v>
+      </c>
+      <c r="J14" s="24" t="inlineStr">
+        <is>
+          <t>-0.155**</t>
+        </is>
       </c>
       <c r="K14" s="24" t="n">
-        <v>-0.034</v>
+        <v>-0.038</v>
       </c>
       <c r="L14" s="24" t="n">
-        <v>-0.013</v>
+        <v>-0.031</v>
       </c>
       <c r="M14" s="24" t="n">
-        <v>0.053</v>
+        <v>0.076</v>
       </c>
       <c r="N14" s="24" t="inlineStr">
         <is>
-          <t>(0.75)</t>
+          <t>(0.82)</t>
         </is>
       </c>
       <c r="O14" s="24" t="n"/>
@@ -2573,52 +2581,54 @@
         </is>
       </c>
       <c r="B15" s="24" t="n">
-        <v>4.521</v>
+        <v>4.526</v>
       </c>
       <c r="C15" s="24" t="n">
-        <v>0.821</v>
+        <v>0.794</v>
       </c>
       <c r="D15" s="24" t="n">
-        <v>-0.016</v>
+        <v>-0.018</v>
       </c>
       <c r="E15" s="24" t="n">
-        <v>-0.028</v>
+        <v>-0.032</v>
       </c>
       <c r="F15" s="24" t="n">
-        <v>-0.038</v>
+        <v>0.007</v>
       </c>
       <c r="G15" s="24" t="n">
-        <v>-0.045</v>
+        <v>-0.033</v>
       </c>
       <c r="H15" s="24" t="inlineStr">
         <is>
-          <t>-0.404***</t>
+          <t>-0.412***</t>
         </is>
       </c>
       <c r="I15" s="24" t="inlineStr">
         <is>
-          <t>0.408***</t>
-        </is>
-      </c>
-      <c r="J15" s="24" t="n">
-        <v>-0.054</v>
+          <t>0.407***</t>
+        </is>
+      </c>
+      <c r="J15" s="24" t="inlineStr">
+        <is>
+          <t>-0.14**</t>
+        </is>
       </c>
       <c r="K15" s="24" t="n">
-        <v>-0.008</v>
+        <v>-0.005</v>
       </c>
       <c r="L15" s="24" t="inlineStr">
         <is>
-          <t>0.574***</t>
+          <t>0.598***</t>
         </is>
       </c>
       <c r="M15" s="24" t="inlineStr">
         <is>
-          <t>-0.583***</t>
+          <t>-0.586***</t>
         </is>
       </c>
       <c r="N15" s="24" t="inlineStr">
         <is>
-          <t>0.425***</t>
+          <t>0.361***</t>
         </is>
       </c>
       <c r="O15" s="24" t="inlineStr">
@@ -2636,55 +2646,55 @@
         </is>
       </c>
       <c r="B16" s="24" t="n">
-        <v>4.987</v>
+        <v>5.006</v>
       </c>
       <c r="C16" s="24" t="n">
-        <v>1.097</v>
+        <v>1.003</v>
       </c>
       <c r="D16" s="24" t="n">
-        <v>-0.08500000000000001</v>
+        <v>-0.08799999999999999</v>
       </c>
       <c r="E16" s="24" t="n">
-        <v>0.011</v>
+        <v>0.001</v>
       </c>
       <c r="F16" s="24" t="n">
-        <v>-0.007</v>
+        <v>-0.077</v>
       </c>
       <c r="G16" s="24" t="n">
-        <v>-0.041</v>
+        <v>-0.083</v>
       </c>
       <c r="H16" s="24" t="inlineStr">
         <is>
-          <t>-0.338***</t>
+          <t>-0.327***</t>
         </is>
       </c>
       <c r="I16" s="24" t="inlineStr">
         <is>
-          <t>0.326***</t>
+          <t>0.349***</t>
         </is>
       </c>
       <c r="J16" s="24" t="n">
-        <v>-0.03</v>
+        <v>-0.047</v>
       </c>
       <c r="K16" s="24" t="n">
-        <v>0.066</v>
+        <v>0.008</v>
       </c>
       <c r="L16" s="24" t="inlineStr">
         <is>
-          <t>0.516***</t>
+          <t>0.418***</t>
         </is>
       </c>
       <c r="M16" s="24" t="inlineStr">
         <is>
-          <t>-0.573***</t>
+          <t>-0.504***</t>
         </is>
       </c>
       <c r="N16" s="24" t="n">
-        <v>0.016</v>
+        <v>0.048</v>
       </c>
       <c r="O16" s="24" t="inlineStr">
         <is>
-          <t>0.481***</t>
+          <t>0.474***</t>
         </is>
       </c>
       <c r="P16" s="24" t="inlineStr">
@@ -2701,60 +2711,62 @@
         </is>
       </c>
       <c r="B17" s="24" t="n">
-        <v>2.674</v>
+        <v>2.6</v>
       </c>
       <c r="C17" s="24" t="n">
-        <v>1.14</v>
+        <v>1.057</v>
       </c>
       <c r="D17" s="24" t="n">
-        <v>0.078</v>
+        <v>0.013</v>
       </c>
       <c r="E17" s="24" t="n">
-        <v>0.011</v>
+        <v>0.026</v>
       </c>
       <c r="F17" s="24" t="n">
-        <v>-0.014</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="G17" s="24" t="n">
-        <v>0.05</v>
+        <v>0.007</v>
       </c>
       <c r="H17" s="24" t="inlineStr">
         <is>
-          <t>0.421***</t>
+          <t>0.425***</t>
         </is>
       </c>
       <c r="I17" s="24" t="inlineStr">
         <is>
-          <t>-0.441***</t>
+          <t>-0.309***</t>
         </is>
       </c>
       <c r="J17" s="24" t="n">
-        <v>-0.047</v>
+        <v>0.031</v>
       </c>
       <c r="K17" s="24" t="n">
-        <v>0.046</v>
+        <v>-0.003</v>
       </c>
       <c r="L17" s="24" t="inlineStr">
         <is>
-          <t>-0.519***</t>
+          <t>-0.473***</t>
         </is>
       </c>
       <c r="M17" s="24" t="inlineStr">
         <is>
-          <t>0.642***</t>
-        </is>
-      </c>
-      <c r="N17" s="24" t="n">
-        <v>0.08599999999999999</v>
+          <t>0.49***</t>
+        </is>
+      </c>
+      <c r="N17" s="24" t="inlineStr">
+        <is>
+          <t>0.121*</t>
+        </is>
       </c>
       <c r="O17" s="24" t="inlineStr">
         <is>
-          <t>-0.425***</t>
+          <t>-0.42***</t>
         </is>
       </c>
       <c r="P17" s="24" t="inlineStr">
         <is>
-          <t>-0.473***</t>
+          <t>-0.5***</t>
         </is>
       </c>
       <c r="Q17" s="24" t="inlineStr">
@@ -3302,11 +3314,11 @@
       </c>
       <c r="J12" s="24" t="inlineStr">
         <is>
-          <t>0.428***</t>
+          <t>0.412***</t>
         </is>
       </c>
       <c r="K12" s="24" t="n">
-        <v>0.047</v>
+        <v>0.048</v>
       </c>
       <c r="L12" s="24" t="inlineStr">
         <is>
@@ -3358,35 +3370,35 @@
       </c>
       <c r="B14" s="24" t="inlineStr">
         <is>
-          <t>-0.146**</t>
+          <t>-0.142**</t>
         </is>
       </c>
       <c r="C14" s="24" t="n">
-        <v>0.051</v>
+        <v>0.052</v>
       </c>
       <c r="D14" s="24" t="inlineStr">
         <is>
-          <t>-0.144**</t>
+          <t>-0.14**</t>
         </is>
       </c>
       <c r="E14" s="24" t="n">
-        <v>0.051</v>
+        <v>0.052</v>
       </c>
       <c r="F14" s="24" t="inlineStr">
         <is>
-          <t>0.321***</t>
+          <t>0.312***</t>
         </is>
       </c>
       <c r="G14" s="24" t="n">
-        <v>0.057</v>
+        <v>0.058</v>
       </c>
       <c r="H14" s="24" t="inlineStr">
         <is>
-          <t>0.318***</t>
+          <t>0.309***</t>
         </is>
       </c>
       <c r="I14" s="24" t="n">
-        <v>0.057</v>
+        <v>0.058</v>
       </c>
       <c r="J14" s="24" t="inlineStr">
         <is>
@@ -3421,35 +3433,35 @@
       </c>
       <c r="B15" s="24" t="inlineStr">
         <is>
-          <t>0.275***</t>
+          <t>0.267***</t>
         </is>
       </c>
       <c r="C15" s="24" t="n">
-        <v>0.048</v>
+        <v>0.049</v>
       </c>
       <c r="D15" s="24" t="inlineStr">
         <is>
-          <t>0.268***</t>
+          <t>0.26***</t>
         </is>
       </c>
       <c r="E15" s="24" t="n">
-        <v>0.048</v>
+        <v>0.049</v>
       </c>
       <c r="F15" s="24" t="inlineStr">
         <is>
-          <t>-0.149**</t>
+          <t>-0.145**</t>
         </is>
       </c>
       <c r="G15" s="24" t="n">
-        <v>0.051</v>
+        <v>0.052</v>
       </c>
       <c r="H15" s="24" t="inlineStr">
         <is>
-          <t>-0.144**</t>
+          <t>-0.14**</t>
         </is>
       </c>
       <c r="I15" s="24" t="n">
-        <v>0.051</v>
+        <v>0.052</v>
       </c>
       <c r="J15" s="24" t="inlineStr">
         <is>
@@ -3668,59 +3680,59 @@
       </c>
       <c r="B20" s="24" t="inlineStr">
         <is>
-          <t>-0.122**</t>
+          <t>-0.118*</t>
         </is>
       </c>
       <c r="C20" s="24" t="n">
-        <v>0.045</v>
+        <v>0.046</v>
       </c>
       <c r="D20" s="24" t="inlineStr">
         <is>
-          <t>-0.122**</t>
+          <t>-0.118*</t>
         </is>
       </c>
       <c r="E20" s="24" t="n">
-        <v>0.045</v>
+        <v>0.046</v>
       </c>
       <c r="F20" s="24" t="inlineStr">
         <is>
-          <t>0.221***</t>
+          <t>0.214***</t>
         </is>
       </c>
       <c r="G20" s="24" t="n">
+        <v>0.047</v>
+      </c>
+      <c r="H20" s="24" t="inlineStr">
+        <is>
+          <t>0.214***</t>
+        </is>
+      </c>
+      <c r="I20" s="24" t="n">
+        <v>0.047</v>
+      </c>
+      <c r="J20" s="24" t="inlineStr">
+        <is>
+          <t>-0.118*</t>
+        </is>
+      </c>
+      <c r="K20" s="24" t="n">
         <v>0.046</v>
       </c>
-      <c r="H20" s="24" t="inlineStr">
-        <is>
-          <t>0.221***</t>
-        </is>
-      </c>
-      <c r="I20" s="24" t="n">
+      <c r="L20" s="24" t="inlineStr">
+        <is>
+          <t>-0.118*</t>
+        </is>
+      </c>
+      <c r="M20" s="24" t="n">
         <v>0.046</v>
       </c>
-      <c r="J20" s="24" t="inlineStr">
-        <is>
-          <t>-0.122**</t>
-        </is>
-      </c>
-      <c r="K20" s="24" t="n">
-        <v>0.045</v>
-      </c>
-      <c r="L20" s="24" t="inlineStr">
-        <is>
-          <t>-0.122**</t>
-        </is>
-      </c>
-      <c r="M20" s="24" t="n">
-        <v>0.045</v>
-      </c>
       <c r="N20" s="24" t="inlineStr">
         <is>
-          <t>-0.122**</t>
+          <t>-0.118*</t>
         </is>
       </c>
       <c r="O20" s="24" t="n">
-        <v>0.045</v>
+        <v>0.046</v>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1" s="37">
@@ -3729,61 +3741,51 @@
           <t>Power distance (T1)</t>
         </is>
       </c>
-      <c r="B21" s="24" t="inlineStr">
-        <is>
-          <t>-0.064†</t>
-        </is>
+      <c r="B21" s="24" t="n">
+        <v>-0.062</v>
       </c>
       <c r="C21" s="24" t="n">
-        <v>0.038</v>
-      </c>
-      <c r="D21" s="24" t="inlineStr">
-        <is>
-          <t>-0.064†</t>
-        </is>
+        <v>0.039</v>
+      </c>
+      <c r="D21" s="24" t="n">
+        <v>-0.062</v>
       </c>
       <c r="E21" s="24" t="n">
-        <v>0.038</v>
+        <v>0.039</v>
       </c>
       <c r="F21" s="24" t="inlineStr">
         <is>
-          <t>0.139**</t>
+          <t>0.135**</t>
         </is>
       </c>
       <c r="G21" s="24" t="n">
-        <v>0.044</v>
+        <v>0.045</v>
       </c>
       <c r="H21" s="24" t="inlineStr">
         <is>
-          <t>0.139**</t>
+          <t>0.135**</t>
         </is>
       </c>
       <c r="I21" s="24" t="n">
-        <v>0.044</v>
-      </c>
-      <c r="J21" s="24" t="inlineStr">
-        <is>
-          <t>-0.064†</t>
-        </is>
+        <v>0.045</v>
+      </c>
+      <c r="J21" s="24" t="n">
+        <v>-0.062</v>
       </c>
       <c r="K21" s="24" t="n">
-        <v>0.038</v>
-      </c>
-      <c r="L21" s="24" t="inlineStr">
-        <is>
-          <t>-0.064†</t>
-        </is>
+        <v>0.039</v>
+      </c>
+      <c r="L21" s="24" t="n">
+        <v>-0.062</v>
       </c>
       <c r="M21" s="24" t="n">
-        <v>0.038</v>
-      </c>
-      <c r="N21" s="24" t="inlineStr">
-        <is>
-          <t>-0.064†</t>
-        </is>
+        <v>0.039</v>
+      </c>
+      <c r="N21" s="24" t="n">
+        <v>-0.062</v>
       </c>
       <c r="O21" s="24" t="n">
-        <v>0.038</v>
+        <v>0.039</v>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1" s="37">
@@ -3824,10 +3826,10 @@
         </is>
       </c>
       <c r="D23" s="24" t="n">
-        <v>-0.014</v>
+        <v>-0.012</v>
       </c>
       <c r="E23" s="24" t="n">
-        <v>0.043</v>
+        <v>0.044</v>
       </c>
       <c r="F23" s="24" t="inlineStr">
         <is>
@@ -3840,10 +3842,10 @@
         </is>
       </c>
       <c r="H23" s="24" t="n">
-        <v>0.027</v>
+        <v>0.024</v>
       </c>
       <c r="I23" s="24" t="n">
-        <v>0.045</v>
+        <v>0.046</v>
       </c>
       <c r="J23" s="24" t="inlineStr">
         <is>
@@ -3893,10 +3895,10 @@
         </is>
       </c>
       <c r="D24" s="24" t="n">
-        <v>0.021</v>
+        <v>0.018</v>
       </c>
       <c r="E24" s="24" t="n">
-        <v>0.036</v>
+        <v>0.037</v>
       </c>
       <c r="F24" s="24" t="inlineStr">
         <is>
@@ -3909,10 +3911,10 @@
         </is>
       </c>
       <c r="H24" s="24" t="n">
-        <v>-0.022</v>
+        <v>-0.019</v>
       </c>
       <c r="I24" s="24" t="n">
-        <v>0.047</v>
+        <v>0.048</v>
       </c>
       <c r="J24" s="24" t="inlineStr">
         <is>
@@ -3962,10 +3964,10 @@
         </is>
       </c>
       <c r="D25" s="24" t="n">
-        <v>0.049</v>
+        <v>0.046</v>
       </c>
       <c r="E25" s="24" t="n">
-        <v>0.04</v>
+        <v>0.041</v>
       </c>
       <c r="F25" s="24" t="inlineStr">
         <is>
@@ -3979,11 +3981,11 @@
       </c>
       <c r="H25" s="24" t="inlineStr">
         <is>
-          <t>-0.116**</t>
+          <t>-0.111**</t>
         </is>
       </c>
       <c r="I25" s="24" t="n">
-        <v>0.038</v>
+        <v>0.039</v>
       </c>
       <c r="J25" s="24" t="inlineStr">
         <is>
@@ -4034,11 +4036,11 @@
       </c>
       <c r="D26" s="24" t="inlineStr">
         <is>
-          <t>-0.101*</t>
+          <t>-0.098*</t>
         </is>
       </c>
       <c r="E26" s="24" t="n">
-        <v>0.044</v>
+        <v>0.045</v>
       </c>
       <c r="F26" s="24" t="inlineStr">
         <is>
@@ -4051,10 +4053,10 @@
         </is>
       </c>
       <c r="H26" s="24" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.067</v>
       </c>
       <c r="I26" s="24" t="n">
-        <v>0.051</v>
+        <v>0.052</v>
       </c>
       <c r="J26" s="24" t="inlineStr">
         <is>
@@ -4303,32 +4305,32 @@
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>-0.035*</t>
+          <t>-0.033*</t>
         </is>
       </c>
       <c r="C8" s="14" t="inlineStr">
         <is>
-          <t>[-0.066, -0.014]</t>
+          <t>[-0.063, -0.012]</t>
         </is>
       </c>
       <c r="D8" s="14" t="inlineStr">
         <is>
-          <t>-0.033*</t>
+          <t>-0.034*</t>
         </is>
       </c>
       <c r="E8" s="14" t="inlineStr">
         <is>
-          <t>[-0.063, -0.013]</t>
+          <t>[-0.065, -0.014]</t>
         </is>
       </c>
       <c r="F8" s="14" t="inlineStr">
         <is>
-          <t>0.012*</t>
+          <t>0.013*</t>
         </is>
       </c>
       <c r="G8" s="14" t="inlineStr">
         <is>
-          <t>[0.001, 0.024]</t>
+          <t>[0.002, 0.025]</t>
         </is>
       </c>
     </row>
@@ -4351,28 +4353,30 @@
           <t>High narcissism (+1 SD)</t>
         </is>
       </c>
-      <c r="B10" s="14" t="n">
-        <v>-0.032</v>
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t>-0.04*</t>
+        </is>
       </c>
       <c r="C10" s="14" t="inlineStr">
         <is>
-          <t>[-0.067, 0.003]</t>
+          <t>[-0.079, -0.001]</t>
         </is>
       </c>
       <c r="D10" s="14" t="n">
-        <v>-0.03</v>
+        <v>-0.026</v>
       </c>
       <c r="E10" s="14" t="inlineStr">
         <is>
-          <t>[-0.064, 0.004]</t>
+          <t>[-0.058, 0.006]</t>
         </is>
       </c>
       <c r="F10" s="14" t="n">
-        <v>0.011</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="G10" s="14" t="inlineStr">
         <is>
-          <t>[-0.014, 0.036]</t>
+          <t>[-0.015, 0.033]</t>
         </is>
       </c>
     </row>
@@ -4383,27 +4387,29 @@
         </is>
       </c>
       <c r="B11" s="14" t="n">
-        <v>-0.038</v>
+        <v>-0.021</v>
       </c>
       <c r="C11" s="14" t="inlineStr">
         <is>
-          <t>[-0.076, 0.000]</t>
-        </is>
-      </c>
-      <c r="D11" s="14" t="n">
-        <v>-0.036</v>
+          <t>[-0.051, 0.009]</t>
+        </is>
+      </c>
+      <c r="D11" s="14" t="inlineStr">
+        <is>
+          <t>-0.045*</t>
+        </is>
       </c>
       <c r="E11" s="14" t="inlineStr">
         <is>
-          <t>[-0.073, 0.001]</t>
+          <t>[-0.087, -0.003]</t>
         </is>
       </c>
       <c r="F11" s="14" t="n">
-        <v>0.013</v>
+        <v>0.018</v>
       </c>
       <c r="G11" s="14" t="inlineStr">
         <is>
-          <t>[-0.013, 0.039]</t>
+          <t>[-0.010, 0.046]</t>
         </is>
       </c>
     </row>
@@ -4414,27 +4420,27 @@
         </is>
       </c>
       <c r="B12" s="14" t="n">
-        <v>0.006</v>
+        <v>-0.019</v>
       </c>
       <c r="C12" s="14" t="inlineStr">
         <is>
-          <t>[-0.018, 0.030]</t>
+          <t>[-0.048, 0.010]</t>
         </is>
       </c>
       <c r="D12" s="14" t="n">
-        <v>0.007</v>
+        <v>0.019</v>
       </c>
       <c r="E12" s="14" t="inlineStr">
         <is>
-          <t>[-0.017, 0.031]</t>
+          <t>[-0.010, 0.048]</t>
         </is>
       </c>
       <c r="F12" s="14" t="n">
-        <v>-0.003</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="G12" s="14" t="inlineStr">
         <is>
-          <t>[-0.027, 0.021]</t>
+          <t>[-0.033, 0.015]</t>
         </is>
       </c>
     </row>
@@ -4458,27 +4464,27 @@
         </is>
       </c>
       <c r="B14" s="14" t="n">
-        <v>-0.014</v>
+        <v>-0.012</v>
       </c>
       <c r="C14" s="14" t="inlineStr">
         <is>
-          <t>[-0.040, 0.012]</t>
+          <t>[-0.037, 0.013]</t>
         </is>
       </c>
       <c r="D14" s="14" t="n">
-        <v>-0.013</v>
+        <v>-0.016</v>
       </c>
       <c r="E14" s="14" t="inlineStr">
         <is>
-          <t>[-0.039, 0.013]</t>
+          <t>[-0.043, 0.011]</t>
         </is>
       </c>
       <c r="F14" s="14" t="n">
-        <v>0.005</v>
+        <v>0.007</v>
       </c>
       <c r="G14" s="14" t="inlineStr">
         <is>
-          <t>[-0.019, 0.029]</t>
+          <t>[-0.017, 0.031]</t>
         </is>
       </c>
     </row>
@@ -4490,30 +4496,30 @@
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>-0.056*</t>
+          <t>-0.061*</t>
         </is>
       </c>
       <c r="C15" s="14" t="inlineStr">
         <is>
-          <t>[-0.103, -0.009]</t>
+          <t>[-0.110, -0.012]</t>
         </is>
       </c>
       <c r="D15" s="14" t="inlineStr">
         <is>
-          <t>-0.052*</t>
+          <t>-0.048*</t>
         </is>
       </c>
       <c r="E15" s="14" t="inlineStr">
         <is>
-          <t>[-0.097, -0.007]</t>
+          <t>[-0.091, -0.005]</t>
         </is>
       </c>
       <c r="F15" s="14" t="n">
-        <v>0.019</v>
+        <v>0.018</v>
       </c>
       <c r="G15" s="14" t="inlineStr">
         <is>
-          <t>[-0.010, 0.048]</t>
+          <t>[-0.010, 0.046]</t>
         </is>
       </c>
     </row>
@@ -4525,30 +4531,28 @@
       </c>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t>0.042*</t>
+          <t>0.05*</t>
         </is>
       </c>
       <c r="C16" s="14" t="inlineStr">
         <is>
-          <t>[0.002, 0.082]</t>
-        </is>
-      </c>
-      <c r="D16" s="14" t="inlineStr">
-        <is>
-          <t>0.04*</t>
-        </is>
+          <t>[0.006, 0.094]</t>
+        </is>
+      </c>
+      <c r="D16" s="14" t="n">
+        <v>0.032</v>
       </c>
       <c r="E16" s="14" t="inlineStr">
         <is>
-          <t>[0.001, 0.079]</t>
+          <t>[-0.003, 0.067]</t>
         </is>
       </c>
       <c r="F16" s="14" t="n">
-        <v>-0.015</v>
+        <v>-0.011</v>
       </c>
       <c r="G16" s="14" t="inlineStr">
         <is>
-          <t>[-0.042, 0.012]</t>
+          <t>[-0.036, 0.014]</t>
         </is>
       </c>
     </row>
@@ -4573,32 +4577,32 @@
       </c>
       <c r="B18" s="16" t="inlineStr">
         <is>
+          <t>0.062*</t>
+        </is>
+      </c>
+      <c r="C18" s="16" t="inlineStr">
+        <is>
+          <t>[0.034, 0.094]</t>
+        </is>
+      </c>
+      <c r="D18" s="16" t="inlineStr">
+        <is>
           <t>0.066*</t>
         </is>
       </c>
-      <c r="C18" s="16" t="inlineStr">
-        <is>
-          <t>[0.038, 0.099]</t>
-        </is>
-      </c>
-      <c r="D18" s="16" t="inlineStr">
-        <is>
-          <t>0.063*</t>
-        </is>
-      </c>
       <c r="E18" s="16" t="inlineStr">
         <is>
-          <t>[0.034, 0.093]</t>
+          <t>[0.036, 0.097]</t>
         </is>
       </c>
       <c r="F18" s="16" t="inlineStr">
         <is>
-          <t>-0.023*</t>
+          <t>-0.026*</t>
         </is>
       </c>
       <c r="G18" s="16" t="inlineStr">
         <is>
-          <t>[-0.046, -0.005]</t>
+          <t>[-0.049, -0.005]</t>
         </is>
       </c>
     </row>
@@ -4623,30 +4627,30 @@
       </c>
       <c r="B20" s="16" t="inlineStr">
         <is>
-          <t>0.07*</t>
+          <t>0.077*</t>
         </is>
       </c>
       <c r="C20" s="16" t="inlineStr">
         <is>
-          <t>[0.016, 0.124]</t>
+          <t>[0.020, 0.134]</t>
         </is>
       </c>
       <c r="D20" s="16" t="inlineStr">
         <is>
-          <t>0.068*</t>
+          <t>0.066*</t>
         </is>
       </c>
       <c r="E20" s="16" t="inlineStr">
         <is>
-          <t>[0.015, 0.121]</t>
+          <t>[0.014, 0.118]</t>
         </is>
       </c>
       <c r="F20" s="16" t="n">
-        <v>-0.025</v>
+        <v>-0.031</v>
       </c>
       <c r="G20" s="16" t="inlineStr">
         <is>
-          <t>[-0.057, 0.007]</t>
+          <t>[-0.066, 0.004]</t>
         </is>
       </c>
     </row>
@@ -4658,22 +4662,22 @@
       </c>
       <c r="B21" s="16" t="inlineStr">
         <is>
-          <t>0.061*</t>
+          <t>0.054*</t>
         </is>
       </c>
       <c r="C21" s="16" t="inlineStr">
         <is>
-          <t>[0.012, 0.110]</t>
+          <t>[0.008, 0.100]</t>
         </is>
       </c>
       <c r="D21" s="16" t="inlineStr">
         <is>
-          <t>0.058*</t>
+          <t>0.066*</t>
         </is>
       </c>
       <c r="E21" s="16" t="inlineStr">
         <is>
-          <t>[0.010, 0.106]</t>
+          <t>[0.014, 0.118]</t>
         </is>
       </c>
       <c r="F21" s="16" t="n">
@@ -4692,27 +4696,27 @@
         </is>
       </c>
       <c r="B22" s="16" t="n">
-        <v>0.008</v>
+        <v>0.023</v>
       </c>
       <c r="C22" s="16" t="inlineStr">
         <is>
-          <t>[-0.016, 0.032]</t>
+          <t>[-0.008, 0.054]</t>
         </is>
       </c>
       <c r="D22" s="16" t="n">
-        <v>0.008999999999999999</v>
+        <v>0</v>
       </c>
       <c r="E22" s="16" t="inlineStr">
         <is>
-          <t>[-0.015, 0.033]</t>
+          <t>[-0.024, 0.024]</t>
         </is>
       </c>
       <c r="F22" s="16" t="n">
-        <v>-0.003</v>
+        <v>-0.01</v>
       </c>
       <c r="G22" s="16" t="inlineStr">
         <is>
-          <t>[-0.027, 0.021]</t>
+          <t>[-0.035, 0.015]</t>
         </is>
       </c>
     </row>
@@ -4722,28 +4726,30 @@
           <t>High power distance (+1 SD)</t>
         </is>
       </c>
-      <c r="B23" s="16" t="n">
-        <v>0.038</v>
+      <c r="B23" s="16" t="inlineStr">
+        <is>
+          <t>0.042*</t>
+        </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
         <is>
-          <t>[-0.000, 0.076]</t>
+          <t>[0.002, 0.082]</t>
         </is>
       </c>
       <c r="D23" s="16" t="n">
-        <v>0.036</v>
+        <v>0.029</v>
       </c>
       <c r="E23" s="16" t="inlineStr">
         <is>
-          <t>[-0.001, 0.073]</t>
+          <t>[-0.005, 0.063]</t>
         </is>
       </c>
       <c r="F23" s="16" t="n">
-        <v>-0.013</v>
+        <v>-0.011</v>
       </c>
       <c r="G23" s="16" t="inlineStr">
         <is>
-          <t>[-0.039, 0.013]</t>
+          <t>[-0.036, 0.014]</t>
         </is>
       </c>
     </row>
@@ -4755,30 +4761,32 @@
       </c>
       <c r="B24" s="16" t="inlineStr">
         <is>
-          <t>0.093*</t>
+          <t>0.09*</t>
         </is>
       </c>
       <c r="C24" s="16" t="inlineStr">
         <is>
-          <t>[0.028, 0.158]</t>
+          <t>[0.026, 0.154]</t>
         </is>
       </c>
       <c r="D24" s="16" t="inlineStr">
         <is>
-          <t>0.09*</t>
+          <t>0.104*</t>
         </is>
       </c>
       <c r="E24" s="16" t="inlineStr">
         <is>
-          <t>[0.026, 0.154]</t>
-        </is>
-      </c>
-      <c r="F24" s="16" t="n">
-        <v>-0.033</v>
+          <t>[0.033, 0.175]</t>
+        </is>
+      </c>
+      <c r="F24" s="16" t="inlineStr">
+        <is>
+          <t>-0.042*</t>
+        </is>
       </c>
       <c r="G24" s="16" t="inlineStr">
         <is>
-          <t>[-0.069, 0.003]</t>
+          <t>[-0.082, -0.002]</t>
         </is>
       </c>
     </row>
@@ -4790,30 +4798,30 @@
       </c>
       <c r="B25" s="16" t="inlineStr">
         <is>
-          <t>-0.055*</t>
+          <t>-0.048*</t>
         </is>
       </c>
       <c r="C25" s="16" t="inlineStr">
         <is>
-          <t>[-0.102, -0.008]</t>
+          <t>[-0.091, -0.005]</t>
         </is>
       </c>
       <c r="D25" s="16" t="inlineStr">
         <is>
-          <t>-0.054*</t>
+          <t>-0.075*</t>
         </is>
       </c>
       <c r="E25" s="16" t="inlineStr">
         <is>
-          <t>[-0.100, -0.008]</t>
+          <t>[-0.131, -0.019]</t>
         </is>
       </c>
       <c r="F25" s="16" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="G25" s="16" t="inlineStr">
         <is>
-          <t>[-0.009, 0.049]</t>
+          <t>[-0.004, 0.064]</t>
         </is>
       </c>
     </row>
@@ -4851,32 +4859,32 @@
       </c>
       <c r="B28" s="18" t="inlineStr">
         <is>
-          <t>-0.066*</t>
+          <t>-0.062*</t>
         </is>
       </c>
       <c r="C28" s="18" t="inlineStr">
         <is>
-          <t>[-0.103, -0.038]</t>
+          <t>[-0.098, -0.034]</t>
         </is>
       </c>
       <c r="D28" s="18" t="inlineStr">
         <is>
-          <t>-0.037*</t>
+          <t>-0.04*</t>
         </is>
       </c>
       <c r="E28" s="18" t="inlineStr">
         <is>
-          <t>[-0.069, -0.013]</t>
+          <t>[-0.072, -0.014]</t>
         </is>
       </c>
       <c r="F28" s="18" t="inlineStr">
         <is>
-          <t>0.099*</t>
+          <t>0.094*</t>
         </is>
       </c>
       <c r="G28" s="18" t="inlineStr">
         <is>
-          <t>[0.063, 0.140]</t>
+          <t>[0.060, 0.131]</t>
         </is>
       </c>
     </row>
@@ -4888,22 +4896,20 @@
       </c>
       <c r="B29" s="18" t="inlineStr">
         <is>
-          <t>-0.071*</t>
+          <t>-0.076*</t>
         </is>
       </c>
       <c r="C29" s="18" t="inlineStr">
         <is>
-          <t>[-0.125, -0.017]</t>
-        </is>
-      </c>
-      <c r="D29" s="18" t="inlineStr">
-        <is>
-          <t>-0.04*</t>
-        </is>
+          <t>[-0.133, -0.019]</t>
+        </is>
+      </c>
+      <c r="D29" s="18" t="n">
+        <v>-0.036</v>
       </c>
       <c r="E29" s="18" t="inlineStr">
         <is>
-          <t>[-0.079, -0.001]</t>
+          <t>[-0.073, 0.001]</t>
         </is>
       </c>
       <c r="F29" s="18" t="inlineStr">
@@ -4925,30 +4931,32 @@
       </c>
       <c r="B30" s="18" t="inlineStr">
         <is>
-          <t>-0.06*</t>
+          <t>-0.056*</t>
         </is>
       </c>
       <c r="C30" s="18" t="inlineStr">
         <is>
-          <t>[-0.109, -0.011]</t>
-        </is>
-      </c>
-      <c r="D30" s="18" t="n">
-        <v>-0.034</v>
+          <t>[-0.103, -0.009]</t>
+        </is>
+      </c>
+      <c r="D30" s="18" t="inlineStr">
+        <is>
+          <t>-0.044*</t>
+        </is>
       </c>
       <c r="E30" s="18" t="inlineStr">
         <is>
-          <t>[-0.070, 0.002]</t>
+          <t>[-0.085, -0.003]</t>
         </is>
       </c>
       <c r="F30" s="18" t="inlineStr">
         <is>
-          <t>0.092*</t>
+          <t>0.083*</t>
         </is>
       </c>
       <c r="G30" s="18" t="inlineStr">
         <is>
-          <t>[0.027, 0.157]</t>
+          <t>[0.023, 0.143]</t>
         </is>
       </c>
     </row>
@@ -4959,27 +4967,27 @@
         </is>
       </c>
       <c r="B31" s="18" t="n">
-        <v>-0.011</v>
+        <v>-0.02</v>
       </c>
       <c r="C31" s="18" t="inlineStr">
         <is>
-          <t>[-0.036, 0.014]</t>
+          <t>[-0.049, 0.009]</t>
         </is>
       </c>
       <c r="D31" s="18" t="n">
-        <v>-0.006</v>
+        <v>0.008</v>
       </c>
       <c r="E31" s="18" t="inlineStr">
         <is>
-          <t>[-0.030, 0.018]</t>
+          <t>[-0.016, 0.032]</t>
         </is>
       </c>
       <c r="F31" s="18" t="n">
-        <v>0.014</v>
+        <v>0.023</v>
       </c>
       <c r="G31" s="18" t="inlineStr">
         <is>
-          <t>[-0.012, 0.040]</t>
+          <t>[-0.008, 0.054]</t>
         </is>
       </c>
     </row>
@@ -4991,30 +4999,30 @@
       </c>
       <c r="B32" s="18" t="inlineStr">
         <is>
-          <t>-0.042*</t>
+          <t>-0.04*</t>
         </is>
       </c>
       <c r="C32" s="18" t="inlineStr">
         <is>
-          <t>[-0.082, -0.002]</t>
+          <t>[-0.079, -0.001]</t>
         </is>
       </c>
       <c r="D32" s="18" t="n">
-        <v>-0.023</v>
+        <v>-0.028</v>
       </c>
       <c r="E32" s="18" t="inlineStr">
         <is>
-          <t>[-0.054, 0.008]</t>
+          <t>[-0.061, 0.005]</t>
         </is>
       </c>
       <c r="F32" s="18" t="inlineStr">
         <is>
-          <t>0.063*</t>
+          <t>0.066*</t>
         </is>
       </c>
       <c r="G32" s="18" t="inlineStr">
         <is>
-          <t>[0.013, 0.113]</t>
+          <t>[0.014, 0.118]</t>
         </is>
       </c>
     </row>
@@ -5026,32 +5034,32 @@
       </c>
       <c r="B33" s="18" t="inlineStr">
         <is>
-          <t>-0.089*</t>
+          <t>-0.098*</t>
         </is>
       </c>
       <c r="C33" s="18" t="inlineStr">
         <is>
-          <t>[-0.152, -0.026]</t>
+          <t>[-0.166, -0.030]</t>
         </is>
       </c>
       <c r="D33" s="18" t="inlineStr">
         <is>
-          <t>-0.051*</t>
+          <t>-0.049*</t>
         </is>
       </c>
       <c r="E33" s="18" t="inlineStr">
         <is>
-          <t>[-0.096, -0.006]</t>
+          <t>[-0.093, -0.005]</t>
         </is>
       </c>
       <c r="F33" s="18" t="inlineStr">
         <is>
-          <t>0.134*</t>
+          <t>0.116*</t>
         </is>
       </c>
       <c r="G33" s="18" t="inlineStr">
         <is>
-          <t>[0.049, 0.219]</t>
+          <t>[0.040, 0.192]</t>
         </is>
       </c>
     </row>
@@ -5063,30 +5071,30 @@
       </c>
       <c r="B34" s="18" t="inlineStr">
         <is>
-          <t>0.047*</t>
+          <t>0.057*</t>
         </is>
       </c>
       <c r="C34" s="18" t="inlineStr">
         <is>
-          <t>[0.004, 0.090]</t>
+          <t>[0.009, 0.105]</t>
         </is>
       </c>
       <c r="D34" s="18" t="n">
-        <v>0.027</v>
+        <v>0.021</v>
       </c>
       <c r="E34" s="18" t="inlineStr">
         <is>
-          <t>[-0.006, 0.060]</t>
+          <t>[-0.009, 0.051]</t>
         </is>
       </c>
       <c r="F34" s="18" t="inlineStr">
         <is>
-          <t>-0.072*</t>
+          <t>-0.05*</t>
         </is>
       </c>
       <c r="G34" s="18" t="inlineStr">
         <is>
-          <t>[-0.127, -0.017]</t>
+          <t>[-0.094, -0.006]</t>
         </is>
       </c>
     </row>
@@ -5111,32 +5119,32 @@
       </c>
       <c r="B36" s="20" t="inlineStr">
         <is>
-          <t>0.031*</t>
+          <t>0.029*</t>
         </is>
       </c>
       <c r="C36" s="20" t="inlineStr">
         <is>
-          <t>[0.012, 0.055]</t>
+          <t>[0.011, 0.052]</t>
         </is>
       </c>
       <c r="D36" s="20" t="inlineStr">
         <is>
-          <t>0.017*</t>
+          <t>0.019*</t>
         </is>
       </c>
       <c r="E36" s="20" t="inlineStr">
         <is>
-          <t>[0.005, 0.034]</t>
+          <t>[0.006, 0.038]</t>
         </is>
       </c>
       <c r="F36" s="20" t="inlineStr">
         <is>
-          <t>-0.046*</t>
+          <t>-0.048*</t>
         </is>
       </c>
       <c r="G36" s="20" t="inlineStr">
         <is>
-          <t>[-0.078, -0.018]</t>
+          <t>[-0.082, -0.020]</t>
         </is>
       </c>
     </row>
@@ -5147,29 +5155,29 @@
         </is>
       </c>
       <c r="B37" s="20" t="n">
-        <v>0.028</v>
+        <v>0.025</v>
       </c>
       <c r="C37" s="20" t="inlineStr">
         <is>
-          <t>[-0.005, 0.061]</t>
+          <t>[-0.007, 0.057]</t>
         </is>
       </c>
       <c r="D37" s="20" t="n">
-        <v>0.015</v>
+        <v>0.021</v>
       </c>
       <c r="E37" s="20" t="inlineStr">
         <is>
-          <t>[-0.012, 0.042]</t>
+          <t>[-0.009, 0.051]</t>
         </is>
       </c>
       <c r="F37" s="20" t="inlineStr">
         <is>
-          <t>-0.041*</t>
+          <t>-0.048*</t>
         </is>
       </c>
       <c r="G37" s="20" t="inlineStr">
         <is>
-          <t>[-0.081, -0.001]</t>
+          <t>[-0.091, -0.005]</t>
         </is>
       </c>
     </row>
@@ -5180,29 +5188,29 @@
         </is>
       </c>
       <c r="B38" s="20" t="n">
-        <v>0.034</v>
+        <v>0.036</v>
       </c>
       <c r="C38" s="20" t="inlineStr">
         <is>
-          <t>[-0.002, 0.070]</t>
+          <t>[-0.001, 0.073]</t>
         </is>
       </c>
       <c r="D38" s="20" t="n">
-        <v>0.019</v>
+        <v>0.017</v>
       </c>
       <c r="E38" s="20" t="inlineStr">
         <is>
-          <t>[-0.010, 0.048]</t>
+          <t>[-0.011, 0.045]</t>
         </is>
       </c>
       <c r="F38" s="20" t="inlineStr">
         <is>
-          <t>-0.051*</t>
+          <t>-0.048*</t>
         </is>
       </c>
       <c r="G38" s="20" t="inlineStr">
         <is>
-          <t>[-0.096, -0.006]</t>
+          <t>[-0.091, -0.005]</t>
         </is>
       </c>
     </row>
@@ -5213,27 +5221,27 @@
         </is>
       </c>
       <c r="B39" s="20" t="n">
-        <v>-0.006</v>
+        <v>-0.011</v>
       </c>
       <c r="C39" s="20" t="inlineStr">
         <is>
-          <t>[-0.030, 0.018]</t>
+          <t>[-0.036, 0.014]</t>
         </is>
       </c>
       <c r="D39" s="20" t="n">
-        <v>-0.004</v>
+        <v>0.005</v>
       </c>
       <c r="E39" s="20" t="inlineStr">
         <is>
-          <t>[-0.028, 0.020]</t>
+          <t>[-0.019, 0.029]</t>
         </is>
       </c>
       <c r="F39" s="20" t="n">
-        <v>0.008999999999999999</v>
+        <v>0</v>
       </c>
       <c r="G39" s="20" t="inlineStr">
         <is>
-          <t>[-0.015, 0.033]</t>
+          <t>[-0.024, 0.024]</t>
         </is>
       </c>
     </row>
@@ -5245,30 +5253,30 @@
       </c>
       <c r="B40" s="20" t="inlineStr">
         <is>
-          <t>0.049*</t>
+          <t>0.042*</t>
         </is>
       </c>
       <c r="C40" s="20" t="inlineStr">
         <is>
-          <t>[0.005, 0.093]</t>
+          <t>[0.002, 0.082]</t>
         </is>
       </c>
       <c r="D40" s="20" t="n">
-        <v>0.027</v>
+        <v>0.036</v>
       </c>
       <c r="E40" s="20" t="inlineStr">
         <is>
-          <t>[-0.006, 0.060]</t>
+          <t>[-0.001, 0.073]</t>
         </is>
       </c>
       <c r="F40" s="20" t="inlineStr">
         <is>
-          <t>-0.072*</t>
+          <t>-0.068*</t>
         </is>
       </c>
       <c r="G40" s="20" t="inlineStr">
         <is>
-          <t>[-0.127, -0.017]</t>
+          <t>[-0.121, -0.015]</t>
         </is>
       </c>
     </row>
@@ -5279,27 +5287,27 @@
         </is>
       </c>
       <c r="B41" s="20" t="n">
-        <v>0.013</v>
+        <v>0.021</v>
       </c>
       <c r="C41" s="20" t="inlineStr">
         <is>
-          <t>[-0.013, 0.039]</t>
+          <t>[-0.009, 0.051]</t>
         </is>
       </c>
       <c r="D41" s="20" t="n">
-        <v>0.007</v>
+        <v>0.004</v>
       </c>
       <c r="E41" s="20" t="inlineStr">
         <is>
-          <t>[-0.017, 0.031]</t>
+          <t>[-0.020, 0.028]</t>
         </is>
       </c>
       <c r="F41" s="20" t="n">
-        <v>-0.021</v>
+        <v>-0.031</v>
       </c>
       <c r="G41" s="20" t="inlineStr">
         <is>
-          <t>[-0.051, 0.009]</t>
+          <t>[-0.066, 0.004]</t>
         </is>
       </c>
     </row>
@@ -5310,29 +5318,27 @@
         </is>
       </c>
       <c r="B42" s="20" t="n">
-        <v>0.036</v>
+        <v>0.021</v>
       </c>
       <c r="C42" s="20" t="inlineStr">
         <is>
-          <t>[-0.001, 0.073]</t>
+          <t>[-0.009, 0.051]</t>
         </is>
       </c>
       <c r="D42" s="20" t="n">
-        <v>0.02</v>
+        <v>0.031</v>
       </c>
       <c r="E42" s="20" t="inlineStr">
         <is>
-          <t>[-0.009, 0.049]</t>
-        </is>
-      </c>
-      <c r="F42" s="20" t="inlineStr">
-        <is>
-          <t>-0.052*</t>
-        </is>
+          <t>[-0.004, 0.066]</t>
+        </is>
+      </c>
+      <c r="F42" s="20" t="n">
+        <v>-0.037</v>
       </c>
       <c r="G42" s="20" t="inlineStr">
         <is>
-          <t>[-0.097, -0.007]</t>
+          <t>[-0.075, 0.001]</t>
         </is>
       </c>
     </row>
@@ -5560,53 +5566,53 @@
         </is>
       </c>
       <c r="D5" s="4" t="n">
-        <v>-0.013</v>
+        <v>-0.012</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>0.038</v>
+        <v>0.04</v>
       </c>
       <c r="F5" s="4" t="n">
         <v>0.764</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>-0.092</v>
+        <v>-0.091</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>0.068</v>
+        <v>0.067</v>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>-0.16*</t>
+          <t>-0.154*</t>
         </is>
       </c>
       <c r="J5" s="4" t="n">
-        <v>0.06</v>
+        <v>0.062</v>
       </c>
       <c r="K5" s="4" t="n">
         <v>0.013</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>-0.283</v>
+        <v>-0.276</v>
       </c>
       <c r="M5" s="4" t="n">
-        <v>-0.031</v>
+        <v>-0.032</v>
       </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
-          <t>-0.135*</t>
+          <t>-0.13*</t>
         </is>
       </c>
       <c r="O5" s="4" t="n">
-        <v>0.066</v>
+        <v>0.064</v>
       </c>
       <c r="P5" s="4" t="n">
         <v>0.042</v>
       </c>
       <c r="Q5" s="4" t="n">
-        <v>-0.251</v>
+        <v>-0.255</v>
       </c>
       <c r="R5" s="4" t="n">
-        <v>-0.006</v>
+        <v>-0.005</v>
       </c>
       <c r="S5" s="4" t="n">
         <v>-0.024</v>
@@ -5618,10 +5624,10 @@
         <v>0.764</v>
       </c>
       <c r="V5" s="4" t="n">
-        <v>-0.183</v>
+        <v>-0.181</v>
       </c>
       <c r="W5" s="4" t="n">
-        <v>0.14</v>
+        <v>0.133</v>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1" s="37">
@@ -5641,68 +5647,68 @@
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.017</v>
+        <v>0.018</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.037</v>
+        <v>0.039</v>
       </c>
       <c r="F6" s="4" t="n">
         <v>0.645</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.055</v>
+        <v>-0.058</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.093</v>
+        <v>0.094</v>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>0.276***</t>
+          <t>0.285***</t>
         </is>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.058</v>
+        <v>0.059</v>
       </c>
       <c r="K6" s="4" t="n">
         <v>0</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.167</v>
+        <v>0.169</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.419</v>
+        <v>0.401</v>
       </c>
       <c r="N6" s="4" t="inlineStr">
         <is>
-          <t>0.242***</t>
+          <t>0.249***</t>
         </is>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.058</v>
+        <v>0.06</v>
       </c>
       <c r="P6" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>0.132</v>
+        <v>0.131</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>0.369</v>
+        <v>0.367</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>0.038</v>
+        <v>0.036</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>0.081</v>
+        <v>0.078</v>
       </c>
       <c r="U6" s="4" t="n">
         <v>0.645</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>-0.119</v>
+        <v>-0.117</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>0.183</v>
+        <v>0.189</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" s="37">
@@ -5722,66 +5728,66 @@
         </is>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.048</v>
+        <v>0.046</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.043</v>
+        <v>0.041</v>
       </c>
       <c r="F7" s="4" t="n">
         <v>0.263</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.036</v>
+        <v>-0.034</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.129</v>
+        <v>0.126</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-0.038</v>
+        <v>-0.039</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>0.064</v>
+        <v>0.063</v>
       </c>
       <c r="K7" s="4" t="n">
         <v>0.535</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-0.167</v>
+        <v>-0.162</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="N7" s="4" t="inlineStr">
         <is>
-          <t>-0.152*</t>
+          <t>-0.156*</t>
         </is>
       </c>
       <c r="O7" s="4" t="n">
-        <v>0.065</v>
+        <v>0.067</v>
       </c>
       <c r="P7" s="4" t="n">
         <v>0.02</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>-0.284</v>
+        <v>-0.288</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>-0.025</v>
+        <v>-0.024</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>0.112</v>
+        <v>0.117</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>0.081</v>
+        <v>0.082</v>
       </c>
       <c r="U7" s="4" t="n">
         <v>0.155</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>-0.044</v>
+        <v>-0.043</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>0.274</v>
+        <v>0.277</v>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1" s="37">
@@ -5802,41 +5808,41 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>-0.097*</t>
+          <t>-0.098*</t>
         </is>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.04</v>
+        <v>0.039</v>
       </c>
       <c r="F8" s="4" t="n">
         <v>0.012</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.166</v>
+        <v>-0.174</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.021</v>
+        <v>-0.022</v>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>0.177**</t>
+          <t>0.196**</t>
         </is>
       </c>
       <c r="J8" s="4" t="n">
-        <v>0.061</v>
+        <v>0.059</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.004</v>
+        <v>0.001</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.052</v>
+        <v>0.08</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.276</v>
+        <v>0.312</v>
       </c>
       <c r="N8" s="4" t="inlineStr">
         <is>
-          <t>0.37***</t>
+          <t>0.346***</t>
         </is>
       </c>
       <c r="O8" s="4" t="n">
@@ -5846,27 +5852,27 @@
         <v>0</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>0.247</v>
+        <v>0.224</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>0.467</v>
+        <v>0.468</v>
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>-0.202*</t>
+          <t>-0.15†</t>
         </is>
       </c>
       <c r="T8" s="4" t="n">
-        <v>0.081</v>
+        <v>0.078</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>0.012</v>
+        <v>0.055</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>-0.345</v>
+        <v>-0.303</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>-0.042</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" s="37">
@@ -5886,7 +5892,7 @@
         </is>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.023</v>
+        <v>0.024</v>
       </c>
       <c r="E9" s="4" t="n">
         <v>0.043</v>
@@ -5895,59 +5901,59 @@
         <v>0.577</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.058</v>
+        <v>-0.06</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.11</v>
+        <v>0.108</v>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>0.353***</t>
+          <t>0.336***</t>
         </is>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.067</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="K9" s="4" t="n">
         <v>0</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.2</v>
+        <v>0.201</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.485</v>
+        <v>0.471</v>
       </c>
       <c r="N9" s="4" t="inlineStr">
         <is>
-          <t>0.286***</t>
+          <t>0.288***</t>
         </is>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0.073</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="P9" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>0.15</v>
+        <v>0.149</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>0.411</v>
+        <v>0.427</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>0.046</v>
+        <v>0.048</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>0.09</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="U9" s="4" t="n">
         <v>0.577</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>-0.126</v>
+        <v>-0.121</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>0.21</v>
+        <v>0.217</v>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" s="37">
@@ -5970,13 +5976,13 @@
         <v>-0.019</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.042</v>
+        <v>0.041</v>
       </c>
       <c r="F10" s="4" t="n">
         <v>0.643</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.095</v>
+        <v>-0.099</v>
       </c>
       <c r="H10" s="4" t="n">
         <v>0.061</v>
@@ -5987,48 +5993,48 @@
         </is>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.062</v>
+        <v>0.06</v>
       </c>
       <c r="K10" s="4" t="n">
         <v>0.006</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-0.288</v>
+        <v>-0.282</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-0.047</v>
+        <v>-0.046</v>
       </c>
       <c r="N10" s="4" t="inlineStr">
         <is>
-          <t>-0.125*</t>
+          <t>-0.126*</t>
         </is>
       </c>
       <c r="O10" s="4" t="n">
-        <v>0.064</v>
+        <v>0.063</v>
       </c>
       <c r="P10" s="4" t="n">
         <v>0.045</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>-0.261</v>
+        <v>-0.249</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>-0.004</v>
+        <v>-0.003</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>-0.039</v>
+        <v>-0.038</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.082</v>
       </c>
       <c r="U10" s="4" t="n">
         <v>0.643</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>-0.195</v>
+        <v>-0.199</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>0.129</v>
+        <v>0.123</v>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" s="37">
@@ -6049,71 +6055,71 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>-0.108**</t>
+          <t>-0.111**</t>
         </is>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.04</v>
+        <v>0.041</v>
       </c>
       <c r="F11" s="4" t="n">
         <v>0.007</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.186</v>
+        <v>-0.191</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.029</v>
+        <v>-0.031</v>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>0.198**</t>
+          <t>0.243***</t>
         </is>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.063</v>
+        <v>0.066</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.114</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.323</v>
+        <v>0.372</v>
       </c>
       <c r="N11" s="4" t="inlineStr">
         <is>
-          <t>0.409***</t>
+          <t>0.398***</t>
         </is>
       </c>
       <c r="O11" s="4" t="n">
-        <v>0.066</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="P11" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>0.277</v>
+        <v>0.263</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>0.578</v>
+        <v>0.533</v>
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>-0.232**</t>
+          <t>-0.155†</t>
         </is>
       </c>
       <c r="T11" s="4" t="n">
-        <v>0.083</v>
+        <v>0.082</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>0.007</v>
+        <v>0.06</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>-0.394</v>
+        <v>-0.316</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>-0.063</v>
+        <v>0.006</v>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1" s="37">
@@ -6134,23 +6140,23 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>0.069†</t>
+          <t>0.067†</t>
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.037</v>
+        <v>0.038</v>
       </c>
       <c r="F12" s="4" t="n">
         <v>0.078</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.008999999999999999</v>
+        <v>-0.008</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.141</v>
+        <v>0.142</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-0.076</v>
+        <v>-0.078</v>
       </c>
       <c r="J12" s="4" t="n">
         <v>0.06</v>
@@ -6159,27 +6165,27 @@
         <v>0.193</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-0.189</v>
+        <v>-0.196</v>
       </c>
       <c r="M12" s="4" t="n">
         <v>0.04</v>
       </c>
       <c r="N12" s="4" t="inlineStr">
         <is>
-          <t>-0.211**</t>
+          <t>-0.212**</t>
         </is>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0.063</v>
+        <v>0.062</v>
       </c>
       <c r="P12" s="4" t="n">
         <v>0.001</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>-0.335</v>
+        <v>-0.334</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>-0.08799999999999999</v>
+        <v>-0.09</v>
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
@@ -6187,16 +6193,16 @@
         </is>
       </c>
       <c r="T12" s="4" t="n">
-        <v>0.073</v>
+        <v>0.076</v>
       </c>
       <c r="U12" s="4" t="n">
         <v>0.078</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>-0.016</v>
+        <v>-0.015</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>0.291</v>
+        <v>0.283</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="37">

--- a/results/Model3.xlsx
+++ b/results/Model3.xlsx
@@ -2108,10 +2108,10 @@
         </is>
       </c>
       <c r="B4" s="24" t="n">
-        <v>0.531</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="C4" s="24" t="n">
-        <v>0.488</v>
+        <v>0.486</v>
       </c>
       <c r="D4" s="24" t="inlineStr">
         <is>
@@ -2139,13 +2139,13 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>30.962</v>
+        <v>30.911</v>
       </c>
       <c r="C5" s="24" t="n">
-        <v>4.55</v>
+        <v>4.594</v>
       </c>
       <c r="D5" s="24" t="n">
-        <v>0.032</v>
+        <v>0.005</v>
       </c>
       <c r="E5" s="24" t="inlineStr">
         <is>
@@ -2172,17 +2172,17 @@
         </is>
       </c>
       <c r="B6" s="24" t="n">
-        <v>2.374</v>
+        <v>2.385</v>
       </c>
       <c r="C6" s="24" t="n">
-        <v>1.496</v>
+        <v>1.484</v>
       </c>
       <c r="D6" s="24" t="n">
-        <v>-0.001</v>
+        <v>-0.023</v>
       </c>
       <c r="E6" s="24" t="inlineStr">
         <is>
-          <t>0.171**</t>
+          <t>0.174***</t>
         </is>
       </c>
       <c r="F6" s="24" t="inlineStr">
@@ -2209,19 +2209,19 @@
         </is>
       </c>
       <c r="B7" s="24" t="n">
-        <v>3.328</v>
+        <v>3.327</v>
       </c>
       <c r="C7" s="24" t="n">
-        <v>1.072</v>
+        <v>1.062</v>
       </c>
       <c r="D7" s="24" t="n">
-        <v>0.079</v>
+        <v>0.099</v>
       </c>
       <c r="E7" s="24" t="n">
-        <v>-0.011</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="F7" s="24" t="n">
-        <v>-0.08599999999999999</v>
+        <v>-0.08500000000000001</v>
       </c>
       <c r="G7" s="24" t="inlineStr">
         <is>
@@ -2246,24 +2246,22 @@
         </is>
       </c>
       <c r="B8" s="24" t="n">
-        <v>4.115</v>
+        <v>4.123</v>
       </c>
       <c r="C8" s="24" t="n">
-        <v>0.886</v>
+        <v>0.878</v>
       </c>
       <c r="D8" s="24" t="n">
-        <v>-0.019</v>
+        <v>-0.066</v>
       </c>
       <c r="E8" s="24" t="n">
-        <v>-0.005</v>
-      </c>
-      <c r="F8" s="24" t="inlineStr">
-        <is>
-          <t>0.109*</t>
-        </is>
+        <v>-0.026</v>
+      </c>
+      <c r="F8" s="24" t="n">
+        <v>0.075</v>
       </c>
       <c r="G8" s="24" t="n">
-        <v>-0.007</v>
+        <v>0.014</v>
       </c>
       <c r="H8" s="23" t="inlineStr">
         <is>
@@ -2287,26 +2285,26 @@
         </is>
       </c>
       <c r="B9" s="24" t="n">
-        <v>4.919</v>
+        <v>4.936</v>
       </c>
       <c r="C9" s="24" t="n">
-        <v>0.921</v>
+        <v>0.956</v>
       </c>
       <c r="D9" s="24" t="n">
-        <v>-0.02</v>
+        <v>-0.023</v>
       </c>
       <c r="E9" s="24" t="n">
-        <v>-0.013</v>
+        <v>-0.017</v>
       </c>
       <c r="F9" s="24" t="n">
-        <v>0.028</v>
+        <v>0.039</v>
       </c>
       <c r="G9" s="24" t="n">
-        <v>-0.053</v>
+        <v>-0.077</v>
       </c>
       <c r="H9" s="24" t="inlineStr">
         <is>
-          <t>-0.33***</t>
+          <t>-0.332***</t>
         </is>
       </c>
       <c r="I9" s="24" t="inlineStr">
@@ -2330,28 +2328,28 @@
         </is>
       </c>
       <c r="B10" s="24" t="n">
-        <v>3.484</v>
+        <v>3.478</v>
       </c>
       <c r="C10" s="24" t="n">
-        <v>0.9360000000000001</v>
+        <v>0.907</v>
       </c>
       <c r="D10" s="24" t="n">
-        <v>-0.08500000000000001</v>
+        <v>-0.058</v>
       </c>
       <c r="E10" s="24" t="n">
-        <v>-0.062</v>
+        <v>-0.025</v>
       </c>
       <c r="F10" s="24" t="n">
-        <v>0.044</v>
+        <v>0.054</v>
       </c>
       <c r="G10" s="24" t="n">
-        <v>-0.068</v>
+        <v>-0.077</v>
       </c>
       <c r="H10" s="24" t="n">
-        <v>-0.014</v>
+        <v>0.016</v>
       </c>
       <c r="I10" s="24" t="n">
-        <v>0.091</v>
+        <v>0.081</v>
       </c>
       <c r="J10" s="24" t="inlineStr">
         <is>
@@ -2373,33 +2371,31 @@
         </is>
       </c>
       <c r="B11" s="24" t="n">
-        <v>4.639</v>
+        <v>4.612</v>
       </c>
       <c r="C11" s="24" t="n">
-        <v>0.892</v>
+        <v>0.902</v>
       </c>
       <c r="D11" s="24" t="n">
-        <v>-0.068</v>
+        <v>-0.098</v>
       </c>
       <c r="E11" s="24" t="n">
-        <v>-0.08</v>
-      </c>
-      <c r="F11" s="24" t="inlineStr">
-        <is>
-          <t>-0.12*</t>
-        </is>
+        <v>-0.055</v>
+      </c>
+      <c r="F11" s="24" t="n">
+        <v>-0.08799999999999999</v>
       </c>
       <c r="G11" s="24" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.077</v>
       </c>
       <c r="H11" s="24" t="n">
-        <v>-0.078</v>
+        <v>-0.042</v>
       </c>
       <c r="I11" s="24" t="n">
-        <v>-0.024</v>
+        <v>-0.026</v>
       </c>
       <c r="J11" s="24" t="n">
-        <v>0.007</v>
+        <v>-0.018</v>
       </c>
       <c r="K11" s="24" t="inlineStr">
         <is>
@@ -2420,38 +2416,38 @@
         </is>
       </c>
       <c r="B12" s="24" t="n">
-        <v>4.483</v>
+        <v>4.476</v>
       </c>
       <c r="C12" s="24" t="n">
-        <v>1.205</v>
+        <v>1.211</v>
       </c>
       <c r="D12" s="24" t="n">
-        <v>-0.07099999999999999</v>
+        <v>-0.049</v>
       </c>
       <c r="E12" s="24" t="n">
-        <v>0.031</v>
+        <v>0.042</v>
       </c>
       <c r="F12" s="24" t="n">
-        <v>-0.037</v>
+        <v>0.003</v>
       </c>
       <c r="G12" s="24" t="n">
-        <v>-0.037</v>
+        <v>-0.064</v>
       </c>
       <c r="H12" s="24" t="inlineStr">
         <is>
-          <t>-0.524***</t>
+          <t>-0.517***</t>
         </is>
       </c>
       <c r="I12" s="24" t="inlineStr">
         <is>
-          <t>0.498***</t>
+          <t>0.519***</t>
         </is>
       </c>
       <c r="J12" s="24" t="n">
-        <v>0.008999999999999999</v>
+        <v>-0.005</v>
       </c>
       <c r="K12" s="24" t="n">
-        <v>-0.023</v>
+        <v>-0.02</v>
       </c>
       <c r="L12" s="24" t="inlineStr">
         <is>
@@ -2471,44 +2467,42 @@
         </is>
       </c>
       <c r="B13" s="24" t="n">
-        <v>3.07</v>
+        <v>3.087</v>
       </c>
       <c r="C13" s="24" t="n">
-        <v>1.213</v>
+        <v>1.233</v>
       </c>
       <c r="D13" s="24" t="n">
-        <v>0.031</v>
+        <v>-0.007</v>
       </c>
       <c r="E13" s="24" t="n">
-        <v>0.013</v>
+        <v>-0.003</v>
       </c>
       <c r="F13" s="24" t="n">
-        <v>0.008</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="G13" s="24" t="n">
-        <v>0.031</v>
+        <v>0.045</v>
       </c>
       <c r="H13" s="24" t="inlineStr">
         <is>
-          <t>0.52***</t>
+          <t>0.534***</t>
         </is>
       </c>
       <c r="I13" s="24" t="inlineStr">
         <is>
-          <t>-0.506***</t>
+          <t>-0.51***</t>
         </is>
       </c>
       <c r="J13" s="24" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="K13" s="24" t="inlineStr">
-        <is>
-          <t>-0.106*</t>
-        </is>
+        <v>0.04</v>
+      </c>
+      <c r="K13" s="24" t="n">
+        <v>-0.08699999999999999</v>
       </c>
       <c r="L13" s="24" t="inlineStr">
         <is>
-          <t>-0.446***</t>
+          <t>-0.431***</t>
         </is>
       </c>
       <c r="M13" s="24" t="inlineStr">
@@ -2528,42 +2522,42 @@
         </is>
       </c>
       <c r="B14" s="24" t="n">
-        <v>4.419</v>
+        <v>4.438</v>
       </c>
       <c r="C14" s="24" t="n">
-        <v>0.61</v>
+        <v>0.628</v>
       </c>
       <c r="D14" s="24" t="n">
-        <v>0.021</v>
+        <v>0.024</v>
       </c>
       <c r="E14" s="24" t="n">
+        <v>-0.029</v>
+      </c>
+      <c r="F14" s="24" t="n">
+        <v>-0.035</v>
+      </c>
+      <c r="G14" s="24" t="n">
         <v>-0.031</v>
       </c>
-      <c r="F14" s="24" t="n">
-        <v>0.006</v>
-      </c>
-      <c r="G14" s="24" t="n">
-        <v>-0.042</v>
-      </c>
       <c r="H14" s="24" t="n">
-        <v>0.031</v>
+        <v>0.059</v>
       </c>
       <c r="I14" s="24" t="n">
-        <v>-0.043</v>
+        <v>-0.053</v>
       </c>
       <c r="J14" s="24" t="inlineStr">
         <is>
-          <t>-0.155**</t>
+          <t>-0.124*</t>
         </is>
       </c>
       <c r="K14" s="24" t="n">
-        <v>-0.038</v>
+        <v>-0.082</v>
       </c>
       <c r="L14" s="24" t="n">
-        <v>-0.031</v>
+        <v>-0.006</v>
       </c>
       <c r="M14" s="24" t="n">
-        <v>0.076</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="N14" s="24" t="inlineStr">
         <is>
@@ -2581,54 +2575,52 @@
         </is>
       </c>
       <c r="B15" s="24" t="n">
-        <v>4.526</v>
+        <v>4.51</v>
       </c>
       <c r="C15" s="24" t="n">
-        <v>0.794</v>
+        <v>0.782</v>
       </c>
       <c r="D15" s="24" t="n">
-        <v>-0.018</v>
+        <v>-0.034</v>
       </c>
       <c r="E15" s="24" t="n">
-        <v>-0.032</v>
+        <v>-0.002</v>
       </c>
       <c r="F15" s="24" t="n">
-        <v>0.007</v>
+        <v>0.028</v>
       </c>
       <c r="G15" s="24" t="n">
-        <v>-0.033</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="H15" s="24" t="inlineStr">
         <is>
-          <t>-0.412***</t>
+          <t>-0.452***</t>
         </is>
       </c>
       <c r="I15" s="24" t="inlineStr">
         <is>
-          <t>0.407***</t>
-        </is>
-      </c>
-      <c r="J15" s="24" t="inlineStr">
-        <is>
-          <t>-0.14**</t>
-        </is>
+          <t>0.41***</t>
+        </is>
+      </c>
+      <c r="J15" s="24" t="n">
+        <v>-0.054</v>
       </c>
       <c r="K15" s="24" t="n">
-        <v>-0.005</v>
+        <v>0.004</v>
       </c>
       <c r="L15" s="24" t="inlineStr">
         <is>
-          <t>0.598***</t>
+          <t>0.562***</t>
         </is>
       </c>
       <c r="M15" s="24" t="inlineStr">
         <is>
-          <t>-0.586***</t>
+          <t>-0.59***</t>
         </is>
       </c>
       <c r="N15" s="24" t="inlineStr">
         <is>
-          <t>0.361***</t>
+          <t>0.393***</t>
         </is>
       </c>
       <c r="O15" s="24" t="inlineStr">
@@ -2646,38 +2638,38 @@
         </is>
       </c>
       <c r="B16" s="24" t="n">
-        <v>5.006</v>
+        <v>4.985</v>
       </c>
       <c r="C16" s="24" t="n">
-        <v>1.003</v>
+        <v>1.07</v>
       </c>
       <c r="D16" s="24" t="n">
-        <v>-0.08799999999999999</v>
+        <v>-0.007</v>
       </c>
       <c r="E16" s="24" t="n">
-        <v>0.001</v>
+        <v>0.042</v>
       </c>
       <c r="F16" s="24" t="n">
-        <v>-0.077</v>
+        <v>-0.017</v>
       </c>
       <c r="G16" s="24" t="n">
-        <v>-0.083</v>
+        <v>0.043</v>
       </c>
       <c r="H16" s="24" t="inlineStr">
         <is>
-          <t>-0.327***</t>
+          <t>-0.462***</t>
         </is>
       </c>
       <c r="I16" s="24" t="inlineStr">
         <is>
-          <t>0.349***</t>
+          <t>0.339***</t>
         </is>
       </c>
       <c r="J16" s="24" t="n">
-        <v>-0.047</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="K16" s="24" t="n">
-        <v>0.008</v>
+        <v>0.1</v>
       </c>
       <c r="L16" s="24" t="inlineStr">
         <is>
@@ -2686,15 +2678,15 @@
       </c>
       <c r="M16" s="24" t="inlineStr">
         <is>
-          <t>-0.504***</t>
+          <t>-0.5***</t>
         </is>
       </c>
       <c r="N16" s="24" t="n">
-        <v>0.048</v>
+        <v>-0.01</v>
       </c>
       <c r="O16" s="24" t="inlineStr">
         <is>
-          <t>0.474***</t>
+          <t>0.39***</t>
         </is>
       </c>
       <c r="P16" s="24" t="inlineStr">
@@ -2711,42 +2703,44 @@
         </is>
       </c>
       <c r="B17" s="24" t="n">
-        <v>2.6</v>
+        <v>2.648</v>
       </c>
       <c r="C17" s="24" t="n">
-        <v>1.057</v>
+        <v>1.112</v>
       </c>
       <c r="D17" s="24" t="n">
-        <v>0.013</v>
+        <v>0.035</v>
       </c>
       <c r="E17" s="24" t="n">
-        <v>0.026</v>
+        <v>-0.031</v>
       </c>
       <c r="F17" s="24" t="n">
-        <v>0.07099999999999999</v>
-      </c>
-      <c r="G17" s="24" t="n">
-        <v>0.007</v>
+        <v>-0.032</v>
+      </c>
+      <c r="G17" s="24" t="inlineStr">
+        <is>
+          <t>0.154**</t>
+        </is>
       </c>
       <c r="H17" s="24" t="inlineStr">
         <is>
-          <t>0.425***</t>
+          <t>0.413***</t>
         </is>
       </c>
       <c r="I17" s="24" t="inlineStr">
         <is>
-          <t>-0.309***</t>
+          <t>-0.333***</t>
         </is>
       </c>
       <c r="J17" s="24" t="n">
-        <v>0.031</v>
+        <v>-0.057</v>
       </c>
       <c r="K17" s="24" t="n">
-        <v>-0.003</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="L17" s="24" t="inlineStr">
         <is>
-          <t>-0.473***</t>
+          <t>-0.524***</t>
         </is>
       </c>
       <c r="M17" s="24" t="inlineStr">
@@ -2754,14 +2748,12 @@
           <t>0.49***</t>
         </is>
       </c>
-      <c r="N17" s="24" t="inlineStr">
-        <is>
-          <t>0.121*</t>
-        </is>
+      <c r="N17" s="24" t="n">
+        <v>-0.058</v>
       </c>
       <c r="O17" s="24" t="inlineStr">
         <is>
-          <t>-0.42***</t>
+          <t>-0.442***</t>
         </is>
       </c>
       <c r="P17" s="24" t="inlineStr">

--- a/results/Model3.xlsx
+++ b/results/Model3.xlsx
@@ -1657,7 +1657,7 @@
         <v>0.043</v>
       </c>
       <c r="G4" s="35" t="n">
-        <v>0.039</v>
+        <v>0.032</v>
       </c>
       <c r="H4" s="35" t="n">
         <v>0.008999999999999999</v>
@@ -1939,28 +1939,28 @@
         </is>
       </c>
       <c r="D6" s="32" t="n">
-        <v>2614.9</v>
+        <v>2531.6</v>
       </c>
       <c r="E6" s="32" t="n">
         <v>882</v>
       </c>
       <c r="F6" s="32" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="G6" s="32" t="n">
-        <v>0.878</v>
+        <v>0.889</v>
       </c>
       <c r="H6" s="32" t="n">
-        <v>0.066</v>
+        <v>0.064</v>
       </c>
       <c r="I6" s="32" t="n">
-        <v>0.058</v>
+        <v>0.057</v>
       </c>
       <c r="J6" s="32" t="n">
-        <v>0.076</v>
+        <v>0.075</v>
       </c>
       <c r="K6" s="32" t="n">
-        <v>31881.3</v>
+        <v>31807.6</v>
       </c>
     </row>
     <row r="7" ht="46.5" customHeight="1" s="37">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="P16" s="24" t="inlineStr">
         <is>
-          <t>(0.81)</t>
+          <t>(0.85)</t>
         </is>
       </c>
       <c r="Q16" s="24" t="n"/>

--- a/results/Model3.xlsx
+++ b/results/Model3.xlsx
@@ -2108,10 +2108,10 @@
         </is>
       </c>
       <c r="B4" s="24" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="C4" s="24" t="n">
-        <v>0.486</v>
+        <v>0.497</v>
       </c>
       <c r="D4" s="24" t="inlineStr">
         <is>
@@ -2139,13 +2139,13 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>30.911</v>
+        <v>30.781</v>
       </c>
       <c r="C5" s="24" t="n">
-        <v>4.594</v>
+        <v>4.593</v>
       </c>
       <c r="D5" s="24" t="n">
-        <v>0.005</v>
+        <v>0.017</v>
       </c>
       <c r="E5" s="24" t="inlineStr">
         <is>
@@ -2172,17 +2172,17 @@
         </is>
       </c>
       <c r="B6" s="24" t="n">
-        <v>2.385</v>
+        <v>2.359</v>
       </c>
       <c r="C6" s="24" t="n">
-        <v>1.484</v>
+        <v>1.476</v>
       </c>
       <c r="D6" s="24" t="n">
-        <v>-0.023</v>
+        <v>-0.027</v>
       </c>
       <c r="E6" s="24" t="inlineStr">
         <is>
-          <t>0.174***</t>
+          <t>0.178***</t>
         </is>
       </c>
       <c r="F6" s="24" t="inlineStr">
@@ -2209,19 +2209,19 @@
         </is>
       </c>
       <c r="B7" s="24" t="n">
-        <v>3.327</v>
+        <v>3.296</v>
       </c>
       <c r="C7" s="24" t="n">
-        <v>1.062</v>
+        <v>1.071</v>
       </c>
       <c r="D7" s="24" t="n">
-        <v>0.099</v>
+        <v>0.101</v>
       </c>
       <c r="E7" s="24" t="n">
         <v>-0.008999999999999999</v>
       </c>
       <c r="F7" s="24" t="n">
-        <v>-0.08500000000000001</v>
+        <v>-0.079</v>
       </c>
       <c r="G7" s="24" t="inlineStr">
         <is>
@@ -2246,22 +2246,22 @@
         </is>
       </c>
       <c r="B8" s="24" t="n">
-        <v>4.123</v>
+        <v>4.083</v>
       </c>
       <c r="C8" s="24" t="n">
-        <v>0.878</v>
+        <v>0.885</v>
       </c>
       <c r="D8" s="24" t="n">
-        <v>-0.066</v>
+        <v>-0.059</v>
       </c>
       <c r="E8" s="24" t="n">
-        <v>-0.026</v>
+        <v>-0.034</v>
       </c>
       <c r="F8" s="24" t="n">
-        <v>0.075</v>
+        <v>0.077</v>
       </c>
       <c r="G8" s="24" t="n">
-        <v>0.014</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="H8" s="23" t="inlineStr">
         <is>
@@ -2285,26 +2285,26 @@
         </is>
       </c>
       <c r="B9" s="24" t="n">
-        <v>4.936</v>
+        <v>4.898</v>
       </c>
       <c r="C9" s="24" t="n">
-        <v>0.956</v>
+        <v>0.971</v>
       </c>
       <c r="D9" s="24" t="n">
-        <v>-0.023</v>
+        <v>-0.025</v>
       </c>
       <c r="E9" s="24" t="n">
-        <v>-0.017</v>
+        <v>-0.008</v>
       </c>
       <c r="F9" s="24" t="n">
-        <v>0.039</v>
+        <v>0.035</v>
       </c>
       <c r="G9" s="24" t="n">
-        <v>-0.077</v>
+        <v>-0.08400000000000001</v>
       </c>
       <c r="H9" s="24" t="inlineStr">
         <is>
-          <t>-0.332***</t>
+          <t>-0.342***</t>
         </is>
       </c>
       <c r="I9" s="24" t="inlineStr">
@@ -2328,28 +2328,28 @@
         </is>
       </c>
       <c r="B10" s="24" t="n">
-        <v>3.478</v>
+        <v>3.479</v>
       </c>
       <c r="C10" s="24" t="n">
-        <v>0.907</v>
+        <v>0.885</v>
       </c>
       <c r="D10" s="24" t="n">
-        <v>-0.058</v>
+        <v>-0.05</v>
       </c>
       <c r="E10" s="24" t="n">
-        <v>-0.025</v>
+        <v>-0.032</v>
       </c>
       <c r="F10" s="24" t="n">
-        <v>0.054</v>
+        <v>0.06</v>
       </c>
       <c r="G10" s="24" t="n">
-        <v>-0.077</v>
+        <v>-0.066</v>
       </c>
       <c r="H10" s="24" t="n">
-        <v>0.016</v>
+        <v>0.021</v>
       </c>
       <c r="I10" s="24" t="n">
-        <v>0.081</v>
+        <v>0.078</v>
       </c>
       <c r="J10" s="24" t="inlineStr">
         <is>
@@ -2371,31 +2371,31 @@
         </is>
       </c>
       <c r="B11" s="24" t="n">
-        <v>4.612</v>
+        <v>4.599</v>
       </c>
       <c r="C11" s="24" t="n">
-        <v>0.902</v>
+        <v>0.893</v>
       </c>
       <c r="D11" s="24" t="n">
-        <v>-0.098</v>
+        <v>-0.092</v>
       </c>
       <c r="E11" s="24" t="n">
-        <v>-0.055</v>
+        <v>-0.061</v>
       </c>
       <c r="F11" s="24" t="n">
-        <v>-0.08799999999999999</v>
+        <v>-0.08</v>
       </c>
       <c r="G11" s="24" t="n">
-        <v>-0.077</v>
+        <v>-0.076</v>
       </c>
       <c r="H11" s="24" t="n">
-        <v>-0.042</v>
+        <v>-0.036</v>
       </c>
       <c r="I11" s="24" t="n">
-        <v>-0.026</v>
+        <v>-0.017</v>
       </c>
       <c r="J11" s="24" t="n">
-        <v>-0.018</v>
+        <v>-0.024</v>
       </c>
       <c r="K11" s="24" t="inlineStr">
         <is>
@@ -2416,38 +2416,38 @@
         </is>
       </c>
       <c r="B12" s="24" t="n">
-        <v>4.476</v>
+        <v>4.46</v>
       </c>
       <c r="C12" s="24" t="n">
-        <v>1.211</v>
+        <v>1.236</v>
       </c>
       <c r="D12" s="24" t="n">
-        <v>-0.049</v>
+        <v>-0.042</v>
       </c>
       <c r="E12" s="24" t="n">
-        <v>0.042</v>
+        <v>0.029</v>
       </c>
       <c r="F12" s="24" t="n">
-        <v>0.003</v>
+        <v>0.007</v>
       </c>
       <c r="G12" s="24" t="n">
-        <v>-0.064</v>
+        <v>-0.07099999999999999</v>
       </c>
       <c r="H12" s="24" t="inlineStr">
         <is>
-          <t>-0.517***</t>
+          <t>-0.521***</t>
         </is>
       </c>
       <c r="I12" s="24" t="inlineStr">
         <is>
-          <t>0.519***</t>
+          <t>0.522***</t>
         </is>
       </c>
       <c r="J12" s="24" t="n">
-        <v>-0.005</v>
+        <v>0.001</v>
       </c>
       <c r="K12" s="24" t="n">
-        <v>-0.02</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="L12" s="24" t="inlineStr">
         <is>
@@ -2467,38 +2467,38 @@
         </is>
       </c>
       <c r="B13" s="24" t="n">
-        <v>3.087</v>
+        <v>3.095</v>
       </c>
       <c r="C13" s="24" t="n">
-        <v>1.233</v>
+        <v>1.208</v>
       </c>
       <c r="D13" s="24" t="n">
-        <v>-0.007</v>
+        <v>0.002</v>
       </c>
       <c r="E13" s="24" t="n">
-        <v>-0.003</v>
+        <v>0.004</v>
       </c>
       <c r="F13" s="24" t="n">
-        <v>-0.06900000000000001</v>
+        <v>-0.067</v>
       </c>
       <c r="G13" s="24" t="n">
-        <v>0.045</v>
+        <v>0.04</v>
       </c>
       <c r="H13" s="24" t="inlineStr">
         <is>
-          <t>0.534***</t>
+          <t>0.54***</t>
         </is>
       </c>
       <c r="I13" s="24" t="inlineStr">
         <is>
-          <t>-0.51***</t>
+          <t>-0.508***</t>
         </is>
       </c>
       <c r="J13" s="24" t="n">
-        <v>0.04</v>
+        <v>0.042</v>
       </c>
       <c r="K13" s="24" t="n">
-        <v>-0.08699999999999999</v>
+        <v>-0.076</v>
       </c>
       <c r="L13" s="24" t="inlineStr">
         <is>
@@ -2522,42 +2522,42 @@
         </is>
       </c>
       <c r="B14" s="24" t="n">
-        <v>4.438</v>
+        <v>4.399</v>
       </c>
       <c r="C14" s="24" t="n">
-        <v>0.628</v>
+        <v>0.644</v>
       </c>
       <c r="D14" s="24" t="n">
-        <v>0.024</v>
+        <v>0.015</v>
       </c>
       <c r="E14" s="24" t="n">
-        <v>-0.029</v>
+        <v>-0.019</v>
       </c>
       <c r="F14" s="24" t="n">
-        <v>-0.035</v>
+        <v>-0.026</v>
       </c>
       <c r="G14" s="24" t="n">
-        <v>-0.031</v>
+        <v>-0.025</v>
       </c>
       <c r="H14" s="24" t="n">
-        <v>0.059</v>
+        <v>0.058</v>
       </c>
       <c r="I14" s="24" t="n">
-        <v>-0.053</v>
+        <v>-0.066</v>
       </c>
       <c r="J14" s="24" t="inlineStr">
         <is>
-          <t>-0.124*</t>
+          <t>-0.135*</t>
         </is>
       </c>
       <c r="K14" s="24" t="n">
-        <v>-0.082</v>
+        <v>-0.076</v>
       </c>
       <c r="L14" s="24" t="n">
-        <v>-0.006</v>
+        <v>0.003</v>
       </c>
       <c r="M14" s="24" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.08</v>
       </c>
       <c r="N14" s="24" t="inlineStr">
         <is>
@@ -2575,52 +2575,52 @@
         </is>
       </c>
       <c r="B15" s="24" t="n">
-        <v>4.51</v>
+        <v>4.498</v>
       </c>
       <c r="C15" s="24" t="n">
-        <v>0.782</v>
+        <v>0.766</v>
       </c>
       <c r="D15" s="24" t="n">
-        <v>-0.034</v>
+        <v>-0.026</v>
       </c>
       <c r="E15" s="24" t="n">
-        <v>-0.002</v>
+        <v>0.005</v>
       </c>
       <c r="F15" s="24" t="n">
-        <v>0.028</v>
+        <v>0.04</v>
       </c>
       <c r="G15" s="24" t="n">
-        <v>-0.06900000000000001</v>
+        <v>-0.068</v>
       </c>
       <c r="H15" s="24" t="inlineStr">
         <is>
-          <t>-0.452***</t>
+          <t>-0.443***</t>
         </is>
       </c>
       <c r="I15" s="24" t="inlineStr">
         <is>
-          <t>0.41***</t>
+          <t>0.422***</t>
         </is>
       </c>
       <c r="J15" s="24" t="n">
-        <v>-0.054</v>
+        <v>-0.041</v>
       </c>
       <c r="K15" s="24" t="n">
-        <v>0.004</v>
+        <v>0.011</v>
       </c>
       <c r="L15" s="24" t="inlineStr">
         <is>
-          <t>0.562***</t>
+          <t>0.56***</t>
         </is>
       </c>
       <c r="M15" s="24" t="inlineStr">
         <is>
-          <t>-0.59***</t>
+          <t>-0.602***</t>
         </is>
       </c>
       <c r="N15" s="24" t="inlineStr">
         <is>
-          <t>0.393***</t>
+          <t>0.398***</t>
         </is>
       </c>
       <c r="O15" s="24" t="inlineStr">
@@ -2638,7 +2638,7 @@
         </is>
       </c>
       <c r="B16" s="24" t="n">
-        <v>4.985</v>
+        <v>4.78</v>
       </c>
       <c r="C16" s="24" t="n">
         <v>1.07</v>
@@ -2972,35 +2972,35 @@
       </c>
       <c r="B6" s="24" t="inlineStr">
         <is>
-          <t>3.793***</t>
+          <t>3.821***</t>
         </is>
       </c>
       <c r="C6" s="24" t="n">
-        <v>0.092</v>
+        <v>0.094</v>
       </c>
       <c r="D6" s="24" t="inlineStr">
         <is>
-          <t>3.793***</t>
+          <t>3.821***</t>
         </is>
       </c>
       <c r="E6" s="24" t="n">
-        <v>0.092</v>
+        <v>0.094</v>
       </c>
       <c r="F6" s="24" t="inlineStr">
         <is>
-          <t>3.785***</t>
+          <t>3.812***</t>
         </is>
       </c>
       <c r="G6" s="24" t="n">
-        <v>0.094</v>
+        <v>0.096</v>
       </c>
       <c r="H6" s="24" t="inlineStr">
         <is>
-          <t>3.785***</t>
+          <t>3.812***</t>
         </is>
       </c>
       <c r="I6" s="24" t="n">
-        <v>0.094</v>
+        <v>0.096</v>
       </c>
       <c r="J6" s="24" t="inlineStr">
         <is>

--- a/results/Model3.xlsx
+++ b/results/Model3.xlsx
@@ -1904,10 +1904,10 @@
         <v>877</v>
       </c>
       <c r="F5" s="32" t="n">
-        <v>0.906</v>
+        <v>0.908</v>
       </c>
       <c r="G5" s="32" t="n">
-        <v>0.897</v>
+        <v>0.899</v>
       </c>
       <c r="H5" s="32" t="n">
         <v>0.062</v>
@@ -1939,28 +1939,28 @@
         </is>
       </c>
       <c r="D6" s="32" t="n">
-        <v>2531.6</v>
+        <v>2895.6</v>
       </c>
       <c r="E6" s="32" t="n">
         <v>882</v>
       </c>
       <c r="F6" s="32" t="n">
-        <v>0.9</v>
+        <v>0.898</v>
       </c>
       <c r="G6" s="32" t="n">
-        <v>0.889</v>
+        <v>0.886</v>
       </c>
       <c r="H6" s="32" t="n">
-        <v>0.064</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="I6" s="32" t="n">
-        <v>0.057</v>
+        <v>0.061</v>
       </c>
       <c r="J6" s="32" t="n">
-        <v>0.075</v>
+        <v>0.082</v>
       </c>
       <c r="K6" s="32" t="n">
-        <v>31807.6</v>
+        <v>32171.8</v>
       </c>
     </row>
     <row r="7" ht="46.5" customHeight="1" s="37">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="D8" s="14" t="inlineStr">
         <is>
-          <t>-0.034*</t>
+          <t>-0.044*</t>
         </is>
       </c>
       <c r="E8" s="14" t="inlineStr">
         <is>
-          <t>[-0.065, -0.014]</t>
+          <t>[-0.078, -0.022]</t>
         </is>
       </c>
       <c r="F8" s="14" t="inlineStr">
@@ -4356,11 +4356,11 @@
         </is>
       </c>
       <c r="D10" s="14" t="n">
-        <v>-0.026</v>
+        <v>-0.033</v>
       </c>
       <c r="E10" s="14" t="inlineStr">
         <is>
-          <t>[-0.058, 0.006]</t>
+          <t>[-0.069, 0.003]</t>
         </is>
       </c>
       <c r="F10" s="14" t="n">
@@ -4388,12 +4388,12 @@
       </c>
       <c r="D11" s="14" t="inlineStr">
         <is>
-          <t>-0.045*</t>
+          <t>-0.058*</t>
         </is>
       </c>
       <c r="E11" s="14" t="inlineStr">
         <is>
-          <t>[-0.087, -0.003]</t>
+          <t>[-0.106, -0.010]</t>
         </is>
       </c>
       <c r="F11" s="14" t="n">
@@ -4420,11 +4420,11 @@
         </is>
       </c>
       <c r="D12" s="14" t="n">
-        <v>0.019</v>
+        <v>0.024</v>
       </c>
       <c r="E12" s="14" t="inlineStr">
         <is>
-          <t>[-0.010, 0.048]</t>
+          <t>[-0.007, 0.055]</t>
         </is>
       </c>
       <c r="F12" s="14" t="n">
@@ -4464,11 +4464,11 @@
         </is>
       </c>
       <c r="D14" s="14" t="n">
-        <v>-0.016</v>
+        <v>-0.021</v>
       </c>
       <c r="E14" s="14" t="inlineStr">
         <is>
-          <t>[-0.043, 0.011]</t>
+          <t>[-0.051, 0.009]</t>
         </is>
       </c>
       <c r="F14" s="14" t="n">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="D15" s="14" t="inlineStr">
         <is>
-          <t>-0.048*</t>
+          <t>-0.062*</t>
         </is>
       </c>
       <c r="E15" s="14" t="inlineStr">
         <is>
-          <t>[-0.091, -0.005]</t>
+          <t>[-0.112, -0.012]</t>
         </is>
       </c>
       <c r="F15" s="14" t="n">
@@ -4531,12 +4531,14 @@
           <t>[0.006, 0.094]</t>
         </is>
       </c>
-      <c r="D16" s="14" t="n">
-        <v>0.032</v>
+      <c r="D16" s="14" t="inlineStr">
+        <is>
+          <t>0.041*</t>
+        </is>
       </c>
       <c r="E16" s="14" t="inlineStr">
         <is>
-          <t>[-0.003, 0.067]</t>
+          <t>[0.001, 0.081]</t>
         </is>
       </c>
       <c r="F16" s="14" t="n">
@@ -4861,12 +4863,12 @@
       </c>
       <c r="D28" s="18" t="inlineStr">
         <is>
-          <t>-0.04*</t>
+          <t>-0.062*</t>
         </is>
       </c>
       <c r="E28" s="18" t="inlineStr">
         <is>
-          <t>[-0.072, -0.014]</t>
+          <t>[-0.099, -0.029]</t>
         </is>
       </c>
       <c r="F28" s="18" t="inlineStr">
@@ -4896,12 +4898,14 @@
           <t>[-0.133, -0.019]</t>
         </is>
       </c>
-      <c r="D29" s="18" t="n">
-        <v>-0.036</v>
+      <c r="D29" s="18" t="inlineStr">
+        <is>
+          <t>-0.056*</t>
+        </is>
       </c>
       <c r="E29" s="18" t="inlineStr">
         <is>
-          <t>[-0.073, 0.001]</t>
+          <t>[-0.103, -0.009]</t>
         </is>
       </c>
       <c r="F29" s="18" t="inlineStr">
@@ -4933,12 +4937,12 @@
       </c>
       <c r="D30" s="18" t="inlineStr">
         <is>
-          <t>-0.044*</t>
+          <t>-0.068*</t>
         </is>
       </c>
       <c r="E30" s="18" t="inlineStr">
         <is>
-          <t>[-0.085, -0.003]</t>
+          <t>[-0.121, -0.015]</t>
         </is>
       </c>
       <c r="F30" s="18" t="inlineStr">
@@ -4967,11 +4971,11 @@
         </is>
       </c>
       <c r="D31" s="18" t="n">
-        <v>0.008</v>
+        <v>0.013</v>
       </c>
       <c r="E31" s="18" t="inlineStr">
         <is>
-          <t>[-0.016, 0.032]</t>
+          <t>[-0.013, 0.039]</t>
         </is>
       </c>
       <c r="F31" s="18" t="n">
@@ -4999,12 +5003,14 @@
           <t>[-0.079, -0.001]</t>
         </is>
       </c>
-      <c r="D32" s="18" t="n">
-        <v>-0.028</v>
+      <c r="D32" s="18" t="inlineStr">
+        <is>
+          <t>-0.043*</t>
+        </is>
       </c>
       <c r="E32" s="18" t="inlineStr">
         <is>
-          <t>[-0.061, 0.005]</t>
+          <t>[-0.084, -0.002]</t>
         </is>
       </c>
       <c r="F32" s="18" t="inlineStr">
@@ -5036,12 +5042,12 @@
       </c>
       <c r="D33" s="18" t="inlineStr">
         <is>
-          <t>-0.049*</t>
+          <t>-0.076*</t>
         </is>
       </c>
       <c r="E33" s="18" t="inlineStr">
         <is>
-          <t>[-0.093, -0.005]</t>
+          <t>[-0.133, -0.019]</t>
         </is>
       </c>
       <c r="F33" s="18" t="inlineStr">
@@ -5072,11 +5078,11 @@
         </is>
       </c>
       <c r="D34" s="18" t="n">
-        <v>0.021</v>
+        <v>0.033</v>
       </c>
       <c r="E34" s="18" t="inlineStr">
         <is>
-          <t>[-0.009, 0.051]</t>
+          <t>[-0.003, 0.069]</t>
         </is>
       </c>
       <c r="F34" s="18" t="inlineStr">
@@ -5121,12 +5127,12 @@
       </c>
       <c r="D36" s="20" t="inlineStr">
         <is>
-          <t>0.019*</t>
+          <t>0.034*</t>
         </is>
       </c>
       <c r="E36" s="20" t="inlineStr">
         <is>
-          <t>[0.006, 0.038]</t>
+          <t>[0.014, 0.054]</t>
         </is>
       </c>
       <c r="F36" s="20" t="inlineStr">
@@ -5155,11 +5161,11 @@
         </is>
       </c>
       <c r="D37" s="20" t="n">
-        <v>0.021</v>
+        <v>0.038</v>
       </c>
       <c r="E37" s="20" t="inlineStr">
         <is>
-          <t>[-0.009, 0.051]</t>
+          <t>[-0.000, 0.076]</t>
         </is>
       </c>
       <c r="F37" s="20" t="inlineStr">
@@ -5188,11 +5194,11 @@
         </is>
       </c>
       <c r="D38" s="20" t="n">
-        <v>0.017</v>
+        <v>0.03</v>
       </c>
       <c r="E38" s="20" t="inlineStr">
         <is>
-          <t>[-0.011, 0.045]</t>
+          <t>[-0.004, 0.064]</t>
         </is>
       </c>
       <c r="F38" s="20" t="inlineStr">
@@ -5221,11 +5227,11 @@
         </is>
       </c>
       <c r="D39" s="20" t="n">
-        <v>0.005</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="E39" s="20" t="inlineStr">
         <is>
-          <t>[-0.019, 0.029]</t>
+          <t>[-0.015, 0.033]</t>
         </is>
       </c>
       <c r="F39" s="20" t="n">
@@ -5253,12 +5259,14 @@
           <t>[0.002, 0.082]</t>
         </is>
       </c>
-      <c r="D40" s="20" t="n">
-        <v>0.036</v>
+      <c r="D40" s="20" t="inlineStr">
+        <is>
+          <t>0.064*</t>
+        </is>
       </c>
       <c r="E40" s="20" t="inlineStr">
         <is>
-          <t>[-0.001, 0.073]</t>
+          <t>[0.013, 0.115]</t>
         </is>
       </c>
       <c r="F40" s="20" t="inlineStr">
@@ -5287,11 +5295,11 @@
         </is>
       </c>
       <c r="D41" s="20" t="n">
-        <v>0.004</v>
+        <v>0.007</v>
       </c>
       <c r="E41" s="20" t="inlineStr">
         <is>
-          <t>[-0.020, 0.028]</t>
+          <t>[-0.017, 0.031]</t>
         </is>
       </c>
       <c r="F41" s="20" t="n">
@@ -5317,12 +5325,14 @@
           <t>[-0.009, 0.051]</t>
         </is>
       </c>
-      <c r="D42" s="20" t="n">
-        <v>0.031</v>
+      <c r="D42" s="20" t="inlineStr">
+        <is>
+          <t>0.056*</t>
+        </is>
       </c>
       <c r="E42" s="20" t="inlineStr">
         <is>
-          <t>[-0.004, 0.066]</t>
+          <t>[0.009, 0.103]</t>
         </is>
       </c>
       <c r="F42" s="20" t="n">

--- a/results/Model3.xlsx
+++ b/results/Model3.xlsx
@@ -3004,11 +3004,11 @@
       </c>
       <c r="J6" s="24" t="inlineStr">
         <is>
-          <t>4.412***</t>
+          <t>4.402***</t>
         </is>
       </c>
       <c r="K6" s="24" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="L6" s="24" t="inlineStr">
         <is>
@@ -3549,11 +3549,11 @@
       </c>
       <c r="J17" s="24" t="inlineStr">
         <is>
-          <t>0.248***</t>
+          <t>0.234***</t>
         </is>
       </c>
       <c r="K17" s="24" t="n">
-        <v>0.045</v>
+        <v>0.046</v>
       </c>
       <c r="L17" s="24" t="inlineStr">
         <is>
@@ -3620,11 +3620,11 @@
       </c>
       <c r="J18" s="24" t="inlineStr">
         <is>
-          <t>-0.212***</t>
+          <t>-0.198***</t>
         </is>
       </c>
       <c r="K18" s="24" t="n">
-        <v>0.05</v>
+        <v>0.051</v>
       </c>
       <c r="L18" s="24" t="inlineStr">
         <is>
@@ -4100,7 +4100,7 @@
         <v>0.198</v>
       </c>
       <c r="J27" s="24" t="n">
-        <v>0.358</v>
+        <v>0.342</v>
       </c>
       <c r="L27" s="24" t="n">
         <v>0.247</v>
@@ -4128,7 +4128,7 @@
         <v>0.118</v>
       </c>
       <c r="J28" s="27" t="n">
-        <v>0.231</v>
+        <v>0.218</v>
       </c>
       <c r="L28" s="27" t="n">
         <v>0.149</v>

--- a/results/Model3.xlsx
+++ b/results/Model3.xlsx
@@ -2108,7 +2108,7 @@
         </is>
       </c>
       <c r="B4" s="24" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="C4" s="24" t="n">
         <v>0.497</v>
@@ -2139,13 +2139,13 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>30.781</v>
+        <v>30.794</v>
       </c>
       <c r="C5" s="24" t="n">
-        <v>4.593</v>
+        <v>4.649</v>
       </c>
       <c r="D5" s="24" t="n">
-        <v>0.017</v>
+        <v>0.018</v>
       </c>
       <c r="E5" s="24" t="inlineStr">
         <is>
@@ -2172,17 +2172,17 @@
         </is>
       </c>
       <c r="B6" s="24" t="n">
-        <v>2.359</v>
+        <v>2.374</v>
       </c>
       <c r="C6" s="24" t="n">
-        <v>1.476</v>
+        <v>1.486</v>
       </c>
       <c r="D6" s="24" t="n">
         <v>-0.027</v>
       </c>
       <c r="E6" s="24" t="inlineStr">
         <is>
-          <t>0.178***</t>
+          <t>0.18***</t>
         </is>
       </c>
       <c r="F6" s="24" t="inlineStr">
@@ -2209,19 +2209,19 @@
         </is>
       </c>
       <c r="B7" s="24" t="n">
-        <v>3.296</v>
+        <v>3.291</v>
       </c>
       <c r="C7" s="24" t="n">
-        <v>1.071</v>
+        <v>1.078</v>
       </c>
       <c r="D7" s="24" t="n">
-        <v>0.101</v>
+        <v>0.09</v>
       </c>
       <c r="E7" s="24" t="n">
-        <v>-0.008999999999999999</v>
+        <v>-0.01</v>
       </c>
       <c r="F7" s="24" t="n">
-        <v>-0.079</v>
+        <v>-0.055</v>
       </c>
       <c r="G7" s="24" t="inlineStr">
         <is>
@@ -2246,19 +2246,19 @@
         </is>
       </c>
       <c r="B8" s="24" t="n">
-        <v>4.083</v>
+        <v>4.068</v>
       </c>
       <c r="C8" s="24" t="n">
-        <v>0.885</v>
+        <v>0.897</v>
       </c>
       <c r="D8" s="24" t="n">
-        <v>-0.059</v>
+        <v>-0.051</v>
       </c>
       <c r="E8" s="24" t="n">
-        <v>-0.034</v>
+        <v>-0.045</v>
       </c>
       <c r="F8" s="24" t="n">
-        <v>0.077</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="G8" s="24" t="n">
         <v>0.008999999999999999</v>
@@ -2285,26 +2285,26 @@
         </is>
       </c>
       <c r="B9" s="24" t="n">
-        <v>4.898</v>
+        <v>4.918</v>
       </c>
       <c r="C9" s="24" t="n">
-        <v>0.971</v>
+        <v>0.963</v>
       </c>
       <c r="D9" s="24" t="n">
-        <v>-0.025</v>
+        <v>-0.013</v>
       </c>
       <c r="E9" s="24" t="n">
         <v>-0.008</v>
       </c>
       <c r="F9" s="24" t="n">
-        <v>0.035</v>
+        <v>0</v>
       </c>
       <c r="G9" s="24" t="n">
-        <v>-0.08400000000000001</v>
+        <v>-0.068</v>
       </c>
       <c r="H9" s="24" t="inlineStr">
         <is>
-          <t>-0.342***</t>
+          <t>-0.338***</t>
         </is>
       </c>
       <c r="I9" s="24" t="inlineStr">
@@ -2328,28 +2328,28 @@
         </is>
       </c>
       <c r="B10" s="24" t="n">
-        <v>3.479</v>
+        <v>3.477</v>
       </c>
       <c r="C10" s="24" t="n">
-        <v>0.885</v>
+        <v>0.886</v>
       </c>
       <c r="D10" s="24" t="n">
-        <v>-0.05</v>
+        <v>-0.066</v>
       </c>
       <c r="E10" s="24" t="n">
-        <v>-0.032</v>
+        <v>-0.037</v>
       </c>
       <c r="F10" s="24" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="G10" s="24" t="n">
-        <v>-0.066</v>
+        <v>-0.063</v>
       </c>
       <c r="H10" s="24" t="n">
-        <v>0.021</v>
+        <v>0.034</v>
       </c>
       <c r="I10" s="24" t="n">
-        <v>0.078</v>
+        <v>0.061</v>
       </c>
       <c r="J10" s="24" t="inlineStr">
         <is>
@@ -2371,31 +2371,31 @@
         </is>
       </c>
       <c r="B11" s="24" t="n">
-        <v>4.599</v>
+        <v>4.609</v>
       </c>
       <c r="C11" s="24" t="n">
-        <v>0.893</v>
+        <v>0.889</v>
       </c>
       <c r="D11" s="24" t="n">
-        <v>-0.092</v>
+        <v>-0.096</v>
       </c>
       <c r="E11" s="24" t="n">
-        <v>-0.061</v>
+        <v>-0.048</v>
       </c>
       <c r="F11" s="24" t="n">
-        <v>-0.08</v>
+        <v>-0.08599999999999999</v>
       </c>
       <c r="G11" s="24" t="n">
-        <v>-0.076</v>
+        <v>-0.07099999999999999</v>
       </c>
       <c r="H11" s="24" t="n">
-        <v>-0.036</v>
+        <v>-0.034</v>
       </c>
       <c r="I11" s="24" t="n">
-        <v>-0.017</v>
+        <v>-0.045</v>
       </c>
       <c r="J11" s="24" t="n">
-        <v>-0.024</v>
+        <v>-0.023</v>
       </c>
       <c r="K11" s="24" t="inlineStr">
         <is>
@@ -2416,38 +2416,38 @@
         </is>
       </c>
       <c r="B12" s="24" t="n">
-        <v>4.46</v>
+        <v>4.439</v>
       </c>
       <c r="C12" s="24" t="n">
-        <v>1.236</v>
+        <v>1.259</v>
       </c>
       <c r="D12" s="24" t="n">
-        <v>-0.042</v>
+        <v>0.004</v>
       </c>
       <c r="E12" s="24" t="n">
-        <v>0.029</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="F12" s="24" t="n">
-        <v>0.007</v>
+        <v>0.015</v>
       </c>
       <c r="G12" s="24" t="n">
-        <v>-0.07099999999999999</v>
+        <v>-0.031</v>
       </c>
       <c r="H12" s="24" t="inlineStr">
         <is>
-          <t>-0.521***</t>
+          <t>-0.487***</t>
         </is>
       </c>
       <c r="I12" s="24" t="inlineStr">
         <is>
-          <t>0.522***</t>
+          <t>0.519***</t>
         </is>
       </c>
       <c r="J12" s="24" t="n">
-        <v>0.001</v>
+        <v>-0.022</v>
       </c>
       <c r="K12" s="24" t="n">
-        <v>-0.008999999999999999</v>
+        <v>-0.058</v>
       </c>
       <c r="L12" s="24" t="inlineStr">
         <is>
@@ -2467,42 +2467,42 @@
         </is>
       </c>
       <c r="B13" s="24" t="n">
-        <v>3.095</v>
+        <v>3.137</v>
       </c>
       <c r="C13" s="24" t="n">
-        <v>1.208</v>
+        <v>1.201</v>
       </c>
       <c r="D13" s="24" t="n">
-        <v>0.002</v>
+        <v>-0.076</v>
       </c>
       <c r="E13" s="24" t="n">
-        <v>0.004</v>
+        <v>-0.008</v>
       </c>
       <c r="F13" s="24" t="n">
-        <v>-0.067</v>
+        <v>0.056</v>
       </c>
       <c r="G13" s="24" t="n">
-        <v>0.04</v>
+        <v>0.028</v>
       </c>
       <c r="H13" s="24" t="inlineStr">
         <is>
-          <t>0.54***</t>
+          <t>0.539***</t>
         </is>
       </c>
       <c r="I13" s="24" t="inlineStr">
         <is>
-          <t>-0.508***</t>
+          <t>-0.467***</t>
         </is>
       </c>
       <c r="J13" s="24" t="n">
-        <v>0.042</v>
+        <v>0.038</v>
       </c>
       <c r="K13" s="24" t="n">
-        <v>-0.076</v>
+        <v>0.051</v>
       </c>
       <c r="L13" s="24" t="inlineStr">
         <is>
-          <t>-0.431***</t>
+          <t>-0.427***</t>
         </is>
       </c>
       <c r="M13" s="24" t="inlineStr">
@@ -2522,42 +2522,44 @@
         </is>
       </c>
       <c r="B14" s="24" t="n">
-        <v>4.399</v>
+        <v>4.398</v>
       </c>
       <c r="C14" s="24" t="n">
-        <v>0.644</v>
+        <v>0.65</v>
       </c>
       <c r="D14" s="24" t="n">
-        <v>0.015</v>
+        <v>0.048</v>
       </c>
       <c r="E14" s="24" t="n">
-        <v>-0.019</v>
+        <v>-0.011</v>
       </c>
       <c r="F14" s="24" t="n">
-        <v>-0.026</v>
+        <v>-0.015</v>
       </c>
       <c r="G14" s="24" t="n">
-        <v>-0.025</v>
+        <v>-0.017</v>
       </c>
       <c r="H14" s="24" t="n">
-        <v>0.058</v>
+        <v>0.065</v>
       </c>
       <c r="I14" s="24" t="n">
-        <v>-0.066</v>
+        <v>-0.07199999999999999</v>
       </c>
       <c r="J14" s="24" t="inlineStr">
         <is>
-          <t>-0.135*</t>
+          <t>-0.12*</t>
         </is>
       </c>
       <c r="K14" s="24" t="n">
-        <v>-0.076</v>
-      </c>
-      <c r="L14" s="24" t="n">
-        <v>0.003</v>
+        <v>-0.08799999999999999</v>
+      </c>
+      <c r="L14" s="24" t="inlineStr">
+        <is>
+          <t>0.116*</t>
+        </is>
       </c>
       <c r="M14" s="24" t="n">
-        <v>0.08</v>
+        <v>-0.074</v>
       </c>
       <c r="N14" s="24" t="inlineStr">
         <is>
@@ -2575,52 +2577,52 @@
         </is>
       </c>
       <c r="B15" s="24" t="n">
-        <v>4.498</v>
+        <v>4.49</v>
       </c>
       <c r="C15" s="24" t="n">
-        <v>0.766</v>
+        <v>0.781</v>
       </c>
       <c r="D15" s="24" t="n">
-        <v>-0.026</v>
+        <v>0.024</v>
       </c>
       <c r="E15" s="24" t="n">
-        <v>0.005</v>
+        <v>-0.056</v>
       </c>
       <c r="F15" s="24" t="n">
-        <v>0.04</v>
+        <v>-0.03</v>
       </c>
       <c r="G15" s="24" t="n">
-        <v>-0.068</v>
+        <v>-0.022</v>
       </c>
       <c r="H15" s="24" t="inlineStr">
         <is>
-          <t>-0.443***</t>
+          <t>-0.279***</t>
         </is>
       </c>
       <c r="I15" s="24" t="inlineStr">
         <is>
-          <t>0.422***</t>
+          <t>0.307***</t>
         </is>
       </c>
       <c r="J15" s="24" t="n">
-        <v>-0.041</v>
+        <v>-0.056</v>
       </c>
       <c r="K15" s="24" t="n">
-        <v>0.011</v>
+        <v>-0.038</v>
       </c>
       <c r="L15" s="24" t="inlineStr">
         <is>
-          <t>0.56***</t>
+          <t>0.482***</t>
         </is>
       </c>
       <c r="M15" s="24" t="inlineStr">
         <is>
-          <t>-0.602***</t>
+          <t>-0.407***</t>
         </is>
       </c>
       <c r="N15" s="24" t="inlineStr">
         <is>
-          <t>0.398***</t>
+          <t>0.389***</t>
         </is>
       </c>
       <c r="O15" s="24" t="inlineStr">
@@ -2641,35 +2643,37 @@
         <v>4.78</v>
       </c>
       <c r="C16" s="24" t="n">
-        <v>1.07</v>
+        <v>1.057</v>
       </c>
       <c r="D16" s="24" t="n">
-        <v>-0.007</v>
+        <v>0.062</v>
       </c>
       <c r="E16" s="24" t="n">
-        <v>0.042</v>
+        <v>-0.022</v>
       </c>
       <c r="F16" s="24" t="n">
-        <v>-0.017</v>
-      </c>
-      <c r="G16" s="24" t="n">
-        <v>0.043</v>
+        <v>0.03</v>
+      </c>
+      <c r="G16" s="24" t="inlineStr">
+        <is>
+          <t>-0.108*</t>
+        </is>
       </c>
       <c r="H16" s="24" t="inlineStr">
         <is>
-          <t>-0.462***</t>
+          <t>-0.18***</t>
         </is>
       </c>
       <c r="I16" s="24" t="inlineStr">
         <is>
-          <t>0.339***</t>
+          <t>0.231***</t>
         </is>
       </c>
       <c r="J16" s="24" t="n">
-        <v>0.008999999999999999</v>
+        <v>-0.062</v>
       </c>
       <c r="K16" s="24" t="n">
-        <v>0.1</v>
+        <v>-0.098</v>
       </c>
       <c r="L16" s="24" t="inlineStr">
         <is>
@@ -2678,15 +2682,15 @@
       </c>
       <c r="M16" s="24" t="inlineStr">
         <is>
-          <t>-0.5***</t>
+          <t>-0.285***</t>
         </is>
       </c>
       <c r="N16" s="24" t="n">
-        <v>-0.01</v>
+        <v>0.081</v>
       </c>
       <c r="O16" s="24" t="inlineStr">
         <is>
-          <t>0.39***</t>
+          <t>0.316***</t>
         </is>
       </c>
       <c r="P16" s="24" t="inlineStr">
@@ -2703,44 +2707,42 @@
         </is>
       </c>
       <c r="B17" s="24" t="n">
-        <v>2.648</v>
+        <v>2.702</v>
       </c>
       <c r="C17" s="24" t="n">
-        <v>1.112</v>
+        <v>1.04</v>
       </c>
       <c r="D17" s="24" t="n">
-        <v>0.035</v>
+        <v>-0.073</v>
       </c>
       <c r="E17" s="24" t="n">
-        <v>-0.031</v>
+        <v>0.008</v>
       </c>
       <c r="F17" s="24" t="n">
-        <v>-0.032</v>
-      </c>
-      <c r="G17" s="24" t="inlineStr">
-        <is>
-          <t>0.154**</t>
-        </is>
+        <v>0.006</v>
+      </c>
+      <c r="G17" s="24" t="n">
+        <v>0.005</v>
       </c>
       <c r="H17" s="24" t="inlineStr">
         <is>
-          <t>0.413***</t>
+          <t>0.342***</t>
         </is>
       </c>
       <c r="I17" s="24" t="inlineStr">
         <is>
-          <t>-0.333***</t>
+          <t>-0.267***</t>
         </is>
       </c>
       <c r="J17" s="24" t="n">
-        <v>-0.057</v>
+        <v>0.093</v>
       </c>
       <c r="K17" s="24" t="n">
-        <v>-0.008999999999999999</v>
+        <v>0.025</v>
       </c>
       <c r="L17" s="24" t="inlineStr">
         <is>
-          <t>-0.524***</t>
+          <t>-0.298***</t>
         </is>
       </c>
       <c r="M17" s="24" t="inlineStr">
@@ -2749,11 +2751,11 @@
         </is>
       </c>
       <c r="N17" s="24" t="n">
-        <v>-0.058</v>
+        <v>-0.037</v>
       </c>
       <c r="O17" s="24" t="inlineStr">
         <is>
-          <t>-0.442***</t>
+          <t>-0.266***</t>
         </is>
       </c>
       <c r="P17" s="24" t="inlineStr">
@@ -2972,59 +2974,59 @@
       </c>
       <c r="B6" s="24" t="inlineStr">
         <is>
-          <t>3.821***</t>
+          <t>0.023</t>
         </is>
       </c>
       <c r="C6" s="24" t="n">
-        <v>0.094</v>
+        <v>0.081</v>
       </c>
       <c r="D6" s="24" t="inlineStr">
         <is>
-          <t>3.821***</t>
+          <t>0.013</t>
         </is>
       </c>
       <c r="E6" s="24" t="n">
-        <v>0.094</v>
+        <v>0.081</v>
       </c>
       <c r="F6" s="24" t="inlineStr">
         <is>
-          <t>3.812***</t>
+          <t>0.070</t>
         </is>
       </c>
       <c r="G6" s="24" t="n">
-        <v>0.096</v>
+        <v>0.077</v>
       </c>
       <c r="H6" s="24" t="inlineStr">
         <is>
-          <t>3.812***</t>
+          <t>0.050</t>
         </is>
       </c>
       <c r="I6" s="24" t="n">
-        <v>0.096</v>
+        <v>0.077</v>
       </c>
       <c r="J6" s="24" t="inlineStr">
         <is>
-          <t>4.402***</t>
+          <t>0.006</t>
         </is>
       </c>
       <c r="K6" s="24" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.05</v>
       </c>
       <c r="L6" s="24" t="inlineStr">
         <is>
-          <t>4.952***</t>
+          <t>-0.061</t>
         </is>
       </c>
       <c r="M6" s="24" t="n">
-        <v>0.102</v>
+        <v>0.08</v>
       </c>
       <c r="N6" s="24" t="inlineStr">
         <is>
-          <t>2.654***</t>
+          <t>0.041</t>
         </is>
       </c>
       <c r="O6" s="24" t="n">
-        <v>0.097</v>
+        <v>0.074</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" s="37">
@@ -3054,47 +3056,61 @@
           <t>Age</t>
         </is>
       </c>
-      <c r="B8" s="24" t="n">
-        <v>-0.021</v>
+      <c r="B8" s="24" t="inlineStr">
+        <is>
+          <t>0.013</t>
+        </is>
       </c>
       <c r="C8" s="24" t="n">
-        <v>0.022</v>
-      </c>
-      <c r="D8" s="24" t="n">
-        <v>-0.022</v>
+        <v>0.012</v>
+      </c>
+      <c r="D8" s="24" t="inlineStr">
+        <is>
+          <t>0.010</t>
+        </is>
       </c>
       <c r="E8" s="24" t="n">
-        <v>0.022</v>
-      </c>
-      <c r="F8" s="24" t="n">
-        <v>-0.017</v>
+        <v>0.012</v>
+      </c>
+      <c r="F8" s="24" t="inlineStr">
+        <is>
+          <t>0.003</t>
+        </is>
       </c>
       <c r="G8" s="24" t="n">
-        <v>0.023</v>
-      </c>
-      <c r="H8" s="24" t="n">
-        <v>-0.018</v>
+        <v>0.011</v>
+      </c>
+      <c r="H8" s="24" t="inlineStr">
+        <is>
+          <t>0.003</t>
+        </is>
       </c>
       <c r="I8" s="24" t="n">
-        <v>0.023</v>
-      </c>
-      <c r="J8" s="24" t="n">
-        <v>-0.014</v>
+        <v>0.011</v>
+      </c>
+      <c r="J8" s="24" t="inlineStr">
+        <is>
+          <t>-0.013†</t>
+        </is>
       </c>
       <c r="K8" s="24" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="L8" s="24" t="n">
-        <v>-0.027</v>
+        <v>0.007</v>
+      </c>
+      <c r="L8" s="24" t="inlineStr">
+        <is>
+          <t>-0.014</t>
+        </is>
       </c>
       <c r="M8" s="24" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="N8" s="24" t="n">
-        <v>-0.012</v>
+        <v>0.011</v>
+      </c>
+      <c r="N8" s="24" t="inlineStr">
+        <is>
+          <t>0.007</t>
+        </is>
       </c>
       <c r="O8" s="24" t="n">
-        <v>0.023</v>
+        <v>0.011</v>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" s="37">
@@ -3103,47 +3119,61 @@
           <t>Gender</t>
         </is>
       </c>
-      <c r="B9" s="24" t="n">
-        <v>0.038</v>
+      <c r="B9" s="24" t="inlineStr">
+        <is>
+          <t>-0.041</t>
+        </is>
       </c>
       <c r="C9" s="24" t="n">
-        <v>0.041</v>
-      </c>
-      <c r="D9" s="24" t="n">
-        <v>0.041</v>
+        <v>0.109</v>
+      </c>
+      <c r="D9" s="24" t="inlineStr">
+        <is>
+          <t>-0.036</t>
+        </is>
       </c>
       <c r="E9" s="24" t="n">
-        <v>0.041</v>
-      </c>
-      <c r="F9" s="24" t="n">
-        <v>0.032</v>
+        <v>0.109</v>
+      </c>
+      <c r="F9" s="24" t="inlineStr">
+        <is>
+          <t>-0.125</t>
+        </is>
       </c>
       <c r="G9" s="24" t="n">
-        <v>0.043</v>
-      </c>
-      <c r="H9" s="24" t="n">
-        <v>0.033</v>
+        <v>0.104</v>
+      </c>
+      <c r="H9" s="24" t="inlineStr">
+        <is>
+          <t>-0.101</t>
+        </is>
       </c>
       <c r="I9" s="24" t="n">
-        <v>0.043</v>
-      </c>
-      <c r="J9" s="24" t="n">
-        <v>0.046</v>
+        <v>0.103</v>
+      </c>
+      <c r="J9" s="24" t="inlineStr">
+        <is>
+          <t>-0.011</t>
+        </is>
       </c>
       <c r="K9" s="24" t="n">
-        <v>0.039</v>
-      </c>
-      <c r="L9" s="24" t="n">
-        <v>0.018</v>
+        <v>0.067</v>
+      </c>
+      <c r="L9" s="24" t="inlineStr">
+        <is>
+          <t>0.107</t>
+        </is>
       </c>
       <c r="M9" s="24" t="n">
-        <v>0.045</v>
-      </c>
-      <c r="N9" s="24" t="n">
-        <v>0.057</v>
+        <v>0.104</v>
+      </c>
+      <c r="N9" s="24" t="inlineStr">
+        <is>
+          <t>-0.073</t>
+        </is>
       </c>
       <c r="O9" s="24" t="n">
-        <v>0.041</v>
+        <v>0.099</v>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" s="37">
@@ -3152,47 +3182,61 @@
           <t xml:space="preserve">Tenure with current leader </t>
         </is>
       </c>
-      <c r="B10" s="24" t="n">
-        <v>0.015</v>
+      <c r="B10" s="24" t="inlineStr">
+        <is>
+          <t>0.028</t>
+        </is>
       </c>
       <c r="C10" s="24" t="n">
-        <v>0.018</v>
-      </c>
-      <c r="D10" s="24" t="n">
-        <v>0.017</v>
+        <v>0.037</v>
+      </c>
+      <c r="D10" s="24" t="inlineStr">
+        <is>
+          <t>0.033</t>
+        </is>
       </c>
       <c r="E10" s="24" t="n">
-        <v>0.018</v>
-      </c>
-      <c r="F10" s="24" t="n">
-        <v>0.011</v>
+        <v>0.037</v>
+      </c>
+      <c r="F10" s="24" t="inlineStr">
+        <is>
+          <t>0.016</t>
+        </is>
       </c>
       <c r="G10" s="24" t="n">
-        <v>0.019</v>
-      </c>
-      <c r="H10" s="24" t="n">
-        <v>0.012</v>
+        <v>0.035</v>
+      </c>
+      <c r="H10" s="24" t="inlineStr">
+        <is>
+          <t>0.009</t>
+        </is>
       </c>
       <c r="I10" s="24" t="n">
-        <v>0.019</v>
-      </c>
-      <c r="J10" s="24" t="n">
-        <v>0.02</v>
+        <v>0.035</v>
+      </c>
+      <c r="J10" s="24" t="inlineStr">
+        <is>
+          <t>-0.001</t>
+        </is>
       </c>
       <c r="K10" s="24" t="n">
-        <v>0.017</v>
-      </c>
-      <c r="L10" s="24" t="n">
-        <v>0.003</v>
+        <v>0.023</v>
+      </c>
+      <c r="L10" s="24" t="inlineStr">
+        <is>
+          <t>0.019</t>
+        </is>
       </c>
       <c r="M10" s="24" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="N10" s="24" t="n">
-        <v>0.025</v>
+        <v>0.035</v>
+      </c>
+      <c r="N10" s="24" t="inlineStr">
+        <is>
+          <t>-0.022</t>
+        </is>
       </c>
       <c r="O10" s="24" t="n">
-        <v>0.019</v>
+        <v>0.034</v>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" s="37">
@@ -3203,59 +3247,59 @@
       </c>
       <c r="B11" s="24" t="inlineStr">
         <is>
-          <t>0.091**</t>
+          <t>-0.003</t>
         </is>
       </c>
       <c r="C11" s="24" t="n">
-        <v>0.034</v>
+        <v>0.05</v>
       </c>
       <c r="D11" s="24" t="inlineStr">
         <is>
-          <t>0.09**</t>
+          <t>0.005</t>
         </is>
       </c>
       <c r="E11" s="24" t="n">
-        <v>0.034</v>
+        <v>0.05</v>
       </c>
       <c r="F11" s="24" t="inlineStr">
         <is>
-          <t>0.095**</t>
+          <t>0.016</t>
         </is>
       </c>
       <c r="G11" s="24" t="n">
-        <v>0.035</v>
+        <v>0.048</v>
       </c>
       <c r="H11" s="24" t="inlineStr">
         <is>
-          <t>0.094**</t>
+          <t>0.008</t>
         </is>
       </c>
       <c r="I11" s="24" t="n">
-        <v>0.035</v>
+        <v>0.047</v>
       </c>
       <c r="J11" s="24" t="inlineStr">
         <is>
-          <t>0.081*</t>
+          <t>0.003</t>
         </is>
       </c>
       <c r="K11" s="24" t="n">
-        <v>0.033</v>
+        <v>0.031</v>
       </c>
       <c r="L11" s="24" t="inlineStr">
         <is>
-          <t>0.114**</t>
+          <t>-0.105*</t>
         </is>
       </c>
       <c r="M11" s="24" t="n">
-        <v>0.037</v>
+        <v>0.048</v>
       </c>
       <c r="N11" s="24" t="inlineStr">
         <is>
-          <t>0.066†</t>
+          <t>-0.004</t>
         </is>
       </c>
       <c r="O11" s="24" t="n">
-        <v>0.034</v>
+        <v>0.046</v>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1" s="37">
@@ -3310,7 +3354,7 @@
         </is>
       </c>
       <c r="K12" s="24" t="n">
-        <v>0.048</v>
+        <v>0.053</v>
       </c>
       <c r="L12" s="24" t="inlineStr">
         <is>
@@ -3362,59 +3406,59 @@
       </c>
       <c r="B14" s="24" t="inlineStr">
         <is>
-          <t>-0.142**</t>
+          <t>-0.496***</t>
         </is>
       </c>
       <c r="C14" s="24" t="n">
-        <v>0.052</v>
+        <v>0.064</v>
       </c>
       <c r="D14" s="24" t="inlineStr">
         <is>
-          <t>-0.14**</t>
+          <t>-0.503***</t>
         </is>
       </c>
       <c r="E14" s="24" t="n">
-        <v>0.052</v>
+        <v>0.064</v>
       </c>
       <c r="F14" s="24" t="inlineStr">
         <is>
-          <t>0.312***</t>
+          <t>0.571***</t>
         </is>
       </c>
       <c r="G14" s="24" t="n">
-        <v>0.058</v>
+        <v>0.061</v>
       </c>
       <c r="H14" s="24" t="inlineStr">
         <is>
-          <t>0.309***</t>
+          <t>0.593***</t>
         </is>
       </c>
       <c r="I14" s="24" t="n">
-        <v>0.058</v>
+        <v>0.061</v>
       </c>
       <c r="J14" s="24" t="inlineStr">
         <is>
-          <t>-0.082*</t>
+          <t>-0.011</t>
         </is>
       </c>
       <c r="K14" s="24" t="n">
-        <v>0.041</v>
+        <v>0.047</v>
       </c>
       <c r="L14" s="24" t="inlineStr">
         <is>
-          <t>-0.078†</t>
+          <t>0.101</t>
         </is>
       </c>
       <c r="M14" s="24" t="n">
-        <v>0.041</v>
+        <v>0.073</v>
       </c>
       <c r="N14" s="24" t="inlineStr">
         <is>
-          <t>0.118**</t>
+          <t>0.096</t>
         </is>
       </c>
       <c r="O14" s="24" t="n">
-        <v>0.045</v>
+        <v>0.06900000000000001</v>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1" s="37">
@@ -3425,39 +3469,39 @@
       </c>
       <c r="B15" s="24" t="inlineStr">
         <is>
-          <t>0.267***</t>
+          <t>0.523***</t>
         </is>
       </c>
       <c r="C15" s="24" t="n">
-        <v>0.049</v>
+        <v>0.059</v>
       </c>
       <c r="D15" s="24" t="inlineStr">
         <is>
-          <t>0.26***</t>
+          <t>0.520***</t>
         </is>
       </c>
       <c r="E15" s="24" t="n">
-        <v>0.049</v>
+        <v>0.06</v>
       </c>
       <c r="F15" s="24" t="inlineStr">
         <is>
-          <t>-0.145**</t>
+          <t>-0.402***</t>
         </is>
       </c>
       <c r="G15" s="24" t="n">
-        <v>0.052</v>
+        <v>0.057</v>
       </c>
       <c r="H15" s="24" t="inlineStr">
         <is>
-          <t>-0.14**</t>
+          <t>-0.397***</t>
         </is>
       </c>
       <c r="I15" s="24" t="n">
-        <v>0.052</v>
+        <v>0.056</v>
       </c>
       <c r="J15" s="24" t="inlineStr">
         <is>
-          <t>0.118**</t>
+          <t>0.051</t>
         </is>
       </c>
       <c r="K15" s="24" t="n">
@@ -3465,19 +3509,19 @@
       </c>
       <c r="L15" s="24" t="inlineStr">
         <is>
-          <t>0.108*</t>
+          <t>-0.032</t>
         </is>
       </c>
       <c r="M15" s="24" t="n">
-        <v>0.042</v>
+        <v>0.067</v>
       </c>
       <c r="N15" s="24" t="inlineStr">
         <is>
-          <t>-0.084*</t>
+          <t>-0.018</t>
         </is>
       </c>
       <c r="O15" s="24" t="n">
-        <v>0.041</v>
+        <v>0.063</v>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1" s="37">
@@ -3549,27 +3593,27 @@
       </c>
       <c r="J17" s="24" t="inlineStr">
         <is>
-          <t>0.234***</t>
+          <t>0.199***</t>
         </is>
       </c>
       <c r="K17" s="24" t="n">
-        <v>0.046</v>
+        <v>0.034</v>
       </c>
       <c r="L17" s="24" t="inlineStr">
         <is>
-          <t>0.235***</t>
+          <t>0.318***</t>
         </is>
       </c>
       <c r="M17" s="24" t="n">
-        <v>0.046</v>
+        <v>0.052</v>
       </c>
       <c r="N17" s="24" t="inlineStr">
         <is>
-          <t>-0.085*</t>
+          <t>-0.065</t>
         </is>
       </c>
       <c r="O17" s="24" t="n">
-        <v>0.043</v>
+        <v>0.049</v>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1" s="37">
@@ -3620,27 +3664,27 @@
       </c>
       <c r="J18" s="24" t="inlineStr">
         <is>
-          <t>-0.198***</t>
+          <t>-0.137***</t>
         </is>
       </c>
       <c r="K18" s="24" t="n">
-        <v>0.051</v>
+        <v>0.035</v>
       </c>
       <c r="L18" s="24" t="inlineStr">
         <is>
-          <t>-0.118*</t>
+          <t>-0.153**</t>
         </is>
       </c>
       <c r="M18" s="24" t="n">
+        <v>0.054</v>
+      </c>
+      <c r="N18" s="24" t="inlineStr">
+        <is>
+          <t>0.344***</t>
+        </is>
+      </c>
+      <c r="O18" s="24" t="n">
         <v>0.052</v>
-      </c>
-      <c r="N18" s="24" t="inlineStr">
-        <is>
-          <t>0.318***</t>
-        </is>
-      </c>
-      <c r="O18" s="24" t="n">
-        <v>0.054</v>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1" s="37">
@@ -3672,59 +3716,59 @@
       </c>
       <c r="B20" s="24" t="inlineStr">
         <is>
-          <t>-0.118*</t>
+          <t>-0.052</t>
         </is>
       </c>
       <c r="C20" s="24" t="n">
-        <v>0.046</v>
+        <v>0.061</v>
       </c>
       <c r="D20" s="24" t="inlineStr">
         <is>
-          <t>-0.118*</t>
+          <t>-0.057</t>
         </is>
       </c>
       <c r="E20" s="24" t="n">
-        <v>0.046</v>
+        <v>0.061</v>
       </c>
       <c r="F20" s="24" t="inlineStr">
         <is>
-          <t>0.214***</t>
+          <t>0.056</t>
         </is>
       </c>
       <c r="G20" s="24" t="n">
-        <v>0.047</v>
+        <v>0.058</v>
       </c>
       <c r="H20" s="24" t="inlineStr">
         <is>
-          <t>0.214***</t>
+          <t>0.050</t>
         </is>
       </c>
       <c r="I20" s="24" t="n">
-        <v>0.047</v>
+        <v>0.058</v>
       </c>
       <c r="J20" s="24" t="inlineStr">
         <is>
-          <t>-0.118*</t>
+          <t>-0.005</t>
         </is>
       </c>
       <c r="K20" s="24" t="n">
-        <v>0.046</v>
+        <v>0.038</v>
       </c>
       <c r="L20" s="24" t="inlineStr">
         <is>
-          <t>-0.118*</t>
+          <t>-0.067</t>
         </is>
       </c>
       <c r="M20" s="24" t="n">
-        <v>0.046</v>
+        <v>0.059</v>
       </c>
       <c r="N20" s="24" t="inlineStr">
         <is>
-          <t>-0.118*</t>
+          <t>0.087</t>
         </is>
       </c>
       <c r="O20" s="24" t="n">
-        <v>0.046</v>
+        <v>0.055</v>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1" s="37">
@@ -3733,51 +3777,61 @@
           <t>Power distance (T1)</t>
         </is>
       </c>
-      <c r="B21" s="24" t="n">
-        <v>-0.062</v>
+      <c r="B21" s="24" t="inlineStr">
+        <is>
+          <t>-0.071</t>
+        </is>
       </c>
       <c r="C21" s="24" t="n">
-        <v>0.039</v>
-      </c>
-      <c r="D21" s="24" t="n">
-        <v>-0.062</v>
+        <v>0.061</v>
+      </c>
+      <c r="D21" s="24" t="inlineStr">
+        <is>
+          <t>-0.084</t>
+        </is>
       </c>
       <c r="E21" s="24" t="n">
-        <v>0.039</v>
+        <v>0.061</v>
       </c>
       <c r="F21" s="24" t="inlineStr">
         <is>
-          <t>0.135**</t>
+          <t>0.069</t>
         </is>
       </c>
       <c r="G21" s="24" t="n">
-        <v>0.045</v>
+        <v>0.058</v>
       </c>
       <c r="H21" s="24" t="inlineStr">
         <is>
-          <t>0.135**</t>
+          <t>0.076</t>
         </is>
       </c>
       <c r="I21" s="24" t="n">
-        <v>0.045</v>
-      </c>
-      <c r="J21" s="24" t="n">
-        <v>-0.062</v>
+        <v>0.058</v>
+      </c>
+      <c r="J21" s="24" t="inlineStr">
+        <is>
+          <t>0.018</t>
+        </is>
       </c>
       <c r="K21" s="24" t="n">
-        <v>0.039</v>
-      </c>
-      <c r="L21" s="24" t="n">
-        <v>-0.062</v>
+        <v>0.038</v>
+      </c>
+      <c r="L21" s="24" t="inlineStr">
+        <is>
+          <t>-0.074</t>
+        </is>
       </c>
       <c r="M21" s="24" t="n">
-        <v>0.039</v>
-      </c>
-      <c r="N21" s="24" t="n">
-        <v>-0.062</v>
+        <v>0.059</v>
+      </c>
+      <c r="N21" s="24" t="inlineStr">
+        <is>
+          <t>-0.001</t>
+        </is>
       </c>
       <c r="O21" s="24" t="n">
-        <v>0.039</v>
+        <v>0.056</v>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1" s="37">
@@ -3817,11 +3871,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="D23" s="24" t="n">
-        <v>-0.012</v>
+      <c r="D23" s="24" t="inlineStr">
+        <is>
+          <t>-0.042</t>
+        </is>
       </c>
       <c r="E23" s="24" t="n">
-        <v>0.044</v>
+        <v>0.075</v>
       </c>
       <c r="F23" s="24" t="inlineStr">
         <is>
@@ -3833,11 +3889,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H23" s="24" t="n">
-        <v>0.024</v>
+      <c r="H23" s="24" t="inlineStr">
+        <is>
+          <t>0.059</t>
+        </is>
       </c>
       <c r="I23" s="24" t="n">
-        <v>0.046</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="J23" s="24" t="inlineStr">
         <is>
@@ -3886,11 +3944,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="D24" s="24" t="n">
-        <v>0.018</v>
+      <c r="D24" s="24" t="inlineStr">
+        <is>
+          <t>0.031</t>
+        </is>
       </c>
       <c r="E24" s="24" t="n">
-        <v>0.037</v>
+        <v>0.075</v>
       </c>
       <c r="F24" s="24" t="inlineStr">
         <is>
@@ -3902,11 +3962,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H24" s="24" t="n">
-        <v>-0.019</v>
+      <c r="H24" s="24" t="inlineStr">
+        <is>
+          <t>0.072</t>
+        </is>
       </c>
       <c r="I24" s="24" t="n">
-        <v>0.048</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="J24" s="24" t="inlineStr">
         <is>
@@ -3955,11 +4017,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="D25" s="24" t="n">
-        <v>0.046</v>
+      <c r="D25" s="24" t="inlineStr">
+        <is>
+          <t>-0.023</t>
+        </is>
       </c>
       <c r="E25" s="24" t="n">
-        <v>0.041</v>
+        <v>0.067</v>
       </c>
       <c r="F25" s="24" t="inlineStr">
         <is>
@@ -3973,11 +4037,11 @@
       </c>
       <c r="H25" s="24" t="inlineStr">
         <is>
-          <t>-0.111**</t>
+          <t>-0.130*</t>
         </is>
       </c>
       <c r="I25" s="24" t="n">
-        <v>0.039</v>
+        <v>0.064</v>
       </c>
       <c r="J25" s="24" t="inlineStr">
         <is>
@@ -4028,11 +4092,11 @@
       </c>
       <c r="D26" s="24" t="inlineStr">
         <is>
-          <t>-0.098*</t>
+          <t>-0.153*</t>
         </is>
       </c>
       <c r="E26" s="24" t="n">
-        <v>0.045</v>
+        <v>0.063</v>
       </c>
       <c r="F26" s="24" t="inlineStr">
         <is>
@@ -4044,11 +4108,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H26" s="24" t="n">
-        <v>0.067</v>
+      <c r="H26" s="24" t="inlineStr">
+        <is>
+          <t>0.059</t>
+        </is>
       </c>
       <c r="I26" s="24" t="n">
-        <v>0.052</v>
+        <v>0.06</v>
       </c>
       <c r="J26" s="24" t="inlineStr">
         <is>
@@ -4297,32 +4363,32 @@
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>-0.033*</t>
+          <t>-0.099*</t>
         </is>
       </c>
       <c r="C8" s="14" t="inlineStr">
         <is>
-          <t>[-0.063, -0.012]</t>
+          <t>[-0.144, -0.060]</t>
         </is>
       </c>
       <c r="D8" s="14" t="inlineStr">
         <is>
-          <t>-0.044*</t>
+          <t>-0.158*</t>
         </is>
       </c>
       <c r="E8" s="14" t="inlineStr">
         <is>
-          <t>[-0.078, -0.022]</t>
+          <t>[-0.227, -0.098]</t>
         </is>
       </c>
       <c r="F8" s="14" t="inlineStr">
         <is>
-          <t>0.013*</t>
+          <t>0.032</t>
         </is>
       </c>
       <c r="G8" s="14" t="inlineStr">
         <is>
-          <t>[0.002, 0.025]</t>
+          <t>[-0.015, 0.084]</t>
         </is>
       </c>
     </row>
@@ -4347,28 +4413,32 @@
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>-0.04*</t>
+          <t>-0.107*</t>
         </is>
       </c>
       <c r="C10" s="14" t="inlineStr">
         <is>
-          <t>[-0.079, -0.001]</t>
-        </is>
-      </c>
-      <c r="D10" s="14" t="n">
-        <v>-0.033</v>
+          <t>[-0.179, -0.035]</t>
+        </is>
+      </c>
+      <c r="D10" s="14" t="inlineStr">
+        <is>
+          <t>-0.172*</t>
+        </is>
       </c>
       <c r="E10" s="14" t="inlineStr">
         <is>
-          <t>[-0.069, 0.003]</t>
-        </is>
-      </c>
-      <c r="F10" s="14" t="n">
-        <v>0.008999999999999999</v>
+          <t>[-0.275, -0.068]</t>
+        </is>
+      </c>
+      <c r="F10" s="14" t="inlineStr">
+        <is>
+          <t>0.035</t>
+        </is>
       </c>
       <c r="G10" s="14" t="inlineStr">
         <is>
-          <t>[-0.015, 0.033]</t>
+          <t>[-0.002, 0.072]</t>
         </is>
       </c>
     </row>
@@ -4378,30 +4448,34 @@
           <t>Low narcissism (−1 SD)</t>
         </is>
       </c>
-      <c r="B11" s="14" t="n">
-        <v>-0.021</v>
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t>-0.092*</t>
+        </is>
       </c>
       <c r="C11" s="14" t="inlineStr">
         <is>
-          <t>[-0.051, 0.009]</t>
+          <t>[-0.157, -0.028]</t>
         </is>
       </c>
       <c r="D11" s="14" t="inlineStr">
         <is>
-          <t>-0.058*</t>
+          <t>-0.148*</t>
         </is>
       </c>
       <c r="E11" s="14" t="inlineStr">
         <is>
-          <t>[-0.106, -0.010]</t>
-        </is>
-      </c>
-      <c r="F11" s="14" t="n">
-        <v>0.018</v>
+          <t>[-0.240, -0.056]</t>
+        </is>
+      </c>
+      <c r="F11" s="14" t="inlineStr">
+        <is>
+          <t>0.030</t>
+        </is>
       </c>
       <c r="G11" s="14" t="inlineStr">
         <is>
-          <t>[-0.010, 0.046]</t>
+          <t>[-0.004, 0.065]</t>
         </is>
       </c>
     </row>
@@ -4411,28 +4485,34 @@
           <t>Difference</t>
         </is>
       </c>
-      <c r="B12" s="14" t="n">
-        <v>-0.019</v>
+      <c r="B12" s="14" t="inlineStr">
+        <is>
+          <t>-0.015</t>
+        </is>
       </c>
       <c r="C12" s="14" t="inlineStr">
         <is>
-          <t>[-0.048, 0.010]</t>
-        </is>
-      </c>
-      <c r="D12" s="14" t="n">
-        <v>0.024</v>
+          <t>[-0.041, 0.012]</t>
+        </is>
+      </c>
+      <c r="D12" s="14" t="inlineStr">
+        <is>
+          <t>-0.024</t>
+        </is>
       </c>
       <c r="E12" s="14" t="inlineStr">
         <is>
-          <t>[-0.007, 0.055]</t>
-        </is>
-      </c>
-      <c r="F12" s="14" t="n">
-        <v>-0.008999999999999999</v>
+          <t>[-0.055, 0.008]</t>
+        </is>
+      </c>
+      <c r="F12" s="14" t="inlineStr">
+        <is>
+          <t>0.005</t>
+        </is>
       </c>
       <c r="G12" s="14" t="inlineStr">
         <is>
-          <t>[-0.033, 0.015]</t>
+          <t>[-0.019, 0.028]</t>
         </is>
       </c>
     </row>
@@ -4455,28 +4535,34 @@
           <t>High power distance (+1 SD)</t>
         </is>
       </c>
-      <c r="B14" s="14" t="n">
-        <v>-0.012</v>
+      <c r="B14" s="14" t="inlineStr">
+        <is>
+          <t>-0.104*</t>
+        </is>
       </c>
       <c r="C14" s="14" t="inlineStr">
         <is>
-          <t>[-0.037, 0.013]</t>
-        </is>
-      </c>
-      <c r="D14" s="14" t="n">
-        <v>-0.021</v>
+          <t>[-0.174, -0.033]</t>
+        </is>
+      </c>
+      <c r="D14" s="14" t="inlineStr">
+        <is>
+          <t>-0.167*</t>
+        </is>
       </c>
       <c r="E14" s="14" t="inlineStr">
         <is>
-          <t>[-0.051, 0.009]</t>
-        </is>
-      </c>
-      <c r="F14" s="14" t="n">
-        <v>0.007</v>
+          <t>[-0.268, -0.065]</t>
+        </is>
+      </c>
+      <c r="F14" s="14" t="inlineStr">
+        <is>
+          <t>0.034</t>
+        </is>
       </c>
       <c r="G14" s="14" t="inlineStr">
         <is>
-          <t>[-0.017, 0.031]</t>
+          <t>[-0.002, 0.071]</t>
         </is>
       </c>
     </row>
@@ -4488,30 +4574,32 @@
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>-0.061*</t>
+          <t>-0.096*</t>
         </is>
       </c>
       <c r="C15" s="14" t="inlineStr">
         <is>
-          <t>[-0.110, -0.012]</t>
+          <t>[-0.162, -0.029]</t>
         </is>
       </c>
       <c r="D15" s="14" t="inlineStr">
         <is>
-          <t>-0.062*</t>
+          <t>-0.153*</t>
         </is>
       </c>
       <c r="E15" s="14" t="inlineStr">
         <is>
-          <t>[-0.112, -0.012]</t>
-        </is>
-      </c>
-      <c r="F15" s="14" t="n">
-        <v>0.018</v>
+          <t>[-0.248, -0.059]</t>
+        </is>
+      </c>
+      <c r="F15" s="14" t="inlineStr">
+        <is>
+          <t>0.032</t>
+        </is>
       </c>
       <c r="G15" s="14" t="inlineStr">
         <is>
-          <t>[-0.010, 0.046]</t>
+          <t>[-0.004, 0.067]</t>
         </is>
       </c>
     </row>
@@ -4523,30 +4611,32 @@
       </c>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t>0.05*</t>
+          <t>-0.008</t>
         </is>
       </c>
       <c r="C16" s="14" t="inlineStr">
         <is>
-          <t>[0.006, 0.094]</t>
+          <t>[-0.032, 0.015]</t>
         </is>
       </c>
       <c r="D16" s="14" t="inlineStr">
         <is>
-          <t>0.041*</t>
+          <t>-0.013</t>
         </is>
       </c>
       <c r="E16" s="14" t="inlineStr">
         <is>
-          <t>[0.001, 0.081]</t>
-        </is>
-      </c>
-      <c r="F16" s="14" t="n">
-        <v>-0.011</v>
+          <t>[-0.039, 0.013]</t>
+        </is>
+      </c>
+      <c r="F16" s="14" t="inlineStr">
+        <is>
+          <t>0.003</t>
+        </is>
       </c>
       <c r="G16" s="14" t="inlineStr">
         <is>
-          <t>[-0.036, 0.014]</t>
+          <t>[-0.021, 0.026]</t>
         </is>
       </c>
     </row>
@@ -4571,32 +4661,32 @@
       </c>
       <c r="B18" s="16" t="inlineStr">
         <is>
-          <t>0.062*</t>
+          <t>0.104*</t>
         </is>
       </c>
       <c r="C18" s="16" t="inlineStr">
         <is>
-          <t>[0.034, 0.094]</t>
+          <t>[0.065, 0.149]</t>
         </is>
       </c>
       <c r="D18" s="16" t="inlineStr">
         <is>
-          <t>0.066*</t>
+          <t>0.167*</t>
         </is>
       </c>
       <c r="E18" s="16" t="inlineStr">
         <is>
-          <t>[0.036, 0.097]</t>
+          <t>[0.107, 0.237]</t>
         </is>
       </c>
       <c r="F18" s="16" t="inlineStr">
         <is>
-          <t>-0.026*</t>
+          <t>-0.034</t>
         </is>
       </c>
       <c r="G18" s="16" t="inlineStr">
         <is>
-          <t>[-0.049, -0.005]</t>
+          <t>[-0.087, 0.017]</t>
         </is>
       </c>
     </row>
@@ -4621,30 +4711,32 @@
       </c>
       <c r="B20" s="16" t="inlineStr">
         <is>
-          <t>0.077*</t>
+          <t>0.109*</t>
         </is>
       </c>
       <c r="C20" s="16" t="inlineStr">
         <is>
-          <t>[0.020, 0.134]</t>
+          <t>[0.036, 0.182]</t>
         </is>
       </c>
       <c r="D20" s="16" t="inlineStr">
         <is>
-          <t>0.066*</t>
+          <t>0.174*</t>
         </is>
       </c>
       <c r="E20" s="16" t="inlineStr">
         <is>
-          <t>[0.014, 0.118]</t>
-        </is>
-      </c>
-      <c r="F20" s="16" t="n">
-        <v>-0.031</v>
+          <t>[0.069, 0.279]</t>
+        </is>
+      </c>
+      <c r="F20" s="16" t="inlineStr">
+        <is>
+          <t>-0.036</t>
+        </is>
       </c>
       <c r="G20" s="16" t="inlineStr">
         <is>
-          <t>[-0.066, 0.004]</t>
+          <t>[-0.073, 0.001]</t>
         </is>
       </c>
     </row>
@@ -4656,30 +4748,32 @@
       </c>
       <c r="B21" s="16" t="inlineStr">
         <is>
-          <t>0.054*</t>
+          <t>0.098*</t>
         </is>
       </c>
       <c r="C21" s="16" t="inlineStr">
         <is>
-          <t>[0.008, 0.100]</t>
+          <t>[0.030, 0.166]</t>
         </is>
       </c>
       <c r="D21" s="16" t="inlineStr">
         <is>
-          <t>0.066*</t>
+          <t>0.157*</t>
         </is>
       </c>
       <c r="E21" s="16" t="inlineStr">
         <is>
-          <t>[0.014, 0.118]</t>
-        </is>
-      </c>
-      <c r="F21" s="16" t="n">
-        <v>-0.021</v>
+          <t>[0.060, 0.253]</t>
+        </is>
+      </c>
+      <c r="F21" s="16" t="inlineStr">
+        <is>
+          <t>-0.032</t>
+        </is>
       </c>
       <c r="G21" s="16" t="inlineStr">
         <is>
-          <t>[-0.051, 0.009]</t>
+          <t>[-0.068, 0.003]</t>
         </is>
       </c>
     </row>
@@ -4689,28 +4783,34 @@
           <t>Difference</t>
         </is>
       </c>
-      <c r="B22" s="16" t="n">
-        <v>0.023</v>
+      <c r="B22" s="16" t="inlineStr">
+        <is>
+          <t>0.011</t>
+        </is>
       </c>
       <c r="C22" s="16" t="inlineStr">
         <is>
-          <t>[-0.008, 0.054]</t>
-        </is>
-      </c>
-      <c r="D22" s="16" t="n">
-        <v>0</v>
+          <t>[-0.014, 0.036]</t>
+        </is>
+      </c>
+      <c r="D22" s="16" t="inlineStr">
+        <is>
+          <t>0.017</t>
+        </is>
       </c>
       <c r="E22" s="16" t="inlineStr">
         <is>
-          <t>[-0.024, 0.024]</t>
-        </is>
-      </c>
-      <c r="F22" s="16" t="n">
-        <v>-0.01</v>
+          <t>[-0.011, 0.045]</t>
+        </is>
+      </c>
+      <c r="F22" s="16" t="inlineStr">
+        <is>
+          <t>-0.004</t>
+        </is>
       </c>
       <c r="G22" s="16" t="inlineStr">
         <is>
-          <t>[-0.035, 0.015]</t>
+          <t>[-0.027, 0.020]</t>
         </is>
       </c>
     </row>
@@ -4722,28 +4822,32 @@
       </c>
       <c r="B23" s="16" t="inlineStr">
         <is>
-          <t>0.042*</t>
+          <t>0.076*</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
         <is>
-          <t>[0.002, 0.082]</t>
-        </is>
-      </c>
-      <c r="D23" s="16" t="n">
-        <v>0.029</v>
+          <t>[0.019, 0.133]</t>
+        </is>
+      </c>
+      <c r="D23" s="16" t="inlineStr">
+        <is>
+          <t>0.122*</t>
+        </is>
       </c>
       <c r="E23" s="16" t="inlineStr">
         <is>
-          <t>[-0.005, 0.063]</t>
-        </is>
-      </c>
-      <c r="F23" s="16" t="n">
-        <v>-0.011</v>
+          <t>[0.043, 0.202]</t>
+        </is>
+      </c>
+      <c r="F23" s="16" t="inlineStr">
+        <is>
+          <t>-0.025</t>
+        </is>
       </c>
       <c r="G23" s="16" t="inlineStr">
         <is>
-          <t>[-0.036, 0.014]</t>
+          <t>[-0.057, 0.007]</t>
         </is>
       </c>
     </row>
@@ -4755,32 +4859,32 @@
       </c>
       <c r="B24" s="16" t="inlineStr">
         <is>
-          <t>0.09*</t>
+          <t>0.130*</t>
         </is>
       </c>
       <c r="C24" s="16" t="inlineStr">
         <is>
-          <t>[0.026, 0.154]</t>
+          <t>[0.047, 0.214]</t>
         </is>
       </c>
       <c r="D24" s="16" t="inlineStr">
         <is>
-          <t>0.104*</t>
+          <t>0.210*</t>
         </is>
       </c>
       <c r="E24" s="16" t="inlineStr">
         <is>
-          <t>[0.033, 0.175]</t>
+          <t>[0.087, 0.332]</t>
         </is>
       </c>
       <c r="F24" s="16" t="inlineStr">
         <is>
-          <t>-0.042*</t>
+          <t>-0.043*</t>
         </is>
       </c>
       <c r="G24" s="16" t="inlineStr">
         <is>
-          <t>[-0.082, -0.002]</t>
+          <t>[-0.084, -0.002]</t>
         </is>
       </c>
     </row>
@@ -4792,30 +4896,32 @@
       </c>
       <c r="B25" s="16" t="inlineStr">
         <is>
-          <t>-0.048*</t>
+          <t>-0.054*</t>
         </is>
       </c>
       <c r="C25" s="16" t="inlineStr">
         <is>
-          <t>[-0.091, -0.005]</t>
+          <t>[-0.100, -0.008]</t>
         </is>
       </c>
       <c r="D25" s="16" t="inlineStr">
         <is>
-          <t>-0.075*</t>
+          <t>-0.087*</t>
         </is>
       </c>
       <c r="E25" s="16" t="inlineStr">
         <is>
-          <t>[-0.131, -0.019]</t>
-        </is>
-      </c>
-      <c r="F25" s="16" t="n">
-        <v>0.03</v>
+          <t>[-0.150, -0.025]</t>
+        </is>
+      </c>
+      <c r="F25" s="16" t="inlineStr">
+        <is>
+          <t>0.018</t>
+        </is>
       </c>
       <c r="G25" s="16" t="inlineStr">
         <is>
-          <t>[-0.004, 0.064]</t>
+          <t>[-0.010, 0.046]</t>
         </is>
       </c>
     </row>
@@ -4853,32 +4959,32 @@
       </c>
       <c r="B28" s="18" t="inlineStr">
         <is>
-          <t>-0.062*</t>
+          <t>-0.078*</t>
         </is>
       </c>
       <c r="C28" s="18" t="inlineStr">
         <is>
-          <t>[-0.098, -0.034]</t>
+          <t>[-0.124, -0.037]</t>
         </is>
       </c>
       <c r="D28" s="18" t="inlineStr">
         <is>
-          <t>-0.062*</t>
+          <t>-0.087*</t>
         </is>
       </c>
       <c r="E28" s="18" t="inlineStr">
         <is>
-          <t>[-0.099, -0.029]</t>
+          <t>[-0.154, -0.025]</t>
         </is>
       </c>
       <c r="F28" s="18" t="inlineStr">
         <is>
-          <t>0.094*</t>
+          <t>0.197*</t>
         </is>
       </c>
       <c r="G28" s="18" t="inlineStr">
         <is>
-          <t>[0.060, 0.131]</t>
+          <t>[0.129, 0.273]</t>
         </is>
       </c>
     </row>
@@ -4890,32 +4996,32 @@
       </c>
       <c r="B29" s="18" t="inlineStr">
         <is>
-          <t>-0.076*</t>
+          <t>-0.088*</t>
         </is>
       </c>
       <c r="C29" s="18" t="inlineStr">
         <is>
-          <t>[-0.133, -0.019]</t>
+          <t>[-0.151, -0.025]</t>
         </is>
       </c>
       <c r="D29" s="18" t="inlineStr">
         <is>
-          <t>-0.056*</t>
+          <t>-0.098*</t>
         </is>
       </c>
       <c r="E29" s="18" t="inlineStr">
         <is>
-          <t>[-0.103, -0.009]</t>
+          <t>[-0.166, -0.031]</t>
         </is>
       </c>
       <c r="F29" s="18" t="inlineStr">
         <is>
-          <t>0.106*</t>
+          <t>0.222*</t>
         </is>
       </c>
       <c r="G29" s="18" t="inlineStr">
         <is>
-          <t>[0.034, 0.178]</t>
+          <t>[0.094, 0.351]</t>
         </is>
       </c>
     </row>
@@ -4927,32 +5033,32 @@
       </c>
       <c r="B30" s="18" t="inlineStr">
         <is>
-          <t>-0.056*</t>
+          <t>-0.074*</t>
         </is>
       </c>
       <c r="C30" s="18" t="inlineStr">
         <is>
-          <t>[-0.103, -0.009]</t>
+          <t>[-0.130, -0.018]</t>
         </is>
       </c>
       <c r="D30" s="18" t="inlineStr">
         <is>
-          <t>-0.068*</t>
+          <t>-0.082*</t>
         </is>
       </c>
       <c r="E30" s="18" t="inlineStr">
         <is>
-          <t>[-0.121, -0.015]</t>
+          <t>[-0.142, -0.022]</t>
         </is>
       </c>
       <c r="F30" s="18" t="inlineStr">
         <is>
-          <t>0.083*</t>
+          <t>0.186*</t>
         </is>
       </c>
       <c r="G30" s="18" t="inlineStr">
         <is>
-          <t>[0.023, 0.143]</t>
+          <t>[0.076, 0.297]</t>
         </is>
       </c>
     </row>
@@ -4962,28 +5068,34 @@
           <t>Difference</t>
         </is>
       </c>
-      <c r="B31" s="18" t="n">
-        <v>-0.02</v>
+      <c r="B31" s="18" t="inlineStr">
+        <is>
+          <t>-0.014</t>
+        </is>
       </c>
       <c r="C31" s="18" t="inlineStr">
         <is>
-          <t>[-0.049, 0.009]</t>
-        </is>
-      </c>
-      <c r="D31" s="18" t="n">
-        <v>0.013</v>
+          <t>[-0.041, 0.012]</t>
+        </is>
+      </c>
+      <c r="D31" s="18" t="inlineStr">
+        <is>
+          <t>-0.016</t>
+        </is>
       </c>
       <c r="E31" s="18" t="inlineStr">
         <is>
-          <t>[-0.013, 0.039]</t>
-        </is>
-      </c>
-      <c r="F31" s="18" t="n">
-        <v>0.023</v>
+          <t>[-0.043, 0.011]</t>
+        </is>
+      </c>
+      <c r="F31" s="18" t="inlineStr">
+        <is>
+          <t>0.036</t>
+        </is>
       </c>
       <c r="G31" s="18" t="inlineStr">
         <is>
-          <t>[-0.008, 0.054]</t>
+          <t>[-0.001, 0.073]</t>
         </is>
       </c>
     </row>
@@ -4995,32 +5107,32 @@
       </c>
       <c r="B32" s="18" t="inlineStr">
         <is>
-          <t>-0.04*</t>
+          <t>-0.065*</t>
         </is>
       </c>
       <c r="C32" s="18" t="inlineStr">
         <is>
-          <t>[-0.079, -0.001]</t>
+          <t>[-0.117, -0.014]</t>
         </is>
       </c>
       <c r="D32" s="18" t="inlineStr">
         <is>
-          <t>-0.043*</t>
+          <t>-0.073*</t>
         </is>
       </c>
       <c r="E32" s="18" t="inlineStr">
         <is>
-          <t>[-0.084, -0.002]</t>
+          <t>[-0.128, -0.018]</t>
         </is>
       </c>
       <c r="F32" s="18" t="inlineStr">
         <is>
-          <t>0.066*</t>
+          <t>0.164*</t>
         </is>
       </c>
       <c r="G32" s="18" t="inlineStr">
         <is>
-          <t>[0.014, 0.118]</t>
+          <t>[0.064, 0.265]</t>
         </is>
       </c>
     </row>
@@ -5032,32 +5144,32 @@
       </c>
       <c r="B33" s="18" t="inlineStr">
         <is>
-          <t>-0.098*</t>
+          <t>-0.097*</t>
         </is>
       </c>
       <c r="C33" s="18" t="inlineStr">
         <is>
-          <t>[-0.166, -0.030]</t>
+          <t>[-0.164, -0.030]</t>
         </is>
       </c>
       <c r="D33" s="18" t="inlineStr">
         <is>
-          <t>-0.076*</t>
+          <t>-0.108*</t>
         </is>
       </c>
       <c r="E33" s="18" t="inlineStr">
         <is>
-          <t>[-0.133, -0.019]</t>
+          <t>[-0.180, -0.035]</t>
         </is>
       </c>
       <c r="F33" s="18" t="inlineStr">
         <is>
-          <t>0.116*</t>
+          <t>0.244*</t>
         </is>
       </c>
       <c r="G33" s="18" t="inlineStr">
         <is>
-          <t>[0.040, 0.192]</t>
+          <t>[0.105, 0.383]</t>
         </is>
       </c>
     </row>
@@ -5069,30 +5181,32 @@
       </c>
       <c r="B34" s="18" t="inlineStr">
         <is>
-          <t>0.057*</t>
+          <t>0.031</t>
         </is>
       </c>
       <c r="C34" s="18" t="inlineStr">
         <is>
-          <t>[0.009, 0.105]</t>
-        </is>
-      </c>
-      <c r="D34" s="18" t="n">
-        <v>0.033</v>
+          <t>[-0.004, 0.066]</t>
+        </is>
+      </c>
+      <c r="D34" s="18" t="inlineStr">
+        <is>
+          <t>0.035</t>
+        </is>
       </c>
       <c r="E34" s="18" t="inlineStr">
         <is>
-          <t>[-0.003, 0.069]</t>
+          <t>[-0.002, 0.072]</t>
         </is>
       </c>
       <c r="F34" s="18" t="inlineStr">
         <is>
-          <t>-0.05*</t>
+          <t>-0.079*</t>
         </is>
       </c>
       <c r="G34" s="18" t="inlineStr">
         <is>
-          <t>[-0.094, -0.006]</t>
+          <t>[-0.138, -0.021]</t>
         </is>
       </c>
     </row>
@@ -5117,32 +5231,32 @@
       </c>
       <c r="B36" s="20" t="inlineStr">
         <is>
-          <t>0.029*</t>
+          <t>0.055*</t>
         </is>
       </c>
       <c r="C36" s="20" t="inlineStr">
         <is>
-          <t>[0.011, 0.052]</t>
+          <t>[0.025, 0.090]</t>
         </is>
       </c>
       <c r="D36" s="20" t="inlineStr">
         <is>
-          <t>0.034*</t>
+          <t>0.061*</t>
         </is>
       </c>
       <c r="E36" s="20" t="inlineStr">
         <is>
-          <t>[0.014, 0.054]</t>
+          <t>[0.018, 0.111]</t>
         </is>
       </c>
       <c r="F36" s="20" t="inlineStr">
         <is>
-          <t>-0.048*</t>
+          <t>-0.138*</t>
         </is>
       </c>
       <c r="G36" s="20" t="inlineStr">
         <is>
-          <t>[-0.082, -0.020]</t>
+          <t>[-0.199, -0.086]</t>
         </is>
       </c>
     </row>
@@ -5152,30 +5266,34 @@
           <t>High narcissism (+1 SD)</t>
         </is>
       </c>
-      <c r="B37" s="20" t="n">
-        <v>0.025</v>
+      <c r="B37" s="20" t="inlineStr">
+        <is>
+          <t>0.046*</t>
+        </is>
       </c>
       <c r="C37" s="20" t="inlineStr">
         <is>
-          <t>[-0.007, 0.057]</t>
-        </is>
-      </c>
-      <c r="D37" s="20" t="n">
-        <v>0.038</v>
+          <t>[0.004, 0.088]</t>
+        </is>
+      </c>
+      <c r="D37" s="20" t="inlineStr">
+        <is>
+          <t>0.051*</t>
+        </is>
       </c>
       <c r="E37" s="20" t="inlineStr">
         <is>
-          <t>[-0.000, 0.076]</t>
+          <t>[0.006, 0.095]</t>
         </is>
       </c>
       <c r="F37" s="20" t="inlineStr">
         <is>
-          <t>-0.048*</t>
+          <t>-0.115*</t>
         </is>
       </c>
       <c r="G37" s="20" t="inlineStr">
         <is>
-          <t>[-0.091, -0.005]</t>
+          <t>[-0.191, -0.039]</t>
         </is>
       </c>
     </row>
@@ -5185,30 +5303,34 @@
           <t>Low narcissism (−1 SD)</t>
         </is>
       </c>
-      <c r="B38" s="20" t="n">
-        <v>0.036</v>
+      <c r="B38" s="20" t="inlineStr">
+        <is>
+          <t>0.063*</t>
+        </is>
       </c>
       <c r="C38" s="20" t="inlineStr">
         <is>
-          <t>[-0.001, 0.073]</t>
-        </is>
-      </c>
-      <c r="D38" s="20" t="n">
-        <v>0.03</v>
+          <t>[0.013, 0.114]</t>
+        </is>
+      </c>
+      <c r="D38" s="20" t="inlineStr">
+        <is>
+          <t>0.070*</t>
+        </is>
       </c>
       <c r="E38" s="20" t="inlineStr">
         <is>
-          <t>[-0.004, 0.064]</t>
+          <t>[0.016, 0.124]</t>
         </is>
       </c>
       <c r="F38" s="20" t="inlineStr">
         <is>
-          <t>-0.048*</t>
+          <t>-0.159*</t>
         </is>
       </c>
       <c r="G38" s="20" t="inlineStr">
         <is>
-          <t>[-0.091, -0.005]</t>
+          <t>[-0.256, -0.061]</t>
         </is>
       </c>
     </row>
@@ -5218,28 +5340,34 @@
           <t>Difference</t>
         </is>
       </c>
-      <c r="B39" s="20" t="n">
-        <v>-0.011</v>
+      <c r="B39" s="20" t="inlineStr">
+        <is>
+          <t>-0.017</t>
+        </is>
       </c>
       <c r="C39" s="20" t="inlineStr">
         <is>
-          <t>[-0.036, 0.014]</t>
-        </is>
-      </c>
-      <c r="D39" s="20" t="n">
-        <v>0.008999999999999999</v>
+          <t>[-0.046, 0.011]</t>
+        </is>
+      </c>
+      <c r="D39" s="20" t="inlineStr">
+        <is>
+          <t>-0.019</t>
+        </is>
       </c>
       <c r="E39" s="20" t="inlineStr">
         <is>
-          <t>[-0.015, 0.033]</t>
-        </is>
-      </c>
-      <c r="F39" s="20" t="n">
-        <v>0</v>
+          <t>[-0.049, 0.010]</t>
+        </is>
+      </c>
+      <c r="F39" s="20" t="inlineStr">
+        <is>
+          <t>0.044*</t>
+        </is>
       </c>
       <c r="G39" s="20" t="inlineStr">
         <is>
-          <t>[-0.024, 0.024]</t>
+          <t>[0.003, 0.084]</t>
         </is>
       </c>
     </row>
@@ -5251,32 +5379,32 @@
       </c>
       <c r="B40" s="20" t="inlineStr">
         <is>
-          <t>0.042*</t>
+          <t>0.047*</t>
         </is>
       </c>
       <c r="C40" s="20" t="inlineStr">
         <is>
-          <t>[0.002, 0.082]</t>
+          <t>[0.004, 0.090]</t>
         </is>
       </c>
       <c r="D40" s="20" t="inlineStr">
         <is>
-          <t>0.064*</t>
+          <t>0.053*</t>
         </is>
       </c>
       <c r="E40" s="20" t="inlineStr">
         <is>
-          <t>[0.013, 0.115]</t>
+          <t>[0.007, 0.098]</t>
         </is>
       </c>
       <c r="F40" s="20" t="inlineStr">
         <is>
-          <t>-0.068*</t>
+          <t>-0.119*</t>
         </is>
       </c>
       <c r="G40" s="20" t="inlineStr">
         <is>
-          <t>[-0.121, -0.015]</t>
+          <t>[-0.196, -0.041]</t>
         </is>
       </c>
     </row>
@@ -5286,28 +5414,34 @@
           <t>Low power distance (−1 SD)</t>
         </is>
       </c>
-      <c r="B41" s="20" t="n">
-        <v>0.021</v>
+      <c r="B41" s="20" t="inlineStr">
+        <is>
+          <t>0.061*</t>
+        </is>
       </c>
       <c r="C41" s="20" t="inlineStr">
         <is>
-          <t>[-0.009, 0.051]</t>
-        </is>
-      </c>
-      <c r="D41" s="20" t="n">
-        <v>0.007</v>
+          <t>[0.012, 0.111]</t>
+        </is>
+      </c>
+      <c r="D41" s="20" t="inlineStr">
+        <is>
+          <t>0.069*</t>
+        </is>
       </c>
       <c r="E41" s="20" t="inlineStr">
         <is>
-          <t>[-0.017, 0.031]</t>
-        </is>
-      </c>
-      <c r="F41" s="20" t="n">
-        <v>-0.031</v>
+          <t>[0.015, 0.122]</t>
+        </is>
+      </c>
+      <c r="F41" s="20" t="inlineStr">
+        <is>
+          <t>-0.155*</t>
+        </is>
       </c>
       <c r="G41" s="20" t="inlineStr">
         <is>
-          <t>[-0.066, 0.004]</t>
+          <t>[-0.251, -0.060]</t>
         </is>
       </c>
     </row>
@@ -5317,30 +5451,34 @@
           <t>Difference</t>
         </is>
       </c>
-      <c r="B42" s="20" t="n">
-        <v>0.021</v>
+      <c r="B42" s="20" t="inlineStr">
+        <is>
+          <t>-0.014</t>
+        </is>
       </c>
       <c r="C42" s="20" t="inlineStr">
         <is>
-          <t>[-0.009, 0.051]</t>
+          <t>[-0.041, 0.012]</t>
         </is>
       </c>
       <c r="D42" s="20" t="inlineStr">
         <is>
-          <t>0.056*</t>
+          <t>-0.016</t>
         </is>
       </c>
       <c r="E42" s="20" t="inlineStr">
         <is>
-          <t>[0.009, 0.103]</t>
-        </is>
-      </c>
-      <c r="F42" s="20" t="n">
-        <v>-0.037</v>
+          <t>[-0.044, 0.011]</t>
+        </is>
+      </c>
+      <c r="F42" s="20" t="inlineStr">
+        <is>
+          <t>0.037</t>
+        </is>
       </c>
       <c r="G42" s="20" t="inlineStr">
         <is>
-          <t>[-0.075, 0.001]</t>
+          <t>[-0.001, 0.074]</t>
         </is>
       </c>
     </row>
@@ -5567,69 +5705,73 @@
           <t>Narcissism</t>
         </is>
       </c>
-      <c r="D5" s="4" t="n">
-        <v>-0.012</v>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>-0.042</t>
+        </is>
       </c>
       <c r="E5" s="4" t="n">
-        <v>0.04</v>
+        <v>0.075</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>0.764</v>
+        <v>0.575</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>-0.091</v>
+        <v>-0.189</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>0.067</v>
+        <v>0.105</v>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>-0.154*</t>
+          <t>-0.540***</t>
         </is>
       </c>
       <c r="J5" s="4" t="n">
-        <v>0.062</v>
+        <v>0.094</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>0.013</v>
+        <v>0</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>-0.276</v>
+        <v>-0.724</v>
       </c>
       <c r="M5" s="4" t="n">
-        <v>-0.032</v>
+        <v>-0.355</v>
       </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
-          <t>-0.13*</t>
+          <t>-0.465***</t>
         </is>
       </c>
       <c r="O5" s="4" t="n">
-        <v>0.064</v>
+        <v>0.09</v>
       </c>
       <c r="P5" s="4" t="n">
-        <v>0.042</v>
+        <v>0</v>
       </c>
       <c r="Q5" s="4" t="n">
-        <v>-0.255</v>
+        <v>-0.642</v>
       </c>
       <c r="R5" s="4" t="n">
-        <v>-0.005</v>
-      </c>
-      <c r="S5" s="4" t="n">
-        <v>-0.024</v>
+        <v>-0.289</v>
+      </c>
+      <c r="S5" s="4" t="inlineStr">
+        <is>
+          <t>-0.074</t>
+        </is>
       </c>
       <c r="T5" s="4" t="n">
-        <v>0.08</v>
+        <v>0.13</v>
       </c>
       <c r="U5" s="4" t="n">
-        <v>0.764</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="V5" s="4" t="n">
-        <v>-0.181</v>
+        <v>-0.33</v>
       </c>
       <c r="W5" s="4" t="n">
-        <v>0.133</v>
+        <v>0.181</v>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1" s="37">
@@ -5648,69 +5790,73 @@
           <t>Narcissism</t>
         </is>
       </c>
-      <c r="D6" s="4" t="n">
-        <v>0.018</v>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>0.031</t>
+        </is>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.039</v>
+        <v>0.075</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.645</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.058</v>
+        <v>-0.116</v>
       </c>
       <c r="H6" s="4" t="n">
+        <v>0.178</v>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>0.548***</t>
+        </is>
+      </c>
+      <c r="J6" s="4" t="n">
         <v>0.094</v>
-      </c>
-      <c r="I6" s="4" t="inlineStr">
-        <is>
-          <t>0.285***</t>
-        </is>
-      </c>
-      <c r="J6" s="4" t="n">
-        <v>0.059</v>
       </c>
       <c r="K6" s="4" t="n">
         <v>0</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.169</v>
+        <v>0.364</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.401</v>
+        <v>0.732</v>
       </c>
       <c r="N6" s="4" t="inlineStr">
         <is>
-          <t>0.249***</t>
+          <t>0.493***</t>
         </is>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.06</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="P6" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>0.131</v>
+        <v>0.328</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>0.367</v>
-      </c>
-      <c r="S6" s="4" t="n">
-        <v>0.036</v>
+        <v>0.658</v>
+      </c>
+      <c r="S6" s="4" t="inlineStr">
+        <is>
+          <t>0.055</t>
+        </is>
       </c>
       <c r="T6" s="4" t="n">
-        <v>0.078</v>
+        <v>0.126</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>0.645</v>
+        <v>0.665</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>-0.117</v>
+        <v>-0.193</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>0.189</v>
+        <v>0.302</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" s="37">
@@ -5729,67 +5875,73 @@
           <t>Power distance</t>
         </is>
       </c>
-      <c r="D7" s="4" t="n">
-        <v>0.046</v>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>-0.023</t>
+        </is>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.041</v>
+        <v>0.067</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.263</v>
+        <v>0.727</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.034</v>
+        <v>-0.155</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.126</v>
-      </c>
-      <c r="I7" s="4" t="n">
-        <v>-0.039</v>
+        <v>0.108</v>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>-0.523***</t>
+        </is>
       </c>
       <c r="J7" s="4" t="n">
-        <v>0.063</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.535</v>
+        <v>0</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-0.162</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0.08400000000000001</v>
+        <v>-0.357</v>
       </c>
       <c r="N7" s="4" t="inlineStr">
         <is>
-          <t>-0.156*</t>
+          <t>-0.482***</t>
         </is>
       </c>
       <c r="O7" s="4" t="n">
-        <v>0.067</v>
+        <v>0.09</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>-0.288</v>
+        <v>-0.658</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>-0.024</v>
-      </c>
-      <c r="S7" s="4" t="n">
-        <v>0.117</v>
+        <v>-0.306</v>
+      </c>
+      <c r="S7" s="4" t="inlineStr">
+        <is>
+          <t>-0.042</t>
+        </is>
       </c>
       <c r="T7" s="4" t="n">
-        <v>0.082</v>
+        <v>0.124</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>0.155</v>
+        <v>0.737</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>-0.043</v>
+        <v>-0.284</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>0.277</v>
+        <v>0.201</v>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1" s="37">
@@ -5810,71 +5962,71 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>-0.098*</t>
+          <t>-0.153*</t>
         </is>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.039</v>
+        <v>0.063</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.012</v>
+        <v>0.016</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.174</v>
+        <v>-0.277</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.022</v>
+        <v>-0.029</v>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>0.196**</t>
+          <t>0.384***</t>
         </is>
       </c>
       <c r="J8" s="4" t="n">
-        <v>0.059</v>
+        <v>0.083</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.08</v>
+        <v>0.222</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.312</v>
+        <v>0.546</v>
       </c>
       <c r="N8" s="4" t="inlineStr">
         <is>
-          <t>0.346***</t>
+          <t>0.657***</t>
         </is>
       </c>
       <c r="O8" s="4" t="n">
-        <v>0.062</v>
+        <v>0.081</v>
       </c>
       <c r="P8" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>0.224</v>
+        <v>0.498</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>0.468</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>-0.15†</t>
+          <t>-0.273*</t>
         </is>
       </c>
       <c r="T8" s="4" t="n">
-        <v>0.078</v>
+        <v>0.116</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>0.055</v>
+        <v>0.019</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>-0.303</v>
+        <v>-0.499</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>0.003</v>
+        <v>-0.046</v>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" s="37">
@@ -5893,69 +6045,73 @@
           <t>Narcissism</t>
         </is>
       </c>
-      <c r="D9" s="4" t="n">
-        <v>0.024</v>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>0.059</t>
+        </is>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.043</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.577</v>
+        <v>0.405</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.06</v>
+        <v>-0.08</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.108</v>
+        <v>0.198</v>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>0.336***</t>
+          <t>0.645***</t>
         </is>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.089</v>
       </c>
       <c r="K9" s="4" t="n">
         <v>0</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.201</v>
+        <v>0.47</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.471</v>
+        <v>0.82</v>
       </c>
       <c r="N9" s="4" t="inlineStr">
         <is>
-          <t>0.288***</t>
+          <t>0.540***</t>
         </is>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="P9" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>0.149</v>
+        <v>0.373</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>0.427</v>
-      </c>
-      <c r="S9" s="4" t="n">
-        <v>0.048</v>
+        <v>0.708</v>
+      </c>
+      <c r="S9" s="4" t="inlineStr">
+        <is>
+          <t>0.105</t>
+        </is>
       </c>
       <c r="T9" s="4" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.124</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>0.577</v>
+        <v>0.397</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>-0.121</v>
+        <v>-0.137</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>0.217</v>
+        <v>0.347</v>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" s="37">
@@ -5974,69 +6130,73 @@
           <t>Narcissism</t>
         </is>
       </c>
-      <c r="D10" s="4" t="n">
-        <v>-0.019</v>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>0.072</t>
+        </is>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.041</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.643</v>
+        <v>0.313</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.099</v>
+        <v>-0.068</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0.061</v>
+        <v>0.211</v>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>-0.164**</t>
+          <t>-0.333***</t>
         </is>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.06</v>
+        <v>0.089</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.006</v>
+        <v>0</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-0.282</v>
+        <v>-0.508</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-0.046</v>
+        <v>-0.159</v>
       </c>
       <c r="N10" s="4" t="inlineStr">
         <is>
-          <t>-0.126*</t>
+          <t>-0.461***</t>
         </is>
       </c>
       <c r="O10" s="4" t="n">
-        <v>0.063</v>
+        <v>0.08</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>0.045</v>
+        <v>0</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>-0.249</v>
+        <v>-0.617</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>-0.003</v>
-      </c>
-      <c r="S10" s="4" t="n">
-        <v>-0.038</v>
+        <v>-0.304</v>
+      </c>
+      <c r="S10" s="4" t="inlineStr">
+        <is>
+          <t>0.127</t>
+        </is>
       </c>
       <c r="T10" s="4" t="n">
-        <v>0.082</v>
+        <v>0.12</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>0.643</v>
+        <v>0.288</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>-0.199</v>
+        <v>-0.107</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>0.123</v>
+        <v>0.362</v>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" s="37">
@@ -6057,71 +6217,71 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>-0.111**</t>
+          <t>-0.130*</t>
         </is>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.041</v>
+        <v>0.064</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.007</v>
+        <v>0.042</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.191</v>
+        <v>-0.254</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.031</v>
+        <v>-0.005</v>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>0.243***</t>
+          <t>0.477***</t>
         </is>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.066</v>
+        <v>0.08</v>
       </c>
       <c r="K11" s="4" t="n">
         <v>0</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.114</v>
+        <v>0.319</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.372</v>
+        <v>0.635</v>
       </c>
       <c r="N11" s="4" t="inlineStr">
         <is>
-          <t>0.398***</t>
+          <t>0.708***</t>
         </is>
       </c>
       <c r="O11" s="4" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="P11" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>0.263</v>
+        <v>0.541</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>0.533</v>
+        <v>0.875</v>
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>-0.155†</t>
+          <t>-0.231*</t>
         </is>
       </c>
       <c r="T11" s="4" t="n">
-        <v>0.082</v>
+        <v>0.117</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>0.06</v>
+        <v>0.049</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>-0.316</v>
+        <v>-0.461</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>0.006</v>
+        <v>-0.001</v>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1" s="37">
@@ -6142,69 +6302,71 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>0.067†</t>
+          <t>0.059</t>
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.038</v>
+        <v>0.06</v>
       </c>
       <c r="F12" s="4" t="n">
+        <v>0.326</v>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>-0.058</v>
+      </c>
+      <c r="H12" s="4" t="n">
+        <v>0.176</v>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>-0.345***</t>
+        </is>
+      </c>
+      <c r="J12" s="4" t="n">
         <v>0.078</v>
       </c>
-      <c r="G12" s="4" t="n">
-        <v>-0.008</v>
-      </c>
-      <c r="H12" s="4" t="n">
-        <v>0.142</v>
-      </c>
-      <c r="I12" s="4" t="n">
-        <v>-0.078</v>
-      </c>
-      <c r="J12" s="4" t="n">
-        <v>0.06</v>
-      </c>
       <c r="K12" s="4" t="n">
-        <v>0.193</v>
+        <v>0</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-0.196</v>
+        <v>-0.498</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.04</v>
+        <v>-0.191</v>
       </c>
       <c r="N12" s="4" t="inlineStr">
         <is>
-          <t>-0.212**</t>
+          <t>-0.449***</t>
         </is>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0.062</v>
+        <v>0.077</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>-0.334</v>
+        <v>-0.6</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>-0.09</v>
+        <v>-0.299</v>
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>0.134†</t>
+          <t>0.105</t>
         </is>
       </c>
       <c r="T12" s="4" t="n">
-        <v>0.076</v>
+        <v>0.11</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>0.078</v>
+        <v>0.34</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>-0.015</v>
+        <v>-0.11</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>0.283</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="37">

--- a/results/Model3.xlsx
+++ b/results/Model3.xlsx
@@ -2467,43 +2467,41 @@
         </is>
       </c>
       <c r="B13" s="24" t="n">
-        <v>3.137</v>
+        <v>3.156</v>
       </c>
       <c r="C13" s="24" t="n">
-        <v>1.201</v>
+        <v>1.172</v>
       </c>
       <c r="D13" s="24" t="n">
-        <v>-0.076</v>
+        <v>-0.07099999999999999</v>
       </c>
       <c r="E13" s="24" t="n">
-        <v>-0.008</v>
+        <v>0.034</v>
       </c>
       <c r="F13" s="24" t="n">
-        <v>0.056</v>
+        <v>0.082</v>
       </c>
       <c r="G13" s="24" t="n">
-        <v>0.028</v>
+        <v>0.05</v>
       </c>
       <c r="H13" s="24" t="inlineStr">
         <is>
-          <t>0.539***</t>
+          <t>0.561***</t>
         </is>
       </c>
       <c r="I13" s="24" t="inlineStr">
         <is>
-          <t>-0.467***</t>
+          <t>-0.471***</t>
         </is>
       </c>
       <c r="J13" s="24" t="n">
-        <v>0.038</v>
+        <v>-0.005</v>
       </c>
       <c r="K13" s="24" t="n">
-        <v>0.051</v>
-      </c>
-      <c r="L13" s="24" t="inlineStr">
-        <is>
-          <t>-0.427***</t>
-        </is>
+        <v>-0.001</v>
+      </c>
+      <c r="L13" s="24" t="n">
+        <v>-0.08</v>
       </c>
       <c r="M13" s="24" t="inlineStr">
         <is>
@@ -2559,7 +2557,7 @@
         </is>
       </c>
       <c r="M14" s="24" t="n">
-        <v>-0.074</v>
+        <v>-0.068</v>
       </c>
       <c r="N14" s="24" t="inlineStr">
         <is>
@@ -2577,52 +2575,52 @@
         </is>
       </c>
       <c r="B15" s="24" t="n">
-        <v>4.49</v>
+        <v>4.486</v>
       </c>
       <c r="C15" s="24" t="n">
-        <v>0.781</v>
+        <v>0.78</v>
       </c>
       <c r="D15" s="24" t="n">
-        <v>0.024</v>
+        <v>0.032</v>
       </c>
       <c r="E15" s="24" t="n">
-        <v>-0.056</v>
+        <v>-0.052</v>
       </c>
       <c r="F15" s="24" t="n">
-        <v>-0.03</v>
+        <v>-0.029</v>
       </c>
       <c r="G15" s="24" t="n">
-        <v>-0.022</v>
+        <v>-0.045</v>
       </c>
       <c r="H15" s="24" t="inlineStr">
         <is>
-          <t>-0.279***</t>
+          <t>-0.386***</t>
         </is>
       </c>
       <c r="I15" s="24" t="inlineStr">
         <is>
-          <t>0.307***</t>
+          <t>0.401***</t>
         </is>
       </c>
       <c r="J15" s="24" t="n">
-        <v>-0.056</v>
+        <v>-0.047</v>
       </c>
       <c r="K15" s="24" t="n">
-        <v>-0.038</v>
+        <v>-0.026</v>
       </c>
       <c r="L15" s="24" t="inlineStr">
         <is>
-          <t>0.482***</t>
+          <t>0.494***</t>
         </is>
       </c>
       <c r="M15" s="24" t="inlineStr">
         <is>
-          <t>-0.407***</t>
+          <t>-0.42***</t>
         </is>
       </c>
       <c r="N15" s="24" t="inlineStr">
         <is>
-          <t>0.389***</t>
+          <t>0.39***</t>
         </is>
       </c>
       <c r="O15" s="24" t="inlineStr">
@@ -2643,37 +2641,37 @@
         <v>4.78</v>
       </c>
       <c r="C16" s="24" t="n">
-        <v>1.057</v>
+        <v>1.063</v>
       </c>
       <c r="D16" s="24" t="n">
         <v>0.062</v>
       </c>
       <c r="E16" s="24" t="n">
-        <v>-0.022</v>
+        <v>-0.032</v>
       </c>
       <c r="F16" s="24" t="n">
-        <v>0.03</v>
+        <v>0.017</v>
       </c>
       <c r="G16" s="24" t="inlineStr">
         <is>
-          <t>-0.108*</t>
+          <t>-0.116*</t>
         </is>
       </c>
       <c r="H16" s="24" t="inlineStr">
         <is>
-          <t>-0.18***</t>
+          <t>-0.186***</t>
         </is>
       </c>
       <c r="I16" s="24" t="inlineStr">
         <is>
-          <t>0.231***</t>
+          <t>0.367***</t>
         </is>
       </c>
       <c r="J16" s="24" t="n">
-        <v>-0.062</v>
+        <v>-0.038</v>
       </c>
       <c r="K16" s="24" t="n">
-        <v>-0.098</v>
+        <v>-0.089</v>
       </c>
       <c r="L16" s="24" t="inlineStr">
         <is>
@@ -2682,15 +2680,15 @@
       </c>
       <c r="M16" s="24" t="inlineStr">
         <is>
-          <t>-0.285***</t>
+          <t>-0.311***</t>
         </is>
       </c>
       <c r="N16" s="24" t="n">
-        <v>0.081</v>
+        <v>0.098</v>
       </c>
       <c r="O16" s="24" t="inlineStr">
         <is>
-          <t>0.316***</t>
+          <t>0.315***</t>
         </is>
       </c>
       <c r="P16" s="24" t="inlineStr">
@@ -2707,22 +2705,22 @@
         </is>
       </c>
       <c r="B17" s="24" t="n">
-        <v>2.702</v>
+        <v>2.696</v>
       </c>
       <c r="C17" s="24" t="n">
-        <v>1.04</v>
+        <v>1.044</v>
       </c>
       <c r="D17" s="24" t="n">
-        <v>-0.073</v>
+        <v>-0.061</v>
       </c>
       <c r="E17" s="24" t="n">
-        <v>0.008</v>
+        <v>0.015</v>
       </c>
       <c r="F17" s="24" t="n">
-        <v>0.006</v>
+        <v>0.028</v>
       </c>
       <c r="G17" s="24" t="n">
-        <v>0.005</v>
+        <v>0.012</v>
       </c>
       <c r="H17" s="24" t="inlineStr">
         <is>
@@ -2731,18 +2729,18 @@
       </c>
       <c r="I17" s="24" t="inlineStr">
         <is>
-          <t>-0.267***</t>
+          <t>-0.366***</t>
         </is>
       </c>
       <c r="J17" s="24" t="n">
-        <v>0.093</v>
+        <v>0.054</v>
       </c>
       <c r="K17" s="24" t="n">
-        <v>0.025</v>
+        <v>0.002</v>
       </c>
       <c r="L17" s="24" t="inlineStr">
         <is>
-          <t>-0.298***</t>
+          <t>-0.279***</t>
         </is>
       </c>
       <c r="M17" s="24" t="inlineStr">
@@ -2751,11 +2749,11 @@
         </is>
       </c>
       <c r="N17" s="24" t="n">
-        <v>-0.037</v>
+        <v>-0.031</v>
       </c>
       <c r="O17" s="24" t="inlineStr">
         <is>
-          <t>-0.266***</t>
+          <t>-0.25***</t>
         </is>
       </c>
       <c r="P17" s="24" t="inlineStr">
@@ -2990,11 +2988,11 @@
       </c>
       <c r="F6" s="24" t="inlineStr">
         <is>
-          <t>0.070</t>
+          <t>0.072</t>
         </is>
       </c>
       <c r="G6" s="24" t="n">
-        <v>0.077</v>
+        <v>0.074</v>
       </c>
       <c r="H6" s="24" t="inlineStr">
         <is>
@@ -3002,31 +3000,31 @@
         </is>
       </c>
       <c r="I6" s="24" t="n">
-        <v>0.077</v>
+        <v>0.074</v>
       </c>
       <c r="J6" s="24" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>0.004</t>
         </is>
       </c>
       <c r="K6" s="24" t="n">
-        <v>0.05</v>
+        <v>0.046</v>
       </c>
       <c r="L6" s="24" t="inlineStr">
         <is>
-          <t>-0.061</t>
+          <t>-0.054</t>
         </is>
       </c>
       <c r="M6" s="24" t="n">
-        <v>0.08</v>
+        <v>0.075</v>
       </c>
       <c r="N6" s="24" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>0.030</t>
         </is>
       </c>
       <c r="O6" s="24" t="n">
-        <v>0.074</v>
+        <v>0.07099999999999999</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" s="37">
@@ -3074,7 +3072,7 @@
       </c>
       <c r="F8" s="24" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>0.012</t>
         </is>
       </c>
       <c r="G8" s="24" t="n">
@@ -3082,7 +3080,7 @@
       </c>
       <c r="H8" s="24" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>0.012</t>
         </is>
       </c>
       <c r="I8" s="24" t="n">
@@ -3090,7 +3088,7 @@
       </c>
       <c r="J8" s="24" t="inlineStr">
         <is>
-          <t>-0.013†</t>
+          <t>-0.011†</t>
         </is>
       </c>
       <c r="K8" s="24" t="n">
@@ -3098,7 +3096,7 @@
       </c>
       <c r="L8" s="24" t="inlineStr">
         <is>
-          <t>-0.014</t>
+          <t>-0.013</t>
         </is>
       </c>
       <c r="M8" s="24" t="n">
@@ -3106,11 +3104,11 @@
       </c>
       <c r="N8" s="24" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>0.004</t>
         </is>
       </c>
       <c r="O8" s="24" t="n">
-        <v>0.011</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" s="37">
@@ -3137,43 +3135,43 @@
       </c>
       <c r="F9" s="24" t="inlineStr">
         <is>
-          <t>-0.125</t>
+          <t>-0.128</t>
         </is>
       </c>
       <c r="G9" s="24" t="n">
-        <v>0.104</v>
+        <v>0.099</v>
       </c>
       <c r="H9" s="24" t="inlineStr">
         <is>
-          <t>-0.101</t>
+          <t>-0.102</t>
         </is>
       </c>
       <c r="I9" s="24" t="n">
-        <v>0.103</v>
+        <v>0.099</v>
       </c>
       <c r="J9" s="24" t="inlineStr">
         <is>
-          <t>-0.011</t>
+          <t>-0.007</t>
         </is>
       </c>
       <c r="K9" s="24" t="n">
-        <v>0.067</v>
+        <v>0.061</v>
       </c>
       <c r="L9" s="24" t="inlineStr">
         <is>
-          <t>0.107</t>
+          <t>0.095</t>
         </is>
       </c>
       <c r="M9" s="24" t="n">
-        <v>0.104</v>
+        <v>0.098</v>
       </c>
       <c r="N9" s="24" t="inlineStr">
         <is>
-          <t>-0.073</t>
+          <t>-0.053</t>
         </is>
       </c>
       <c r="O9" s="24" t="n">
-        <v>0.099</v>
+        <v>0.096</v>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" s="37">
@@ -3200,43 +3198,43 @@
       </c>
       <c r="F10" s="24" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>0.029</t>
         </is>
       </c>
       <c r="G10" s="24" t="n">
-        <v>0.035</v>
+        <v>0.034</v>
       </c>
       <c r="H10" s="24" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>0.024</t>
         </is>
       </c>
       <c r="I10" s="24" t="n">
-        <v>0.035</v>
+        <v>0.033</v>
       </c>
       <c r="J10" s="24" t="inlineStr">
         <is>
-          <t>-0.001</t>
+          <t>0.006</t>
         </is>
       </c>
       <c r="K10" s="24" t="n">
-        <v>0.023</v>
+        <v>0.021</v>
       </c>
       <c r="L10" s="24" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>0.014</t>
         </is>
       </c>
       <c r="M10" s="24" t="n">
-        <v>0.035</v>
+        <v>0.033</v>
       </c>
       <c r="N10" s="24" t="inlineStr">
         <is>
-          <t>-0.022</t>
+          <t>-0.008</t>
         </is>
       </c>
       <c r="O10" s="24" t="n">
-        <v>0.034</v>
+        <v>0.032</v>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" s="37">
@@ -3263,43 +3261,43 @@
       </c>
       <c r="F11" s="24" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>0.035</t>
         </is>
       </c>
       <c r="G11" s="24" t="n">
-        <v>0.048</v>
+        <v>0.046</v>
       </c>
       <c r="H11" s="24" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>0.030</t>
         </is>
       </c>
       <c r="I11" s="24" t="n">
-        <v>0.047</v>
+        <v>0.045</v>
       </c>
       <c r="J11" s="24" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>-0.003</t>
         </is>
       </c>
       <c r="K11" s="24" t="n">
-        <v>0.031</v>
+        <v>0.028</v>
       </c>
       <c r="L11" s="24" t="inlineStr">
         <is>
-          <t>-0.105*</t>
+          <t>-0.091*</t>
         </is>
       </c>
       <c r="M11" s="24" t="n">
-        <v>0.048</v>
+        <v>0.045</v>
       </c>
       <c r="N11" s="24" t="inlineStr">
         <is>
-          <t>-0.004</t>
+          <t>-0.019</t>
         </is>
       </c>
       <c r="O11" s="24" t="n">
-        <v>0.046</v>
+        <v>0.044</v>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1" s="37">
@@ -3350,11 +3348,11 @@
       </c>
       <c r="J12" s="24" t="inlineStr">
         <is>
-          <t>0.412***</t>
+          <t>0.392***</t>
         </is>
       </c>
       <c r="K12" s="24" t="n">
-        <v>0.053</v>
+        <v>0.051</v>
       </c>
       <c r="L12" s="24" t="inlineStr">
         <is>
@@ -3422,43 +3420,43 @@
       </c>
       <c r="F14" s="24" t="inlineStr">
         <is>
-          <t>0.571***</t>
+          <t>0.588***</t>
         </is>
       </c>
       <c r="G14" s="24" t="n">
-        <v>0.061</v>
+        <v>0.058</v>
       </c>
       <c r="H14" s="24" t="inlineStr">
         <is>
-          <t>0.593***</t>
+          <t>0.607***</t>
         </is>
       </c>
       <c r="I14" s="24" t="n">
-        <v>0.061</v>
+        <v>0.058</v>
       </c>
       <c r="J14" s="24" t="inlineStr">
         <is>
-          <t>-0.011</t>
+          <t>-0.008</t>
         </is>
       </c>
       <c r="K14" s="24" t="n">
-        <v>0.047</v>
+        <v>0.052</v>
       </c>
       <c r="L14" s="24" t="inlineStr">
         <is>
-          <t>0.101</t>
+          <t>0.375***</t>
         </is>
       </c>
       <c r="M14" s="24" t="n">
-        <v>0.073</v>
+        <v>0.08</v>
       </c>
       <c r="N14" s="24" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>-0.109</t>
         </is>
       </c>
       <c r="O14" s="24" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.078</v>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1" s="37">
@@ -3485,43 +3483,43 @@
       </c>
       <c r="F15" s="24" t="inlineStr">
         <is>
-          <t>-0.402***</t>
+          <t>-0.385***</t>
         </is>
       </c>
       <c r="G15" s="24" t="n">
-        <v>0.057</v>
+        <v>0.054</v>
       </c>
       <c r="H15" s="24" t="inlineStr">
         <is>
-          <t>-0.397***</t>
+          <t>-0.384***</t>
         </is>
       </c>
       <c r="I15" s="24" t="n">
-        <v>0.056</v>
+        <v>0.054</v>
       </c>
       <c r="J15" s="24" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>0.046</t>
         </is>
       </c>
       <c r="K15" s="24" t="n">
-        <v>0.043</v>
+        <v>0.046</v>
       </c>
       <c r="L15" s="24" t="inlineStr">
         <is>
-          <t>-0.032</t>
+          <t>-0.029</t>
         </is>
       </c>
       <c r="M15" s="24" t="n">
-        <v>0.067</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="N15" s="24" t="inlineStr">
         <is>
-          <t>-0.018</t>
+          <t>-0.013</t>
         </is>
       </c>
       <c r="O15" s="24" t="n">
-        <v>0.063</v>
+        <v>0.06900000000000001</v>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1" s="37">
@@ -3593,27 +3591,27 @@
       </c>
       <c r="J17" s="24" t="inlineStr">
         <is>
-          <t>0.199***</t>
+          <t>0.249***</t>
         </is>
       </c>
       <c r="K17" s="24" t="n">
-        <v>0.034</v>
+        <v>0.037</v>
       </c>
       <c r="L17" s="24" t="inlineStr">
         <is>
-          <t>0.318***</t>
+          <t>0.451***</t>
         </is>
       </c>
       <c r="M17" s="24" t="n">
-        <v>0.052</v>
+        <v>0.056</v>
       </c>
       <c r="N17" s="24" t="inlineStr">
         <is>
-          <t>-0.065</t>
+          <t>-0.230***</t>
         </is>
       </c>
       <c r="O17" s="24" t="n">
-        <v>0.049</v>
+        <v>0.055</v>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1" s="37">
@@ -3664,27 +3662,27 @@
       </c>
       <c r="J18" s="24" t="inlineStr">
         <is>
-          <t>-0.137***</t>
+          <t>-0.222***</t>
         </is>
       </c>
       <c r="K18" s="24" t="n">
-        <v>0.035</v>
+        <v>0.041</v>
       </c>
       <c r="L18" s="24" t="inlineStr">
         <is>
-          <t>-0.153**</t>
+          <t>-0.409***</t>
         </is>
       </c>
       <c r="M18" s="24" t="n">
-        <v>0.054</v>
+        <v>0.061</v>
       </c>
       <c r="N18" s="24" t="inlineStr">
         <is>
-          <t>0.344***</t>
+          <t>0.467***</t>
         </is>
       </c>
       <c r="O18" s="24" t="n">
-        <v>0.052</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1" s="37">
@@ -3732,43 +3730,43 @@
       </c>
       <c r="F20" s="24" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>-0.004</t>
         </is>
       </c>
       <c r="G20" s="24" t="n">
-        <v>0.058</v>
+        <v>0.056</v>
       </c>
       <c r="H20" s="24" t="inlineStr">
         <is>
-          <t>0.050</t>
+          <t>-0.008</t>
         </is>
       </c>
       <c r="I20" s="24" t="n">
-        <v>0.058</v>
+        <v>0.055</v>
       </c>
       <c r="J20" s="24" t="inlineStr">
         <is>
-          <t>-0.005</t>
+          <t>-0.006</t>
         </is>
       </c>
       <c r="K20" s="24" t="n">
-        <v>0.038</v>
+        <v>0.035</v>
       </c>
       <c r="L20" s="24" t="inlineStr">
         <is>
-          <t>-0.067</t>
+          <t>-0.053</t>
         </is>
       </c>
       <c r="M20" s="24" t="n">
-        <v>0.059</v>
+        <v>0.055</v>
       </c>
       <c r="N20" s="24" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>0.061</t>
         </is>
       </c>
       <c r="O20" s="24" t="n">
-        <v>0.055</v>
+        <v>0.053</v>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1" s="37">
@@ -3795,43 +3793,43 @@
       </c>
       <c r="F21" s="24" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>0.003</t>
         </is>
       </c>
       <c r="G21" s="24" t="n">
-        <v>0.058</v>
+        <v>0.056</v>
       </c>
       <c r="H21" s="24" t="inlineStr">
         <is>
-          <t>0.076</t>
+          <t>0.006</t>
         </is>
       </c>
       <c r="I21" s="24" t="n">
-        <v>0.058</v>
+        <v>0.055</v>
       </c>
       <c r="J21" s="24" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>0.022</t>
         </is>
       </c>
       <c r="K21" s="24" t="n">
-        <v>0.038</v>
+        <v>0.035</v>
       </c>
       <c r="L21" s="24" t="inlineStr">
         <is>
-          <t>-0.074</t>
+          <t>-0.053</t>
         </is>
       </c>
       <c r="M21" s="24" t="n">
-        <v>0.059</v>
+        <v>0.055</v>
       </c>
       <c r="N21" s="24" t="inlineStr">
         <is>
-          <t>-0.001</t>
+          <t>-0.024</t>
         </is>
       </c>
       <c r="O21" s="24" t="n">
-        <v>0.056</v>
+        <v>0.054</v>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1" s="37">
@@ -3891,11 +3889,11 @@
       </c>
       <c r="H23" s="24" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>0.016</t>
         </is>
       </c>
       <c r="I23" s="24" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.068</v>
       </c>
       <c r="J23" s="24" t="inlineStr">
         <is>
@@ -3964,11 +3962,11 @@
       </c>
       <c r="H24" s="24" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>0.067</t>
         </is>
       </c>
       <c r="I24" s="24" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.068</v>
       </c>
       <c r="J24" s="24" t="inlineStr">
         <is>
@@ -4037,11 +4035,11 @@
       </c>
       <c r="H25" s="24" t="inlineStr">
         <is>
-          <t>-0.130*</t>
+          <t>-0.143*</t>
         </is>
       </c>
       <c r="I25" s="24" t="n">
-        <v>0.064</v>
+        <v>0.061</v>
       </c>
       <c r="J25" s="24" t="inlineStr">
         <is>
@@ -4110,11 +4108,11 @@
       </c>
       <c r="H26" s="24" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>0.016</t>
         </is>
       </c>
       <c r="I26" s="24" t="n">
-        <v>0.06</v>
+        <v>0.057</v>
       </c>
       <c r="J26" s="24" t="inlineStr">
         <is>
@@ -4363,32 +4361,32 @@
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>-0.099*</t>
+          <t>-0.123*</t>
         </is>
       </c>
       <c r="C8" s="14" t="inlineStr">
         <is>
-          <t>[-0.144, -0.060]</t>
+          <t>[-0.176, -0.078]</t>
         </is>
       </c>
       <c r="D8" s="14" t="inlineStr">
         <is>
-          <t>-0.158*</t>
+          <t>-0.223*</t>
         </is>
       </c>
       <c r="E8" s="14" t="inlineStr">
         <is>
-          <t>[-0.227, -0.098]</t>
+          <t>[-0.307, -0.150]</t>
         </is>
       </c>
       <c r="F8" s="14" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>0.114*</t>
         </is>
       </c>
       <c r="G8" s="14" t="inlineStr">
         <is>
-          <t>[-0.015, 0.084]</t>
+          <t>[0.057, 0.180]</t>
         </is>
       </c>
     </row>
@@ -4413,32 +4411,32 @@
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>-0.107*</t>
+          <t>-0.134*</t>
         </is>
       </c>
       <c r="C10" s="14" t="inlineStr">
         <is>
-          <t>[-0.179, -0.035]</t>
+          <t>[-0.219, -0.049]</t>
         </is>
       </c>
       <c r="D10" s="14" t="inlineStr">
         <is>
-          <t>-0.172*</t>
+          <t>-0.243*</t>
         </is>
       </c>
       <c r="E10" s="14" t="inlineStr">
         <is>
-          <t>[-0.275, -0.068]</t>
+          <t>[-0.382, -0.104]</t>
         </is>
       </c>
       <c r="F10" s="14" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>0.124*</t>
         </is>
       </c>
       <c r="G10" s="14" t="inlineStr">
         <is>
-          <t>[-0.002, 0.072]</t>
+          <t>[0.044, 0.204]</t>
         </is>
       </c>
     </row>
@@ -4450,32 +4448,32 @@
       </c>
       <c r="B11" s="14" t="inlineStr">
         <is>
-          <t>-0.092*</t>
+          <t>-0.116*</t>
         </is>
       </c>
       <c r="C11" s="14" t="inlineStr">
         <is>
-          <t>[-0.157, -0.028]</t>
+          <t>[-0.192, -0.039]</t>
         </is>
       </c>
       <c r="D11" s="14" t="inlineStr">
         <is>
-          <t>-0.148*</t>
+          <t>-0.210*</t>
         </is>
       </c>
       <c r="E11" s="14" t="inlineStr">
         <is>
-          <t>[-0.240, -0.056]</t>
+          <t>[-0.332, -0.087]</t>
         </is>
       </c>
       <c r="F11" s="14" t="inlineStr">
         <is>
-          <t>0.030</t>
+          <t>0.107*</t>
         </is>
       </c>
       <c r="G11" s="14" t="inlineStr">
         <is>
-          <t>[-0.004, 0.065]</t>
+          <t>[0.035, 0.179]</t>
         </is>
       </c>
     </row>
@@ -4487,32 +4485,32 @@
       </c>
       <c r="B12" s="14" t="inlineStr">
         <is>
-          <t>-0.015</t>
+          <t>-0.018</t>
         </is>
       </c>
       <c r="C12" s="14" t="inlineStr">
         <is>
-          <t>[-0.041, 0.012]</t>
+          <t>[-0.047, 0.010]</t>
         </is>
       </c>
       <c r="D12" s="14" t="inlineStr">
         <is>
-          <t>-0.024</t>
+          <t>-0.033</t>
         </is>
       </c>
       <c r="E12" s="14" t="inlineStr">
         <is>
-          <t>[-0.055, 0.008]</t>
+          <t>[-0.069, 0.003]</t>
         </is>
       </c>
       <c r="F12" s="14" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>0.017</t>
         </is>
       </c>
       <c r="G12" s="14" t="inlineStr">
         <is>
-          <t>[-0.019, 0.028]</t>
+          <t>[-0.011, 0.045]</t>
         </is>
       </c>
     </row>
@@ -4537,32 +4535,32 @@
       </c>
       <c r="B14" s="14" t="inlineStr">
         <is>
-          <t>-0.104*</t>
+          <t>-0.130*</t>
         </is>
       </c>
       <c r="C14" s="14" t="inlineStr">
         <is>
-          <t>[-0.174, -0.033]</t>
+          <t>[-0.213, -0.047]</t>
         </is>
       </c>
       <c r="D14" s="14" t="inlineStr">
         <is>
-          <t>-0.167*</t>
+          <t>-0.236*</t>
         </is>
       </c>
       <c r="E14" s="14" t="inlineStr">
         <is>
-          <t>[-0.268, -0.065]</t>
+          <t>[-0.371, -0.101]</t>
         </is>
       </c>
       <c r="F14" s="14" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>0.121*</t>
         </is>
       </c>
       <c r="G14" s="14" t="inlineStr">
         <is>
-          <t>[-0.002, 0.071]</t>
+          <t>[0.042, 0.200]</t>
         </is>
       </c>
     </row>
@@ -4574,32 +4572,32 @@
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>-0.096*</t>
+          <t>-0.120*</t>
         </is>
       </c>
       <c r="C15" s="14" t="inlineStr">
         <is>
-          <t>[-0.162, -0.029]</t>
+          <t>[-0.198, -0.041]</t>
         </is>
       </c>
       <c r="D15" s="14" t="inlineStr">
         <is>
-          <t>-0.153*</t>
+          <t>-0.217*</t>
         </is>
       </c>
       <c r="E15" s="14" t="inlineStr">
         <is>
-          <t>[-0.248, -0.059]</t>
+          <t>[-0.343, -0.091]</t>
         </is>
       </c>
       <c r="F15" s="14" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>0.111*</t>
         </is>
       </c>
       <c r="G15" s="14" t="inlineStr">
         <is>
-          <t>[-0.004, 0.067]</t>
+          <t>[0.037, 0.185]</t>
         </is>
       </c>
     </row>
@@ -4611,32 +4609,32 @@
       </c>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t>-0.008</t>
+          <t>-0.010</t>
         </is>
       </c>
       <c r="C16" s="14" t="inlineStr">
         <is>
-          <t>[-0.032, 0.015]</t>
+          <t>[-0.035, 0.014]</t>
         </is>
       </c>
       <c r="D16" s="14" t="inlineStr">
         <is>
-          <t>-0.013</t>
+          <t>-0.019</t>
         </is>
       </c>
       <c r="E16" s="14" t="inlineStr">
         <is>
-          <t>[-0.039, 0.013]</t>
+          <t>[-0.047, 0.010]</t>
         </is>
       </c>
       <c r="F16" s="14" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>0.010</t>
         </is>
       </c>
       <c r="G16" s="14" t="inlineStr">
         <is>
-          <t>[-0.021, 0.026]</t>
+          <t>[-0.015, 0.034]</t>
         </is>
       </c>
     </row>
@@ -4661,32 +4659,32 @@
       </c>
       <c r="B18" s="16" t="inlineStr">
         <is>
-          <t>0.104*</t>
+          <t>0.130*</t>
         </is>
       </c>
       <c r="C18" s="16" t="inlineStr">
         <is>
-          <t>[0.065, 0.149]</t>
+          <t>[0.085, 0.182]</t>
         </is>
       </c>
       <c r="D18" s="16" t="inlineStr">
         <is>
-          <t>0.167*</t>
+          <t>0.237*</t>
         </is>
       </c>
       <c r="E18" s="16" t="inlineStr">
         <is>
-          <t>[0.107, 0.237]</t>
+          <t>[0.164, 0.319]</t>
         </is>
       </c>
       <c r="F18" s="16" t="inlineStr">
         <is>
-          <t>-0.034</t>
+          <t>-0.121*</t>
         </is>
       </c>
       <c r="G18" s="16" t="inlineStr">
         <is>
-          <t>[-0.087, 0.017]</t>
+          <t>[-0.187, -0.062]</t>
         </is>
       </c>
     </row>
@@ -4711,32 +4709,32 @@
       </c>
       <c r="B20" s="16" t="inlineStr">
         <is>
-          <t>0.109*</t>
+          <t>0.136*</t>
         </is>
       </c>
       <c r="C20" s="16" t="inlineStr">
         <is>
-          <t>[0.036, 0.182]</t>
+          <t>[0.050, 0.223]</t>
         </is>
       </c>
       <c r="D20" s="16" t="inlineStr">
         <is>
-          <t>0.174*</t>
+          <t>0.246*</t>
         </is>
       </c>
       <c r="E20" s="16" t="inlineStr">
         <is>
-          <t>[0.069, 0.279]</t>
+          <t>[0.106, 0.386]</t>
         </is>
       </c>
       <c r="F20" s="16" t="inlineStr">
         <is>
-          <t>-0.036</t>
+          <t>-0.126*</t>
         </is>
       </c>
       <c r="G20" s="16" t="inlineStr">
         <is>
-          <t>[-0.073, 0.001]</t>
+          <t>[-0.208, -0.045]</t>
         </is>
       </c>
     </row>
@@ -4748,32 +4746,32 @@
       </c>
       <c r="B21" s="16" t="inlineStr">
         <is>
-          <t>0.098*</t>
+          <t>0.123*</t>
         </is>
       </c>
       <c r="C21" s="16" t="inlineStr">
         <is>
-          <t>[0.030, 0.166]</t>
+          <t>[0.043, 0.202]</t>
         </is>
       </c>
       <c r="D21" s="16" t="inlineStr">
         <is>
-          <t>0.157*</t>
+          <t>0.222*</t>
         </is>
       </c>
       <c r="E21" s="16" t="inlineStr">
         <is>
-          <t>[0.060, 0.253]</t>
+          <t>[0.094, 0.350]</t>
         </is>
       </c>
       <c r="F21" s="16" t="inlineStr">
         <is>
-          <t>-0.032</t>
+          <t>-0.114*</t>
         </is>
       </c>
       <c r="G21" s="16" t="inlineStr">
         <is>
-          <t>[-0.068, 0.003]</t>
+          <t>[-0.189, -0.038]</t>
         </is>
       </c>
     </row>
@@ -4785,32 +4783,32 @@
       </c>
       <c r="B22" s="16" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>0.014</t>
         </is>
       </c>
       <c r="C22" s="16" t="inlineStr">
         <is>
-          <t>[-0.014, 0.036]</t>
+          <t>[-0.013, 0.040]</t>
         </is>
       </c>
       <c r="D22" s="16" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>0.024</t>
         </is>
       </c>
       <c r="E22" s="16" t="inlineStr">
         <is>
-          <t>[-0.011, 0.045]</t>
+          <t>[-0.007, 0.056]</t>
         </is>
       </c>
       <c r="F22" s="16" t="inlineStr">
         <is>
-          <t>-0.004</t>
+          <t>-0.013</t>
         </is>
       </c>
       <c r="G22" s="16" t="inlineStr">
         <is>
-          <t>[-0.027, 0.020]</t>
+          <t>[-0.038, 0.013]</t>
         </is>
       </c>
     </row>
@@ -4822,32 +4820,32 @@
       </c>
       <c r="B23" s="16" t="inlineStr">
         <is>
-          <t>0.076*</t>
+          <t>0.096*</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
         <is>
-          <t>[0.019, 0.133]</t>
+          <t>[0.029, 0.162]</t>
         </is>
       </c>
       <c r="D23" s="16" t="inlineStr">
         <is>
-          <t>0.122*</t>
+          <t>0.173*</t>
         </is>
       </c>
       <c r="E23" s="16" t="inlineStr">
         <is>
-          <t>[0.043, 0.202]</t>
+          <t>[0.069, 0.277]</t>
         </is>
       </c>
       <c r="F23" s="16" t="inlineStr">
         <is>
-          <t>-0.025</t>
+          <t>-0.089*</t>
         </is>
       </c>
       <c r="G23" s="16" t="inlineStr">
         <is>
-          <t>[-0.057, 0.007]</t>
+          <t>[-0.152, -0.026]</t>
         </is>
       </c>
     </row>
@@ -4859,32 +4857,32 @@
       </c>
       <c r="B24" s="16" t="inlineStr">
         <is>
-          <t>0.130*</t>
+          <t>0.163*</t>
         </is>
       </c>
       <c r="C24" s="16" t="inlineStr">
         <is>
-          <t>[0.047, 0.214]</t>
+          <t>[0.064, 0.263]</t>
         </is>
       </c>
       <c r="D24" s="16" t="inlineStr">
         <is>
-          <t>0.210*</t>
+          <t>0.296*</t>
         </is>
       </c>
       <c r="E24" s="16" t="inlineStr">
         <is>
-          <t>[0.087, 0.332]</t>
+          <t>[0.132, 0.461]</t>
         </is>
       </c>
       <c r="F24" s="16" t="inlineStr">
         <is>
-          <t>-0.043*</t>
+          <t>-0.152*</t>
         </is>
       </c>
       <c r="G24" s="16" t="inlineStr">
         <is>
-          <t>[-0.084, -0.002]</t>
+          <t>[-0.246, -0.058]</t>
         </is>
       </c>
     </row>
@@ -4896,32 +4894,32 @@
       </c>
       <c r="B25" s="16" t="inlineStr">
         <is>
-          <t>-0.054*</t>
+          <t>-0.067*</t>
         </is>
       </c>
       <c r="C25" s="16" t="inlineStr">
         <is>
-          <t>[-0.100, -0.008]</t>
+          <t>[-0.120, -0.015]</t>
         </is>
       </c>
       <c r="D25" s="16" t="inlineStr">
         <is>
-          <t>-0.087*</t>
+          <t>-0.123*</t>
         </is>
       </c>
       <c r="E25" s="16" t="inlineStr">
         <is>
-          <t>[-0.150, -0.025]</t>
+          <t>[-0.204, -0.043]</t>
         </is>
       </c>
       <c r="F25" s="16" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>0.063*</t>
         </is>
       </c>
       <c r="G25" s="16" t="inlineStr">
         <is>
-          <t>[-0.010, 0.046]</t>
+          <t>[0.013, 0.114]</t>
         </is>
       </c>
     </row>
@@ -4959,32 +4957,32 @@
       </c>
       <c r="B28" s="18" t="inlineStr">
         <is>
-          <t>-0.078*</t>
+          <t>-0.130*</t>
         </is>
       </c>
       <c r="C28" s="18" t="inlineStr">
         <is>
-          <t>[-0.124, -0.037]</t>
+          <t>[-0.187, -0.080]</t>
         </is>
       </c>
       <c r="D28" s="18" t="inlineStr">
         <is>
-          <t>-0.087*</t>
+          <t>-0.240*</t>
         </is>
       </c>
       <c r="E28" s="18" t="inlineStr">
         <is>
-          <t>[-0.154, -0.025]</t>
+          <t>[-0.331, -0.160]</t>
         </is>
       </c>
       <c r="F28" s="18" t="inlineStr">
         <is>
-          <t>0.197*</t>
+          <t>0.275*</t>
         </is>
       </c>
       <c r="G28" s="18" t="inlineStr">
         <is>
-          <t>[0.129, 0.273]</t>
+          <t>[0.191, 0.368]</t>
         </is>
       </c>
     </row>
@@ -4996,32 +4994,32 @@
       </c>
       <c r="B29" s="18" t="inlineStr">
         <is>
-          <t>-0.088*</t>
+          <t>-0.138*</t>
         </is>
       </c>
       <c r="C29" s="18" t="inlineStr">
         <is>
-          <t>[-0.151, -0.025]</t>
+          <t>[-0.225, -0.051]</t>
         </is>
       </c>
       <c r="D29" s="18" t="inlineStr">
         <is>
-          <t>-0.098*</t>
+          <t>-0.254*</t>
         </is>
       </c>
       <c r="E29" s="18" t="inlineStr">
         <is>
-          <t>[-0.166, -0.031]</t>
+          <t>[-0.398, -0.110]</t>
         </is>
       </c>
       <c r="F29" s="18" t="inlineStr">
         <is>
-          <t>0.222*</t>
+          <t>0.291*</t>
         </is>
       </c>
       <c r="G29" s="18" t="inlineStr">
         <is>
-          <t>[0.094, 0.351]</t>
+          <t>[0.129, 0.453]</t>
         </is>
       </c>
     </row>
@@ -5033,32 +5031,32 @@
       </c>
       <c r="B30" s="18" t="inlineStr">
         <is>
-          <t>-0.074*</t>
+          <t>-0.131*</t>
         </is>
       </c>
       <c r="C30" s="18" t="inlineStr">
         <is>
-          <t>[-0.130, -0.018]</t>
+          <t>[-0.215, -0.047]</t>
         </is>
       </c>
       <c r="D30" s="18" t="inlineStr">
         <is>
-          <t>-0.082*</t>
+          <t>-0.242*</t>
         </is>
       </c>
       <c r="E30" s="18" t="inlineStr">
         <is>
-          <t>[-0.142, -0.022]</t>
+          <t>[-0.380, -0.104]</t>
         </is>
       </c>
       <c r="F30" s="18" t="inlineStr">
         <is>
-          <t>0.186*</t>
+          <t>0.278*</t>
         </is>
       </c>
       <c r="G30" s="18" t="inlineStr">
         <is>
-          <t>[0.076, 0.297]</t>
+          <t>[0.122, 0.433]</t>
         </is>
       </c>
     </row>
@@ -5070,32 +5068,32 @@
       </c>
       <c r="B31" s="18" t="inlineStr">
         <is>
-          <t>-0.014</t>
+          <t>-0.006</t>
         </is>
       </c>
       <c r="C31" s="18" t="inlineStr">
         <is>
-          <t>[-0.041, 0.012]</t>
+          <t>[-0.030, 0.017]</t>
         </is>
       </c>
       <c r="D31" s="18" t="inlineStr">
         <is>
-          <t>-0.016</t>
+          <t>-0.012</t>
         </is>
       </c>
       <c r="E31" s="18" t="inlineStr">
         <is>
-          <t>[-0.043, 0.011]</t>
+          <t>[-0.037, 0.014]</t>
         </is>
       </c>
       <c r="F31" s="18" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>0.013</t>
         </is>
       </c>
       <c r="G31" s="18" t="inlineStr">
         <is>
-          <t>[-0.001, 0.073]</t>
+          <t>[-0.013, 0.039]</t>
         </is>
       </c>
     </row>
@@ -5107,32 +5105,32 @@
       </c>
       <c r="B32" s="18" t="inlineStr">
         <is>
-          <t>-0.065*</t>
+          <t>-0.107*</t>
         </is>
       </c>
       <c r="C32" s="18" t="inlineStr">
         <is>
-          <t>[-0.117, -0.014]</t>
+          <t>[-0.178, -0.035]</t>
         </is>
       </c>
       <c r="D32" s="18" t="inlineStr">
         <is>
-          <t>-0.073*</t>
+          <t>-0.197*</t>
         </is>
       </c>
       <c r="E32" s="18" t="inlineStr">
         <is>
-          <t>[-0.128, -0.018]</t>
+          <t>[-0.313, -0.081]</t>
         </is>
       </c>
       <c r="F32" s="18" t="inlineStr">
         <is>
-          <t>0.164*</t>
+          <t>0.225*</t>
         </is>
       </c>
       <c r="G32" s="18" t="inlineStr">
         <is>
-          <t>[0.064, 0.265]</t>
+          <t>[0.095, 0.355]</t>
         </is>
       </c>
     </row>
@@ -5144,32 +5142,32 @@
       </c>
       <c r="B33" s="18" t="inlineStr">
         <is>
-          <t>-0.097*</t>
+          <t>-0.162*</t>
         </is>
       </c>
       <c r="C33" s="18" t="inlineStr">
         <is>
-          <t>[-0.164, -0.030]</t>
+          <t>[-0.261, -0.063]</t>
         </is>
       </c>
       <c r="D33" s="18" t="inlineStr">
         <is>
-          <t>-0.108*</t>
+          <t>-0.300*</t>
         </is>
       </c>
       <c r="E33" s="18" t="inlineStr">
         <is>
-          <t>[-0.180, -0.035]</t>
+          <t>[-0.466, -0.133]</t>
         </is>
       </c>
       <c r="F33" s="18" t="inlineStr">
         <is>
-          <t>0.244*</t>
+          <t>0.343*</t>
         </is>
       </c>
       <c r="G33" s="18" t="inlineStr">
         <is>
-          <t>[0.105, 0.383]</t>
+          <t>[0.155, 0.530]</t>
         </is>
       </c>
     </row>
@@ -5181,32 +5179,32 @@
       </c>
       <c r="B34" s="18" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>0.056*</t>
         </is>
       </c>
       <c r="C34" s="18" t="inlineStr">
         <is>
-          <t>[-0.004, 0.066]</t>
+          <t>[0.009, 0.103]</t>
         </is>
       </c>
       <c r="D34" s="18" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>0.103*</t>
         </is>
       </c>
       <c r="E34" s="18" t="inlineStr">
         <is>
-          <t>[-0.002, 0.072]</t>
+          <t>[0.033, 0.173]</t>
         </is>
       </c>
       <c r="F34" s="18" t="inlineStr">
         <is>
-          <t>-0.079*</t>
+          <t>-0.118*</t>
         </is>
       </c>
       <c r="G34" s="18" t="inlineStr">
         <is>
-          <t>[-0.138, -0.021]</t>
+          <t>[-0.195, -0.041]</t>
         </is>
       </c>
     </row>
@@ -5231,32 +5229,32 @@
       </c>
       <c r="B36" s="20" t="inlineStr">
         <is>
-          <t>0.055*</t>
+          <t>0.085*</t>
         </is>
       </c>
       <c r="C36" s="20" t="inlineStr">
         <is>
-          <t>[0.025, 0.090]</t>
+          <t>[0.049, 0.127]</t>
         </is>
       </c>
       <c r="D36" s="20" t="inlineStr">
         <is>
-          <t>0.061*</t>
+          <t>0.157*</t>
         </is>
       </c>
       <c r="E36" s="20" t="inlineStr">
         <is>
-          <t>[0.018, 0.111]</t>
+          <t>[0.098, 0.226]</t>
         </is>
       </c>
       <c r="F36" s="20" t="inlineStr">
         <is>
-          <t>-0.138*</t>
+          <t>-0.180*</t>
         </is>
       </c>
       <c r="G36" s="20" t="inlineStr">
         <is>
-          <t>[-0.199, -0.086]</t>
+          <t>[-0.252, -0.116]</t>
         </is>
       </c>
     </row>
@@ -5268,32 +5266,32 @@
       </c>
       <c r="B37" s="20" t="inlineStr">
         <is>
-          <t>0.046*</t>
+          <t>0.072*</t>
         </is>
       </c>
       <c r="C37" s="20" t="inlineStr">
         <is>
-          <t>[0.004, 0.088]</t>
+          <t>[0.017, 0.127]</t>
         </is>
       </c>
       <c r="D37" s="20" t="inlineStr">
         <is>
-          <t>0.051*</t>
+          <t>0.132*</t>
         </is>
       </c>
       <c r="E37" s="20" t="inlineStr">
         <is>
-          <t>[0.006, 0.095]</t>
+          <t>[0.048, 0.216]</t>
         </is>
       </c>
       <c r="F37" s="20" t="inlineStr">
         <is>
-          <t>-0.115*</t>
+          <t>-0.152*</t>
         </is>
       </c>
       <c r="G37" s="20" t="inlineStr">
         <is>
-          <t>[-0.191, -0.039]</t>
+          <t>[-0.246, -0.058]</t>
         </is>
       </c>
     </row>
@@ -5305,32 +5303,32 @@
       </c>
       <c r="B38" s="20" t="inlineStr">
         <is>
-          <t>0.063*</t>
+          <t>0.098*</t>
         </is>
       </c>
       <c r="C38" s="20" t="inlineStr">
         <is>
-          <t>[0.013, 0.114]</t>
+          <t>[0.031, 0.166]</t>
         </is>
       </c>
       <c r="D38" s="20" t="inlineStr">
         <is>
-          <t>0.070*</t>
+          <t>0.181*</t>
         </is>
       </c>
       <c r="E38" s="20" t="inlineStr">
         <is>
-          <t>[0.016, 0.124]</t>
+          <t>[0.073, 0.289]</t>
         </is>
       </c>
       <c r="F38" s="20" t="inlineStr">
         <is>
-          <t>-0.159*</t>
+          <t>-0.207*</t>
         </is>
       </c>
       <c r="G38" s="20" t="inlineStr">
         <is>
-          <t>[-0.256, -0.061]</t>
+          <t>[-0.328, -0.086]</t>
         </is>
       </c>
     </row>
@@ -5342,32 +5340,32 @@
       </c>
       <c r="B39" s="20" t="inlineStr">
         <is>
-          <t>-0.017</t>
+          <t>-0.027</t>
         </is>
       </c>
       <c r="C39" s="20" t="inlineStr">
         <is>
-          <t>[-0.046, 0.011]</t>
+          <t>[-0.059, 0.006]</t>
         </is>
       </c>
       <c r="D39" s="20" t="inlineStr">
         <is>
-          <t>-0.019</t>
+          <t>-0.049*</t>
         </is>
       </c>
       <c r="E39" s="20" t="inlineStr">
         <is>
-          <t>[-0.049, 0.010]</t>
+          <t>[-0.093, -0.005]</t>
         </is>
       </c>
       <c r="F39" s="20" t="inlineStr">
         <is>
-          <t>0.044*</t>
+          <t>0.055*</t>
         </is>
       </c>
       <c r="G39" s="20" t="inlineStr">
         <is>
-          <t>[0.003, 0.084]</t>
+          <t>[0.009, 0.102]</t>
         </is>
       </c>
     </row>
@@ -5379,32 +5377,32 @@
       </c>
       <c r="B40" s="20" t="inlineStr">
         <is>
-          <t>0.047*</t>
+          <t>0.082*</t>
         </is>
       </c>
       <c r="C40" s="20" t="inlineStr">
         <is>
-          <t>[0.004, 0.090]</t>
+          <t>[0.022, 0.141]</t>
         </is>
       </c>
       <c r="D40" s="20" t="inlineStr">
         <is>
-          <t>0.053*</t>
+          <t>0.151*</t>
         </is>
       </c>
       <c r="E40" s="20" t="inlineStr">
         <is>
-          <t>[0.007, 0.098]</t>
+          <t>[0.057, 0.245]</t>
         </is>
       </c>
       <c r="F40" s="20" t="inlineStr">
         <is>
-          <t>-0.119*</t>
+          <t>-0.173*</t>
         </is>
       </c>
       <c r="G40" s="20" t="inlineStr">
         <is>
-          <t>[-0.196, -0.041]</t>
+          <t>[-0.277, -0.069]</t>
         </is>
       </c>
     </row>
@@ -5416,32 +5414,32 @@
       </c>
       <c r="B41" s="20" t="inlineStr">
         <is>
-          <t>0.061*</t>
+          <t>0.088*</t>
         </is>
       </c>
       <c r="C41" s="20" t="inlineStr">
         <is>
-          <t>[0.012, 0.111]</t>
+          <t>[0.025, 0.150]</t>
         </is>
       </c>
       <c r="D41" s="20" t="inlineStr">
         <is>
-          <t>0.069*</t>
+          <t>0.163*</t>
         </is>
       </c>
       <c r="E41" s="20" t="inlineStr">
         <is>
-          <t>[0.015, 0.122]</t>
+          <t>[0.063, 0.262]</t>
         </is>
       </c>
       <c r="F41" s="20" t="inlineStr">
         <is>
-          <t>-0.155*</t>
+          <t>-0.186*</t>
         </is>
       </c>
       <c r="G41" s="20" t="inlineStr">
         <is>
-          <t>[-0.251, -0.060]</t>
+          <t>[-0.297, -0.075]</t>
         </is>
       </c>
     </row>
@@ -5453,32 +5451,32 @@
       </c>
       <c r="B42" s="20" t="inlineStr">
         <is>
-          <t>-0.014</t>
+          <t>-0.006</t>
         </is>
       </c>
       <c r="C42" s="20" t="inlineStr">
         <is>
-          <t>[-0.041, 0.012]</t>
+          <t>[-0.030, 0.017]</t>
         </is>
       </c>
       <c r="D42" s="20" t="inlineStr">
         <is>
-          <t>-0.016</t>
+          <t>-0.011</t>
         </is>
       </c>
       <c r="E42" s="20" t="inlineStr">
         <is>
-          <t>[-0.044, 0.011]</t>
+          <t>[-0.037, 0.014]</t>
         </is>
       </c>
       <c r="F42" s="20" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>0.014</t>
         </is>
       </c>
       <c r="G42" s="20" t="inlineStr">
         <is>
-          <t>[-0.001, 0.074]</t>
+          <t>[-0.013, 0.040]</t>
         </is>
       </c>
     </row>
@@ -6047,71 +6045,71 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>0.016</t>
         </is>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.068</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.405</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.08</v>
+        <v>-0.117</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.198</v>
+        <v>0.15</v>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>0.645***</t>
+          <t>0.622***</t>
         </is>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.089</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="K9" s="4" t="n">
         <v>0</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.47</v>
+        <v>0.454</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.82</v>
+        <v>0.789</v>
       </c>
       <c r="N9" s="4" t="inlineStr">
         <is>
-          <t>0.540***</t>
+          <t>0.593***</t>
         </is>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.082</v>
       </c>
       <c r="P9" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>0.373</v>
+        <v>0.432</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>0.708</v>
+        <v>0.754</v>
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>0.105</t>
+          <t>0.029</t>
         </is>
       </c>
       <c r="T9" s="4" t="n">
-        <v>0.124</v>
+        <v>0.119</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>0.397</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>-0.137</v>
+        <v>-0.204</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>0.347</v>
+        <v>0.261</v>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" s="37">
@@ -6132,71 +6130,71 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>0.067</t>
         </is>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.068</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.313</v>
+        <v>0.324</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.068</v>
+        <v>-0.066</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0.211</v>
+        <v>0.201</v>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>-0.333***</t>
+          <t>-0.324***</t>
         </is>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.089</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="K10" s="4" t="n">
         <v>0</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-0.508</v>
+        <v>-0.491</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-0.159</v>
+        <v>-0.157</v>
       </c>
       <c r="N10" s="4" t="inlineStr">
         <is>
-          <t>-0.461***</t>
+          <t>-0.444***</t>
         </is>
       </c>
       <c r="O10" s="4" t="n">
-        <v>0.08</v>
+        <v>0.077</v>
       </c>
       <c r="P10" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>-0.617</v>
+        <v>-0.594</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>-0.304</v>
+        <v>-0.293</v>
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>0.127</t>
+          <t>0.119</t>
         </is>
       </c>
       <c r="T10" s="4" t="n">
-        <v>0.12</v>
+        <v>0.115</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>0.288</v>
+        <v>0.298</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>-0.107</v>
+        <v>-0.105</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>0.362</v>
+        <v>0.344</v>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" s="37">
@@ -6217,71 +6215,71 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>-0.130*</t>
+          <t>-0.143*</t>
         </is>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.064</v>
+        <v>0.061</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.042</v>
+        <v>0.02</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.254</v>
+        <v>-0.262</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.005</v>
+        <v>-0.023</v>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>0.477***</t>
+          <t>0.481***</t>
         </is>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.08</v>
+        <v>0.077</v>
       </c>
       <c r="K11" s="4" t="n">
         <v>0</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.319</v>
+        <v>0.329</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.635</v>
+        <v>0.632</v>
       </c>
       <c r="N11" s="4" t="inlineStr">
         <is>
-          <t>0.708***</t>
+          <t>0.734***</t>
         </is>
       </c>
       <c r="O11" s="4" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.082</v>
       </c>
       <c r="P11" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>0.541</v>
+        <v>0.574</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>0.875</v>
+        <v>0.894</v>
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>-0.231*</t>
+          <t>-0.254*</t>
         </is>
       </c>
       <c r="T11" s="4" t="n">
-        <v>0.117</v>
+        <v>0.112</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>0.049</v>
+        <v>0.025</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>-0.461</v>
+        <v>-0.474</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>-0.001</v>
+        <v>-0.033</v>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1" s="37">
@@ -6302,71 +6300,71 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>0.016</t>
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.06</v>
+        <v>0.057</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.326</v>
+        <v>0.787</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.058</v>
+        <v>-0.097</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.176</v>
+        <v>0.128</v>
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>-0.345***</t>
+          <t>-0.370***</t>
         </is>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.078</v>
+        <v>0.075</v>
       </c>
       <c r="K12" s="4" t="n">
         <v>0</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-0.498</v>
+        <v>-0.518</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-0.191</v>
+        <v>-0.223</v>
       </c>
       <c r="N12" s="4" t="inlineStr">
         <is>
-          <t>-0.449***</t>
+          <t>-0.398***</t>
         </is>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0.077</v>
+        <v>0.074</v>
       </c>
       <c r="P12" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>-0.6</v>
+        <v>-0.542</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>-0.299</v>
+        <v>-0.254</v>
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>0.105</t>
+          <t>0.028</t>
         </is>
       </c>
       <c r="T12" s="4" t="n">
-        <v>0.11</v>
+        <v>0.105</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>0.34</v>
+        <v>0.793</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>-0.11</v>
+        <v>-0.179</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>0.32</v>
+        <v>0.234</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="37">

--- a/results/Model3.xlsx
+++ b/results/Model3.xlsx
@@ -3004,27 +3004,27 @@
       </c>
       <c r="J6" s="24" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="K6" s="24" t="n">
-        <v>0.046</v>
+        <v>0</v>
       </c>
       <c r="L6" s="24" t="inlineStr">
         <is>
-          <t>-0.054</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="M6" s="24" t="n">
-        <v>0.075</v>
+        <v>0</v>
       </c>
       <c r="N6" s="24" t="inlineStr">
         <is>
-          <t>0.030</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="O6" s="24" t="n">
-        <v>0.07099999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" s="37">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="J8" s="24" t="inlineStr">
         <is>
-          <t>-0.011†</t>
+          <t>-0.011</t>
         </is>
       </c>
       <c r="K8" s="24" t="n">
@@ -3096,7 +3096,7 @@
       </c>
       <c r="L8" s="24" t="inlineStr">
         <is>
-          <t>-0.013</t>
+          <t>-0.010</t>
         </is>
       </c>
       <c r="M8" s="24" t="n">
@@ -3104,7 +3104,7 @@
       </c>
       <c r="N8" s="24" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>0.002</t>
         </is>
       </c>
       <c r="O8" s="24" t="n">
@@ -3151,7 +3151,7 @@
       </c>
       <c r="J9" s="24" t="inlineStr">
         <is>
-          <t>-0.007</t>
+          <t>-0.003</t>
         </is>
       </c>
       <c r="K9" s="24" t="n">
@@ -3159,15 +3159,15 @@
       </c>
       <c r="L9" s="24" t="inlineStr">
         <is>
-          <t>0.095</t>
+          <t>0.085</t>
         </is>
       </c>
       <c r="M9" s="24" t="n">
-        <v>0.098</v>
+        <v>0.099</v>
       </c>
       <c r="N9" s="24" t="inlineStr">
         <is>
-          <t>-0.053</t>
+          <t>-0.043</t>
         </is>
       </c>
       <c r="O9" s="24" t="n">
@@ -3214,7 +3214,7 @@
       </c>
       <c r="J10" s="24" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>0.004</t>
         </is>
       </c>
       <c r="K10" s="24" t="n">
@@ -3222,7 +3222,7 @@
       </c>
       <c r="L10" s="24" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>0.012</t>
         </is>
       </c>
       <c r="M10" s="24" t="n">
@@ -3230,7 +3230,7 @@
       </c>
       <c r="N10" s="24" t="inlineStr">
         <is>
-          <t>-0.008</t>
+          <t>-0.004</t>
         </is>
       </c>
       <c r="O10" s="24" t="n">
@@ -3277,7 +3277,7 @@
       </c>
       <c r="J11" s="24" t="inlineStr">
         <is>
-          <t>-0.003</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="K11" s="24" t="n">
@@ -3293,7 +3293,7 @@
       </c>
       <c r="N11" s="24" t="inlineStr">
         <is>
-          <t>-0.019</t>
+          <t>-0.017</t>
         </is>
       </c>
       <c r="O11" s="24" t="n">
@@ -3348,11 +3348,11 @@
       </c>
       <c r="J12" s="24" t="inlineStr">
         <is>
-          <t>0.392***</t>
+          <t>0.389***</t>
         </is>
       </c>
       <c r="K12" s="24" t="n">
-        <v>0.051</v>
+        <v>0.048</v>
       </c>
       <c r="L12" s="24" t="inlineStr">
         <is>
@@ -3436,7 +3436,7 @@
       </c>
       <c r="J14" s="24" t="inlineStr">
         <is>
-          <t>-0.008</t>
+          <t>-0.004</t>
         </is>
       </c>
       <c r="K14" s="24" t="n">
@@ -3444,19 +3444,19 @@
       </c>
       <c r="L14" s="24" t="inlineStr">
         <is>
-          <t>0.375***</t>
+          <t>0.365***</t>
         </is>
       </c>
       <c r="M14" s="24" t="n">
+        <v>0.083</v>
+      </c>
+      <c r="N14" s="24" t="inlineStr">
+        <is>
+          <t>-0.103</t>
+        </is>
+      </c>
+      <c r="O14" s="24" t="n">
         <v>0.08</v>
-      </c>
-      <c r="N14" s="24" t="inlineStr">
-        <is>
-          <t>-0.109</t>
-        </is>
-      </c>
-      <c r="O14" s="24" t="n">
-        <v>0.078</v>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1" s="37">
@@ -3499,27 +3499,27 @@
       </c>
       <c r="J15" s="24" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>0.042</t>
         </is>
       </c>
       <c r="K15" s="24" t="n">
-        <v>0.046</v>
+        <v>0.045</v>
       </c>
       <c r="L15" s="24" t="inlineStr">
         <is>
-          <t>-0.029</t>
+          <t>-0.016</t>
         </is>
       </c>
       <c r="M15" s="24" t="n">
+        <v>0.074</v>
+      </c>
+      <c r="N15" s="24" t="inlineStr">
+        <is>
+          <t>-0.017</t>
+        </is>
+      </c>
+      <c r="O15" s="24" t="n">
         <v>0.07099999999999999</v>
-      </c>
-      <c r="N15" s="24" t="inlineStr">
-        <is>
-          <t>-0.013</t>
-        </is>
-      </c>
-      <c r="O15" s="24" t="n">
-        <v>0.06900000000000001</v>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1" s="37">
@@ -3591,27 +3591,27 @@
       </c>
       <c r="J17" s="24" t="inlineStr">
         <is>
-          <t>0.249***</t>
+          <t>0.251***</t>
         </is>
       </c>
       <c r="K17" s="24" t="n">
-        <v>0.037</v>
+        <v>0.036</v>
       </c>
       <c r="L17" s="24" t="inlineStr">
         <is>
-          <t>0.451***</t>
+          <t>0.423***</t>
         </is>
       </c>
       <c r="M17" s="24" t="n">
-        <v>0.056</v>
+        <v>0.058</v>
       </c>
       <c r="N17" s="24" t="inlineStr">
         <is>
-          <t>-0.230***</t>
+          <t>-0.205***</t>
         </is>
       </c>
       <c r="O17" s="24" t="n">
-        <v>0.055</v>
+        <v>0.057</v>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1" s="37">
@@ -3662,27 +3662,27 @@
       </c>
       <c r="J18" s="24" t="inlineStr">
         <is>
-          <t>-0.222***</t>
+          <t>-0.231***</t>
         </is>
       </c>
       <c r="K18" s="24" t="n">
-        <v>0.041</v>
+        <v>0.043</v>
       </c>
       <c r="L18" s="24" t="inlineStr">
         <is>
-          <t>-0.409***</t>
+          <t>-0.417***</t>
         </is>
       </c>
       <c r="M18" s="24" t="n">
-        <v>0.061</v>
+        <v>0.066</v>
       </c>
       <c r="N18" s="24" t="inlineStr">
         <is>
-          <t>0.467***</t>
+          <t>0.484***</t>
         </is>
       </c>
       <c r="O18" s="24" t="n">
-        <v>0.06</v>
+        <v>0.066</v>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1" s="37">
@@ -3746,15 +3746,15 @@
       </c>
       <c r="J20" s="24" t="inlineStr">
         <is>
-          <t>-0.006</t>
+          <t>-0.004</t>
         </is>
       </c>
       <c r="K20" s="24" t="n">
-        <v>0.035</v>
+        <v>0.034</v>
       </c>
       <c r="L20" s="24" t="inlineStr">
         <is>
-          <t>-0.053</t>
+          <t>-0.059</t>
         </is>
       </c>
       <c r="M20" s="24" t="n">
@@ -3762,7 +3762,7 @@
       </c>
       <c r="N20" s="24" t="inlineStr">
         <is>
-          <t>0.061</t>
+          <t>0.073</t>
         </is>
       </c>
       <c r="O20" s="24" t="n">
@@ -3809,27 +3809,27 @@
       </c>
       <c r="J21" s="24" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>0.027</t>
         </is>
       </c>
       <c r="K21" s="24" t="n">
-        <v>0.035</v>
+        <v>0.034</v>
       </c>
       <c r="L21" s="24" t="inlineStr">
         <is>
-          <t>-0.053</t>
+          <t>-0.059</t>
         </is>
       </c>
       <c r="M21" s="24" t="n">
-        <v>0.055</v>
+        <v>0.056</v>
       </c>
       <c r="N21" s="24" t="inlineStr">
         <is>
-          <t>-0.024</t>
+          <t>-0.022</t>
         </is>
       </c>
       <c r="O21" s="24" t="n">
-        <v>0.054</v>
+        <v>0.053</v>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1" s="37">

--- a/results/Model3.xlsx
+++ b/results/Model3.xlsx
@@ -2575,52 +2575,52 @@
         </is>
       </c>
       <c r="B15" s="24" t="n">
-        <v>4.486</v>
+        <v>4.493</v>
       </c>
       <c r="C15" s="24" t="n">
-        <v>0.78</v>
+        <v>0.789</v>
       </c>
       <c r="D15" s="24" t="n">
-        <v>0.032</v>
+        <v>0.018</v>
       </c>
       <c r="E15" s="24" t="n">
-        <v>-0.052</v>
+        <v>-0.098</v>
       </c>
       <c r="F15" s="24" t="n">
-        <v>-0.029</v>
+        <v>-0.033</v>
       </c>
       <c r="G15" s="24" t="n">
-        <v>-0.045</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="H15" s="24" t="inlineStr">
         <is>
-          <t>-0.386***</t>
+          <t>-0.199***</t>
         </is>
       </c>
       <c r="I15" s="24" t="inlineStr">
         <is>
-          <t>0.401***</t>
+          <t>0.212***</t>
         </is>
       </c>
       <c r="J15" s="24" t="n">
-        <v>-0.047</v>
+        <v>-0.017</v>
       </c>
       <c r="K15" s="24" t="n">
-        <v>-0.026</v>
+        <v>0.013</v>
       </c>
       <c r="L15" s="24" t="inlineStr">
         <is>
-          <t>0.494***</t>
+          <t>0.187***</t>
         </is>
       </c>
       <c r="M15" s="24" t="inlineStr">
         <is>
-          <t>-0.42***</t>
+          <t>-0.249***</t>
         </is>
       </c>
       <c r="N15" s="24" t="inlineStr">
         <is>
-          <t>0.39***</t>
+          <t>0.134*</t>
         </is>
       </c>
       <c r="O15" s="24" t="inlineStr">
@@ -2641,37 +2641,37 @@
         <v>4.78</v>
       </c>
       <c r="C16" s="24" t="n">
-        <v>1.063</v>
+        <v>1.056</v>
       </c>
       <c r="D16" s="24" t="n">
-        <v>0.062</v>
+        <v>0.068</v>
       </c>
       <c r="E16" s="24" t="n">
-        <v>-0.032</v>
+        <v>-0.047</v>
       </c>
       <c r="F16" s="24" t="n">
-        <v>0.017</v>
+        <v>0.016</v>
       </c>
       <c r="G16" s="24" t="inlineStr">
         <is>
-          <t>-0.116*</t>
+          <t>-0.115*</t>
         </is>
       </c>
       <c r="H16" s="24" t="inlineStr">
         <is>
-          <t>-0.186***</t>
+          <t>-0.181***</t>
         </is>
       </c>
       <c r="I16" s="24" t="inlineStr">
         <is>
-          <t>0.367***</t>
+          <t>0.366***</t>
         </is>
       </c>
       <c r="J16" s="24" t="n">
-        <v>-0.038</v>
+        <v>-0.042</v>
       </c>
       <c r="K16" s="24" t="n">
-        <v>-0.089</v>
+        <v>-0.092</v>
       </c>
       <c r="L16" s="24" t="inlineStr">
         <is>
@@ -2680,15 +2680,17 @@
       </c>
       <c r="M16" s="24" t="inlineStr">
         <is>
-          <t>-0.311***</t>
-        </is>
-      </c>
-      <c r="N16" s="24" t="n">
-        <v>0.098</v>
+          <t>-0.302***</t>
+        </is>
+      </c>
+      <c r="N16" s="24" t="inlineStr">
+        <is>
+          <t>0.13*</t>
+        </is>
       </c>
       <c r="O16" s="24" t="inlineStr">
         <is>
-          <t>0.315***</t>
+          <t>0.319***</t>
         </is>
       </c>
       <c r="P16" s="24" t="inlineStr">
@@ -2705,42 +2707,42 @@
         </is>
       </c>
       <c r="B17" s="24" t="n">
-        <v>2.696</v>
+        <v>2.704</v>
       </c>
       <c r="C17" s="24" t="n">
         <v>1.044</v>
       </c>
       <c r="D17" s="24" t="n">
-        <v>-0.061</v>
+        <v>-0.06</v>
       </c>
       <c r="E17" s="24" t="n">
-        <v>0.015</v>
+        <v>0.011</v>
       </c>
       <c r="F17" s="24" t="n">
-        <v>0.028</v>
+        <v>0.014</v>
       </c>
       <c r="G17" s="24" t="n">
-        <v>0.012</v>
+        <v>0.007</v>
       </c>
       <c r="H17" s="24" t="inlineStr">
         <is>
-          <t>0.342***</t>
+          <t>0.362***</t>
         </is>
       </c>
       <c r="I17" s="24" t="inlineStr">
         <is>
-          <t>-0.366***</t>
+          <t>-0.368***</t>
         </is>
       </c>
       <c r="J17" s="24" t="n">
-        <v>0.054</v>
+        <v>0.074</v>
       </c>
       <c r="K17" s="24" t="n">
-        <v>0.002</v>
+        <v>0.011</v>
       </c>
       <c r="L17" s="24" t="inlineStr">
         <is>
-          <t>-0.279***</t>
+          <t>-0.3***</t>
         </is>
       </c>
       <c r="M17" s="24" t="inlineStr">
@@ -2749,11 +2751,11 @@
         </is>
       </c>
       <c r="N17" s="24" t="n">
-        <v>-0.031</v>
+        <v>-0.077</v>
       </c>
       <c r="O17" s="24" t="inlineStr">
         <is>
-          <t>-0.25***</t>
+          <t>-0.26***</t>
         </is>
       </c>
       <c r="P17" s="24" t="inlineStr">
@@ -3088,15 +3090,15 @@
       </c>
       <c r="J8" s="24" t="inlineStr">
         <is>
-          <t>-0.011</t>
+          <t>-0.018*</t>
         </is>
       </c>
       <c r="K8" s="24" t="n">
-        <v>0.007</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="L8" s="24" t="inlineStr">
         <is>
-          <t>-0.010</t>
+          <t>-0.014</t>
         </is>
       </c>
       <c r="M8" s="24" t="n">
@@ -3104,7 +3106,7 @@
       </c>
       <c r="N8" s="24" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>0.003</t>
         </is>
       </c>
       <c r="O8" s="24" t="n">
@@ -3151,19 +3153,19 @@
       </c>
       <c r="J9" s="24" t="inlineStr">
         <is>
-          <t>-0.003</t>
+          <t>0.018</t>
         </is>
       </c>
       <c r="K9" s="24" t="n">
-        <v>0.061</v>
+        <v>0.082</v>
       </c>
       <c r="L9" s="24" t="inlineStr">
         <is>
-          <t>0.085</t>
+          <t>0.103</t>
         </is>
       </c>
       <c r="M9" s="24" t="n">
-        <v>0.099</v>
+        <v>0.098</v>
       </c>
       <c r="N9" s="24" t="inlineStr">
         <is>
@@ -3171,7 +3173,7 @@
         </is>
       </c>
       <c r="O9" s="24" t="n">
-        <v>0.096</v>
+        <v>0.095</v>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" s="37">
@@ -3214,15 +3216,15 @@
       </c>
       <c r="J10" s="24" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>0.001</t>
         </is>
       </c>
       <c r="K10" s="24" t="n">
-        <v>0.021</v>
+        <v>0.028</v>
       </c>
       <c r="L10" s="24" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>0.014</t>
         </is>
       </c>
       <c r="M10" s="24" t="n">
@@ -3230,7 +3232,7 @@
       </c>
       <c r="N10" s="24" t="inlineStr">
         <is>
-          <t>-0.004</t>
+          <t>-0.014</t>
         </is>
       </c>
       <c r="O10" s="24" t="n">
@@ -3277,15 +3279,15 @@
       </c>
       <c r="J11" s="24" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.013</t>
         </is>
       </c>
       <c r="K11" s="24" t="n">
-        <v>0.028</v>
+        <v>0.038</v>
       </c>
       <c r="L11" s="24" t="inlineStr">
         <is>
-          <t>-0.091*</t>
+          <t>-0.090*</t>
         </is>
       </c>
       <c r="M11" s="24" t="n">
@@ -3293,7 +3295,7 @@
       </c>
       <c r="N11" s="24" t="inlineStr">
         <is>
-          <t>-0.017</t>
+          <t>-0.021</t>
         </is>
       </c>
       <c r="O11" s="24" t="n">
@@ -3348,11 +3350,11 @@
       </c>
       <c r="J12" s="24" t="inlineStr">
         <is>
-          <t>0.389***</t>
+          <t>0.146*</t>
         </is>
       </c>
       <c r="K12" s="24" t="n">
-        <v>0.048</v>
+        <v>0.063</v>
       </c>
       <c r="L12" s="24" t="inlineStr">
         <is>
@@ -3436,15 +3438,15 @@
       </c>
       <c r="J14" s="24" t="inlineStr">
         <is>
-          <t>-0.004</t>
+          <t>-0.010</t>
         </is>
       </c>
       <c r="K14" s="24" t="n">
-        <v>0.052</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="L14" s="24" t="inlineStr">
         <is>
-          <t>0.365***</t>
+          <t>0.358***</t>
         </is>
       </c>
       <c r="M14" s="24" t="n">
@@ -3452,11 +3454,11 @@
       </c>
       <c r="N14" s="24" t="inlineStr">
         <is>
-          <t>-0.103</t>
+          <t>-0.064</t>
         </is>
       </c>
       <c r="O14" s="24" t="n">
-        <v>0.08</v>
+        <v>0.079</v>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1" s="37">
@@ -3499,15 +3501,15 @@
       </c>
       <c r="J15" s="24" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>0.041</t>
         </is>
       </c>
       <c r="K15" s="24" t="n">
-        <v>0.045</v>
+        <v>0.06</v>
       </c>
       <c r="L15" s="24" t="inlineStr">
         <is>
-          <t>-0.016</t>
+          <t>-0.009</t>
         </is>
       </c>
       <c r="M15" s="24" t="n">
@@ -3515,11 +3517,11 @@
       </c>
       <c r="N15" s="24" t="inlineStr">
         <is>
-          <t>-0.017</t>
+          <t>-0.019</t>
         </is>
       </c>
       <c r="O15" s="24" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1" s="37">
@@ -3591,15 +3593,15 @@
       </c>
       <c r="J17" s="24" t="inlineStr">
         <is>
-          <t>0.251***</t>
+          <t>0.094†</t>
         </is>
       </c>
       <c r="K17" s="24" t="n">
-        <v>0.036</v>
+        <v>0.049</v>
       </c>
       <c r="L17" s="24" t="inlineStr">
         <is>
-          <t>0.423***</t>
+          <t>0.422***</t>
         </is>
       </c>
       <c r="M17" s="24" t="n">
@@ -3607,7 +3609,7 @@
       </c>
       <c r="N17" s="24" t="inlineStr">
         <is>
-          <t>-0.205***</t>
+          <t>-0.211***</t>
         </is>
       </c>
       <c r="O17" s="24" t="n">
@@ -3662,15 +3664,15 @@
       </c>
       <c r="J18" s="24" t="inlineStr">
         <is>
-          <t>-0.231***</t>
+          <t>-0.131*</t>
         </is>
       </c>
       <c r="K18" s="24" t="n">
-        <v>0.043</v>
+        <v>0.056</v>
       </c>
       <c r="L18" s="24" t="inlineStr">
         <is>
-          <t>-0.417***</t>
+          <t>-0.396***</t>
         </is>
       </c>
       <c r="M18" s="24" t="n">
@@ -3678,7 +3680,7 @@
       </c>
       <c r="N18" s="24" t="inlineStr">
         <is>
-          <t>0.484***</t>
+          <t>0.456***</t>
         </is>
       </c>
       <c r="O18" s="24" t="n">
@@ -3746,15 +3748,15 @@
       </c>
       <c r="J20" s="24" t="inlineStr">
         <is>
-          <t>-0.004</t>
+          <t>0.005</t>
         </is>
       </c>
       <c r="K20" s="24" t="n">
-        <v>0.034</v>
+        <v>0.045</v>
       </c>
       <c r="L20" s="24" t="inlineStr">
         <is>
-          <t>-0.059</t>
+          <t>-0.065</t>
         </is>
       </c>
       <c r="M20" s="24" t="n">
@@ -3762,7 +3764,7 @@
       </c>
       <c r="N20" s="24" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>0.101†</t>
         </is>
       </c>
       <c r="O20" s="24" t="n">
@@ -3809,15 +3811,15 @@
       </c>
       <c r="J21" s="24" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>0.036</t>
         </is>
       </c>
       <c r="K21" s="24" t="n">
-        <v>0.034</v>
+        <v>0.045</v>
       </c>
       <c r="L21" s="24" t="inlineStr">
         <is>
-          <t>-0.059</t>
+          <t>-0.061</t>
         </is>
       </c>
       <c r="M21" s="24" t="n">
@@ -3825,11 +3827,11 @@
       </c>
       <c r="N21" s="24" t="inlineStr">
         <is>
-          <t>-0.022</t>
+          <t>-0.012</t>
         </is>
       </c>
       <c r="O21" s="24" t="n">
-        <v>0.053</v>
+        <v>0.052</v>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1" s="37">
@@ -4361,32 +4363,32 @@
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>-0.123*</t>
+          <t>-0.039</t>
         </is>
       </c>
       <c r="C8" s="14" t="inlineStr">
         <is>
-          <t>[-0.176, -0.078]</t>
+          <t>[-0.092, 0.010]</t>
         </is>
       </c>
       <c r="D8" s="14" t="inlineStr">
         <is>
-          <t>-0.223*</t>
+          <t>-0.218*</t>
         </is>
       </c>
       <c r="E8" s="14" t="inlineStr">
         <is>
-          <t>[-0.307, -0.150]</t>
+          <t>[-0.301, -0.146]</t>
         </is>
       </c>
       <c r="F8" s="14" t="inlineStr">
         <is>
-          <t>0.114*</t>
+          <t>0.117*</t>
         </is>
       </c>
       <c r="G8" s="14" t="inlineStr">
         <is>
-          <t>[0.057, 0.180]</t>
+          <t>[0.060, 0.184]</t>
         </is>
       </c>
     </row>
@@ -4411,32 +4413,32 @@
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>-0.134*</t>
+          <t>-0.042*</t>
         </is>
       </c>
       <c r="C10" s="14" t="inlineStr">
         <is>
-          <t>[-0.219, -0.049]</t>
+          <t>[-0.082, -0.002]</t>
         </is>
       </c>
       <c r="D10" s="14" t="inlineStr">
         <is>
-          <t>-0.243*</t>
+          <t>-0.237*</t>
         </is>
       </c>
       <c r="E10" s="14" t="inlineStr">
         <is>
-          <t>[-0.382, -0.104]</t>
+          <t>[-0.373, -0.101]</t>
         </is>
       </c>
       <c r="F10" s="14" t="inlineStr">
         <is>
-          <t>0.124*</t>
+          <t>0.127*</t>
         </is>
       </c>
       <c r="G10" s="14" t="inlineStr">
         <is>
-          <t>[0.044, 0.204]</t>
+          <t>[0.045, 0.209]</t>
         </is>
       </c>
     </row>
@@ -4448,32 +4450,32 @@
       </c>
       <c r="B11" s="14" t="inlineStr">
         <is>
-          <t>-0.116*</t>
+          <t>-0.036</t>
         </is>
       </c>
       <c r="C11" s="14" t="inlineStr">
         <is>
-          <t>[-0.192, -0.039]</t>
+          <t>[-0.073, 0.001]</t>
         </is>
       </c>
       <c r="D11" s="14" t="inlineStr">
         <is>
-          <t>-0.210*</t>
+          <t>-0.205*</t>
         </is>
       </c>
       <c r="E11" s="14" t="inlineStr">
         <is>
-          <t>[-0.332, -0.087]</t>
+          <t>[-0.324, -0.085]</t>
         </is>
       </c>
       <c r="F11" s="14" t="inlineStr">
         <is>
-          <t>0.107*</t>
+          <t>0.110*</t>
         </is>
       </c>
       <c r="G11" s="14" t="inlineStr">
         <is>
-          <t>[0.035, 0.179]</t>
+          <t>[0.036, 0.183]</t>
         </is>
       </c>
     </row>
@@ -4485,12 +4487,12 @@
       </c>
       <c r="B12" s="14" t="inlineStr">
         <is>
-          <t>-0.018</t>
+          <t>-0.006</t>
         </is>
       </c>
       <c r="C12" s="14" t="inlineStr">
         <is>
-          <t>[-0.047, 0.010]</t>
+          <t>[-0.029, 0.018]</t>
         </is>
       </c>
       <c r="D12" s="14" t="inlineStr">
@@ -4500,7 +4502,7 @@
       </c>
       <c r="E12" s="14" t="inlineStr">
         <is>
-          <t>[-0.069, 0.003]</t>
+          <t>[-0.068, 0.003]</t>
         </is>
       </c>
       <c r="F12" s="14" t="inlineStr">
@@ -4510,7 +4512,7 @@
       </c>
       <c r="G12" s="14" t="inlineStr">
         <is>
-          <t>[-0.011, 0.045]</t>
+          <t>[-0.011, 0.046]</t>
         </is>
       </c>
     </row>
@@ -4535,32 +4537,32 @@
       </c>
       <c r="B14" s="14" t="inlineStr">
         <is>
-          <t>-0.130*</t>
+          <t>-0.040*</t>
         </is>
       </c>
       <c r="C14" s="14" t="inlineStr">
         <is>
-          <t>[-0.213, -0.047]</t>
+          <t>[-0.080, -0.001]</t>
         </is>
       </c>
       <c r="D14" s="14" t="inlineStr">
         <is>
-          <t>-0.236*</t>
+          <t>-0.230*</t>
         </is>
       </c>
       <c r="E14" s="14" t="inlineStr">
         <is>
-          <t>[-0.371, -0.101]</t>
+          <t>[-0.362, -0.098]</t>
         </is>
       </c>
       <c r="F14" s="14" t="inlineStr">
         <is>
-          <t>0.121*</t>
+          <t>0.124*</t>
         </is>
       </c>
       <c r="G14" s="14" t="inlineStr">
         <is>
-          <t>[0.042, 0.200]</t>
+          <t>[0.044, 0.204]</t>
         </is>
       </c>
     </row>
@@ -4572,32 +4574,32 @@
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>-0.120*</t>
+          <t>-0.037</t>
         </is>
       </c>
       <c r="C15" s="14" t="inlineStr">
         <is>
-          <t>[-0.198, -0.041]</t>
+          <t>[-0.075, 0.001]</t>
         </is>
       </c>
       <c r="D15" s="14" t="inlineStr">
         <is>
-          <t>-0.217*</t>
+          <t>-0.212*</t>
         </is>
       </c>
       <c r="E15" s="14" t="inlineStr">
         <is>
-          <t>[-0.343, -0.091]</t>
+          <t>[-0.335, -0.088]</t>
         </is>
       </c>
       <c r="F15" s="14" t="inlineStr">
         <is>
-          <t>0.111*</t>
+          <t>0.114*</t>
         </is>
       </c>
       <c r="G15" s="14" t="inlineStr">
         <is>
-          <t>[0.037, 0.185]</t>
+          <t>[0.039, 0.190]</t>
         </is>
       </c>
     </row>
@@ -4609,17 +4611,17 @@
       </c>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t>-0.010</t>
+          <t>-0.003</t>
         </is>
       </c>
       <c r="C16" s="14" t="inlineStr">
         <is>
-          <t>[-0.035, 0.014]</t>
+          <t>[-0.027, 0.020]</t>
         </is>
       </c>
       <c r="D16" s="14" t="inlineStr">
         <is>
-          <t>-0.019</t>
+          <t>-0.018</t>
         </is>
       </c>
       <c r="E16" s="14" t="inlineStr">
@@ -4634,7 +4636,7 @@
       </c>
       <c r="G16" s="14" t="inlineStr">
         <is>
-          <t>[-0.015, 0.034]</t>
+          <t>[-0.014, 0.035]</t>
         </is>
       </c>
     </row>
@@ -4659,32 +4661,32 @@
       </c>
       <c r="B18" s="16" t="inlineStr">
         <is>
-          <t>0.130*</t>
+          <t>0.041</t>
         </is>
       </c>
       <c r="C18" s="16" t="inlineStr">
         <is>
-          <t>[0.085, 0.182]</t>
+          <t>[-0.010, 0.096]</t>
         </is>
       </c>
       <c r="D18" s="16" t="inlineStr">
         <is>
-          <t>0.237*</t>
+          <t>0.231*</t>
         </is>
       </c>
       <c r="E18" s="16" t="inlineStr">
         <is>
-          <t>[0.164, 0.319]</t>
+          <t>[0.159, 0.312]</t>
         </is>
       </c>
       <c r="F18" s="16" t="inlineStr">
         <is>
-          <t>-0.121*</t>
+          <t>-0.124*</t>
         </is>
       </c>
       <c r="G18" s="16" t="inlineStr">
         <is>
-          <t>[-0.187, -0.062]</t>
+          <t>[-0.191, -0.065]</t>
         </is>
       </c>
     </row>
@@ -4709,32 +4711,32 @@
       </c>
       <c r="B20" s="16" t="inlineStr">
         <is>
-          <t>0.136*</t>
+          <t>0.043*</t>
         </is>
       </c>
       <c r="C20" s="16" t="inlineStr">
         <is>
-          <t>[0.050, 0.223]</t>
+          <t>[0.002, 0.083]</t>
         </is>
       </c>
       <c r="D20" s="16" t="inlineStr">
         <is>
-          <t>0.246*</t>
+          <t>0.240*</t>
         </is>
       </c>
       <c r="E20" s="16" t="inlineStr">
         <is>
-          <t>[0.106, 0.386]</t>
+          <t>[0.103, 0.377]</t>
         </is>
       </c>
       <c r="F20" s="16" t="inlineStr">
         <is>
-          <t>-0.126*</t>
+          <t>-0.130*</t>
         </is>
       </c>
       <c r="G20" s="16" t="inlineStr">
         <is>
-          <t>[-0.208, -0.045]</t>
+          <t>[-0.213, -0.047]</t>
         </is>
       </c>
     </row>
@@ -4746,32 +4748,32 @@
       </c>
       <c r="B21" s="16" t="inlineStr">
         <is>
-          <t>0.123*</t>
+          <t>0.039*</t>
         </is>
       </c>
       <c r="C21" s="16" t="inlineStr">
         <is>
-          <t>[0.043, 0.202]</t>
+          <t>[0.000, 0.077]</t>
         </is>
       </c>
       <c r="D21" s="16" t="inlineStr">
         <is>
-          <t>0.222*</t>
+          <t>0.217*</t>
         </is>
       </c>
       <c r="E21" s="16" t="inlineStr">
         <is>
-          <t>[0.094, 0.350]</t>
+          <t>[0.091, 0.342]</t>
         </is>
       </c>
       <c r="F21" s="16" t="inlineStr">
         <is>
-          <t>-0.114*</t>
+          <t>-0.117*</t>
         </is>
       </c>
       <c r="G21" s="16" t="inlineStr">
         <is>
-          <t>[-0.189, -0.038]</t>
+          <t>[-0.194, -0.040]</t>
         </is>
       </c>
     </row>
@@ -4783,12 +4785,12 @@
       </c>
       <c r="B22" s="16" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>0.004</t>
         </is>
       </c>
       <c r="C22" s="16" t="inlineStr">
         <is>
-          <t>[-0.013, 0.040]</t>
+          <t>[-0.019, 0.028]</t>
         </is>
       </c>
       <c r="D22" s="16" t="inlineStr">
@@ -4798,7 +4800,7 @@
       </c>
       <c r="E22" s="16" t="inlineStr">
         <is>
-          <t>[-0.007, 0.056]</t>
+          <t>[-0.008, 0.055]</t>
         </is>
       </c>
       <c r="F22" s="16" t="inlineStr">
@@ -4808,7 +4810,7 @@
       </c>
       <c r="G22" s="16" t="inlineStr">
         <is>
-          <t>[-0.038, 0.013]</t>
+          <t>[-0.039, 0.013]</t>
         </is>
       </c>
     </row>
@@ -4820,32 +4822,32 @@
       </c>
       <c r="B23" s="16" t="inlineStr">
         <is>
-          <t>0.096*</t>
+          <t>0.030</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
         <is>
-          <t>[0.029, 0.162]</t>
+          <t>[-0.004, 0.064]</t>
         </is>
       </c>
       <c r="D23" s="16" t="inlineStr">
         <is>
-          <t>0.173*</t>
+          <t>0.169*</t>
         </is>
       </c>
       <c r="E23" s="16" t="inlineStr">
         <is>
-          <t>[0.069, 0.277]</t>
+          <t>[0.066, 0.271]</t>
         </is>
       </c>
       <c r="F23" s="16" t="inlineStr">
         <is>
-          <t>-0.089*</t>
+          <t>-0.091*</t>
         </is>
       </c>
       <c r="G23" s="16" t="inlineStr">
         <is>
-          <t>[-0.152, -0.026]</t>
+          <t>[-0.155, -0.027]</t>
         </is>
       </c>
     </row>
@@ -4857,32 +4859,32 @@
       </c>
       <c r="B24" s="16" t="inlineStr">
         <is>
-          <t>0.163*</t>
+          <t>0.051*</t>
         </is>
       </c>
       <c r="C24" s="16" t="inlineStr">
         <is>
-          <t>[0.064, 0.263]</t>
+          <t>[0.006, 0.095]</t>
         </is>
       </c>
       <c r="D24" s="16" t="inlineStr">
         <is>
-          <t>0.296*</t>
+          <t>0.289*</t>
         </is>
       </c>
       <c r="E24" s="16" t="inlineStr">
         <is>
-          <t>[0.132, 0.461]</t>
+          <t>[0.128, 0.451]</t>
         </is>
       </c>
       <c r="F24" s="16" t="inlineStr">
         <is>
-          <t>-0.152*</t>
+          <t>-0.156*</t>
         </is>
       </c>
       <c r="G24" s="16" t="inlineStr">
         <is>
-          <t>[-0.246, -0.058]</t>
+          <t>[-0.252, -0.060]</t>
         </is>
       </c>
     </row>
@@ -4894,32 +4896,32 @@
       </c>
       <c r="B25" s="16" t="inlineStr">
         <is>
-          <t>-0.067*</t>
+          <t>-0.021</t>
         </is>
       </c>
       <c r="C25" s="16" t="inlineStr">
         <is>
-          <t>[-0.120, -0.015]</t>
+          <t>[-0.051, 0.009]</t>
         </is>
       </c>
       <c r="D25" s="16" t="inlineStr">
         <is>
-          <t>-0.123*</t>
+          <t>-0.121*</t>
         </is>
       </c>
       <c r="E25" s="16" t="inlineStr">
         <is>
-          <t>[-0.204, -0.043]</t>
+          <t>[-0.199, -0.042]</t>
         </is>
       </c>
       <c r="F25" s="16" t="inlineStr">
         <is>
-          <t>0.063*</t>
+          <t>0.065*</t>
         </is>
       </c>
       <c r="G25" s="16" t="inlineStr">
         <is>
-          <t>[0.013, 0.114]</t>
+          <t>[0.013, 0.116]</t>
         </is>
       </c>
     </row>
@@ -4957,32 +4959,32 @@
       </c>
       <c r="B28" s="18" t="inlineStr">
         <is>
-          <t>-0.130*</t>
+          <t>-0.074*</t>
         </is>
       </c>
       <c r="C28" s="18" t="inlineStr">
         <is>
-          <t>[-0.187, -0.080]</t>
+          <t>[-0.140, -0.011]</t>
         </is>
       </c>
       <c r="D28" s="18" t="inlineStr">
         <is>
-          <t>-0.240*</t>
+          <t>-0.229*</t>
         </is>
       </c>
       <c r="E28" s="18" t="inlineStr">
         <is>
-          <t>[-0.331, -0.160]</t>
+          <t>[-0.318, -0.151]</t>
         </is>
       </c>
       <c r="F28" s="18" t="inlineStr">
         <is>
-          <t>0.275*</t>
+          <t>0.263*</t>
         </is>
       </c>
       <c r="G28" s="18" t="inlineStr">
         <is>
-          <t>[0.191, 0.368]</t>
+          <t>[0.181, 0.355]</t>
         </is>
       </c>
     </row>
@@ -4994,32 +4996,32 @@
       </c>
       <c r="B29" s="18" t="inlineStr">
         <is>
-          <t>-0.138*</t>
+          <t>-0.078*</t>
         </is>
       </c>
       <c r="C29" s="18" t="inlineStr">
         <is>
-          <t>[-0.225, -0.051]</t>
+          <t>[-0.136, -0.020]</t>
         </is>
       </c>
       <c r="D29" s="18" t="inlineStr">
         <is>
-          <t>-0.254*</t>
+          <t>-0.242*</t>
         </is>
       </c>
       <c r="E29" s="18" t="inlineStr">
         <is>
-          <t>[-0.398, -0.110]</t>
+          <t>[-0.381, -0.104]</t>
         </is>
       </c>
       <c r="F29" s="18" t="inlineStr">
         <is>
-          <t>0.291*</t>
+          <t>0.278*</t>
         </is>
       </c>
       <c r="G29" s="18" t="inlineStr">
         <is>
-          <t>[0.129, 0.453]</t>
+          <t>[0.122, 0.434]</t>
         </is>
       </c>
     </row>
@@ -5031,32 +5033,32 @@
       </c>
       <c r="B30" s="18" t="inlineStr">
         <is>
-          <t>-0.131*</t>
+          <t>-0.074*</t>
         </is>
       </c>
       <c r="C30" s="18" t="inlineStr">
         <is>
-          <t>[-0.215, -0.047]</t>
+          <t>[-0.130, -0.018]</t>
         </is>
       </c>
       <c r="D30" s="18" t="inlineStr">
         <is>
-          <t>-0.242*</t>
+          <t>-0.231*</t>
         </is>
       </c>
       <c r="E30" s="18" t="inlineStr">
         <is>
-          <t>[-0.380, -0.104]</t>
+          <t>[-0.364, -0.098]</t>
         </is>
       </c>
       <c r="F30" s="18" t="inlineStr">
         <is>
-          <t>0.278*</t>
+          <t>0.266*</t>
         </is>
       </c>
       <c r="G30" s="18" t="inlineStr">
         <is>
-          <t>[0.122, 0.433]</t>
+          <t>[0.116, 0.416]</t>
         </is>
       </c>
     </row>
@@ -5068,32 +5070,32 @@
       </c>
       <c r="B31" s="18" t="inlineStr">
         <is>
-          <t>-0.006</t>
+          <t>-0.004</t>
         </is>
       </c>
       <c r="C31" s="18" t="inlineStr">
         <is>
-          <t>[-0.030, 0.017]</t>
+          <t>[-0.027, 0.020]</t>
         </is>
       </c>
       <c r="D31" s="18" t="inlineStr">
         <is>
-          <t>-0.012</t>
+          <t>-0.011</t>
         </is>
       </c>
       <c r="E31" s="18" t="inlineStr">
         <is>
-          <t>[-0.037, 0.014]</t>
+          <t>[-0.036, 0.014]</t>
         </is>
       </c>
       <c r="F31" s="18" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>0.012</t>
         </is>
       </c>
       <c r="G31" s="18" t="inlineStr">
         <is>
-          <t>[-0.013, 0.039]</t>
+          <t>[-0.013, 0.038]</t>
         </is>
       </c>
     </row>
@@ -5105,32 +5107,32 @@
       </c>
       <c r="B32" s="18" t="inlineStr">
         <is>
-          <t>-0.107*</t>
+          <t>-0.060*</t>
         </is>
       </c>
       <c r="C32" s="18" t="inlineStr">
         <is>
-          <t>[-0.178, -0.035]</t>
+          <t>[-0.109, -0.011]</t>
         </is>
       </c>
       <c r="D32" s="18" t="inlineStr">
         <is>
-          <t>-0.197*</t>
+          <t>-0.188*</t>
         </is>
       </c>
       <c r="E32" s="18" t="inlineStr">
         <is>
-          <t>[-0.313, -0.081]</t>
+          <t>[-0.299, -0.076]</t>
         </is>
       </c>
       <c r="F32" s="18" t="inlineStr">
         <is>
-          <t>0.225*</t>
+          <t>0.215*</t>
         </is>
       </c>
       <c r="G32" s="18" t="inlineStr">
         <is>
-          <t>[0.095, 0.355]</t>
+          <t>[0.090, 0.340]</t>
         </is>
       </c>
     </row>
@@ -5142,32 +5144,32 @@
       </c>
       <c r="B33" s="18" t="inlineStr">
         <is>
-          <t>-0.162*</t>
+          <t>-0.092*</t>
         </is>
       </c>
       <c r="C33" s="18" t="inlineStr">
         <is>
-          <t>[-0.261, -0.063]</t>
+          <t>[-0.156, -0.027]</t>
         </is>
       </c>
       <c r="D33" s="18" t="inlineStr">
         <is>
-          <t>-0.300*</t>
+          <t>-0.286*</t>
         </is>
       </c>
       <c r="E33" s="18" t="inlineStr">
         <is>
-          <t>[-0.466, -0.133]</t>
+          <t>[-0.445, -0.126]</t>
         </is>
       </c>
       <c r="F33" s="18" t="inlineStr">
         <is>
-          <t>0.343*</t>
+          <t>0.328*</t>
         </is>
       </c>
       <c r="G33" s="18" t="inlineStr">
         <is>
-          <t>[0.155, 0.530]</t>
+          <t>[0.148, 0.509]</t>
         </is>
       </c>
     </row>
@@ -5179,32 +5181,32 @@
       </c>
       <c r="B34" s="18" t="inlineStr">
         <is>
-          <t>0.056*</t>
+          <t>0.031</t>
         </is>
       </c>
       <c r="C34" s="18" t="inlineStr">
         <is>
-          <t>[0.009, 0.103]</t>
+          <t>[-0.004, 0.066]</t>
         </is>
       </c>
       <c r="D34" s="18" t="inlineStr">
         <is>
-          <t>0.103*</t>
+          <t>0.098*</t>
         </is>
       </c>
       <c r="E34" s="18" t="inlineStr">
         <is>
-          <t>[0.033, 0.173]</t>
+          <t>[0.030, 0.166]</t>
         </is>
       </c>
       <c r="F34" s="18" t="inlineStr">
         <is>
-          <t>-0.118*</t>
+          <t>-0.113*</t>
         </is>
       </c>
       <c r="G34" s="18" t="inlineStr">
         <is>
-          <t>[-0.195, -0.041]</t>
+          <t>[-0.188, -0.038]</t>
         </is>
       </c>
     </row>
@@ -5229,32 +5231,32 @@
       </c>
       <c r="B36" s="20" t="inlineStr">
         <is>
-          <t>0.085*</t>
+          <t>0.048*</t>
         </is>
       </c>
       <c r="C36" s="20" t="inlineStr">
         <is>
-          <t>[0.049, 0.127]</t>
+          <t>[0.007, 0.094]</t>
         </is>
       </c>
       <c r="D36" s="20" t="inlineStr">
         <is>
-          <t>0.157*</t>
+          <t>0.150*</t>
         </is>
       </c>
       <c r="E36" s="20" t="inlineStr">
         <is>
-          <t>[0.098, 0.226]</t>
+          <t>[0.092, 0.217]</t>
         </is>
       </c>
       <c r="F36" s="20" t="inlineStr">
         <is>
-          <t>-0.180*</t>
+          <t>-0.172*</t>
         </is>
       </c>
       <c r="G36" s="20" t="inlineStr">
         <is>
-          <t>[-0.252, -0.116]</t>
+          <t>[-0.243, -0.110]</t>
         </is>
       </c>
     </row>
@@ -5266,32 +5268,32 @@
       </c>
       <c r="B37" s="20" t="inlineStr">
         <is>
-          <t>0.072*</t>
+          <t>0.041*</t>
         </is>
       </c>
       <c r="C37" s="20" t="inlineStr">
         <is>
-          <t>[0.017, 0.127]</t>
+          <t>[0.001, 0.080]</t>
         </is>
       </c>
       <c r="D37" s="20" t="inlineStr">
         <is>
-          <t>0.132*</t>
+          <t>0.126*</t>
         </is>
       </c>
       <c r="E37" s="20" t="inlineStr">
         <is>
-          <t>[0.048, 0.216]</t>
+          <t>[0.045, 0.207]</t>
         </is>
       </c>
       <c r="F37" s="20" t="inlineStr">
         <is>
-          <t>-0.152*</t>
+          <t>-0.146*</t>
         </is>
       </c>
       <c r="G37" s="20" t="inlineStr">
         <is>
-          <t>[-0.246, -0.058]</t>
+          <t>[-0.236, -0.055]</t>
         </is>
       </c>
     </row>
@@ -5303,32 +5305,32 @@
       </c>
       <c r="B38" s="20" t="inlineStr">
         <is>
-          <t>0.098*</t>
+          <t>0.056*</t>
         </is>
       </c>
       <c r="C38" s="20" t="inlineStr">
         <is>
-          <t>[0.031, 0.166]</t>
+          <t>[0.009, 0.103]</t>
         </is>
       </c>
       <c r="D38" s="20" t="inlineStr">
         <is>
-          <t>0.181*</t>
+          <t>0.173*</t>
         </is>
       </c>
       <c r="E38" s="20" t="inlineStr">
         <is>
-          <t>[0.073, 0.289]</t>
+          <t>[0.068, 0.277]</t>
         </is>
       </c>
       <c r="F38" s="20" t="inlineStr">
         <is>
-          <t>-0.207*</t>
+          <t>-0.199*</t>
         </is>
       </c>
       <c r="G38" s="20" t="inlineStr">
         <is>
-          <t>[-0.328, -0.086]</t>
+          <t>[-0.316, -0.082]</t>
         </is>
       </c>
     </row>
@@ -5340,32 +5342,32 @@
       </c>
       <c r="B39" s="20" t="inlineStr">
         <is>
-          <t>-0.027</t>
+          <t>-0.015</t>
         </is>
       </c>
       <c r="C39" s="20" t="inlineStr">
         <is>
-          <t>[-0.059, 0.006]</t>
+          <t>[-0.042, 0.012]</t>
         </is>
       </c>
       <c r="D39" s="20" t="inlineStr">
         <is>
-          <t>-0.049*</t>
+          <t>-0.047*</t>
         </is>
       </c>
       <c r="E39" s="20" t="inlineStr">
         <is>
-          <t>[-0.093, -0.005]</t>
+          <t>[-0.089, -0.004]</t>
         </is>
       </c>
       <c r="F39" s="20" t="inlineStr">
         <is>
-          <t>0.055*</t>
+          <t>0.053*</t>
         </is>
       </c>
       <c r="G39" s="20" t="inlineStr">
         <is>
-          <t>[0.009, 0.102]</t>
+          <t>[0.007, 0.099]</t>
         </is>
       </c>
     </row>
@@ -5377,32 +5379,32 @@
       </c>
       <c r="B40" s="20" t="inlineStr">
         <is>
-          <t>0.082*</t>
+          <t>0.046*</t>
         </is>
       </c>
       <c r="C40" s="20" t="inlineStr">
         <is>
-          <t>[0.022, 0.141]</t>
+          <t>[0.004, 0.088]</t>
         </is>
       </c>
       <c r="D40" s="20" t="inlineStr">
         <is>
-          <t>0.151*</t>
+          <t>0.144*</t>
         </is>
       </c>
       <c r="E40" s="20" t="inlineStr">
         <is>
-          <t>[0.057, 0.245]</t>
+          <t>[0.054, 0.234]</t>
         </is>
       </c>
       <c r="F40" s="20" t="inlineStr">
         <is>
-          <t>-0.173*</t>
+          <t>-0.166*</t>
         </is>
       </c>
       <c r="G40" s="20" t="inlineStr">
         <is>
-          <t>[-0.277, -0.069]</t>
+          <t>[-0.266, -0.065]</t>
         </is>
       </c>
     </row>
@@ -5414,32 +5416,32 @@
       </c>
       <c r="B41" s="20" t="inlineStr">
         <is>
-          <t>0.088*</t>
+          <t>0.050*</t>
         </is>
       </c>
       <c r="C41" s="20" t="inlineStr">
         <is>
-          <t>[0.025, 0.150]</t>
+          <t>[0.006, 0.094]</t>
         </is>
       </c>
       <c r="D41" s="20" t="inlineStr">
         <is>
-          <t>0.163*</t>
+          <t>0.155*</t>
         </is>
       </c>
       <c r="E41" s="20" t="inlineStr">
         <is>
-          <t>[0.063, 0.262]</t>
+          <t>[0.060, 0.251]</t>
         </is>
       </c>
       <c r="F41" s="20" t="inlineStr">
         <is>
-          <t>-0.186*</t>
+          <t>-0.179*</t>
         </is>
       </c>
       <c r="G41" s="20" t="inlineStr">
         <is>
-          <t>[-0.297, -0.075]</t>
+          <t>[-0.286, -0.071]</t>
         </is>
       </c>
     </row>
@@ -5451,12 +5453,12 @@
       </c>
       <c r="B42" s="20" t="inlineStr">
         <is>
-          <t>-0.006</t>
+          <t>-0.003</t>
         </is>
       </c>
       <c r="C42" s="20" t="inlineStr">
         <is>
-          <t>[-0.030, 0.017]</t>
+          <t>[-0.027, 0.020]</t>
         </is>
       </c>
       <c r="D42" s="20" t="inlineStr">
@@ -5466,17 +5468,17 @@
       </c>
       <c r="E42" s="20" t="inlineStr">
         <is>
-          <t>[-0.037, 0.014]</t>
+          <t>[-0.036, 0.014]</t>
         </is>
       </c>
       <c r="F42" s="20" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>0.013</t>
         </is>
       </c>
       <c r="G42" s="20" t="inlineStr">
         <is>
-          <t>[-0.013, 0.040]</t>
+          <t>[-0.013, 0.039]</t>
         </is>
       </c>
     </row>

--- a/results/Model3.xlsx
+++ b/results/Model3.xlsx
@@ -2265,7 +2265,7 @@
       </c>
       <c r="H8" s="23" t="inlineStr">
         <is>
-          <t>(0.86)</t>
+          <t>(0.78)</t>
         </is>
       </c>
       <c r="I8" s="24" t="n"/>
@@ -2309,7 +2309,7 @@
       </c>
       <c r="I9" s="24" t="inlineStr">
         <is>
-          <t>(0.87)</t>
+          <t>(0.80)</t>
         </is>
       </c>
       <c r="J9" s="24" t="n"/>
@@ -2399,7 +2399,7 @@
       </c>
       <c r="K11" s="24" t="inlineStr">
         <is>
-          <t>(0.74)</t>
+          <t>(0.76)</t>
         </is>
       </c>
       <c r="L11" s="24" t="n"/>
@@ -2451,7 +2451,7 @@
       </c>
       <c r="L12" s="24" t="inlineStr">
         <is>
-          <t>(0.84)</t>
+          <t>(0.80)</t>
         </is>
       </c>
       <c r="M12" s="24" t="n"/>
@@ -2505,7 +2505,7 @@
       </c>
       <c r="M13" s="24" t="inlineStr">
         <is>
-          <t>(0.81)</t>
+          <t>(0.80)</t>
         </is>
       </c>
       <c r="N13" s="24" t="n"/>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="N14" s="24" t="inlineStr">
         <is>
-          <t>(0.82)</t>
+          <t>(0.92)</t>
         </is>
       </c>
       <c r="O14" s="24" t="n"/>
@@ -2625,7 +2625,7 @@
       </c>
       <c r="O15" s="24" t="inlineStr">
         <is>
-          <t>(0.85)</t>
+          <t>(0.91)</t>
         </is>
       </c>
       <c r="P15" s="24" t="n"/>
@@ -2695,7 +2695,7 @@
       </c>
       <c r="P16" s="24" t="inlineStr">
         <is>
-          <t>(0.85)</t>
+          <t>(0.80)</t>
         </is>
       </c>
       <c r="Q16" s="24" t="n"/>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="Q17" s="24" t="inlineStr">
         <is>
-          <t>(0.79)</t>
+          <t>(0.78)</t>
         </is>
       </c>
     </row>

--- a/results/Model3.xlsx
+++ b/results/Model3.xlsx
@@ -2265,7 +2265,7 @@
       </c>
       <c r="H8" s="23" t="inlineStr">
         <is>
-          <t>(0.78)</t>
+          <t>(0.74)</t>
         </is>
       </c>
       <c r="I8" s="24" t="n"/>
@@ -2309,7 +2309,7 @@
       </c>
       <c r="I9" s="24" t="inlineStr">
         <is>
-          <t>(0.80)</t>
+          <t>(0.76)</t>
         </is>
       </c>
       <c r="J9" s="24" t="n"/>
@@ -2353,7 +2353,7 @@
       </c>
       <c r="J10" s="24" t="inlineStr">
         <is>
-          <t>(0.79)</t>
+          <t>(0.73)</t>
         </is>
       </c>
       <c r="K10" s="24" t="n"/>
@@ -2399,7 +2399,7 @@
       </c>
       <c r="K11" s="24" t="inlineStr">
         <is>
-          <t>(0.76)</t>
+          <t>(0.71)</t>
         </is>
       </c>
       <c r="L11" s="24" t="n"/>
@@ -2451,7 +2451,7 @@
       </c>
       <c r="L12" s="24" t="inlineStr">
         <is>
-          <t>(0.80)</t>
+          <t>(0.77)</t>
         </is>
       </c>
       <c r="M12" s="24" t="n"/>
@@ -2505,7 +2505,7 @@
       </c>
       <c r="M13" s="24" t="inlineStr">
         <is>
-          <t>(0.80)</t>
+          <t>(0.75)</t>
         </is>
       </c>
       <c r="N13" s="24" t="n"/>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="N14" s="24" t="inlineStr">
         <is>
-          <t>(0.92)</t>
+          <t>(0.96)</t>
         </is>
       </c>
       <c r="O14" s="24" t="n"/>
@@ -2695,7 +2695,7 @@
       </c>
       <c r="P16" s="24" t="inlineStr">
         <is>
-          <t>(0.80)</t>
+          <t>(0.76)</t>
         </is>
       </c>
       <c r="Q16" s="24" t="n"/>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="Q17" s="24" t="inlineStr">
         <is>
-          <t>(0.78)</t>
+          <t>(0.74)</t>
         </is>
       </c>
     </row>

--- a/results/Model3.xlsx
+++ b/results/Model3.xlsx
@@ -2505,7 +2505,7 @@
       </c>
       <c r="M13" s="24" t="inlineStr">
         <is>
-          <t>(0.80)</t>
+          <t>(0.79)</t>
         </is>
       </c>
       <c r="N13" s="24" t="n"/>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="N14" s="24" t="inlineStr">
         <is>
-          <t>(0.92)</t>
+          <t>(0.86)</t>
         </is>
       </c>
       <c r="O14" s="24" t="n"/>
@@ -2625,7 +2625,7 @@
       </c>
       <c r="O15" s="24" t="inlineStr">
         <is>
-          <t>(0.91)</t>
+          <t>(0.93)</t>
         </is>
       </c>
       <c r="P15" s="24" t="n"/>

--- a/results/Model3.xlsx
+++ b/results/Model3.xlsx
@@ -2451,7 +2451,7 @@
       </c>
       <c r="L12" s="24" t="inlineStr">
         <is>
-          <t>(0.77)</t>
+          <t>(0.76)</t>
         </is>
       </c>
       <c r="M12" s="24" t="n"/>
@@ -2505,7 +2505,7 @@
       </c>
       <c r="M13" s="24" t="inlineStr">
         <is>
-          <t>(0.75)</t>
+          <t>(0.74)</t>
         </is>
       </c>
       <c r="N13" s="24" t="n"/>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="N14" s="24" t="inlineStr">
         <is>
-          <t>(0.96)</t>
+          <t>(0.80)</t>
         </is>
       </c>
       <c r="O14" s="24" t="n"/>
@@ -2625,7 +2625,7 @@
       </c>
       <c r="O15" s="24" t="inlineStr">
         <is>
-          <t>(0.91)</t>
+          <t>(0.88)</t>
         </is>
       </c>
       <c r="P15" s="24" t="n"/>
@@ -2695,7 +2695,7 @@
       </c>
       <c r="P16" s="24" t="inlineStr">
         <is>
-          <t>(0.76)</t>
+          <t>(0.75)</t>
         </is>
       </c>
       <c r="Q16" s="24" t="n"/>
